--- a/data/SVS.MI.xlsx
+++ b/data/SVS.MI.xlsx
@@ -27604,6 +27604,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1185">
+      <c r="A1185" s="1" t="n">
+        <v>46276.2916666667</v>
+      </c>
+      <c r="B1185" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1185" t="n">
+        <v>7.98000001907349</v>
+      </c>
+      <c r="D1185" t="n">
+        <v>7.98000001907349</v>
+      </c>
+      <c r="E1185" t="n">
+        <v>7.98000001907349</v>
+      </c>
+      <c r="F1185" t="n">
+        <v>7.98000001907349</v>
+      </c>
+      <c r="G1185" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SVS.MI.xlsx
+++ b/data/SVS.MI.xlsx
@@ -27627,6 +27627,52 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1186">
+      <c r="A1186" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B1186" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1186" t="n">
+        <v>7.98000001907349</v>
+      </c>
+      <c r="D1186" t="n">
+        <v>7.98000001907349</v>
+      </c>
+      <c r="E1186" t="n">
+        <v>7.98000001907349</v>
+      </c>
+      <c r="F1186" t="n">
+        <v>7.98000001907349</v>
+      </c>
+      <c r="G1186" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1187">
+      <c r="A1187" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B1187" t="n">
+        <v>100</v>
+      </c>
+      <c r="C1187" t="n">
+        <v>7.82000017166138</v>
+      </c>
+      <c r="D1187" t="n">
+        <v>7.82000017166138</v>
+      </c>
+      <c r="E1187" t="n">
+        <v>7.82000017166138</v>
+      </c>
+      <c r="F1187" t="n">
+        <v>7.82000017166138</v>
+      </c>
+      <c r="G1187" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SVS.MI.xlsx
+++ b/data/SVS.MI.xlsx
@@ -27673,6 +27673,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1188">
+      <c r="A1188" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B1188" t="n">
+        <v>1300</v>
+      </c>
+      <c r="C1188" t="n">
+        <v>8.03999996185303</v>
+      </c>
+      <c r="D1188" t="n">
+        <v>8.02000045776367</v>
+      </c>
+      <c r="E1188" t="n">
+        <v>8.02000045776367</v>
+      </c>
+      <c r="F1188" t="n">
+        <v>8.03999996185303</v>
+      </c>
+      <c r="G1188" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SVS.MI.xlsx
+++ b/data/SVS.MI.xlsx
@@ -27537,22 +27537,22 @@
     </row>
     <row r="1182">
       <c r="A1182" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B1182" t="n">
-        <v>100</v>
+        <v>1211</v>
       </c>
       <c r="C1182" t="n">
-        <v>8.02000045776367</v>
+        <v>8.07999992370605</v>
       </c>
       <c r="D1182" t="n">
-        <v>8.02000045776367</v>
+        <v>7.73999977111816</v>
       </c>
       <c r="E1182" t="n">
-        <v>8.02000045776367</v>
+        <v>7.98000001907349</v>
       </c>
       <c r="F1182" t="n">
-        <v>8.02000045776367</v>
+        <v>8.07999992370605</v>
       </c>
       <c r="G1182" t="s">
         <v>7</v>
@@ -27560,10 +27560,10 @@
     </row>
     <row r="1183">
       <c r="A1183" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B1183" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="C1183" t="n">
         <v>8.02000045776367</v>
@@ -27583,22 +27583,22 @@
     </row>
     <row r="1184">
       <c r="A1184" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B1184" t="n">
-        <v>4000</v>
+        <v>500</v>
       </c>
       <c r="C1184" t="n">
-        <v>7.98000001907349</v>
+        <v>8.02000045776367</v>
       </c>
       <c r="D1184" t="n">
-        <v>7.98000001907349</v>
+        <v>8.02000045776367</v>
       </c>
       <c r="E1184" t="n">
-        <v>7.98000001907349</v>
+        <v>8.02000045776367</v>
       </c>
       <c r="F1184" t="n">
-        <v>7.98000001907349</v>
+        <v>8.02000045776367</v>
       </c>
       <c r="G1184" t="s">
         <v>7</v>
@@ -27606,10 +27606,10 @@
     </row>
     <row r="1185">
       <c r="A1185" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B1185" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="C1185" t="n">
         <v>7.98000001907349</v>
@@ -27629,7 +27629,7 @@
     </row>
     <row r="1186">
       <c r="A1186" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B1186" t="n">
         <v>0</v>
@@ -27652,22 +27652,22 @@
     </row>
     <row r="1187">
       <c r="A1187" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B1187" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C1187" t="n">
-        <v>7.82000017166138</v>
+        <v>7.98000001907349</v>
       </c>
       <c r="D1187" t="n">
-        <v>7.82000017166138</v>
+        <v>7.98000001907349</v>
       </c>
       <c r="E1187" t="n">
-        <v>7.82000017166138</v>
+        <v>7.98000001907349</v>
       </c>
       <c r="F1187" t="n">
-        <v>7.82000017166138</v>
+        <v>7.98000001907349</v>
       </c>
       <c r="G1187" t="s">
         <v>7</v>
@@ -27675,24 +27675,70 @@
     </row>
     <row r="1188">
       <c r="A1188" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B1188" t="n">
+        <v>100</v>
+      </c>
+      <c r="C1188" t="n">
+        <v>7.82000017166138</v>
+      </c>
+      <c r="D1188" t="n">
+        <v>7.82000017166138</v>
+      </c>
+      <c r="E1188" t="n">
+        <v>7.82000017166138</v>
+      </c>
+      <c r="F1188" t="n">
+        <v>7.82000017166138</v>
+      </c>
+      <c r="G1188" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1189">
+      <c r="A1189" s="1" t="n">
         <v>46281.2916666667</v>
       </c>
-      <c r="B1188" t="n">
+      <c r="B1189" t="n">
         <v>1300</v>
       </c>
-      <c r="C1188" t="n">
+      <c r="C1189" t="n">
         <v>8.03999996185303</v>
       </c>
-      <c r="D1188" t="n">
+      <c r="D1189" t="n">
         <v>8.02000045776367</v>
       </c>
-      <c r="E1188" t="n">
+      <c r="E1189" t="n">
         <v>8.02000045776367</v>
       </c>
-      <c r="F1188" t="n">
+      <c r="F1189" t="n">
         <v>8.03999996185303</v>
       </c>
-      <c r="G1188" t="s">
+      <c r="G1189" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1190">
+      <c r="A1190" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B1190" t="n">
+        <v>125</v>
+      </c>
+      <c r="C1190" t="n">
+        <v>7.98000001907349</v>
+      </c>
+      <c r="D1190" t="n">
+        <v>7.98000001907349</v>
+      </c>
+      <c r="E1190" t="n">
+        <v>7.98000001907349</v>
+      </c>
+      <c r="F1190" t="n">
+        <v>7.98000001907349</v>
+      </c>
+      <c r="G1190" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/SVS.MI.xlsx
+++ b/data/SVS.MI.xlsx
@@ -31367,6 +31367,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1193">
+      <c r="A1193" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B1193" t="n">
+        <v>1651</v>
+      </c>
+      <c r="C1193" t="n">
+        <v>8.03999996185303</v>
+      </c>
+      <c r="D1193" t="n">
+        <v>7.84000015258789</v>
+      </c>
+      <c r="E1193" t="n">
+        <v>7.96000003814697</v>
+      </c>
+      <c r="F1193" t="n">
+        <v>8.03999996185303</v>
+      </c>
+      <c r="G1193" t="n">
+        <v>8.03999996185303</v>
+      </c>
+      <c r="H1193" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SVS.MI.xlsx
+++ b/data/SVS.MI.xlsx
@@ -31393,6 +31393,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1194">
+      <c r="A1194" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B1194" t="n">
+        <v>300</v>
+      </c>
+      <c r="C1194" t="n">
+        <v>8.03999996185303</v>
+      </c>
+      <c r="D1194" t="n">
+        <v>7.90000009536743</v>
+      </c>
+      <c r="E1194" t="n">
+        <v>7.90000009536743</v>
+      </c>
+      <c r="F1194" t="n">
+        <v>8.03999996185303</v>
+      </c>
+      <c r="G1194" t="n">
+        <v>8.03999996185303</v>
+      </c>
+      <c r="H1194" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SVS.MI.xlsx
+++ b/data/SVS.MI.xlsx
@@ -27834,6 +27834,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1195">
+      <c r="A1195" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B1195" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1195" t="n">
+        <v>8.03999996185303</v>
+      </c>
+      <c r="D1195" t="n">
+        <v>8.03999996185303</v>
+      </c>
+      <c r="E1195" t="n">
+        <v>8.03999996185303</v>
+      </c>
+      <c r="F1195" t="n">
+        <v>8.03999996185303</v>
+      </c>
+      <c r="G1195" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SVS.MI.xlsx
+++ b/data/SVS.MI.xlsx
@@ -27857,6 +27857,50 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1196">
+      <c r="A1196" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B1196" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1196" t="n">
+        <v>8.03999996185303</v>
+      </c>
+      <c r="D1196" t="n">
+        <v>8.03999996185303</v>
+      </c>
+      <c r="E1196" t="n">
+        <v>8.03999996185303</v>
+      </c>
+      <c r="F1196" t="n">
+        <v>8.03999996185303</v>
+      </c>
+      <c r="G1196" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1197">
+      <c r="A1197" s="1" t="n">
+        <v>46293.2916666667</v>
+      </c>
+      <c r="B1197" t="n">
+        <v>360</v>
+      </c>
+      <c r="C1197" t="n">
+        <v>8.02000045776367</v>
+      </c>
+      <c r="D1197" t="n">
+        <v>7.84000015258789</v>
+      </c>
+      <c r="E1197" t="n">
+        <v>7.84000015258789</v>
+      </c>
+      <c r="F1197"/>
+      <c r="G1197" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SVS.MI.xlsx
+++ b/data/SVS.MI.xlsx
@@ -421,7 +421,7 @@
         <v>14.7600002288818</v>
       </c>
       <c r="G2" t="n">
-        <v>13.4660730361938</v>
+        <v>13.4660739898682</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>14.7799997329712</v>
       </c>
       <c r="G4" t="n">
-        <v>13.484320640564</v>
+        <v>13.4843196868896</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G6" t="n">
-        <v>13.4113321304321</v>
+        <v>13.4113330841064</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>14.3199996948242</v>
       </c>
       <c r="G8" t="n">
-        <v>13.0646448135376</v>
+        <v>13.0646457672119</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G10" t="n">
-        <v>12.5902309417725</v>
+        <v>12.5902318954468</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G11" t="n">
-        <v>12.5902309417725</v>
+        <v>12.5902318954468</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G16" t="n">
-        <v>12.2435445785522</v>
+        <v>12.2435436248779</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>13.3400001525879</v>
       </c>
       <c r="G19" t="n">
-        <v>12.1705570220947</v>
+        <v>12.1705560684204</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G25" t="n">
-        <v>12.0428304672241</v>
+        <v>12.0428295135498</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G26" t="n">
-        <v>11.9698429107666</v>
+        <v>11.9698419570923</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G30" t="n">
-        <v>11.3859481811523</v>
+        <v>11.385947227478</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G32" t="n">
-        <v>11.5501680374146</v>
+        <v>11.5501689910889</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G34" t="n">
-        <v>11.2034816741943</v>
+        <v>11.20348072052</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G36" t="n">
-        <v>10.5830926895142</v>
+        <v>10.5830936431885</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G38" t="n">
-        <v>10.5830926895142</v>
+        <v>10.5830936431885</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>10.7600002288818</v>
       </c>
       <c r="G43" t="n">
-        <v>9.81673145294189</v>
+        <v>9.81673240661621</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G44" t="n">
-        <v>10.2181587219238</v>
+        <v>10.2181577682495</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G56" t="n">
-        <v>12.0428304672241</v>
+        <v>12.0428295135498</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G57" t="n">
-        <v>12.0428304672241</v>
+        <v>12.0428295135498</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G58" t="n">
-        <v>12.0428304672241</v>
+        <v>12.0428295135498</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G59" t="n">
-        <v>12.0428304672241</v>
+        <v>12.0428295135498</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G61" t="n">
-        <v>11.4954290390015</v>
+        <v>11.4954280853271</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G63" t="n">
-        <v>11.4954290390015</v>
+        <v>11.4954280853271</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G65" t="n">
-        <v>11.4406871795654</v>
+        <v>11.4406881332397</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G68" t="n">
-        <v>11.1304941177368</v>
+        <v>11.1304931640625</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G69" t="n">
-        <v>11.9698429107666</v>
+        <v>11.9698419570923</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G72" t="n">
-        <v>11.2217283248901</v>
+        <v>11.2217273712158</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>12.4399995803833</v>
       </c>
       <c r="G74" t="n">
-        <v>11.3494539260864</v>
+        <v>11.3494548797607</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G75" t="n">
-        <v>11.8238687515259</v>
+        <v>11.8238697052002</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G79" t="n">
-        <v>10.8020534515381</v>
+        <v>10.8020544052124</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G80" t="n">
-        <v>10.5648460388184</v>
+        <v>10.5648469924927</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G82" t="n">
-        <v>11.2217283248901</v>
+        <v>11.2217273712158</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G84" t="n">
-        <v>10.2181587219238</v>
+        <v>10.2181577682495</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>11.5</v>
       </c>
       <c r="G85" t="n">
-        <v>10.4918594360352</v>
+        <v>10.4918584823608</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G86" t="n">
-        <v>11.2764673233032</v>
+        <v>11.2764682769775</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G87" t="n">
-        <v>10.3276376724243</v>
+        <v>10.3276395797729</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G90" t="n">
-        <v>10.9297800064087</v>
+        <v>10.9297790527344</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G92" t="n">
-        <v>10.5648460388184</v>
+        <v>10.5648469924927</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G93" t="n">
-        <v>10.5648460388184</v>
+        <v>10.5648469924927</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G95" t="n">
-        <v>10.5648460388184</v>
+        <v>10.5648469924927</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G96" t="n">
-        <v>10.5648460388184</v>
+        <v>10.5648469924927</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>11.5</v>
       </c>
       <c r="G97" t="n">
-        <v>10.4918594360352</v>
+        <v>10.4918584823608</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G99" t="n">
-        <v>10.2181587219238</v>
+        <v>10.2181577682495</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G101" t="n">
-        <v>10.5648460388184</v>
+        <v>10.5648469924927</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>11.7799997329712</v>
       </c>
       <c r="G105" t="n">
-        <v>10.7473134994507</v>
+        <v>10.7473125457764</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G106" t="n">
-        <v>10.3093919754028</v>
+        <v>10.3093929290771</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G108" t="n">
-        <v>9.9444580078125</v>
+        <v>9.94445705413818</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G109" t="n">
-        <v>10.2181587219238</v>
+        <v>10.2181577682495</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G110" t="n">
-        <v>10.2181587219238</v>
+        <v>10.2181577682495</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G111" t="n">
-        <v>10.2181587219238</v>
+        <v>10.2181577682495</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G112" t="n">
-        <v>9.85322380065918</v>
+        <v>9.8532247543335</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G113" t="n">
-        <v>10.1269245147705</v>
+        <v>10.1269254684448</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G114" t="n">
-        <v>10.1269245147705</v>
+        <v>10.1269254684448</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G115" t="n">
-        <v>10.2728996276855</v>
+        <v>10.2728986740112</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>11.5</v>
       </c>
       <c r="G116" t="n">
-        <v>10.4918594360352</v>
+        <v>10.4918584823608</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>11.7799997329712</v>
       </c>
       <c r="G119" t="n">
-        <v>10.7473134994507</v>
+        <v>10.7473125457764</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G120" t="n">
-        <v>10.2728996276855</v>
+        <v>10.2728986740112</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G123" t="n">
-        <v>10.2546520233154</v>
+        <v>10.2546510696411</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>11.2799997329712</v>
       </c>
       <c r="G141" t="n">
-        <v>10.291145324707</v>
+        <v>10.2911462783813</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G143" t="n">
-        <v>10.2728996276855</v>
+        <v>10.2728986740112</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G144" t="n">
-        <v>9.9444580078125</v>
+        <v>9.94445705413818</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>11.2799997329712</v>
       </c>
       <c r="G147" t="n">
-        <v>10.291145324707</v>
+        <v>10.2911462783813</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G148" t="n">
-        <v>10.3093919754028</v>
+        <v>10.3093929290771</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G152" t="n">
-        <v>10.1269245147705</v>
+        <v>10.1269254684448</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G156" t="n">
-        <v>10.1269245147705</v>
+        <v>10.1269254684448</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G157" t="n">
-        <v>10.1269245147705</v>
+        <v>10.1269254684448</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G158" t="n">
-        <v>9.9444580078125</v>
+        <v>9.94445705413818</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G159" t="n">
-        <v>10.1269245147705</v>
+        <v>10.1269254684448</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G160" t="n">
-        <v>9.9444580078125</v>
+        <v>9.94445705413818</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G161" t="n">
-        <v>9.9444580078125</v>
+        <v>9.94445705413818</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G162" t="n">
-        <v>9.85322380065918</v>
+        <v>9.8532247543335</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G164" t="n">
-        <v>10.1269245147705</v>
+        <v>10.1269254684448</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G166" t="n">
-        <v>10.3093919754028</v>
+        <v>10.3093929290771</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G169" t="n">
-        <v>9.30582332611084</v>
+        <v>9.30582237243652</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>8.75</v>
       </c>
       <c r="G180" t="n">
-        <v>7.98293685913086</v>
+        <v>7.9829363822937</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G183" t="n">
-        <v>7.57238531112671</v>
+        <v>7.57238578796387</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>8.5</v>
       </c>
       <c r="G184" t="n">
-        <v>7.75485229492188</v>
+        <v>7.75485277175903</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>8.60999965667725</v>
       </c>
       <c r="G185" t="n">
-        <v>7.85520887374878</v>
+        <v>7.85520839691162</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G186" t="n">
-        <v>8.0285530090332</v>
+        <v>8.02855396270752</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>9.01000022888184</v>
       </c>
       <c r="G187" t="n">
-        <v>8.22014427185059</v>
+        <v>8.22014331817627</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G194" t="n">
-        <v>7.73660564422607</v>
+        <v>7.73660516738892</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>8.25</v>
       </c>
       <c r="G197" t="n">
-        <v>7.52676820755005</v>
+        <v>7.52676868438721</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>8.60999965667725</v>
       </c>
       <c r="G202" t="n">
-        <v>7.85520887374878</v>
+        <v>7.85520839691162</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G203" t="n">
-        <v>7.8825798034668</v>
+        <v>7.88257932662964</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G204" t="n">
-        <v>7.8825798034668</v>
+        <v>7.88257932662964</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>8.60999965667725</v>
       </c>
       <c r="G205" t="n">
-        <v>7.85520887374878</v>
+        <v>7.85520839691162</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G211" t="n">
-        <v>7.97381258010864</v>
+        <v>7.9738130569458</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G212" t="n">
-        <v>8.08329296112061</v>
+        <v>8.08329200744629</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G213" t="n">
-        <v>8.0285530090332</v>
+        <v>8.02855396270752</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G220" t="n">
-        <v>8.22926712036133</v>
+        <v>8.22926807403564</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G221" t="n">
-        <v>8.22926712036133</v>
+        <v>8.22926807403564</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G222" t="n">
-        <v>8.22926712036133</v>
+        <v>8.22926807403564</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G223" t="n">
-        <v>8.32050037384033</v>
+        <v>8.32049942016602</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G224" t="n">
-        <v>8.32050037384033</v>
+        <v>8.32049942016602</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G225" t="n">
-        <v>8.32050037384033</v>
+        <v>8.32049942016602</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G226" t="n">
-        <v>8.32050037384033</v>
+        <v>8.32049942016602</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G227" t="n">
-        <v>8.41173362731934</v>
+        <v>8.41173458099365</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G229" t="n">
-        <v>8.57595443725586</v>
+        <v>8.57595348358154</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G236" t="n">
-        <v>8.98650550842285</v>
+        <v>8.98650646209717</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>9.63000011444092</v>
       </c>
       <c r="G242" t="n">
-        <v>8.78579139709473</v>
+        <v>8.78579235076904</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>9.63000011444092</v>
       </c>
       <c r="G243" t="n">
-        <v>8.78579139709473</v>
+        <v>8.78579235076904</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>9.63000011444092</v>
       </c>
       <c r="G244" t="n">
-        <v>8.78579139709473</v>
+        <v>8.78579235076904</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>9.63000011444092</v>
       </c>
       <c r="G245" t="n">
-        <v>8.78579139709473</v>
+        <v>8.78579235076904</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G247" t="n">
-        <v>9.03212261199951</v>
+        <v>9.0321216583252</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G248" t="n">
-        <v>9.03212261199951</v>
+        <v>9.0321216583252</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G258" t="n">
-        <v>9.03212261199951</v>
+        <v>9.0321216583252</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G261" t="n">
-        <v>9.01387500762939</v>
+        <v>9.01387596130371</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G267" t="n">
-        <v>8.98650550842285</v>
+        <v>8.98650646209717</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>8.92000007629395</v>
       </c>
       <c r="G273" t="n">
-        <v>8.13803291320801</v>
+        <v>8.13803386688232</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G274" t="n">
-        <v>8.30225467681885</v>
+        <v>8.30225372314453</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G277" t="n">
-        <v>8.30225467681885</v>
+        <v>8.30225372314453</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>8.72999954223633</v>
       </c>
       <c r="G280" t="n">
-        <v>7.96468925476074</v>
+        <v>7.9646897315979</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>8.90999984741211</v>
       </c>
       <c r="G282" t="n">
-        <v>8.12890911102295</v>
+        <v>8.12891006469727</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>8.77000045776367</v>
       </c>
       <c r="G283" t="n">
-        <v>8.00118350982666</v>
+        <v>8.00118446350098</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>9.27000045776367</v>
       </c>
       <c r="G295" t="n">
-        <v>8.45735168457031</v>
+        <v>8.457350730896</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>8.86999988555908</v>
       </c>
       <c r="G302" t="n">
-        <v>8.09241676330566</v>
+        <v>8.09241580963135</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G304" t="n">
-        <v>8.0285530090332</v>
+        <v>8.02855396270752</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>8.8100004196167</v>
       </c>
       <c r="G305" t="n">
-        <v>8.03767681121826</v>
+        <v>8.03767776489258</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G306" t="n">
-        <v>8.25663661956787</v>
+        <v>8.25663757324219</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G309" t="n">
-        <v>8.19277381896973</v>
+        <v>8.19277286529541</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G310" t="n">
-        <v>8.22926712036133</v>
+        <v>8.22926807403564</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G311" t="n">
-        <v>8.22926712036133</v>
+        <v>8.22926807403564</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G312" t="n">
-        <v>8.22926712036133</v>
+        <v>8.22926807403564</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G313" t="n">
-        <v>8.41173362731934</v>
+        <v>8.41173458099365</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>9.01000022888184</v>
       </c>
       <c r="G314" t="n">
-        <v>8.22014427185059</v>
+        <v>8.22014331817627</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>9.01000022888184</v>
       </c>
       <c r="G315" t="n">
-        <v>8.22014427185059</v>
+        <v>8.22014331817627</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G316" t="n">
-        <v>8.0285530090332</v>
+        <v>8.02855396270752</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G317" t="n">
-        <v>8.0285530090332</v>
+        <v>8.02855396270752</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G318" t="n">
-        <v>8.0285530090332</v>
+        <v>8.02855396270752</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G319" t="n">
-        <v>7.95556688308716</v>
+        <v>7.95556640625</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G325" t="n">
-        <v>8.22926712036133</v>
+        <v>8.22926807403564</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G326" t="n">
-        <v>8.22926712036133</v>
+        <v>8.22926807403564</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>8.92000007629395</v>
       </c>
       <c r="G327" t="n">
-        <v>8.13803291320801</v>
+        <v>8.13803386688232</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G336" t="n">
-        <v>8.41173362731934</v>
+        <v>8.41173458099365</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G339" t="n">
-        <v>7.53589248657227</v>
+        <v>7.53589200973511</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G340" t="n">
-        <v>7.57238531112671</v>
+        <v>7.57238578796387</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G342" t="n">
-        <v>7.37167167663574</v>
+        <v>7.37167119979858</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G343" t="n">
-        <v>7.40816497802734</v>
+        <v>7.40816450119019</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G345" t="n">
-        <v>7.33517789840698</v>
+        <v>7.33517837524414</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G347" t="n">
-        <v>7.53589248657227</v>
+        <v>7.53589200973511</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G348" t="n">
-        <v>7.42641162872314</v>
+        <v>7.4264121055603</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>8</v>
       </c>
       <c r="G349" t="n">
-        <v>7.29868507385254</v>
+        <v>7.29868459701538</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>8</v>
       </c>
       <c r="G350" t="n">
-        <v>7.29868507385254</v>
+        <v>7.29868459701538</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>8</v>
       </c>
       <c r="G351" t="n">
-        <v>7.29868507385254</v>
+        <v>7.29868459701538</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>8</v>
       </c>
       <c r="G353" t="n">
-        <v>7.29868507385254</v>
+        <v>7.29868459701538</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G354" t="n">
-        <v>7.20745134353638</v>
+        <v>7.20745182037354</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G358" t="n">
-        <v>7.11621809005737</v>
+        <v>7.11621761322021</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G359" t="n">
-        <v>7.11621809005737</v>
+        <v>7.11621761322021</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G360" t="n">
-        <v>7.11621809005737</v>
+        <v>7.11621761322021</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G361" t="n">
-        <v>7.11621809005737</v>
+        <v>7.11621761322021</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G377" t="n">
-        <v>7.11621809005737</v>
+        <v>7.11621761322021</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G384" t="n">
-        <v>6.91550397872925</v>
+        <v>6.91550350189209</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G385" t="n">
-        <v>6.91550397872925</v>
+        <v>6.91550350189209</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G386" t="n">
-        <v>6.91550397872925</v>
+        <v>6.91550350189209</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G387" t="n">
-        <v>6.91550397872925</v>
+        <v>6.91550350189209</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G389" t="n">
-        <v>7.17095804214478</v>
+        <v>7.17095756530762</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G390" t="n">
-        <v>7.3899188041687</v>
+        <v>7.38991832733154</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G391" t="n">
-        <v>7.59063148498535</v>
+        <v>7.59063243865967</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G392" t="n">
-        <v>7.57238531112671</v>
+        <v>7.57238578796387</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G393" t="n">
-        <v>7.57238531112671</v>
+        <v>7.57238578796387</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G394" t="n">
-        <v>7.57238531112671</v>
+        <v>7.57238578796387</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G395" t="n">
-        <v>7.57238531112671</v>
+        <v>7.57238578796387</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G396" t="n">
-        <v>7.57238531112671</v>
+        <v>7.57238578796387</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G399" t="n">
-        <v>7.40816497802734</v>
+        <v>7.40816450119019</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G403" t="n">
-        <v>7.49939918518066</v>
+        <v>7.49939870834351</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G406" t="n">
-        <v>7.33517789840698</v>
+        <v>7.33517837524414</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G407" t="n">
-        <v>7.33517789840698</v>
+        <v>7.33517837524414</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>8</v>
       </c>
       <c r="G408" t="n">
-        <v>7.29868507385254</v>
+        <v>7.29868459701538</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>8</v>
       </c>
       <c r="G409" t="n">
-        <v>7.29868507385254</v>
+        <v>7.29868459701538</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>8</v>
       </c>
       <c r="G410" t="n">
-        <v>7.29868507385254</v>
+        <v>7.29868459701538</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G412" t="n">
-        <v>7.42641162872314</v>
+        <v>7.4264121055603</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G413" t="n">
-        <v>7.40816497802734</v>
+        <v>7.40816450119019</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G414" t="n">
-        <v>7.44465827941895</v>
+        <v>7.4446587562561</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G415" t="n">
-        <v>7.44465827941895</v>
+        <v>7.4446587562561</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G416" t="n">
-        <v>7.42641162872314</v>
+        <v>7.4264121055603</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G417" t="n">
-        <v>7.40816497802734</v>
+        <v>7.40816450119019</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G421" t="n">
-        <v>7.4629054069519</v>
+        <v>7.46290588378906</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G424" t="n">
-        <v>7.44465827941895</v>
+        <v>7.4446587562561</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G426" t="n">
-        <v>7.79134654998779</v>
+        <v>7.79134607315063</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G427" t="n">
-        <v>7.8825798034668</v>
+        <v>7.88257932662964</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G428" t="n">
-        <v>7.73660564422607</v>
+        <v>7.73660516738892</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G429" t="n">
-        <v>7.66361808776855</v>
+        <v>7.66361856460571</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G430" t="n">
-        <v>7.66361808776855</v>
+        <v>7.66361856460571</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G434" t="n">
-        <v>7.4629054069519</v>
+        <v>7.46290588378906</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>8</v>
       </c>
       <c r="G438" t="n">
-        <v>7.29868507385254</v>
+        <v>7.29868459701538</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G439" t="n">
-        <v>6.91550397872925</v>
+        <v>6.91550350189209</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G455" t="n">
-        <v>6.58706283569336</v>
+        <v>6.5870623588562</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G463" t="n">
-        <v>6.5323224067688</v>
+        <v>6.53232288360596</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G464" t="n">
-        <v>6.5688157081604</v>
+        <v>6.56881618499756</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G465" t="n">
-        <v>6.5688157081604</v>
+        <v>6.56881618499756</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G466" t="n">
-        <v>6.5688157081604</v>
+        <v>6.56881618499756</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G467" t="n">
-        <v>6.5688157081604</v>
+        <v>6.56881618499756</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G468" t="n">
-        <v>6.5688157081604</v>
+        <v>6.56881618499756</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G469" t="n">
-        <v>6.44108867645264</v>
+        <v>6.44108915328979</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G471" t="n">
-        <v>6.29511547088623</v>
+        <v>6.29511594772339</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G472" t="n">
-        <v>6.49582958221436</v>
+        <v>6.4958291053772</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G474" t="n">
-        <v>6.29511547088623</v>
+        <v>6.29511594772339</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G477" t="n">
-        <v>6.5323224067688</v>
+        <v>6.53232288360596</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G478" t="n">
-        <v>6.73303651809692</v>
+        <v>6.73303699493408</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G479" t="n">
-        <v>6.73303651809692</v>
+        <v>6.73303699493408</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G480" t="n">
-        <v>6.73303651809692</v>
+        <v>6.73303699493408</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G481" t="n">
-        <v>6.73303651809692</v>
+        <v>6.73303699493408</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G482" t="n">
-        <v>6.73303651809692</v>
+        <v>6.73303699493408</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G483" t="n">
-        <v>6.73303651809692</v>
+        <v>6.73303699493408</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G484" t="n">
-        <v>6.58706283569336</v>
+        <v>6.5870623588562</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G485" t="n">
-        <v>6.58706283569336</v>
+        <v>6.5870623588562</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G486" t="n">
-        <v>6.58706283569336</v>
+        <v>6.5870623588562</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>8</v>
       </c>
       <c r="G490" t="n">
-        <v>7.29868507385254</v>
+        <v>7.29868459701538</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G491" t="n">
-        <v>7.18920421600342</v>
+        <v>7.18920469284058</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G492" t="n">
-        <v>7.20745134353638</v>
+        <v>7.20745182037354</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G493" t="n">
-        <v>7.22569751739502</v>
+        <v>7.22569799423218</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>7.78000020980835</v>
       </c>
       <c r="G494" t="n">
-        <v>7.09797048568726</v>
+        <v>7.09797096252441</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>7.78000020980835</v>
       </c>
       <c r="G495" t="n">
-        <v>7.09797048568726</v>
+        <v>7.09797096252441</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G496" t="n">
-        <v>7.15271139144897</v>
+        <v>7.15271091461182</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G500" t="n">
-        <v>7.42641162872314</v>
+        <v>7.4264121055603</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G502" t="n">
-        <v>7.33517789840698</v>
+        <v>7.33517837524414</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>8</v>
       </c>
       <c r="G503" t="n">
-        <v>7.29868507385254</v>
+        <v>7.29868459701538</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G504" t="n">
-        <v>7.37167167663574</v>
+        <v>7.37167119979858</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G505" t="n">
-        <v>7.33517789840698</v>
+        <v>7.33517837524414</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G506" t="n">
-        <v>7.33517789840698</v>
+        <v>7.33517837524414</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G508" t="n">
-        <v>7.37167167663574</v>
+        <v>7.37167119979858</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G509" t="n">
-        <v>7.37167167663574</v>
+        <v>7.37167119979858</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G510" t="n">
-        <v>7.37167167663574</v>
+        <v>7.37167119979858</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G511" t="n">
-        <v>7.20745134353638</v>
+        <v>7.20745182037354</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G513" t="n">
-        <v>7.20745134353638</v>
+        <v>7.20745182037354</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>7.42000007629395</v>
       </c>
       <c r="G522" t="n">
-        <v>6.76952981948853</v>
+        <v>6.76953029632568</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G523" t="n">
-        <v>6.73303651809692</v>
+        <v>6.73303699493408</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G524" t="n">
-        <v>6.73303651809692</v>
+        <v>6.73303699493408</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G528" t="n">
-        <v>7.13446474075317</v>
+        <v>7.13446426391602</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G530" t="n">
-        <v>7.17095804214478</v>
+        <v>7.17095756530762</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G536" t="n">
-        <v>7.3899188041687</v>
+        <v>7.38991832733154</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G537" t="n">
-        <v>7.18920421600342</v>
+        <v>7.18920469284058</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G538" t="n">
-        <v>7.13446474075317</v>
+        <v>7.13446426391602</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G539" t="n">
-        <v>7.20745134353638</v>
+        <v>7.20745182037354</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G540" t="n">
-        <v>7.20745134353638</v>
+        <v>7.20745182037354</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G541" t="n">
-        <v>7.15271139144897</v>
+        <v>7.15271091461182</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G542" t="n">
-        <v>7.15271139144897</v>
+        <v>7.15271091461182</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G543" t="n">
-        <v>7.13446474075317</v>
+        <v>7.13446426391602</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G545" t="n">
-        <v>7.20745134353638</v>
+        <v>7.20745182037354</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>8</v>
       </c>
       <c r="G546" t="n">
-        <v>7.29868507385254</v>
+        <v>7.29868459701538</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G548" t="n">
-        <v>7.3899188041687</v>
+        <v>7.38991832733154</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G550" t="n">
-        <v>7.49939918518066</v>
+        <v>7.49939870834351</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G552" t="n">
-        <v>7.66361808776855</v>
+        <v>7.66361856460571</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G553" t="n">
-        <v>7.68186616897583</v>
+        <v>7.68186521530151</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G554" t="n">
-        <v>7.57238531112671</v>
+        <v>7.57238578796387</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G555" t="n">
-        <v>7.57238531112671</v>
+        <v>7.57238578796387</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G556" t="n">
-        <v>7.68186616897583</v>
+        <v>7.68186521530151</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G560" t="n">
-        <v>7.66361808776855</v>
+        <v>7.66361856460571</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G561" t="n">
-        <v>7.66361808776855</v>
+        <v>7.66361856460571</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G562" t="n">
-        <v>7.66361808776855</v>
+        <v>7.66361856460571</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>8.25</v>
       </c>
       <c r="G571" t="n">
-        <v>7.52676820755005</v>
+        <v>7.52676868438721</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G572" t="n">
-        <v>7.43553495407104</v>
+        <v>7.43553447723389</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G573" t="n">
-        <v>7.43553495407104</v>
+        <v>7.43553447723389</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G574" t="n">
-        <v>7.43553495407104</v>
+        <v>7.43553447723389</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G575" t="n">
-        <v>7.43553495407104</v>
+        <v>7.43553447723389</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>8.25</v>
       </c>
       <c r="G577" t="n">
-        <v>7.52676820755005</v>
+        <v>7.52676868438721</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G578" t="n">
-        <v>7.25306797027588</v>
+        <v>7.25306749343872</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>8</v>
       </c>
       <c r="G579" t="n">
-        <v>7.29868507385254</v>
+        <v>7.29868459701538</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G581" t="n">
-        <v>7.3899188041687</v>
+        <v>7.38991832733154</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>8.25</v>
       </c>
       <c r="G585" t="n">
-        <v>7.52676820755005</v>
+        <v>7.52676868438721</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G586" t="n">
-        <v>7.3899188041687</v>
+        <v>7.38991832733154</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G587" t="n">
-        <v>7.3899188041687</v>
+        <v>7.38991832733154</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>8</v>
       </c>
       <c r="G588" t="n">
-        <v>7.29868507385254</v>
+        <v>7.29868459701538</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G589" t="n">
-        <v>7.3899188041687</v>
+        <v>7.38991832733154</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G590" t="n">
-        <v>7.3899188041687</v>
+        <v>7.38991832733154</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G591" t="n">
-        <v>7.3899188041687</v>
+        <v>7.38991832733154</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G592" t="n">
-        <v>7.3899188041687</v>
+        <v>7.38991832733154</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G595" t="n">
-        <v>7.43553495407104</v>
+        <v>7.43553447723389</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>8</v>
       </c>
       <c r="G596" t="n">
-        <v>7.29868507385254</v>
+        <v>7.29868459701538</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G597" t="n">
-        <v>7.43553495407104</v>
+        <v>7.43553447723389</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>8</v>
       </c>
       <c r="G599" t="n">
-        <v>7.29868507385254</v>
+        <v>7.29868459701538</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>8</v>
       </c>
       <c r="G600" t="n">
-        <v>7.29868507385254</v>
+        <v>7.29868459701538</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G603" t="n">
-        <v>7.25306797027588</v>
+        <v>7.25306749343872</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G626" t="n">
-        <v>7.77841663360596</v>
+        <v>7.7784161567688</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G631" t="n">
-        <v>7.77841663360596</v>
+        <v>7.7784161567688</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>8.25</v>
       </c>
       <c r="G634" t="n">
-        <v>7.82584571838379</v>
+        <v>7.82584619522095</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>8.25</v>
       </c>
       <c r="G635" t="n">
-        <v>7.82584571838379</v>
+        <v>7.82584619522095</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G636" t="n">
-        <v>7.77841663360596</v>
+        <v>7.7784161567688</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>8.25</v>
       </c>
       <c r="G643" t="n">
-        <v>7.82584571838379</v>
+        <v>7.82584619522095</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>8.25</v>
       </c>
       <c r="G644" t="n">
-        <v>7.82584571838379</v>
+        <v>7.82584619522095</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>8.25</v>
       </c>
       <c r="G645" t="n">
-        <v>7.82584571838379</v>
+        <v>7.82584619522095</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>8.25</v>
       </c>
       <c r="G646" t="n">
-        <v>7.82584571838379</v>
+        <v>7.82584619522095</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>8.25</v>
       </c>
       <c r="G647" t="n">
-        <v>7.82584571838379</v>
+        <v>7.82584619522095</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G721" t="n">
-        <v>6.68754100799561</v>
+        <v>6.68754148483276</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G729" t="n">
-        <v>6.68754100799561</v>
+        <v>6.68754148483276</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G734" t="n">
-        <v>6.35553550720215</v>
+        <v>6.35553503036499</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G752" t="n">
-        <v>6.68754100799561</v>
+        <v>6.68754148483276</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G753" t="n">
-        <v>6.68754100799561</v>
+        <v>6.68754148483276</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G755" t="n">
-        <v>6.68754100799561</v>
+        <v>6.68754148483276</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G758" t="n">
-        <v>6.68754100799561</v>
+        <v>6.68754148483276</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G759" t="n">
-        <v>6.68754100799561</v>
+        <v>6.68754148483276</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G781" t="n">
-        <v>7.77841663360596</v>
+        <v>7.7784161567688</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G783" t="n">
-        <v>7.92070436477661</v>
+        <v>7.92070484161377</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G817" t="n">
-        <v>6.68754100799561</v>
+        <v>6.68754148483276</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G819" t="n">
-        <v>6.68754100799561</v>
+        <v>6.68754148483276</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G824" t="n">
-        <v>6.26067638397217</v>
+        <v>6.26067686080933</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G825" t="n">
-        <v>6.39347887039185</v>
+        <v>6.39347839355469</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G830" t="n">
-        <v>6.94365978240967</v>
+        <v>6.94365930557251</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G835" t="n">
-        <v>6.77291393280029</v>
+        <v>6.77291345596313</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G836" t="n">
-        <v>6.77291393280029</v>
+        <v>6.77291345596313</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G838" t="n">
-        <v>7.2472071647644</v>
+        <v>7.24720764160156</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G847" t="n">
-        <v>7.22823524475098</v>
+        <v>7.22823572158813</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G848" t="n">
-        <v>7.2472071647644</v>
+        <v>7.24720764160156</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G852" t="n">
-        <v>7.22823524475098</v>
+        <v>7.22823572158813</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G857" t="n">
-        <v>7.77841663360596</v>
+        <v>7.7784161567688</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G859" t="n">
-        <v>7.77841663360596</v>
+        <v>7.7784161567688</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G865" t="n">
-        <v>7.89224624633789</v>
+        <v>7.89224672317505</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -31520,6 +31520,32 @@
         <v>8.02000045776367</v>
       </c>
       <c r="H1198" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1199">
+      <c r="A1199" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B1199" t="n">
+        <v>250</v>
+      </c>
+      <c r="C1199" t="n">
+        <v>8</v>
+      </c>
+      <c r="D1199" t="n">
+        <v>7.98000001907349</v>
+      </c>
+      <c r="E1199" t="n">
+        <v>7.98000001907349</v>
+      </c>
+      <c r="F1199" t="n">
+        <v>8</v>
+      </c>
+      <c r="G1199" t="n">
+        <v>8</v>
+      </c>
+      <c r="H1199" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/SVS.MI.xlsx
+++ b/data/SVS.MI.xlsx
@@ -28011,8 +28011,31 @@
       <c r="E1202" t="n">
         <v>7.73999977111816</v>
       </c>
-      <c r="F1202"/>
+      <c r="F1202" t="n">
+        <v>7.84000015258789</v>
+      </c>
       <c r="G1202" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1203">
+      <c r="A1203" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B1203" t="n">
+        <v>748</v>
+      </c>
+      <c r="C1203" t="n">
+        <v>7.92000007629395</v>
+      </c>
+      <c r="D1203" t="n">
+        <v>7.69999980926514</v>
+      </c>
+      <c r="E1203" t="n">
+        <v>7.84000015258789</v>
+      </c>
+      <c r="F1203"/>
+      <c r="G1203" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/SVS.MI.xlsx
+++ b/data/SVS.MI.xlsx
@@ -28034,7 +28034,9 @@
       <c r="E1203" t="n">
         <v>7.84000015258789</v>
       </c>
-      <c r="F1203"/>
+      <c r="F1203" t="n">
+        <v>7.90000009536743</v>
+      </c>
       <c r="G1203" t="s">
         <v>7</v>
       </c>

--- a/data/SVS.MI.xlsx
+++ b/data/SVS.MI.xlsx
@@ -28041,6 +28041,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1204">
+      <c r="A1204" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B1204" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1204" t="n">
+        <v>7.90000009536743</v>
+      </c>
+      <c r="D1204" t="n">
+        <v>7.90000009536743</v>
+      </c>
+      <c r="E1204" t="n">
+        <v>7.90000009536743</v>
+      </c>
+      <c r="F1204" t="n">
+        <v>7.90000009536743</v>
+      </c>
+      <c r="G1204" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SVS.MI.xlsx
+++ b/data/SVS.MI.xlsx
@@ -28064,6 +28064,50 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1205">
+      <c r="A1205" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B1205" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1205" t="n">
+        <v>7.90000009536743</v>
+      </c>
+      <c r="D1205" t="n">
+        <v>7.90000009536743</v>
+      </c>
+      <c r="E1205" t="n">
+        <v>7.90000009536743</v>
+      </c>
+      <c r="F1205" t="n">
+        <v>7.90000009536743</v>
+      </c>
+      <c r="G1205" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1206">
+      <c r="A1206" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B1206" t="n">
+        <v>199</v>
+      </c>
+      <c r="C1206" t="n">
+        <v>8</v>
+      </c>
+      <c r="D1206" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1206" t="n">
+        <v>8</v>
+      </c>
+      <c r="F1206"/>
+      <c r="G1206" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SVS.MI.xlsx
+++ b/data/SVS.MI.xlsx
@@ -28110,6 +28110,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1207">
+      <c r="A1207" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B1207" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1207" t="n">
+        <v>8</v>
+      </c>
+      <c r="D1207" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1207" t="n">
+        <v>8</v>
+      </c>
+      <c r="F1207" t="n">
+        <v>8</v>
+      </c>
+      <c r="G1207" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SVS.MI.xlsx
+++ b/data/SVS.MI.xlsx
@@ -499,7 +499,7 @@
         <v>14.5600004196167</v>
       </c>
       <c r="G5" t="n">
-        <v>13.2836055755615</v>
+        <v>13.2836065292358</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G6" t="n">
-        <v>13.4113330841064</v>
+        <v>13.4113321304321</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G16" t="n">
-        <v>12.2435436248779</v>
+        <v>12.2435445785522</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G18" t="n">
-        <v>12.2252960205078</v>
+        <v>12.2252969741821</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G21" t="n">
-        <v>12.4077644348145</v>
+        <v>12.4077634811401</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G23" t="n">
-        <v>12.2252960205078</v>
+        <v>12.2252969741821</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G26" t="n">
-        <v>11.9698429107666</v>
+        <v>11.9698419570923</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>13</v>
       </c>
       <c r="G28" t="n">
-        <v>11.8603620529175</v>
+        <v>11.8603630065918</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G29" t="n">
-        <v>11.6778964996338</v>
+        <v>11.6778955459595</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G34" t="n">
-        <v>11.2034816741943</v>
+        <v>11.20348072052</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G36" t="n">
-        <v>10.5830926895142</v>
+        <v>10.5830936431885</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G38" t="n">
-        <v>10.5830926895142</v>
+        <v>10.5830936431885</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>11</v>
       </c>
       <c r="G39" t="n">
-        <v>10.0356912612915</v>
+        <v>10.0356903076172</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G40" t="n">
-        <v>9.79848384857178</v>
+        <v>9.79848289489746</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G42" t="n">
-        <v>9.76199150085449</v>
+        <v>9.76199054718018</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>10.7600002288818</v>
       </c>
       <c r="G43" t="n">
-        <v>9.81673049926758</v>
+        <v>9.81673145294189</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G44" t="n">
-        <v>10.2181577682495</v>
+        <v>10.2181587219238</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G47" t="n">
-        <v>11.6778964996338</v>
+        <v>11.6778955459595</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>13.0600004196167</v>
       </c>
       <c r="G48" t="n">
-        <v>11.9151039123535</v>
+        <v>11.9151029586792</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>13</v>
       </c>
       <c r="G49" t="n">
-        <v>11.8603620529175</v>
+        <v>11.8603630065918</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>13</v>
       </c>
       <c r="G50" t="n">
-        <v>11.8603620529175</v>
+        <v>11.8603630065918</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G51" t="n">
-        <v>12.2252960205078</v>
+        <v>12.2252969741821</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>13</v>
       </c>
       <c r="G62" t="n">
-        <v>11.8603620529175</v>
+        <v>11.8603630065918</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G66" t="n">
-        <v>11.2399740219116</v>
+        <v>11.2399730682373</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G69" t="n">
-        <v>11.9698429107666</v>
+        <v>11.9698419570923</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G76" t="n">
-        <v>10.7655601501465</v>
+        <v>10.7655591964722</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G84" t="n">
-        <v>10.2181577682495</v>
+        <v>10.2181587219238</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G91" t="n">
-        <v>10.7655601501465</v>
+        <v>10.7655591964722</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G98" t="n">
-        <v>10.1816654205322</v>
+        <v>10.1816644668579</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G99" t="n">
-        <v>10.2181577682495</v>
+        <v>10.2181587219238</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G106" t="n">
-        <v>10.3093919754028</v>
+        <v>10.3093929290771</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>11</v>
       </c>
       <c r="G107" t="n">
-        <v>10.0356912612915</v>
+        <v>10.0356903076172</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G109" t="n">
-        <v>10.2181577682495</v>
+        <v>10.2181587219238</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G110" t="n">
-        <v>10.2181577682495</v>
+        <v>10.2181587219238</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G111" t="n">
-        <v>10.2181577682495</v>
+        <v>10.2181587219238</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G112" t="n">
-        <v>9.85322380065918</v>
+        <v>9.8532247543335</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G113" t="n">
-        <v>10.1269264221191</v>
+        <v>10.1269254684448</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G114" t="n">
-        <v>10.1269264221191</v>
+        <v>10.1269254684448</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G115" t="n">
-        <v>10.2728986740112</v>
+        <v>10.2728977203369</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G120" t="n">
-        <v>10.2728986740112</v>
+        <v>10.2728977203369</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G124" t="n">
-        <v>10.1816654205322</v>
+        <v>10.1816644668579</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>11.039999961853</v>
       </c>
       <c r="G128" t="n">
-        <v>10.0721845626831</v>
+        <v>10.0721855163574</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>11.039999961853</v>
       </c>
       <c r="G129" t="n">
-        <v>10.0721845626831</v>
+        <v>10.0721855163574</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>11</v>
       </c>
       <c r="G130" t="n">
-        <v>10.0356912612915</v>
+        <v>10.0356903076172</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>11</v>
       </c>
       <c r="G131" t="n">
-        <v>10.0356912612915</v>
+        <v>10.0356903076172</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>11</v>
       </c>
       <c r="G132" t="n">
-        <v>10.0356912612915</v>
+        <v>10.0356903076172</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>11</v>
       </c>
       <c r="G133" t="n">
-        <v>10.0356912612915</v>
+        <v>10.0356903076172</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="G134" t="n">
-        <v>10.510106086731</v>
+        <v>10.5101051330566</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G139" t="n">
-        <v>10.1816654205322</v>
+        <v>10.1816644668579</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>11.2799997329712</v>
       </c>
       <c r="G141" t="n">
-        <v>10.2911443710327</v>
+        <v>10.291145324707</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G143" t="n">
-        <v>10.2728986740112</v>
+        <v>10.2728977203369</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>11</v>
       </c>
       <c r="G145" t="n">
-        <v>10.0356912612915</v>
+        <v>10.0356903076172</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>11</v>
       </c>
       <c r="G146" t="n">
-        <v>10.0356912612915</v>
+        <v>10.0356903076172</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>11.2799997329712</v>
       </c>
       <c r="G147" t="n">
-        <v>10.2911443710327</v>
+        <v>10.291145324707</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G148" t="n">
-        <v>10.3093919754028</v>
+        <v>10.3093929290771</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G152" t="n">
-        <v>10.1269264221191</v>
+        <v>10.1269254684448</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G156" t="n">
-        <v>10.1269264221191</v>
+        <v>10.1269254684448</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G157" t="n">
-        <v>10.1269264221191</v>
+        <v>10.1269254684448</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G159" t="n">
-        <v>10.1269264221191</v>
+        <v>10.1269254684448</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G162" t="n">
-        <v>9.85322380065918</v>
+        <v>9.8532247543335</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G164" t="n">
-        <v>10.1269264221191</v>
+        <v>10.1269254684448</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G165" t="n">
-        <v>10.1816654205322</v>
+        <v>10.1816644668579</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G166" t="n">
-        <v>10.3093919754028</v>
+        <v>10.3093929290771</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G167" t="n">
-        <v>10.1816654205322</v>
+        <v>10.1816644668579</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>11</v>
       </c>
       <c r="G168" t="n">
-        <v>10.0356912612915</v>
+        <v>10.0356903076172</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G169" t="n">
-        <v>9.30582332611084</v>
+        <v>9.30582237243652</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>10.3400001525879</v>
       </c>
       <c r="G170" t="n">
-        <v>9.43354988098145</v>
+        <v>9.43355083465576</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>10.3400001525879</v>
       </c>
       <c r="G171" t="n">
-        <v>9.43354988098145</v>
+        <v>9.43355083465576</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G172" t="n">
-        <v>9.39705753326416</v>
+        <v>9.39705657958984</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>9.56999969482422</v>
       </c>
       <c r="G175" t="n">
-        <v>8.73105049133301</v>
+        <v>8.73105144500732</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>9.5</v>
       </c>
       <c r="G176" t="n">
-        <v>8.66718769073486</v>
+        <v>8.66718864440918</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>9.43000030517578</v>
       </c>
       <c r="G179" t="n">
-        <v>8.60332489013672</v>
+        <v>8.6033239364624</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G183" t="n">
-        <v>7.57238531112671</v>
+        <v>7.57238578796387</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>8.60999965667725</v>
       </c>
       <c r="G185" t="n">
-        <v>7.8552098274231</v>
+        <v>7.85520935058594</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>9.01000022888184</v>
       </c>
       <c r="G187" t="n">
-        <v>8.22014427185059</v>
+        <v>8.22014331817627</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G189" t="n">
-        <v>8.27488231658936</v>
+        <v>8.27488327026367</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>8.59000015258789</v>
       </c>
       <c r="G193" t="n">
-        <v>7.83696317672729</v>
+        <v>7.83696269989014</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G195" t="n">
-        <v>7.61800241470337</v>
+        <v>7.61800289154053</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G196" t="n">
-        <v>7.61800241470337</v>
+        <v>7.61800289154053</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>8.25</v>
       </c>
       <c r="G197" t="n">
-        <v>7.52676916122437</v>
+        <v>7.52676868438721</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>8.60999965667725</v>
       </c>
       <c r="G202" t="n">
-        <v>7.8552098274231</v>
+        <v>7.85520935058594</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G203" t="n">
-        <v>7.8825798034668</v>
+        <v>7.88258028030396</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G204" t="n">
-        <v>7.8825798034668</v>
+        <v>7.88258028030396</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>8.60999965667725</v>
       </c>
       <c r="G205" t="n">
-        <v>7.8552098274231</v>
+        <v>7.85520935058594</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G206" t="n">
-        <v>7.93731880187988</v>
+        <v>7.9373197555542</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G207" t="n">
-        <v>7.93731880187988</v>
+        <v>7.9373197555542</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G208" t="n">
-        <v>7.93731880187988</v>
+        <v>7.9373197555542</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G209" t="n">
-        <v>7.93731880187988</v>
+        <v>7.9373197555542</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G210" t="n">
-        <v>7.93731880187988</v>
+        <v>7.9373197555542</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G211" t="n">
-        <v>7.97381258010864</v>
+        <v>7.9738130569458</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G215" t="n">
-        <v>8.27488231658936</v>
+        <v>8.27488327026367</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G229" t="n">
-        <v>8.57595443725586</v>
+        <v>8.57595348358154</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>9.43000030517578</v>
       </c>
       <c r="G230" t="n">
-        <v>8.60332489013672</v>
+        <v>8.6033239364624</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>9.43000030517578</v>
       </c>
       <c r="G234" t="n">
-        <v>8.60332489013672</v>
+        <v>8.6033239364624</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>9.43000030517578</v>
       </c>
       <c r="G235" t="n">
-        <v>8.60332489013672</v>
+        <v>8.6033239364624</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G239" t="n">
-        <v>8.62157154083252</v>
+        <v>8.6215705871582</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>9.63000011444092</v>
       </c>
       <c r="G242" t="n">
-        <v>8.78579139709473</v>
+        <v>8.78579235076904</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>9.63000011444092</v>
       </c>
       <c r="G243" t="n">
-        <v>8.78579139709473</v>
+        <v>8.78579235076904</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>9.63000011444092</v>
       </c>
       <c r="G244" t="n">
-        <v>8.78579139709473</v>
+        <v>8.78579235076904</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>9.63000011444092</v>
       </c>
       <c r="G245" t="n">
-        <v>8.78579139709473</v>
+        <v>8.78579235076904</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G247" t="n">
-        <v>9.03212261199951</v>
+        <v>9.0321216583252</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G248" t="n">
-        <v>9.03212261199951</v>
+        <v>9.0321216583252</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G258" t="n">
-        <v>9.03212261199951</v>
+        <v>9.0321216583252</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G260" t="n">
-        <v>8.84965419769287</v>
+        <v>8.84965515136719</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G261" t="n">
-        <v>9.01387596130371</v>
+        <v>9.01387500762939</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>9.75</v>
       </c>
       <c r="G268" t="n">
-        <v>8.89527225494385</v>
+        <v>8.89527130126953</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>9.75</v>
       </c>
       <c r="G269" t="n">
-        <v>8.89527225494385</v>
+        <v>8.89527130126953</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>8.92000007629395</v>
       </c>
       <c r="G273" t="n">
-        <v>8.13803291320801</v>
+        <v>8.13803386688232</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G276" t="n">
-        <v>8.35699367523193</v>
+        <v>8.35699462890625</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>8.71000003814697</v>
       </c>
       <c r="G279" t="n">
-        <v>7.94644260406494</v>
+        <v>7.9464430809021</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>8.72999954223633</v>
       </c>
       <c r="G280" t="n">
-        <v>7.96468925476074</v>
+        <v>7.9646897315979</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>8.77000045776367</v>
       </c>
       <c r="G283" t="n">
-        <v>8.00118350982666</v>
+        <v>8.00118446350098</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G285" t="n">
-        <v>8.37524032592773</v>
+        <v>8.37524127960205</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>9.09000015258789</v>
       </c>
       <c r="G286" t="n">
-        <v>8.29312992095947</v>
+        <v>8.29313087463379</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>9.09000015258789</v>
       </c>
       <c r="G287" t="n">
-        <v>8.29312992095947</v>
+        <v>8.29313087463379</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G288" t="n">
-        <v>8.27488231658936</v>
+        <v>8.27488327026367</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G293" t="n">
-        <v>8.27488231658936</v>
+        <v>8.27488327026367</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>9.27000045776367</v>
       </c>
       <c r="G295" t="n">
-        <v>8.45735168457031</v>
+        <v>8.457350730896</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G301" t="n">
-        <v>8.34786987304688</v>
+        <v>8.34787082672119</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G308" t="n">
-        <v>8.37524032592773</v>
+        <v>8.37524127960205</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G309" t="n">
-        <v>8.19277381896973</v>
+        <v>8.19277286529541</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>9.01000022888184</v>
       </c>
       <c r="G314" t="n">
-        <v>8.22014427185059</v>
+        <v>8.22014331817627</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>9.01000022888184</v>
       </c>
       <c r="G315" t="n">
-        <v>8.22014427185059</v>
+        <v>8.22014331817627</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>9.5</v>
       </c>
       <c r="G321" t="n">
-        <v>8.66718769073486</v>
+        <v>8.66718864440918</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G323" t="n">
-        <v>8.28400611877441</v>
+        <v>8.28400707244873</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G324" t="n">
-        <v>8.28400611877441</v>
+        <v>8.28400707244873</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>8.92000007629395</v>
       </c>
       <c r="G327" t="n">
-        <v>8.13803291320801</v>
+        <v>8.13803386688232</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G331" t="n">
-        <v>8.59420204162598</v>
+        <v>8.59420108795166</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G335" t="n">
-        <v>8.24751472473145</v>
+        <v>8.24751377105713</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G338" t="n">
-        <v>7.93731880187988</v>
+        <v>7.9373197555542</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G339" t="n">
-        <v>7.53589200973511</v>
+        <v>7.53589153289795</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G340" t="n">
-        <v>7.57238531112671</v>
+        <v>7.57238578796387</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G347" t="n">
-        <v>7.53589200973511</v>
+        <v>7.53589153289795</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G352" t="n">
-        <v>7.3169322013855</v>
+        <v>7.31693172454834</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G354" t="n">
-        <v>7.20745134353638</v>
+        <v>7.20745182037354</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G366" t="n">
-        <v>6.95199728012085</v>
+        <v>6.95199680328369</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>7.51999998092651</v>
       </c>
       <c r="G368" t="n">
-        <v>6.86076307296753</v>
+        <v>6.86076354980469</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>7.51999998092651</v>
       </c>
       <c r="G369" t="n">
-        <v>6.86076307296753</v>
+        <v>6.86076354980469</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>7.5</v>
       </c>
       <c r="G370" t="n">
-        <v>6.84251689910889</v>
+        <v>6.84251737594604</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>7.51999998092651</v>
       </c>
       <c r="G371" t="n">
-        <v>6.86076307296753</v>
+        <v>6.86076354980469</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G372" t="n">
-        <v>6.95199728012085</v>
+        <v>6.95199680328369</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>7.5</v>
       </c>
       <c r="G380" t="n">
-        <v>6.84251689910889</v>
+        <v>6.84251737594604</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>7.5</v>
       </c>
       <c r="G381" t="n">
-        <v>6.84251689910889</v>
+        <v>6.84251737594604</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>7.5</v>
       </c>
       <c r="G382" t="n">
-        <v>6.84251689910889</v>
+        <v>6.84251737594604</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G389" t="n">
-        <v>7.17095804214478</v>
+        <v>7.17095756530762</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G390" t="n">
-        <v>7.3899188041687</v>
+        <v>7.38991832733154</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G392" t="n">
-        <v>7.57238531112671</v>
+        <v>7.57238578796387</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G393" t="n">
-        <v>7.57238531112671</v>
+        <v>7.57238578796387</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G394" t="n">
-        <v>7.57238531112671</v>
+        <v>7.57238578796387</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G395" t="n">
-        <v>7.57238531112671</v>
+        <v>7.57238578796387</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G396" t="n">
-        <v>7.57238531112671</v>
+        <v>7.57238578796387</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G403" t="n">
-        <v>7.49939870834351</v>
+        <v>7.49939918518066</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G414" t="n">
-        <v>7.44465827941895</v>
+        <v>7.4446587562561</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G415" t="n">
-        <v>7.44465827941895</v>
+        <v>7.4446587562561</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G424" t="n">
-        <v>7.44465827941895</v>
+        <v>7.4446587562561</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G425" t="n">
-        <v>7.60887861251831</v>
+        <v>7.60887908935547</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G426" t="n">
-        <v>7.79134559631348</v>
+        <v>7.79134511947632</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G427" t="n">
-        <v>7.8825798034668</v>
+        <v>7.88258028030396</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G431" t="n">
-        <v>7.55413818359375</v>
+        <v>7.55413770675659</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G432" t="n">
-        <v>7.55413818359375</v>
+        <v>7.55413770675659</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G442" t="n">
-        <v>6.80602359771729</v>
+        <v>6.80602312088013</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G443" t="n">
-        <v>6.75128316879272</v>
+        <v>6.75128364562988</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G444" t="n">
-        <v>6.75128316879272</v>
+        <v>6.75128364562988</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G449" t="n">
-        <v>6.75128316879272</v>
+        <v>6.75128364562988</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G450" t="n">
-        <v>6.75128316879272</v>
+        <v>6.75128364562988</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G451" t="n">
-        <v>6.75128316879272</v>
+        <v>6.75128364562988</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G452" t="n">
-        <v>6.75128316879272</v>
+        <v>6.75128364562988</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G453" t="n">
-        <v>6.75128316879272</v>
+        <v>6.75128364562988</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G454" t="n">
-        <v>6.75128316879272</v>
+        <v>6.75128364562988</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G455" t="n">
-        <v>6.58706283569336</v>
+        <v>6.5870623588562</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G456" t="n">
-        <v>6.4775824546814</v>
+        <v>6.47758293151855</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G459" t="n">
-        <v>6.4775824546814</v>
+        <v>6.47758293151855</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G464" t="n">
-        <v>6.56881618499756</v>
+        <v>6.5688157081604</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G465" t="n">
-        <v>6.56881618499756</v>
+        <v>6.5688157081604</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G466" t="n">
-        <v>6.56881618499756</v>
+        <v>6.5688157081604</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G467" t="n">
-        <v>6.56881618499756</v>
+        <v>6.5688157081604</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G468" t="n">
-        <v>6.56881618499756</v>
+        <v>6.5688157081604</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G473" t="n">
-        <v>6.42284297943115</v>
+        <v>6.42284250259399</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G475" t="n">
-        <v>6.67829608917236</v>
+        <v>6.67829656600952</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G476" t="n">
-        <v>6.67829608917236</v>
+        <v>6.67829656600952</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G484" t="n">
-        <v>6.58706283569336</v>
+        <v>6.5870623588562</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G485" t="n">
-        <v>6.58706283569336</v>
+        <v>6.5870623588562</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G486" t="n">
-        <v>6.58706283569336</v>
+        <v>6.5870623588562</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G487" t="n">
-        <v>6.64180278778076</v>
+        <v>6.64180326461792</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>7.5</v>
       </c>
       <c r="G488" t="n">
-        <v>6.84251689910889</v>
+        <v>6.84251737594604</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G491" t="n">
-        <v>7.18920469284058</v>
+        <v>7.18920421600342</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G492" t="n">
-        <v>7.20745134353638</v>
+        <v>7.20745182037354</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G493" t="n">
-        <v>7.22569751739502</v>
+        <v>7.22569799423218</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G507" t="n">
-        <v>7.3169322013855</v>
+        <v>7.31693172454834</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G511" t="n">
-        <v>7.20745134353638</v>
+        <v>7.20745182037354</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G512" t="n">
-        <v>7.3169322013855</v>
+        <v>7.31693172454834</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G513" t="n">
-        <v>7.20745134353638</v>
+        <v>7.20745182037354</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>7.51999998092651</v>
       </c>
       <c r="G517" t="n">
-        <v>6.86076307296753</v>
+        <v>6.86076354980469</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>7.5</v>
       </c>
       <c r="G518" t="n">
-        <v>6.84251689910889</v>
+        <v>6.84251737594604</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G519" t="n">
-        <v>6.80602359771729</v>
+        <v>6.80602312088013</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G530" t="n">
-        <v>7.17095804214478</v>
+        <v>7.17095756530762</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G536" t="n">
-        <v>7.3899188041687</v>
+        <v>7.38991832733154</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G537" t="n">
-        <v>7.18920469284058</v>
+        <v>7.18920421600342</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G539" t="n">
-        <v>7.20745134353638</v>
+        <v>7.20745182037354</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G540" t="n">
-        <v>7.20745134353638</v>
+        <v>7.20745182037354</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G544" t="n">
-        <v>7.3169322013855</v>
+        <v>7.31693172454834</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G545" t="n">
-        <v>7.20745134353638</v>
+        <v>7.20745182037354</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G548" t="n">
-        <v>7.3899188041687</v>
+        <v>7.38991832733154</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G549" t="n">
-        <v>7.55413818359375</v>
+        <v>7.55413770675659</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G550" t="n">
-        <v>7.49939870834351</v>
+        <v>7.49939918518066</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G554" t="n">
-        <v>7.57238531112671</v>
+        <v>7.57238578796387</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G555" t="n">
-        <v>7.57238531112671</v>
+        <v>7.57238578796387</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>8.25</v>
       </c>
       <c r="G571" t="n">
-        <v>7.52676916122437</v>
+        <v>7.52676868438721</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G576" t="n">
-        <v>7.61800241470337</v>
+        <v>7.61800289154053</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>8.25</v>
       </c>
       <c r="G577" t="n">
-        <v>7.52676916122437</v>
+        <v>7.52676868438721</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G578" t="n">
-        <v>7.25306749343872</v>
+        <v>7.25306797027588</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G581" t="n">
-        <v>7.3899188041687</v>
+        <v>7.38991832733154</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>8.25</v>
       </c>
       <c r="G585" t="n">
-        <v>7.52676916122437</v>
+        <v>7.52676868438721</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G586" t="n">
-        <v>7.3899188041687</v>
+        <v>7.38991832733154</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G587" t="n">
-        <v>7.3899188041687</v>
+        <v>7.38991832733154</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G589" t="n">
-        <v>7.3899188041687</v>
+        <v>7.38991832733154</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G590" t="n">
-        <v>7.3899188041687</v>
+        <v>7.38991832733154</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G591" t="n">
-        <v>7.3899188041687</v>
+        <v>7.38991832733154</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G592" t="n">
-        <v>7.3899188041687</v>
+        <v>7.38991832733154</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G603" t="n">
-        <v>7.25306749343872</v>
+        <v>7.25306797027588</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -31806,6 +31806,32 @@
         <v>8</v>
       </c>
       <c r="H1209" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1210">
+      <c r="A1210" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B1210" t="n">
+        <v>50</v>
+      </c>
+      <c r="C1210" t="n">
+        <v>8</v>
+      </c>
+      <c r="D1210" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1210" t="n">
+        <v>8</v>
+      </c>
+      <c r="F1210" t="n">
+        <v>8</v>
+      </c>
+      <c r="G1210" t="n">
+        <v>8</v>
+      </c>
+      <c r="H1210" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/SVS.MI.xlsx
+++ b/data/SVS.MI.xlsx
@@ -514,7 +514,7 @@
         <v>14.5600004196167</v>
       </c>
       <c r="G5" t="n">
-        <v>13.2836055755615</v>
+        <v>13.2836065292358</v>
       </c>
       <c r="H5" t="n">
         <v>2134</v>
@@ -543,7 +543,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G6" t="n">
-        <v>13.4113330841064</v>
+        <v>13.4113321304321</v>
       </c>
       <c r="H6" t="n">
         <v>1997</v>
@@ -572,7 +572,7 @@
         <v>14.539999961853</v>
       </c>
       <c r="G7" t="n">
-        <v>13.2653589248657</v>
+        <v>13.26535987854</v>
       </c>
       <c r="H7" t="n">
         <v>2735</v>
@@ -659,7 +659,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G10" t="n">
-        <v>12.5902309417725</v>
+        <v>12.5902318954468</v>
       </c>
       <c r="H10" t="n">
         <v>670</v>
@@ -688,7 +688,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G11" t="n">
-        <v>12.5902309417725</v>
+        <v>12.5902318954468</v>
       </c>
       <c r="H11" t="n">
         <v>13315</v>
@@ -804,7 +804,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G15" t="n">
-        <v>12.754451751709</v>
+        <v>12.7544498443604</v>
       </c>
       <c r="H15" t="n">
         <v>2068</v>
@@ -920,7 +920,7 @@
         <v>13.3400001525879</v>
       </c>
       <c r="G19" t="n">
-        <v>12.1705560684204</v>
+        <v>12.1705570220947</v>
       </c>
       <c r="H19" t="n">
         <v>3080</v>
@@ -949,7 +949,7 @@
         <v>13.6800003051758</v>
       </c>
       <c r="G20" t="n">
-        <v>12.480751991272</v>
+        <v>12.4807500839233</v>
       </c>
       <c r="H20" t="n">
         <v>2647</v>
@@ -1094,7 +1094,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G25" t="n">
-        <v>12.0428304672241</v>
+        <v>12.0428295135498</v>
       </c>
       <c r="H25" t="n">
         <v>600</v>
@@ -1123,7 +1123,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G26" t="n">
-        <v>11.9698429107666</v>
+        <v>11.9698419570923</v>
       </c>
       <c r="H26" t="n">
         <v>4682</v>
@@ -1181,7 +1181,7 @@
         <v>13</v>
       </c>
       <c r="G28" t="n">
-        <v>11.8603620529175</v>
+        <v>11.8603630065918</v>
       </c>
       <c r="H28" t="n">
         <v>2250</v>
@@ -1210,7 +1210,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G29" t="n">
-        <v>11.6778964996338</v>
+        <v>11.6778955459595</v>
       </c>
       <c r="H29" t="n">
         <v>1108</v>
@@ -1239,7 +1239,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G30" t="n">
-        <v>11.385947227478</v>
+        <v>11.3859481811523</v>
       </c>
       <c r="H30" t="n">
         <v>2251</v>
@@ -1268,7 +1268,7 @@
         <v>13.3599996566772</v>
       </c>
       <c r="G31" t="n">
-        <v>12.1888027191162</v>
+        <v>12.1888036727905</v>
       </c>
       <c r="H31" t="n">
         <v>6448</v>
@@ -1297,7 +1297,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G32" t="n">
-        <v>11.5501689910889</v>
+        <v>11.5501680374146</v>
       </c>
       <c r="H32" t="n">
         <v>2810</v>
@@ -1384,7 +1384,7 @@
         <v>11.3800001144409</v>
       </c>
       <c r="G35" t="n">
-        <v>10.3823795318604</v>
+        <v>10.382378578186</v>
       </c>
       <c r="H35" t="n">
         <v>16969</v>
@@ -1442,7 +1442,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G37" t="n">
-        <v>10.8203001022339</v>
+        <v>10.8202991485596</v>
       </c>
       <c r="H37" t="n">
         <v>1595</v>
@@ -1558,7 +1558,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G41" t="n">
-        <v>10.108678817749</v>
+        <v>10.1086778640747</v>
       </c>
       <c r="H41" t="n">
         <v>22904</v>
@@ -1587,7 +1587,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G42" t="n">
-        <v>9.76199150085449</v>
+        <v>9.76199054718018</v>
       </c>
       <c r="H42" t="n">
         <v>550</v>
@@ -1616,7 +1616,7 @@
         <v>10.7600002288818</v>
       </c>
       <c r="G43" t="n">
-        <v>9.81673049926758</v>
+        <v>9.81673145294189</v>
       </c>
       <c r="H43" t="n">
         <v>1169</v>
@@ -1732,7 +1732,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G47" t="n">
-        <v>11.6778964996338</v>
+        <v>11.6778955459595</v>
       </c>
       <c r="H47" t="n">
         <v>838</v>
@@ -1790,7 +1790,7 @@
         <v>13</v>
       </c>
       <c r="G49" t="n">
-        <v>11.8603620529175</v>
+        <v>11.8603630065918</v>
       </c>
       <c r="H49" t="n">
         <v>2500</v>
@@ -1819,7 +1819,7 @@
         <v>13</v>
       </c>
       <c r="G50" t="n">
-        <v>11.8603620529175</v>
+        <v>11.8603630065918</v>
       </c>
       <c r="H50" t="n">
         <v>220</v>
@@ -1993,7 +1993,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G56" t="n">
-        <v>12.0428304672241</v>
+        <v>12.0428295135498</v>
       </c>
       <c r="H56" t="n">
         <v>275</v>
@@ -2022,7 +2022,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G57" t="n">
-        <v>12.0428304672241</v>
+        <v>12.0428295135498</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G58" t="n">
-        <v>12.0428304672241</v>
+        <v>12.0428295135498</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
@@ -2080,7 +2080,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G59" t="n">
-        <v>12.0428304672241</v>
+        <v>12.0428295135498</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
@@ -2109,7 +2109,7 @@
         <v>13.039999961853</v>
       </c>
       <c r="G60" t="n">
-        <v>11.8968563079834</v>
+        <v>11.8968553543091</v>
       </c>
       <c r="H60" t="n">
         <v>411</v>
@@ -2167,7 +2167,7 @@
         <v>13</v>
       </c>
       <c r="G62" t="n">
-        <v>11.8603620529175</v>
+        <v>11.8603630065918</v>
       </c>
       <c r="H62" t="n">
         <v>4800</v>
@@ -2225,7 +2225,7 @@
         <v>12.5</v>
       </c>
       <c r="G64" t="n">
-        <v>11.4041948318481</v>
+        <v>11.4041957855225</v>
       </c>
       <c r="H64" t="n">
         <v>200</v>
@@ -2312,7 +2312,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G67" t="n">
-        <v>11.5866613388062</v>
+        <v>11.5866622924805</v>
       </c>
       <c r="H67" t="n">
         <v>2052</v>
@@ -2370,7 +2370,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G69" t="n">
-        <v>11.9698429107666</v>
+        <v>11.9698419570923</v>
       </c>
       <c r="H69" t="n">
         <v>660</v>
@@ -2399,7 +2399,7 @@
         <v>12.5</v>
       </c>
       <c r="G70" t="n">
-        <v>11.4041948318481</v>
+        <v>11.4041957855225</v>
       </c>
       <c r="H70" t="n">
         <v>4141</v>
@@ -2486,7 +2486,7 @@
         <v>12.5</v>
       </c>
       <c r="G73" t="n">
-        <v>11.4041948318481</v>
+        <v>11.4041957855225</v>
       </c>
       <c r="H73" t="n">
         <v>2200</v>
@@ -2602,7 +2602,7 @@
         <v>11.9200000762939</v>
       </c>
       <c r="G77" t="n">
-        <v>10.8750400543213</v>
+        <v>10.8750410079956</v>
       </c>
       <c r="H77" t="n">
         <v>724</v>
@@ -2631,7 +2631,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G78" t="n">
-        <v>10.8932867050171</v>
+        <v>10.8932857513428</v>
       </c>
       <c r="H78" t="n">
         <v>100</v>
@@ -2660,7 +2660,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G79" t="n">
-        <v>10.8020534515381</v>
+        <v>10.8020544052124</v>
       </c>
       <c r="H79" t="n">
         <v>950</v>
@@ -2718,7 +2718,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G81" t="n">
-        <v>10.8203001022339</v>
+        <v>10.8202991485596</v>
       </c>
       <c r="H81" t="n">
         <v>1654</v>
@@ -2834,7 +2834,7 @@
         <v>11.5</v>
       </c>
       <c r="G85" t="n">
-        <v>10.4918594360352</v>
+        <v>10.4918584823608</v>
       </c>
       <c r="H85" t="n">
         <v>1710</v>
@@ -2921,7 +2921,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G88" t="n">
-        <v>10.6743259429932</v>
+        <v>10.6743268966675</v>
       </c>
       <c r="H88" t="n">
         <v>4077</v>
@@ -2950,7 +2950,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G89" t="n">
-        <v>10.6743259429932</v>
+        <v>10.6743268966675</v>
       </c>
       <c r="H89" t="n">
         <v>120</v>
@@ -3095,7 +3095,7 @@
         <v>11.9200000762939</v>
       </c>
       <c r="G94" t="n">
-        <v>10.8750400543213</v>
+        <v>10.8750410079956</v>
       </c>
       <c r="H94" t="n">
         <v>3220</v>
@@ -3182,7 +3182,7 @@
         <v>11.5</v>
       </c>
       <c r="G97" t="n">
-        <v>10.4918594360352</v>
+        <v>10.4918584823608</v>
       </c>
       <c r="H97" t="n">
         <v>16862</v>
@@ -3211,7 +3211,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G98" t="n">
-        <v>10.1816654205322</v>
+        <v>10.1816644668579</v>
       </c>
       <c r="H98" t="n">
         <v>35194</v>
@@ -3269,7 +3269,7 @@
         <v>11.9200000762939</v>
       </c>
       <c r="G100" t="n">
-        <v>10.8750400543213</v>
+        <v>10.8750410079956</v>
       </c>
       <c r="H100" t="n">
         <v>4278</v>
@@ -3356,7 +3356,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G103" t="n">
-        <v>10.6743259429932</v>
+        <v>10.6743268966675</v>
       </c>
       <c r="H103" t="n">
         <v>2275</v>
@@ -3385,7 +3385,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G104" t="n">
-        <v>10.6743259429932</v>
+        <v>10.6743268966675</v>
       </c>
       <c r="H104" t="n">
         <v>780</v>
@@ -3414,7 +3414,7 @@
         <v>11.7799997329712</v>
       </c>
       <c r="G105" t="n">
-        <v>10.7473125457764</v>
+        <v>10.7473134994507</v>
       </c>
       <c r="H105" t="n">
         <v>2174</v>
@@ -3501,7 +3501,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G108" t="n">
-        <v>9.94445705413818</v>
+        <v>9.9444580078125</v>
       </c>
       <c r="H108" t="n">
         <v>4150</v>
@@ -3617,7 +3617,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G112" t="n">
-        <v>9.85322380065918</v>
+        <v>9.8532247543335</v>
       </c>
       <c r="H112" t="n">
         <v>600</v>
@@ -3646,7 +3646,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G113" t="n">
-        <v>10.1269264221191</v>
+        <v>10.1269254684448</v>
       </c>
       <c r="H113" t="n">
         <v>1110</v>
@@ -3675,7 +3675,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G114" t="n">
-        <v>10.1269264221191</v>
+        <v>10.1269254684448</v>
       </c>
       <c r="H114" t="n">
         <v>1005</v>
@@ -3704,7 +3704,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G115" t="n">
-        <v>10.2728986740112</v>
+        <v>10.2728996276855</v>
       </c>
       <c r="H115" t="n">
         <v>970</v>
@@ -3733,7 +3733,7 @@
         <v>11.5</v>
       </c>
       <c r="G116" t="n">
-        <v>10.4918594360352</v>
+        <v>10.4918584823608</v>
       </c>
       <c r="H116" t="n">
         <v>1595</v>
@@ -3820,7 +3820,7 @@
         <v>11.7799997329712</v>
       </c>
       <c r="G119" t="n">
-        <v>10.7473125457764</v>
+        <v>10.7473134994507</v>
       </c>
       <c r="H119" t="n">
         <v>1393</v>
@@ -3849,7 +3849,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G120" t="n">
-        <v>10.2728986740112</v>
+        <v>10.2728996276855</v>
       </c>
       <c r="H120" t="n">
         <v>3314</v>
@@ -3936,7 +3936,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G123" t="n">
-        <v>10.2546520233154</v>
+        <v>10.2546510696411</v>
       </c>
       <c r="H123" t="n">
         <v>923</v>
@@ -3965,7 +3965,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G124" t="n">
-        <v>10.1816654205322</v>
+        <v>10.1816644668579</v>
       </c>
       <c r="H124" t="n">
         <v>695</v>
@@ -4081,7 +4081,7 @@
         <v>11.039999961853</v>
       </c>
       <c r="G128" t="n">
-        <v>10.0721845626831</v>
+        <v>10.0721855163574</v>
       </c>
       <c r="H128" t="n">
         <v>5476</v>
@@ -4110,7 +4110,7 @@
         <v>11.039999961853</v>
       </c>
       <c r="G129" t="n">
-        <v>10.0721845626831</v>
+        <v>10.0721855163574</v>
       </c>
       <c r="H129" t="n">
         <v>0</v>
@@ -4400,7 +4400,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G139" t="n">
-        <v>10.1816654205322</v>
+        <v>10.1816644668579</v>
       </c>
       <c r="H139" t="n">
         <v>280</v>
@@ -4458,7 +4458,7 @@
         <v>11.2799997329712</v>
       </c>
       <c r="G141" t="n">
-        <v>10.2911443710327</v>
+        <v>10.291145324707</v>
       </c>
       <c r="H141" t="n">
         <v>250</v>
@@ -4516,7 +4516,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G143" t="n">
-        <v>10.2728986740112</v>
+        <v>10.2728996276855</v>
       </c>
       <c r="H143" t="n">
         <v>354</v>
@@ -4545,7 +4545,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G144" t="n">
-        <v>9.94445705413818</v>
+        <v>9.9444580078125</v>
       </c>
       <c r="H144" t="n">
         <v>9773</v>
@@ -4632,7 +4632,7 @@
         <v>11.2799997329712</v>
       </c>
       <c r="G147" t="n">
-        <v>10.2911443710327</v>
+        <v>10.291145324707</v>
       </c>
       <c r="H147" t="n">
         <v>780</v>
@@ -4777,7 +4777,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G152" t="n">
-        <v>10.1269264221191</v>
+        <v>10.1269254684448</v>
       </c>
       <c r="H152" t="n">
         <v>398</v>
@@ -4893,7 +4893,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G156" t="n">
-        <v>10.1269264221191</v>
+        <v>10.1269254684448</v>
       </c>
       <c r="H156" t="n">
         <v>206</v>
@@ -4922,7 +4922,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G157" t="n">
-        <v>10.1269264221191</v>
+        <v>10.1269254684448</v>
       </c>
       <c r="H157" t="n">
         <v>0</v>
@@ -4951,7 +4951,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G158" t="n">
-        <v>9.94445705413818</v>
+        <v>9.9444580078125</v>
       </c>
       <c r="H158" t="n">
         <v>320</v>
@@ -4980,7 +4980,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G159" t="n">
-        <v>10.1269264221191</v>
+        <v>10.1269254684448</v>
       </c>
       <c r="H159" t="n">
         <v>378</v>
@@ -5009,7 +5009,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G160" t="n">
-        <v>9.94445705413818</v>
+        <v>9.9444580078125</v>
       </c>
       <c r="H160" t="n">
         <v>220</v>
@@ -5038,7 +5038,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G161" t="n">
-        <v>9.94445705413818</v>
+        <v>9.9444580078125</v>
       </c>
       <c r="H161" t="n">
         <v>1909</v>
@@ -5067,7 +5067,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G162" t="n">
-        <v>9.85322380065918</v>
+        <v>9.8532247543335</v>
       </c>
       <c r="H162" t="n">
         <v>559</v>
@@ -5125,7 +5125,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G164" t="n">
-        <v>10.1269264221191</v>
+        <v>10.1269254684448</v>
       </c>
       <c r="H164" t="n">
         <v>207</v>
@@ -5154,7 +5154,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G165" t="n">
-        <v>10.1816654205322</v>
+        <v>10.1816644668579</v>
       </c>
       <c r="H165" t="n">
         <v>40</v>
@@ -5212,7 +5212,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G167" t="n">
-        <v>10.1816654205322</v>
+        <v>10.1816644668579</v>
       </c>
       <c r="H167" t="n">
         <v>3600</v>
@@ -5270,7 +5270,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G169" t="n">
-        <v>9.30582332611084</v>
+        <v>9.30582237243652</v>
       </c>
       <c r="H169" t="n">
         <v>1233</v>
@@ -5357,7 +5357,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G172" t="n">
-        <v>9.39705753326416</v>
+        <v>9.39705657958984</v>
       </c>
       <c r="H172" t="n">
         <v>1640</v>
@@ -5444,7 +5444,7 @@
         <v>9.56999969482422</v>
       </c>
       <c r="G175" t="n">
-        <v>8.73105049133301</v>
+        <v>8.73105144500732</v>
       </c>
       <c r="H175" t="n">
         <v>6256</v>
@@ -5502,7 +5502,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G177" t="n">
-        <v>8.48472118377686</v>
+        <v>8.48472023010254</v>
       </c>
       <c r="H177" t="n">
         <v>19</v>
@@ -5531,7 +5531,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G178" t="n">
-        <v>8.50296688079834</v>
+        <v>8.50296783447266</v>
       </c>
       <c r="H178" t="n">
         <v>369</v>
@@ -5560,7 +5560,7 @@
         <v>9.43000030517578</v>
       </c>
       <c r="G179" t="n">
-        <v>8.60332489013672</v>
+        <v>8.60332584381104</v>
       </c>
       <c r="H179" t="n">
         <v>255</v>
@@ -5589,7 +5589,7 @@
         <v>8.75</v>
       </c>
       <c r="G180" t="n">
-        <v>7.9829363822937</v>
+        <v>7.98293590545654</v>
       </c>
       <c r="H180" t="n">
         <v>2549</v>
@@ -5647,7 +5647,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G182" t="n">
-        <v>7.70923566818237</v>
+        <v>7.70923519134521</v>
       </c>
       <c r="H182" t="n">
         <v>4032</v>
@@ -5734,7 +5734,7 @@
         <v>8.60999965667725</v>
       </c>
       <c r="G185" t="n">
-        <v>7.8552098274231</v>
+        <v>7.85520887374878</v>
       </c>
       <c r="H185" t="n">
         <v>840</v>
@@ -5792,7 +5792,7 @@
         <v>9.01000022888184</v>
       </c>
       <c r="G187" t="n">
-        <v>8.22014427185059</v>
+        <v>8.22014331817627</v>
       </c>
       <c r="H187" t="n">
         <v>2520</v>
@@ -5821,7 +5821,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G188" t="n">
-        <v>8.11978721618652</v>
+        <v>8.11978626251221</v>
       </c>
       <c r="H188" t="n">
         <v>1750</v>
@@ -5850,7 +5850,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G189" t="n">
-        <v>8.27488231658936</v>
+        <v>8.27488422393799</v>
       </c>
       <c r="H189" t="n">
         <v>700</v>
@@ -5966,7 +5966,7 @@
         <v>8.59000015258789</v>
       </c>
       <c r="G193" t="n">
-        <v>7.83696317672729</v>
+        <v>7.83696269989014</v>
       </c>
       <c r="H193" t="n">
         <v>35</v>
@@ -5995,7 +5995,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G194" t="n">
-        <v>7.73660564422607</v>
+        <v>7.73660516738892</v>
       </c>
       <c r="H194" t="n">
         <v>727</v>
@@ -6024,7 +6024,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G195" t="n">
-        <v>7.61800241470337</v>
+        <v>7.61800193786621</v>
       </c>
       <c r="H195" t="n">
         <v>289</v>
@@ -6053,7 +6053,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G196" t="n">
-        <v>7.61800241470337</v>
+        <v>7.61800193786621</v>
       </c>
       <c r="H196" t="n">
         <v>0</v>
@@ -6082,7 +6082,7 @@
         <v>8.25</v>
       </c>
       <c r="G197" t="n">
-        <v>7.52676916122437</v>
+        <v>7.52676868438721</v>
       </c>
       <c r="H197" t="n">
         <v>444</v>
@@ -6169,7 +6169,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G200" t="n">
-        <v>7.70923566818237</v>
+        <v>7.70923519134521</v>
       </c>
       <c r="H200" t="n">
         <v>533</v>
@@ -6198,7 +6198,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G201" t="n">
-        <v>7.70923566818237</v>
+        <v>7.70923519134521</v>
       </c>
       <c r="H201" t="n">
         <v>419</v>
@@ -6227,7 +6227,7 @@
         <v>8.60999965667725</v>
       </c>
       <c r="G202" t="n">
-        <v>7.8552098274231</v>
+        <v>7.85520887374878</v>
       </c>
       <c r="H202" t="n">
         <v>924</v>
@@ -6314,7 +6314,7 @@
         <v>8.60999965667725</v>
       </c>
       <c r="G205" t="n">
-        <v>7.8552098274231</v>
+        <v>7.85520887374878</v>
       </c>
       <c r="H205" t="n">
         <v>460</v>
@@ -6343,7 +6343,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G206" t="n">
-        <v>7.93731880187988</v>
+        <v>7.9373197555542</v>
       </c>
       <c r="H206" t="n">
         <v>1640</v>
@@ -6372,7 +6372,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G207" t="n">
-        <v>7.93731880187988</v>
+        <v>7.9373197555542</v>
       </c>
       <c r="H207" t="n">
         <v>0</v>
@@ -6401,7 +6401,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G208" t="n">
-        <v>7.93731880187988</v>
+        <v>7.9373197555542</v>
       </c>
       <c r="H208" t="n">
         <v>1100</v>
@@ -6430,7 +6430,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G209" t="n">
-        <v>7.93731880187988</v>
+        <v>7.9373197555542</v>
       </c>
       <c r="H209" t="n">
         <v>230</v>
@@ -6459,7 +6459,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G210" t="n">
-        <v>7.93731880187988</v>
+        <v>7.9373197555542</v>
       </c>
       <c r="H210" t="n">
         <v>0</v>
@@ -6604,7 +6604,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G215" t="n">
-        <v>8.27488231658936</v>
+        <v>8.27488422393799</v>
       </c>
       <c r="H215" t="n">
         <v>8078</v>
@@ -6633,7 +6633,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G216" t="n">
-        <v>8.50296688079834</v>
+        <v>8.50296783447266</v>
       </c>
       <c r="H216" t="n">
         <v>862</v>
@@ -6749,7 +6749,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G220" t="n">
-        <v>8.22926807403564</v>
+        <v>8.22926712036133</v>
       </c>
       <c r="H220" t="n">
         <v>1062</v>
@@ -6778,7 +6778,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G221" t="n">
-        <v>8.22926807403564</v>
+        <v>8.22926712036133</v>
       </c>
       <c r="H221" t="n">
         <v>0</v>
@@ -6807,7 +6807,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G222" t="n">
-        <v>8.22926807403564</v>
+        <v>8.22926712036133</v>
       </c>
       <c r="H222" t="n">
         <v>0</v>
@@ -7039,7 +7039,7 @@
         <v>9.43000030517578</v>
       </c>
       <c r="G230" t="n">
-        <v>8.60332489013672</v>
+        <v>8.60332584381104</v>
       </c>
       <c r="H230" t="n">
         <v>26080</v>
@@ -7068,7 +7068,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G231" t="n">
-        <v>8.50296688079834</v>
+        <v>8.50296783447266</v>
       </c>
       <c r="H231" t="n">
         <v>330</v>
@@ -7155,7 +7155,7 @@
         <v>9.43000030517578</v>
       </c>
       <c r="G234" t="n">
-        <v>8.60332489013672</v>
+        <v>8.60332584381104</v>
       </c>
       <c r="H234" t="n">
         <v>96</v>
@@ -7184,7 +7184,7 @@
         <v>9.43000030517578</v>
       </c>
       <c r="G235" t="n">
-        <v>8.60332489013672</v>
+        <v>8.60332584381104</v>
       </c>
       <c r="H235" t="n">
         <v>0</v>
@@ -7242,7 +7242,7 @@
         <v>9.82999992370605</v>
       </c>
       <c r="G237" t="n">
-        <v>8.96825885772705</v>
+        <v>8.96825790405273</v>
       </c>
       <c r="H237" t="n">
         <v>914</v>
@@ -7271,7 +7271,7 @@
         <v>9.82999992370605</v>
       </c>
       <c r="G238" t="n">
-        <v>8.96825885772705</v>
+        <v>8.96825790405273</v>
       </c>
       <c r="H238" t="n">
         <v>0</v>
@@ -7300,7 +7300,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G239" t="n">
-        <v>8.62157154083252</v>
+        <v>8.6215705871582</v>
       </c>
       <c r="H239" t="n">
         <v>2238</v>
@@ -7532,7 +7532,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G247" t="n">
-        <v>9.03212261199951</v>
+        <v>9.0321216583252</v>
       </c>
       <c r="H247" t="n">
         <v>200</v>
@@ -7561,7 +7561,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G248" t="n">
-        <v>9.03212261199951</v>
+        <v>9.0321216583252</v>
       </c>
       <c r="H248" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G251" t="n">
-        <v>9.21458911895752</v>
+        <v>9.21459007263184</v>
       </c>
       <c r="H251" t="n">
         <v>1480</v>
@@ -7677,7 +7677,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G252" t="n">
-        <v>9.21458911895752</v>
+        <v>9.21459007263184</v>
       </c>
       <c r="H252" t="n">
         <v>331</v>
@@ -7706,7 +7706,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G253" t="n">
-        <v>9.19634342193604</v>
+        <v>9.19634246826172</v>
       </c>
       <c r="H253" t="n">
         <v>359</v>
@@ -7735,7 +7735,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G254" t="n">
-        <v>9.19634342193604</v>
+        <v>9.19634246826172</v>
       </c>
       <c r="H254" t="n">
         <v>0</v>
@@ -7851,7 +7851,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G258" t="n">
-        <v>9.03212261199951</v>
+        <v>9.0321216583252</v>
       </c>
       <c r="H258" t="n">
         <v>300</v>
@@ -7880,7 +7880,7 @@
         <v>9.72999954223633</v>
       </c>
       <c r="G259" t="n">
-        <v>8.87702465057373</v>
+        <v>8.87702560424805</v>
       </c>
       <c r="H259" t="n">
         <v>2776</v>
@@ -7909,7 +7909,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G260" t="n">
-        <v>8.84965419769287</v>
+        <v>8.84965515136719</v>
       </c>
       <c r="H260" t="n">
         <v>50</v>
@@ -8054,7 +8054,7 @@
         <v>9.51000022888184</v>
       </c>
       <c r="G265" t="n">
-        <v>8.67631149291992</v>
+        <v>8.67631244659424</v>
       </c>
       <c r="H265" t="n">
         <v>135</v>
@@ -8083,7 +8083,7 @@
         <v>9.89000034332275</v>
       </c>
       <c r="G266" t="n">
-        <v>9.02299976348877</v>
+        <v>9.02299880981445</v>
       </c>
       <c r="H266" t="n">
         <v>500</v>
@@ -8141,7 +8141,7 @@
         <v>9.75</v>
       </c>
       <c r="G268" t="n">
-        <v>8.89527225494385</v>
+        <v>8.89527130126953</v>
       </c>
       <c r="H268" t="n">
         <v>380</v>
@@ -8170,7 +8170,7 @@
         <v>9.75</v>
       </c>
       <c r="G269" t="n">
-        <v>8.89527225494385</v>
+        <v>8.89527130126953</v>
       </c>
       <c r="H269" t="n">
         <v>1149</v>
@@ -8286,7 +8286,7 @@
         <v>8.92000007629395</v>
       </c>
       <c r="G273" t="n">
-        <v>8.13803291320801</v>
+        <v>8.13803386688232</v>
       </c>
       <c r="H273" t="n">
         <v>1470</v>
@@ -8315,7 +8315,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G274" t="n">
-        <v>8.30225372314453</v>
+        <v>8.30225467681885</v>
       </c>
       <c r="H274" t="n">
         <v>709</v>
@@ -8373,7 +8373,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G276" t="n">
-        <v>8.35699367523193</v>
+        <v>8.35699272155762</v>
       </c>
       <c r="H276" t="n">
         <v>12610</v>
@@ -8402,7 +8402,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G277" t="n">
-        <v>8.30225372314453</v>
+        <v>8.30225467681885</v>
       </c>
       <c r="H277" t="n">
         <v>1757</v>
@@ -8431,7 +8431,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G278" t="n">
-        <v>8.11978721618652</v>
+        <v>8.11978626251221</v>
       </c>
       <c r="H278" t="n">
         <v>43332</v>
@@ -8460,7 +8460,7 @@
         <v>8.71000003814697</v>
       </c>
       <c r="G279" t="n">
-        <v>7.94644260406494</v>
+        <v>7.9464430809021</v>
       </c>
       <c r="H279" t="n">
         <v>7948</v>
@@ -8518,7 +8518,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G281" t="n">
-        <v>8.11978721618652</v>
+        <v>8.11978626251221</v>
       </c>
       <c r="H281" t="n">
         <v>1100</v>
@@ -8605,7 +8605,7 @@
         <v>9.21000003814697</v>
       </c>
       <c r="G284" t="n">
-        <v>8.40261077880859</v>
+        <v>8.40261173248291</v>
       </c>
       <c r="H284" t="n">
         <v>10839</v>
@@ -8634,7 +8634,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G285" t="n">
-        <v>8.37524032592773</v>
+        <v>8.37524127960205</v>
       </c>
       <c r="H285" t="n">
         <v>1200</v>
@@ -8721,7 +8721,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G288" t="n">
-        <v>8.27488231658936</v>
+        <v>8.27488422393799</v>
       </c>
       <c r="H288" t="n">
         <v>6201</v>
@@ -8866,7 +8866,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G293" t="n">
-        <v>8.27488231658936</v>
+        <v>8.27488422393799</v>
       </c>
       <c r="H293" t="n">
         <v>1783</v>
@@ -8895,7 +8895,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G294" t="n">
-        <v>8.50296688079834</v>
+        <v>8.50296783447266</v>
       </c>
       <c r="H294" t="n">
         <v>3394</v>
@@ -8924,7 +8924,7 @@
         <v>9.27000045776367</v>
       </c>
       <c r="G295" t="n">
-        <v>8.45735168457031</v>
+        <v>8.457350730896</v>
       </c>
       <c r="H295" t="n">
         <v>260</v>
@@ -9011,7 +9011,7 @@
         <v>9.21000003814697</v>
       </c>
       <c r="G298" t="n">
-        <v>8.40261077880859</v>
+        <v>8.40261173248291</v>
       </c>
       <c r="H298" t="n">
         <v>433</v>
@@ -9040,7 +9040,7 @@
         <v>9.21000003814697</v>
       </c>
       <c r="G299" t="n">
-        <v>8.40261077880859</v>
+        <v>8.40261173248291</v>
       </c>
       <c r="H299" t="n">
         <v>0</v>
@@ -9069,7 +9069,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G300" t="n">
-        <v>8.50296688079834</v>
+        <v>8.50296783447266</v>
       </c>
       <c r="H300" t="n">
         <v>949</v>
@@ -9098,7 +9098,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G301" t="n">
-        <v>8.34786987304688</v>
+        <v>8.34787082672119</v>
       </c>
       <c r="H301" t="n">
         <v>519</v>
@@ -9127,7 +9127,7 @@
         <v>8.86999988555908</v>
       </c>
       <c r="G302" t="n">
-        <v>8.09241676330566</v>
+        <v>8.09241580963135</v>
       </c>
       <c r="H302" t="n">
         <v>2131</v>
@@ -9243,7 +9243,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G306" t="n">
-        <v>8.25663757324219</v>
+        <v>8.25663661956787</v>
       </c>
       <c r="H306" t="n">
         <v>320</v>
@@ -9301,7 +9301,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G308" t="n">
-        <v>8.37524032592773</v>
+        <v>8.37524127960205</v>
       </c>
       <c r="H308" t="n">
         <v>99</v>
@@ -9330,7 +9330,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G309" t="n">
-        <v>8.19277381896973</v>
+        <v>8.19277286529541</v>
       </c>
       <c r="H309" t="n">
         <v>191</v>
@@ -9359,7 +9359,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G310" t="n">
-        <v>8.22926807403564</v>
+        <v>8.22926712036133</v>
       </c>
       <c r="H310" t="n">
         <v>1</v>
@@ -9388,7 +9388,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G311" t="n">
-        <v>8.22926807403564</v>
+        <v>8.22926712036133</v>
       </c>
       <c r="H311" t="n">
         <v>0</v>
@@ -9417,7 +9417,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G312" t="n">
-        <v>8.22926807403564</v>
+        <v>8.22926712036133</v>
       </c>
       <c r="H312" t="n">
         <v>0</v>
@@ -9475,7 +9475,7 @@
         <v>9.01000022888184</v>
       </c>
       <c r="G314" t="n">
-        <v>8.22014427185059</v>
+        <v>8.22014331817627</v>
       </c>
       <c r="H314" t="n">
         <v>680</v>
@@ -9504,7 +9504,7 @@
         <v>9.01000022888184</v>
       </c>
       <c r="G315" t="n">
-        <v>8.22014427185059</v>
+        <v>8.22014331817627</v>
       </c>
       <c r="H315" t="n">
         <v>0</v>
@@ -9620,7 +9620,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G319" t="n">
-        <v>7.95556640625</v>
+        <v>7.95556592941284</v>
       </c>
       <c r="H319" t="n">
         <v>5536</v>
@@ -9736,7 +9736,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G323" t="n">
-        <v>8.28400611877441</v>
+        <v>8.28400707244873</v>
       </c>
       <c r="H323" t="n">
         <v>8366</v>
@@ -9765,7 +9765,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G324" t="n">
-        <v>8.28400611877441</v>
+        <v>8.28400707244873</v>
       </c>
       <c r="H324" t="n">
         <v>0</v>
@@ -9794,7 +9794,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G325" t="n">
-        <v>8.22926807403564</v>
+        <v>8.22926712036133</v>
       </c>
       <c r="H325" t="n">
         <v>72</v>
@@ -9823,7 +9823,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G326" t="n">
-        <v>8.22926807403564</v>
+        <v>8.22926712036133</v>
       </c>
       <c r="H326" t="n">
         <v>0</v>
@@ -9852,7 +9852,7 @@
         <v>8.92000007629395</v>
       </c>
       <c r="G327" t="n">
-        <v>8.13803291320801</v>
+        <v>8.13803386688232</v>
       </c>
       <c r="H327" t="n">
         <v>200</v>
@@ -9881,7 +9881,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G328" t="n">
-        <v>8.11978721618652</v>
+        <v>8.11978626251221</v>
       </c>
       <c r="H328" t="n">
         <v>3732</v>
@@ -9910,7 +9910,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G329" t="n">
-        <v>8.11978721618652</v>
+        <v>8.11978626251221</v>
       </c>
       <c r="H329" t="n">
         <v>200</v>
@@ -9939,7 +9939,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G330" t="n">
-        <v>8.11978721618652</v>
+        <v>8.11978626251221</v>
       </c>
       <c r="H330" t="n">
         <v>451</v>
@@ -9968,7 +9968,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G331" t="n">
-        <v>8.59420204162598</v>
+        <v>8.59420108795166</v>
       </c>
       <c r="H331" t="n">
         <v>5649</v>
@@ -9997,7 +9997,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G332" t="n">
-        <v>8.50296688079834</v>
+        <v>8.50296783447266</v>
       </c>
       <c r="H332" t="n">
         <v>6347</v>
@@ -10055,7 +10055,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G334" t="n">
-        <v>8.48472118377686</v>
+        <v>8.48472023010254</v>
       </c>
       <c r="H334" t="n">
         <v>15021</v>
@@ -10084,7 +10084,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G335" t="n">
-        <v>8.24751472473145</v>
+        <v>8.24751377105713</v>
       </c>
       <c r="H335" t="n">
         <v>7514</v>
@@ -10171,7 +10171,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G338" t="n">
-        <v>7.93731880187988</v>
+        <v>7.9373197555542</v>
       </c>
       <c r="H338" t="n">
         <v>2490</v>
@@ -10287,7 +10287,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G342" t="n">
-        <v>7.37167167663574</v>
+        <v>7.37167119979858</v>
       </c>
       <c r="H342" t="n">
         <v>18625</v>
@@ -10374,7 +10374,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G345" t="n">
-        <v>7.33517789840698</v>
+        <v>7.33517837524414</v>
       </c>
       <c r="H345" t="n">
         <v>3152</v>
@@ -10403,7 +10403,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G346" t="n">
-        <v>7.3534255027771</v>
+        <v>7.35342502593994</v>
       </c>
       <c r="H346" t="n">
         <v>470</v>
@@ -10490,7 +10490,7 @@
         <v>8</v>
       </c>
       <c r="G349" t="n">
-        <v>7.29868459701538</v>
+        <v>7.29868507385254</v>
       </c>
       <c r="H349" t="n">
         <v>1</v>
@@ -10519,7 +10519,7 @@
         <v>8</v>
       </c>
       <c r="G350" t="n">
-        <v>7.29868459701538</v>
+        <v>7.29868507385254</v>
       </c>
       <c r="H350" t="n">
         <v>0</v>
@@ -10548,7 +10548,7 @@
         <v>8</v>
       </c>
       <c r="G351" t="n">
-        <v>7.29868459701538</v>
+        <v>7.29868507385254</v>
       </c>
       <c r="H351" t="n">
         <v>1051</v>
@@ -10577,7 +10577,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G352" t="n">
-        <v>7.3169322013855</v>
+        <v>7.31693172454834</v>
       </c>
       <c r="H352" t="n">
         <v>63</v>
@@ -10606,7 +10606,7 @@
         <v>8</v>
       </c>
       <c r="G353" t="n">
-        <v>7.29868459701538</v>
+        <v>7.29868507385254</v>
       </c>
       <c r="H353" t="n">
         <v>501</v>
@@ -10693,7 +10693,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G356" t="n">
-        <v>7.0432300567627</v>
+        <v>7.04323053359985</v>
       </c>
       <c r="H356" t="n">
         <v>3056</v>
@@ -10896,7 +10896,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G363" t="n">
-        <v>7.0432300567627</v>
+        <v>7.04323053359985</v>
       </c>
       <c r="H363" t="n">
         <v>2201</v>
@@ -10983,7 +10983,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G366" t="n">
-        <v>6.95199728012085</v>
+        <v>6.95199680328369</v>
       </c>
       <c r="H366" t="n">
         <v>3628</v>
@@ -11012,7 +11012,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G367" t="n">
-        <v>6.82426977157593</v>
+        <v>6.82427024841309</v>
       </c>
       <c r="H367" t="n">
         <v>4636</v>
@@ -11041,7 +11041,7 @@
         <v>7.51999998092651</v>
       </c>
       <c r="G368" t="n">
-        <v>6.86076307296753</v>
+        <v>6.86076354980469</v>
       </c>
       <c r="H368" t="n">
         <v>5487</v>
@@ -11070,7 +11070,7 @@
         <v>7.51999998092651</v>
       </c>
       <c r="G369" t="n">
-        <v>6.86076307296753</v>
+        <v>6.86076354980469</v>
       </c>
       <c r="H369" t="n">
         <v>45</v>
@@ -11128,7 +11128,7 @@
         <v>7.51999998092651</v>
       </c>
       <c r="G371" t="n">
-        <v>6.86076307296753</v>
+        <v>6.86076354980469</v>
       </c>
       <c r="H371" t="n">
         <v>50</v>
@@ -11157,7 +11157,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G372" t="n">
-        <v>6.95199728012085</v>
+        <v>6.95199680328369</v>
       </c>
       <c r="H372" t="n">
         <v>500</v>
@@ -11650,7 +11650,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G389" t="n">
-        <v>7.17095804214478</v>
+        <v>7.17095756530762</v>
       </c>
       <c r="H389" t="n">
         <v>7937</v>
@@ -11679,7 +11679,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G390" t="n">
-        <v>7.3899188041687</v>
+        <v>7.38991832733154</v>
       </c>
       <c r="H390" t="n">
         <v>4671</v>
@@ -11882,7 +11882,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G397" t="n">
-        <v>7.62712526321411</v>
+        <v>7.62712574005127</v>
       </c>
       <c r="H397" t="n">
         <v>1616</v>
@@ -11911,7 +11911,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G398" t="n">
-        <v>7.62712526321411</v>
+        <v>7.62712574005127</v>
       </c>
       <c r="H398" t="n">
         <v>0</v>
@@ -11998,7 +11998,7 @@
         <v>8.4399995803833</v>
       </c>
       <c r="G401" t="n">
-        <v>7.70011186599731</v>
+        <v>7.70011234283447</v>
       </c>
       <c r="H401" t="n">
         <v>1732</v>
@@ -12027,7 +12027,7 @@
         <v>8.4399995803833</v>
       </c>
       <c r="G402" t="n">
-        <v>7.70011186599731</v>
+        <v>7.70011234283447</v>
       </c>
       <c r="H402" t="n">
         <v>1250</v>
@@ -12056,7 +12056,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G403" t="n">
-        <v>7.49939870834351</v>
+        <v>7.49939918518066</v>
       </c>
       <c r="H403" t="n">
         <v>750</v>
@@ -12085,7 +12085,7 @@
         <v>8.4399995803833</v>
       </c>
       <c r="G404" t="n">
-        <v>7.70011186599731</v>
+        <v>7.70011234283447</v>
       </c>
       <c r="H404" t="n">
         <v>100</v>
@@ -12143,7 +12143,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G406" t="n">
-        <v>7.33517789840698</v>
+        <v>7.33517837524414</v>
       </c>
       <c r="H406" t="n">
         <v>3302</v>
@@ -12172,7 +12172,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G407" t="n">
-        <v>7.33517789840698</v>
+        <v>7.33517837524414</v>
       </c>
       <c r="H407" t="n">
         <v>0</v>
@@ -12201,7 +12201,7 @@
         <v>8</v>
       </c>
       <c r="G408" t="n">
-        <v>7.29868459701538</v>
+        <v>7.29868507385254</v>
       </c>
       <c r="H408" t="n">
         <v>1100</v>
@@ -12230,7 +12230,7 @@
         <v>8</v>
       </c>
       <c r="G409" t="n">
-        <v>7.29868459701538</v>
+        <v>7.29868507385254</v>
       </c>
       <c r="H409" t="n">
         <v>4000</v>
@@ -12259,7 +12259,7 @@
         <v>8</v>
       </c>
       <c r="G410" t="n">
-        <v>7.29868459701538</v>
+        <v>7.29868507385254</v>
       </c>
       <c r="H410" t="n">
         <v>0</v>
@@ -12723,7 +12723,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G426" t="n">
-        <v>7.79134559631348</v>
+        <v>7.79134654998779</v>
       </c>
       <c r="H426" t="n">
         <v>3239</v>
@@ -12781,7 +12781,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G428" t="n">
-        <v>7.73660564422607</v>
+        <v>7.73660516738892</v>
       </c>
       <c r="H428" t="n">
         <v>4521</v>
@@ -12810,7 +12810,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G429" t="n">
-        <v>7.66361808776855</v>
+        <v>7.66361904144287</v>
       </c>
       <c r="H429" t="n">
         <v>1230</v>
@@ -12839,7 +12839,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G430" t="n">
-        <v>7.66361808776855</v>
+        <v>7.66361904144287</v>
       </c>
       <c r="H430" t="n">
         <v>0</v>
@@ -13013,7 +13013,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G436" t="n">
-        <v>7.3534255027771</v>
+        <v>7.35342502593994</v>
       </c>
       <c r="H436" t="n">
         <v>4810</v>
@@ -13042,7 +13042,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G437" t="n">
-        <v>7.3534255027771</v>
+        <v>7.35342502593994</v>
       </c>
       <c r="H437" t="n">
         <v>1654</v>
@@ -13071,7 +13071,7 @@
         <v>8</v>
       </c>
       <c r="G438" t="n">
-        <v>7.29868459701538</v>
+        <v>7.29868507385254</v>
       </c>
       <c r="H438" t="n">
         <v>810</v>
@@ -13216,7 +13216,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G443" t="n">
-        <v>6.75128316879272</v>
+        <v>6.75128364562988</v>
       </c>
       <c r="H443" t="n">
         <v>690</v>
@@ -13245,7 +13245,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G444" t="n">
-        <v>6.75128316879272</v>
+        <v>6.75128364562988</v>
       </c>
       <c r="H444" t="n">
         <v>740</v>
@@ -13332,7 +13332,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G447" t="n">
-        <v>6.82426977157593</v>
+        <v>6.82427024841309</v>
       </c>
       <c r="H447" t="n">
         <v>24314</v>
@@ -13390,7 +13390,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G449" t="n">
-        <v>6.75128316879272</v>
+        <v>6.75128364562988</v>
       </c>
       <c r="H449" t="n">
         <v>1995</v>
@@ -13419,7 +13419,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G450" t="n">
-        <v>6.75128316879272</v>
+        <v>6.75128364562988</v>
       </c>
       <c r="H450" t="n">
         <v>0</v>
@@ -13448,7 +13448,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G451" t="n">
-        <v>6.75128316879272</v>
+        <v>6.75128364562988</v>
       </c>
       <c r="H451" t="n">
         <v>0</v>
@@ -13477,7 +13477,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G452" t="n">
-        <v>6.75128316879272</v>
+        <v>6.75128364562988</v>
       </c>
       <c r="H452" t="n">
         <v>0</v>
@@ -13506,7 +13506,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G453" t="n">
-        <v>6.75128316879272</v>
+        <v>6.75128364562988</v>
       </c>
       <c r="H453" t="n">
         <v>0</v>
@@ -13535,7 +13535,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G454" t="n">
-        <v>6.75128316879272</v>
+        <v>6.75128364562988</v>
       </c>
       <c r="H454" t="n">
         <v>1400</v>
@@ -13709,7 +13709,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G460" t="n">
-        <v>6.514075756073</v>
+        <v>6.51407623291016</v>
       </c>
       <c r="H460" t="n">
         <v>2800</v>
@@ -14028,7 +14028,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G471" t="n">
-        <v>6.29511547088623</v>
+        <v>6.29511594772339</v>
       </c>
       <c r="H471" t="n">
         <v>882</v>
@@ -14057,7 +14057,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G472" t="n">
-        <v>6.49582958221436</v>
+        <v>6.4958291053772</v>
       </c>
       <c r="H472" t="n">
         <v>1050</v>
@@ -14086,7 +14086,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G473" t="n">
-        <v>6.42284297943115</v>
+        <v>6.42284250259399</v>
       </c>
       <c r="H473" t="n">
         <v>600</v>
@@ -14115,7 +14115,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G474" t="n">
-        <v>6.29511547088623</v>
+        <v>6.29511594772339</v>
       </c>
       <c r="H474" t="n">
         <v>120</v>
@@ -14144,7 +14144,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G475" t="n">
-        <v>6.67829608917236</v>
+        <v>6.67829656600952</v>
       </c>
       <c r="H475" t="n">
         <v>1738</v>
@@ -14173,7 +14173,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G476" t="n">
-        <v>6.67829608917236</v>
+        <v>6.67829656600952</v>
       </c>
       <c r="H476" t="n">
         <v>1500</v>
@@ -14492,7 +14492,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G487" t="n">
-        <v>6.64180278778076</v>
+        <v>6.64180326461792</v>
       </c>
       <c r="H487" t="n">
         <v>565</v>
@@ -14579,7 +14579,7 @@
         <v>8</v>
       </c>
       <c r="G490" t="n">
-        <v>7.29868459701538</v>
+        <v>7.29868507385254</v>
       </c>
       <c r="H490" t="n">
         <v>1281</v>
@@ -14666,7 +14666,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G493" t="n">
-        <v>7.22569751739502</v>
+        <v>7.22569799423218</v>
       </c>
       <c r="H493" t="n">
         <v>800</v>
@@ -14927,7 +14927,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G502" t="n">
-        <v>7.33517789840698</v>
+        <v>7.33517837524414</v>
       </c>
       <c r="H502" t="n">
         <v>517</v>
@@ -14956,7 +14956,7 @@
         <v>8</v>
       </c>
       <c r="G503" t="n">
-        <v>7.29868459701538</v>
+        <v>7.29868507385254</v>
       </c>
       <c r="H503" t="n">
         <v>2647</v>
@@ -14985,7 +14985,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G504" t="n">
-        <v>7.37167167663574</v>
+        <v>7.37167119979858</v>
       </c>
       <c r="H504" t="n">
         <v>1968</v>
@@ -15014,7 +15014,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G505" t="n">
-        <v>7.33517789840698</v>
+        <v>7.33517837524414</v>
       </c>
       <c r="H505" t="n">
         <v>731</v>
@@ -15043,7 +15043,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G506" t="n">
-        <v>7.33517789840698</v>
+        <v>7.33517837524414</v>
       </c>
       <c r="H506" t="n">
         <v>300</v>
@@ -15072,7 +15072,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G507" t="n">
-        <v>7.3169322013855</v>
+        <v>7.31693172454834</v>
       </c>
       <c r="H507" t="n">
         <v>772</v>
@@ -15101,7 +15101,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G508" t="n">
-        <v>7.37167167663574</v>
+        <v>7.37167119979858</v>
       </c>
       <c r="H508" t="n">
         <v>1681</v>
@@ -15130,7 +15130,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G509" t="n">
-        <v>7.37167167663574</v>
+        <v>7.37167119979858</v>
       </c>
       <c r="H509" t="n">
         <v>0</v>
@@ -15159,7 +15159,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G510" t="n">
-        <v>7.37167167663574</v>
+        <v>7.37167119979858</v>
       </c>
       <c r="H510" t="n">
         <v>0</v>
@@ -15217,7 +15217,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G512" t="n">
-        <v>7.3169322013855</v>
+        <v>7.31693172454834</v>
       </c>
       <c r="H512" t="n">
         <v>1280</v>
@@ -15362,7 +15362,7 @@
         <v>7.51999998092651</v>
       </c>
       <c r="G517" t="n">
-        <v>6.86076307296753</v>
+        <v>6.86076354980469</v>
       </c>
       <c r="H517" t="n">
         <v>3626</v>
@@ -15478,7 +15478,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G521" t="n">
-        <v>6.82426977157593</v>
+        <v>6.82427024841309</v>
       </c>
       <c r="H521" t="n">
         <v>13563</v>
@@ -15594,7 +15594,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G525" t="n">
-        <v>6.82426977157593</v>
+        <v>6.82427024841309</v>
       </c>
       <c r="H525" t="n">
         <v>4481</v>
@@ -15739,7 +15739,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G530" t="n">
-        <v>7.17095804214478</v>
+        <v>7.17095756530762</v>
       </c>
       <c r="H530" t="n">
         <v>2115</v>
@@ -15826,7 +15826,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G533" t="n">
-        <v>7.3534255027771</v>
+        <v>7.35342502593994</v>
       </c>
       <c r="H533" t="n">
         <v>2000</v>
@@ -15855,7 +15855,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G534" t="n">
-        <v>7.3534255027771</v>
+        <v>7.35342502593994</v>
       </c>
       <c r="H534" t="n">
         <v>2413</v>
@@ -15884,7 +15884,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G535" t="n">
-        <v>7.64537239074707</v>
+        <v>7.64537191390991</v>
       </c>
       <c r="H535" t="n">
         <v>12922</v>
@@ -15913,7 +15913,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G536" t="n">
-        <v>7.3899188041687</v>
+        <v>7.38991832733154</v>
       </c>
       <c r="H536" t="n">
         <v>18461</v>
@@ -16145,7 +16145,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G544" t="n">
-        <v>7.3169322013855</v>
+        <v>7.31693172454834</v>
       </c>
       <c r="H544" t="n">
         <v>3852</v>
@@ -16203,7 +16203,7 @@
         <v>8</v>
       </c>
       <c r="G546" t="n">
-        <v>7.29868459701538</v>
+        <v>7.29868507385254</v>
       </c>
       <c r="H546" t="n">
         <v>12524</v>
@@ -16261,7 +16261,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G548" t="n">
-        <v>7.3899188041687</v>
+        <v>7.38991832733154</v>
       </c>
       <c r="H548" t="n">
         <v>1200</v>
@@ -16319,7 +16319,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G550" t="n">
-        <v>7.49939870834351</v>
+        <v>7.49939918518066</v>
       </c>
       <c r="H550" t="n">
         <v>4760</v>
@@ -16377,7 +16377,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G552" t="n">
-        <v>7.66361808776855</v>
+        <v>7.66361904144287</v>
       </c>
       <c r="H552" t="n">
         <v>2734</v>
@@ -16522,7 +16522,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G557" t="n">
-        <v>7.62712526321411</v>
+        <v>7.62712574005127</v>
       </c>
       <c r="H557" t="n">
         <v>3160</v>
@@ -16551,7 +16551,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G558" t="n">
-        <v>7.62712526321411</v>
+        <v>7.62712574005127</v>
       </c>
       <c r="H558" t="n">
         <v>0</v>
@@ -16580,7 +16580,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G559" t="n">
-        <v>7.62712526321411</v>
+        <v>7.62712574005127</v>
       </c>
       <c r="H559" t="n">
         <v>0</v>
@@ -16609,7 +16609,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G560" t="n">
-        <v>7.66361808776855</v>
+        <v>7.66361904144287</v>
       </c>
       <c r="H560" t="n">
         <v>3325</v>
@@ -16638,7 +16638,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G561" t="n">
-        <v>7.66361808776855</v>
+        <v>7.66361904144287</v>
       </c>
       <c r="H561" t="n">
         <v>0</v>
@@ -16667,7 +16667,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G562" t="n">
-        <v>7.66361808776855</v>
+        <v>7.66361904144287</v>
       </c>
       <c r="H562" t="n">
         <v>978</v>
@@ -16696,7 +16696,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G563" t="n">
-        <v>7.64537239074707</v>
+        <v>7.64537191390991</v>
       </c>
       <c r="H563" t="n">
         <v>900</v>
@@ -16725,7 +16725,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G564" t="n">
-        <v>7.64537239074707</v>
+        <v>7.64537191390991</v>
       </c>
       <c r="H564" t="n">
         <v>0</v>
@@ -16754,7 +16754,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G565" t="n">
-        <v>7.64537239074707</v>
+        <v>7.64537191390991</v>
       </c>
       <c r="H565" t="n">
         <v>0</v>
@@ -16783,7 +16783,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G566" t="n">
-        <v>7.64537239074707</v>
+        <v>7.64537191390991</v>
       </c>
       <c r="H566" t="n">
         <v>0</v>
@@ -16928,7 +16928,7 @@
         <v>8.25</v>
       </c>
       <c r="G571" t="n">
-        <v>7.52676916122437</v>
+        <v>7.52676868438721</v>
       </c>
       <c r="H571" t="n">
         <v>2468</v>
@@ -16957,7 +16957,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G572" t="n">
-        <v>7.43553447723389</v>
+        <v>7.43553495407104</v>
       </c>
       <c r="H572" t="n">
         <v>3030</v>
@@ -16986,7 +16986,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G573" t="n">
-        <v>7.43553447723389</v>
+        <v>7.43553495407104</v>
       </c>
       <c r="H573" t="n">
         <v>0</v>
@@ -17015,7 +17015,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G574" t="n">
-        <v>7.43553447723389</v>
+        <v>7.43553495407104</v>
       </c>
       <c r="H574" t="n">
         <v>3363</v>
@@ -17044,7 +17044,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G575" t="n">
-        <v>7.43553447723389</v>
+        <v>7.43553495407104</v>
       </c>
       <c r="H575" t="n">
         <v>1531</v>
@@ -17073,7 +17073,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G576" t="n">
-        <v>7.61800241470337</v>
+        <v>7.61800193786621</v>
       </c>
       <c r="H576" t="n">
         <v>4229</v>
@@ -17102,7 +17102,7 @@
         <v>8.25</v>
       </c>
       <c r="G577" t="n">
-        <v>7.52676916122437</v>
+        <v>7.52676868438721</v>
       </c>
       <c r="H577" t="n">
         <v>10687</v>
@@ -17160,7 +17160,7 @@
         <v>8</v>
       </c>
       <c r="G579" t="n">
-        <v>7.29868459701538</v>
+        <v>7.29868507385254</v>
       </c>
       <c r="H579" t="n">
         <v>2771</v>
@@ -17218,7 +17218,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G581" t="n">
-        <v>7.3899188041687</v>
+        <v>7.38991832733154</v>
       </c>
       <c r="H581" t="n">
         <v>540</v>
@@ -17334,7 +17334,7 @@
         <v>8.25</v>
       </c>
       <c r="G585" t="n">
-        <v>7.52676916122437</v>
+        <v>7.52676868438721</v>
       </c>
       <c r="H585" t="n">
         <v>1560</v>
@@ -17363,7 +17363,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G586" t="n">
-        <v>7.3899188041687</v>
+        <v>7.38991832733154</v>
       </c>
       <c r="H586" t="n">
         <v>3341</v>
@@ -17392,7 +17392,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G587" t="n">
-        <v>7.3899188041687</v>
+        <v>7.38991832733154</v>
       </c>
       <c r="H587" t="n">
         <v>340</v>
@@ -17421,7 +17421,7 @@
         <v>8</v>
       </c>
       <c r="G588" t="n">
-        <v>7.29868459701538</v>
+        <v>7.29868507385254</v>
       </c>
       <c r="H588" t="n">
         <v>110</v>
@@ -17450,7 +17450,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G589" t="n">
-        <v>7.3899188041687</v>
+        <v>7.38991832733154</v>
       </c>
       <c r="H589" t="n">
         <v>1325</v>
@@ -17479,7 +17479,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G590" t="n">
-        <v>7.3899188041687</v>
+        <v>7.38991832733154</v>
       </c>
       <c r="H590" t="n">
         <v>851</v>
@@ -17508,7 +17508,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G591" t="n">
-        <v>7.3899188041687</v>
+        <v>7.38991832733154</v>
       </c>
       <c r="H591" t="n">
         <v>22104</v>
@@ -17537,7 +17537,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G592" t="n">
-        <v>7.3899188041687</v>
+        <v>7.38991832733154</v>
       </c>
       <c r="H592" t="n">
         <v>0</v>
@@ -17624,7 +17624,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G595" t="n">
-        <v>7.43553447723389</v>
+        <v>7.43553495407104</v>
       </c>
       <c r="H595" t="n">
         <v>1851</v>
@@ -17653,7 +17653,7 @@
         <v>8</v>
       </c>
       <c r="G596" t="n">
-        <v>7.29868459701538</v>
+        <v>7.29868507385254</v>
       </c>
       <c r="H596" t="n">
         <v>17310</v>
@@ -17682,7 +17682,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G597" t="n">
-        <v>7.43553447723389</v>
+        <v>7.43553495407104</v>
       </c>
       <c r="H597" t="n">
         <v>3661</v>
@@ -17740,7 +17740,7 @@
         <v>8</v>
       </c>
       <c r="G599" t="n">
-        <v>7.29868459701538</v>
+        <v>7.29868507385254</v>
       </c>
       <c r="H599" t="n">
         <v>11533</v>
@@ -17769,7 +17769,7 @@
         <v>8</v>
       </c>
       <c r="G600" t="n">
-        <v>7.29868459701538</v>
+        <v>7.29868507385254</v>
       </c>
       <c r="H600" t="n">
         <v>6728</v>
@@ -18523,7 +18523,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G626" t="n">
-        <v>7.7784161567688</v>
+        <v>7.77841663360596</v>
       </c>
       <c r="H626" t="n">
         <v>9091</v>
@@ -18668,7 +18668,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G631" t="n">
-        <v>7.7784161567688</v>
+        <v>7.77841663360596</v>
       </c>
       <c r="H631" t="n">
         <v>1834</v>
@@ -18755,7 +18755,7 @@
         <v>8.25</v>
       </c>
       <c r="G634" t="n">
-        <v>7.82584619522095</v>
+        <v>7.82584571838379</v>
       </c>
       <c r="H634" t="n">
         <v>811</v>
@@ -18784,7 +18784,7 @@
         <v>8.25</v>
       </c>
       <c r="G635" t="n">
-        <v>7.82584619522095</v>
+        <v>7.82584571838379</v>
       </c>
       <c r="H635" t="n">
         <v>4580</v>
@@ -18813,7 +18813,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G636" t="n">
-        <v>7.7784161567688</v>
+        <v>7.77841663360596</v>
       </c>
       <c r="H636" t="n">
         <v>2333</v>
@@ -19016,7 +19016,7 @@
         <v>8.25</v>
       </c>
       <c r="G643" t="n">
-        <v>7.82584619522095</v>
+        <v>7.82584571838379</v>
       </c>
       <c r="H643" t="n">
         <v>200</v>
@@ -19045,7 +19045,7 @@
         <v>8.25</v>
       </c>
       <c r="G644" t="n">
-        <v>7.82584619522095</v>
+        <v>7.82584571838379</v>
       </c>
       <c r="H644" t="n">
         <v>0</v>
@@ -19074,7 +19074,7 @@
         <v>8.25</v>
       </c>
       <c r="G645" t="n">
-        <v>7.82584619522095</v>
+        <v>7.82584571838379</v>
       </c>
       <c r="H645" t="n">
         <v>350</v>
@@ -19103,7 +19103,7 @@
         <v>8.25</v>
       </c>
       <c r="G646" t="n">
-        <v>7.82584619522095</v>
+        <v>7.82584571838379</v>
       </c>
       <c r="H646" t="n">
         <v>925</v>
@@ -19132,7 +19132,7 @@
         <v>8.25</v>
       </c>
       <c r="G647" t="n">
-        <v>7.82584619522095</v>
+        <v>7.82584571838379</v>
       </c>
       <c r="H647" t="n">
         <v>41854</v>
@@ -21278,7 +21278,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G721" t="n">
-        <v>6.68754148483276</v>
+        <v>6.68754100799561</v>
       </c>
       <c r="H721" t="n">
         <v>4498</v>
@@ -21510,7 +21510,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G729" t="n">
-        <v>6.68754148483276</v>
+        <v>6.68754100799561</v>
       </c>
       <c r="H729" t="n">
         <v>10666</v>
@@ -21655,7 +21655,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G734" t="n">
-        <v>6.35553503036499</v>
+        <v>6.35553550720215</v>
       </c>
       <c r="H734" t="n">
         <v>3775</v>
@@ -22177,7 +22177,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G752" t="n">
-        <v>6.68754148483276</v>
+        <v>6.68754100799561</v>
       </c>
       <c r="H752" t="n">
         <v>210</v>
@@ -22206,7 +22206,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G753" t="n">
-        <v>6.68754148483276</v>
+        <v>6.68754100799561</v>
       </c>
       <c r="H753" t="n">
         <v>0</v>
@@ -22264,7 +22264,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G755" t="n">
-        <v>6.68754148483276</v>
+        <v>6.68754100799561</v>
       </c>
       <c r="H755" t="n">
         <v>2600</v>
@@ -22351,7 +22351,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G758" t="n">
-        <v>6.68754148483276</v>
+        <v>6.68754100799561</v>
       </c>
       <c r="H758" t="n">
         <v>1000</v>
@@ -22380,7 +22380,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G759" t="n">
-        <v>6.68754148483276</v>
+        <v>6.68754100799561</v>
       </c>
       <c r="H759" t="n">
         <v>2199</v>
@@ -23018,7 +23018,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G781" t="n">
-        <v>7.7784161567688</v>
+        <v>7.77841663360596</v>
       </c>
       <c r="H781" t="n">
         <v>3468</v>
@@ -23076,7 +23076,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G783" t="n">
-        <v>7.92070484161377</v>
+        <v>7.92070436477661</v>
       </c>
       <c r="H783" t="n">
         <v>6694</v>
@@ -24062,7 +24062,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G817" t="n">
-        <v>6.68754148483276</v>
+        <v>6.68754100799561</v>
       </c>
       <c r="H817" t="n">
         <v>4357</v>
@@ -24120,7 +24120,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G819" t="n">
-        <v>6.68754148483276</v>
+        <v>6.68754100799561</v>
       </c>
       <c r="H819" t="n">
         <v>800</v>
@@ -24265,7 +24265,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G824" t="n">
-        <v>6.26067686080933</v>
+        <v>6.26067638397217</v>
       </c>
       <c r="H824" t="n">
         <v>2695</v>
@@ -24294,7 +24294,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G825" t="n">
-        <v>6.39347839355469</v>
+        <v>6.39347887039185</v>
       </c>
       <c r="H825" t="n">
         <v>1450</v>
@@ -24439,7 +24439,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G830" t="n">
-        <v>6.94365930557251</v>
+        <v>6.94365978240967</v>
       </c>
       <c r="H830" t="n">
         <v>604</v>
@@ -24584,7 +24584,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G835" t="n">
-        <v>6.77291345596313</v>
+        <v>6.77291393280029</v>
       </c>
       <c r="H835" t="n">
         <v>609</v>
@@ -24613,7 +24613,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G836" t="n">
-        <v>6.77291345596313</v>
+        <v>6.77291393280029</v>
       </c>
       <c r="H836" t="n">
         <v>0</v>
@@ -24671,7 +24671,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G838" t="n">
-        <v>7.24720764160156</v>
+        <v>7.2472071647644</v>
       </c>
       <c r="H838" t="n">
         <v>21285</v>
@@ -24932,7 +24932,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G847" t="n">
-        <v>7.22823572158813</v>
+        <v>7.22823524475098</v>
       </c>
       <c r="H847" t="n">
         <v>3902</v>
@@ -24961,7 +24961,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G848" t="n">
-        <v>7.24720764160156</v>
+        <v>7.2472071647644</v>
       </c>
       <c r="H848" t="n">
         <v>750</v>
@@ -25077,7 +25077,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G852" t="n">
-        <v>7.22823572158813</v>
+        <v>7.22823524475098</v>
       </c>
       <c r="H852" t="n">
         <v>4126</v>
@@ -25222,7 +25222,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G857" t="n">
-        <v>7.7784161567688</v>
+        <v>7.77841663360596</v>
       </c>
       <c r="H857" t="n">
         <v>16854</v>
@@ -25280,7 +25280,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G859" t="n">
-        <v>7.7784161567688</v>
+        <v>7.77841663360596</v>
       </c>
       <c r="H859" t="n">
         <v>1217</v>
@@ -25454,7 +25454,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G865" t="n">
-        <v>7.89224672317505</v>
+        <v>7.89224624633789</v>
       </c>
       <c r="H865" t="n">
         <v>27334</v>
@@ -35494,6 +35494,35 @@
         <v>0</v>
       </c>
       <c r="I1211" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1212">
+      <c r="A1212" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1212" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C1212" t="n">
+        <v>8</v>
+      </c>
+      <c r="D1212" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1212" t="n">
+        <v>8</v>
+      </c>
+      <c r="F1212" t="n">
+        <v>8</v>
+      </c>
+      <c r="G1212" t="n">
+        <v>8</v>
+      </c>
+      <c r="H1212" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1212" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SVS.MI.xlsx
+++ b/data/SVS.MI.xlsx
@@ -427,7 +427,7 @@
         <v>14.7600002288818</v>
       </c>
       <c r="G2" t="n">
-        <v>13.4660739898682</v>
+        <v>13.4660730361938</v>
       </c>
       <c r="H2" t="n">
         <v>1300</v>
@@ -485,7 +485,7 @@
         <v>14.7799997329712</v>
       </c>
       <c r="G4" t="n">
-        <v>13.4843196868896</v>
+        <v>13.484320640564</v>
       </c>
       <c r="H4" t="n">
         <v>3133</v>
@@ -601,7 +601,7 @@
         <v>14.3199996948242</v>
       </c>
       <c r="G8" t="n">
-        <v>13.0646457672119</v>
+        <v>13.0646448135376</v>
       </c>
       <c r="H8" t="n">
         <v>13042</v>
@@ -659,7 +659,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G10" t="n">
-        <v>12.5902318954468</v>
+        <v>12.5902309417725</v>
       </c>
       <c r="H10" t="n">
         <v>670</v>
@@ -688,7 +688,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G11" t="n">
-        <v>12.5902318954468</v>
+        <v>12.5902309417725</v>
       </c>
       <c r="H11" t="n">
         <v>13315</v>
@@ -804,7 +804,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G15" t="n">
-        <v>12.7544498443604</v>
+        <v>12.7544507980347</v>
       </c>
       <c r="H15" t="n">
         <v>2068</v>
@@ -833,7 +833,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G16" t="n">
-        <v>12.2435436248779</v>
+        <v>12.2435445785522</v>
       </c>
       <c r="H16" t="n">
         <v>2540</v>
@@ -891,7 +891,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G18" t="n">
-        <v>12.2252960205078</v>
+        <v>12.2252969741821</v>
       </c>
       <c r="H18" t="n">
         <v>2456</v>
@@ -949,7 +949,7 @@
         <v>13.6800003051758</v>
       </c>
       <c r="G20" t="n">
-        <v>12.4807500839233</v>
+        <v>12.4807510375977</v>
       </c>
       <c r="H20" t="n">
         <v>2647</v>
@@ -978,7 +978,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G21" t="n">
-        <v>12.4077644348145</v>
+        <v>12.4077634811401</v>
       </c>
       <c r="H21" t="n">
         <v>2900</v>
@@ -1036,7 +1036,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G23" t="n">
-        <v>12.2252960205078</v>
+        <v>12.2252969741821</v>
       </c>
       <c r="H23" t="n">
         <v>1882</v>
@@ -1094,7 +1094,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G25" t="n">
-        <v>12.0428295135498</v>
+        <v>12.0428304672241</v>
       </c>
       <c r="H25" t="n">
         <v>600</v>
@@ -1123,7 +1123,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G26" t="n">
-        <v>11.9698419570923</v>
+        <v>11.9698429107666</v>
       </c>
       <c r="H26" t="n">
         <v>4682</v>
@@ -1268,7 +1268,7 @@
         <v>13.3599996566772</v>
       </c>
       <c r="G31" t="n">
-        <v>12.1888036727905</v>
+        <v>12.1888027191162</v>
       </c>
       <c r="H31" t="n">
         <v>6448</v>
@@ -1442,7 +1442,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G37" t="n">
-        <v>10.8202991485596</v>
+        <v>10.8203001022339</v>
       </c>
       <c r="H37" t="n">
         <v>1595</v>
@@ -1645,7 +1645,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G44" t="n">
-        <v>10.2181577682495</v>
+        <v>10.2181587219238</v>
       </c>
       <c r="H44" t="n">
         <v>1100</v>
@@ -1761,7 +1761,7 @@
         <v>13.0600004196167</v>
       </c>
       <c r="G48" t="n">
-        <v>11.9151039123535</v>
+        <v>11.9151029586792</v>
       </c>
       <c r="H48" t="n">
         <v>2600</v>
@@ -1848,7 +1848,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G51" t="n">
-        <v>12.2252960205078</v>
+        <v>12.2252969741821</v>
       </c>
       <c r="H51" t="n">
         <v>1595</v>
@@ -1993,7 +1993,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G56" t="n">
-        <v>12.0428295135498</v>
+        <v>12.0428304672241</v>
       </c>
       <c r="H56" t="n">
         <v>275</v>
@@ -2022,7 +2022,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G57" t="n">
-        <v>12.0428295135498</v>
+        <v>12.0428304672241</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G58" t="n">
-        <v>12.0428295135498</v>
+        <v>12.0428304672241</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
@@ -2080,7 +2080,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G59" t="n">
-        <v>12.0428295135498</v>
+        <v>12.0428304672241</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
@@ -2138,7 +2138,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G61" t="n">
-        <v>11.4954280853271</v>
+        <v>11.4954290390015</v>
       </c>
       <c r="H61" t="n">
         <v>400</v>
@@ -2196,7 +2196,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G63" t="n">
-        <v>11.4954280853271</v>
+        <v>11.4954290390015</v>
       </c>
       <c r="H63" t="n">
         <v>490</v>
@@ -2225,7 +2225,7 @@
         <v>12.5</v>
       </c>
       <c r="G64" t="n">
-        <v>11.4041957855225</v>
+        <v>11.4041948318481</v>
       </c>
       <c r="H64" t="n">
         <v>200</v>
@@ -2254,7 +2254,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G65" t="n">
-        <v>11.4406881332397</v>
+        <v>11.4406871795654</v>
       </c>
       <c r="H65" t="n">
         <v>360</v>
@@ -2370,7 +2370,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G69" t="n">
-        <v>11.9698419570923</v>
+        <v>11.9698429107666</v>
       </c>
       <c r="H69" t="n">
         <v>660</v>
@@ -2399,7 +2399,7 @@
         <v>12.5</v>
       </c>
       <c r="G70" t="n">
-        <v>11.4041957855225</v>
+        <v>11.4041948318481</v>
       </c>
       <c r="H70" t="n">
         <v>4141</v>
@@ -2457,7 +2457,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G72" t="n">
-        <v>11.2217273712158</v>
+        <v>11.2217283248901</v>
       </c>
       <c r="H72" t="n">
         <v>850</v>
@@ -2486,7 +2486,7 @@
         <v>12.5</v>
       </c>
       <c r="G73" t="n">
-        <v>11.4041957855225</v>
+        <v>11.4041948318481</v>
       </c>
       <c r="H73" t="n">
         <v>2200</v>
@@ -2602,7 +2602,7 @@
         <v>11.9200000762939</v>
       </c>
       <c r="G77" t="n">
-        <v>10.8750410079956</v>
+        <v>10.8750400543213</v>
       </c>
       <c r="H77" t="n">
         <v>724</v>
@@ -2660,7 +2660,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G79" t="n">
-        <v>10.8020544052124</v>
+        <v>10.8020534515381</v>
       </c>
       <c r="H79" t="n">
         <v>950</v>
@@ -2718,7 +2718,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G81" t="n">
-        <v>10.8202991485596</v>
+        <v>10.8203001022339</v>
       </c>
       <c r="H81" t="n">
         <v>1654</v>
@@ -2747,7 +2747,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G82" t="n">
-        <v>11.2217273712158</v>
+        <v>11.2217283248901</v>
       </c>
       <c r="H82" t="n">
         <v>2400</v>
@@ -2805,7 +2805,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G84" t="n">
-        <v>10.2181577682495</v>
+        <v>10.2181587219238</v>
       </c>
       <c r="H84" t="n">
         <v>1810</v>
@@ -2834,7 +2834,7 @@
         <v>11.5</v>
       </c>
       <c r="G85" t="n">
-        <v>10.4918584823608</v>
+        <v>10.4918594360352</v>
       </c>
       <c r="H85" t="n">
         <v>1710</v>
@@ -2863,7 +2863,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G86" t="n">
-        <v>11.2764682769775</v>
+        <v>11.2764673233032</v>
       </c>
       <c r="H86" t="n">
         <v>1046</v>
@@ -2892,7 +2892,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G87" t="n">
-        <v>10.3276386260986</v>
+        <v>10.3276376724243</v>
       </c>
       <c r="H87" t="n">
         <v>13938</v>
@@ -2921,7 +2921,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G88" t="n">
-        <v>10.6743268966675</v>
+        <v>10.6743259429932</v>
       </c>
       <c r="H88" t="n">
         <v>4077</v>
@@ -2950,7 +2950,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G89" t="n">
-        <v>10.6743268966675</v>
+        <v>10.6743259429932</v>
       </c>
       <c r="H89" t="n">
         <v>120</v>
@@ -3095,7 +3095,7 @@
         <v>11.9200000762939</v>
       </c>
       <c r="G94" t="n">
-        <v>10.8750410079956</v>
+        <v>10.8750400543213</v>
       </c>
       <c r="H94" t="n">
         <v>3220</v>
@@ -3182,7 +3182,7 @@
         <v>11.5</v>
       </c>
       <c r="G97" t="n">
-        <v>10.4918584823608</v>
+        <v>10.4918594360352</v>
       </c>
       <c r="H97" t="n">
         <v>16862</v>
@@ -3240,7 +3240,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G99" t="n">
-        <v>10.2181577682495</v>
+        <v>10.2181587219238</v>
       </c>
       <c r="H99" t="n">
         <v>1423</v>
@@ -3269,7 +3269,7 @@
         <v>11.9200000762939</v>
       </c>
       <c r="G100" t="n">
-        <v>10.8750410079956</v>
+        <v>10.8750400543213</v>
       </c>
       <c r="H100" t="n">
         <v>4278</v>
@@ -3356,7 +3356,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G103" t="n">
-        <v>10.6743268966675</v>
+        <v>10.6743259429932</v>
       </c>
       <c r="H103" t="n">
         <v>2275</v>
@@ -3385,7 +3385,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G104" t="n">
-        <v>10.6743268966675</v>
+        <v>10.6743259429932</v>
       </c>
       <c r="H104" t="n">
         <v>780</v>
@@ -3530,7 +3530,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G109" t="n">
-        <v>10.2181577682495</v>
+        <v>10.2181587219238</v>
       </c>
       <c r="H109" t="n">
         <v>310</v>
@@ -3559,7 +3559,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G110" t="n">
-        <v>10.2181577682495</v>
+        <v>10.2181587219238</v>
       </c>
       <c r="H110" t="n">
         <v>260</v>
@@ -3588,7 +3588,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G111" t="n">
-        <v>10.2181577682495</v>
+        <v>10.2181587219238</v>
       </c>
       <c r="H111" t="n">
         <v>317</v>
@@ -3617,7 +3617,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G112" t="n">
-        <v>9.8532247543335</v>
+        <v>9.85322380065918</v>
       </c>
       <c r="H112" t="n">
         <v>600</v>
@@ -3646,7 +3646,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G113" t="n">
-        <v>10.1269254684448</v>
+        <v>10.1269245147705</v>
       </c>
       <c r="H113" t="n">
         <v>1110</v>
@@ -3675,7 +3675,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G114" t="n">
-        <v>10.1269254684448</v>
+        <v>10.1269245147705</v>
       </c>
       <c r="H114" t="n">
         <v>1005</v>
@@ -3733,7 +3733,7 @@
         <v>11.5</v>
       </c>
       <c r="G116" t="n">
-        <v>10.4918584823608</v>
+        <v>10.4918594360352</v>
       </c>
       <c r="H116" t="n">
         <v>1595</v>
@@ -3936,7 +3936,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G123" t="n">
-        <v>10.2546510696411</v>
+        <v>10.2546520233154</v>
       </c>
       <c r="H123" t="n">
         <v>923</v>
@@ -4777,7 +4777,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G152" t="n">
-        <v>10.1269254684448</v>
+        <v>10.1269245147705</v>
       </c>
       <c r="H152" t="n">
         <v>398</v>
@@ -4893,7 +4893,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G156" t="n">
-        <v>10.1269254684448</v>
+        <v>10.1269245147705</v>
       </c>
       <c r="H156" t="n">
         <v>206</v>
@@ -4922,7 +4922,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G157" t="n">
-        <v>10.1269254684448</v>
+        <v>10.1269245147705</v>
       </c>
       <c r="H157" t="n">
         <v>0</v>
@@ -4980,7 +4980,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G159" t="n">
-        <v>10.1269254684448</v>
+        <v>10.1269245147705</v>
       </c>
       <c r="H159" t="n">
         <v>378</v>
@@ -5067,7 +5067,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G162" t="n">
-        <v>9.8532247543335</v>
+        <v>9.85322380065918</v>
       </c>
       <c r="H162" t="n">
         <v>559</v>
@@ -5125,7 +5125,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G164" t="n">
-        <v>10.1269254684448</v>
+        <v>10.1269245147705</v>
       </c>
       <c r="H164" t="n">
         <v>207</v>
@@ -5270,7 +5270,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G169" t="n">
-        <v>9.30582237243652</v>
+        <v>9.30582332611084</v>
       </c>
       <c r="H169" t="n">
         <v>1233</v>
@@ -5502,7 +5502,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G177" t="n">
-        <v>8.48472023010254</v>
+        <v>8.48472118377686</v>
       </c>
       <c r="H177" t="n">
         <v>19</v>
@@ -5560,7 +5560,7 @@
         <v>9.43000030517578</v>
       </c>
       <c r="G179" t="n">
-        <v>8.60332584381104</v>
+        <v>8.60332489013672</v>
       </c>
       <c r="H179" t="n">
         <v>255</v>
@@ -5589,7 +5589,7 @@
         <v>8.75</v>
       </c>
       <c r="G180" t="n">
-        <v>7.98293590545654</v>
+        <v>7.98293685913086</v>
       </c>
       <c r="H180" t="n">
         <v>2549</v>
@@ -5647,7 +5647,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G182" t="n">
-        <v>7.70923519134521</v>
+        <v>7.70923566818237</v>
       </c>
       <c r="H182" t="n">
         <v>4032</v>
@@ -5705,7 +5705,7 @@
         <v>8.5</v>
       </c>
       <c r="G184" t="n">
-        <v>7.75485277175903</v>
+        <v>7.75485229492188</v>
       </c>
       <c r="H184" t="n">
         <v>1189</v>
@@ -5792,7 +5792,7 @@
         <v>9.01000022888184</v>
       </c>
       <c r="G187" t="n">
-        <v>8.22014331817627</v>
+        <v>8.22014427185059</v>
       </c>
       <c r="H187" t="n">
         <v>2520</v>
@@ -5995,7 +5995,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G194" t="n">
-        <v>7.73660516738892</v>
+        <v>7.73660564422607</v>
       </c>
       <c r="H194" t="n">
         <v>727</v>
@@ -6082,7 +6082,7 @@
         <v>8.25</v>
       </c>
       <c r="G197" t="n">
-        <v>7.52676868438721</v>
+        <v>7.52676820755005</v>
       </c>
       <c r="H197" t="n">
         <v>444</v>
@@ -6169,7 +6169,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G200" t="n">
-        <v>7.70923519134521</v>
+        <v>7.70923566818237</v>
       </c>
       <c r="H200" t="n">
         <v>533</v>
@@ -6198,7 +6198,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G201" t="n">
-        <v>7.70923519134521</v>
+        <v>7.70923566818237</v>
       </c>
       <c r="H201" t="n">
         <v>419</v>
@@ -6952,7 +6952,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G227" t="n">
-        <v>8.41173458099365</v>
+        <v>8.41173362731934</v>
       </c>
       <c r="H227" t="n">
         <v>475</v>
@@ -7039,7 +7039,7 @@
         <v>9.43000030517578</v>
       </c>
       <c r="G230" t="n">
-        <v>8.60332584381104</v>
+        <v>8.60332489013672</v>
       </c>
       <c r="H230" t="n">
         <v>26080</v>
@@ -7155,7 +7155,7 @@
         <v>9.43000030517578</v>
       </c>
       <c r="G234" t="n">
-        <v>8.60332584381104</v>
+        <v>8.60332489013672</v>
       </c>
       <c r="H234" t="n">
         <v>96</v>
@@ -7184,7 +7184,7 @@
         <v>9.43000030517578</v>
       </c>
       <c r="G235" t="n">
-        <v>8.60332584381104</v>
+        <v>8.60332489013672</v>
       </c>
       <c r="H235" t="n">
         <v>0</v>
@@ -7242,7 +7242,7 @@
         <v>9.82999992370605</v>
       </c>
       <c r="G237" t="n">
-        <v>8.96825790405273</v>
+        <v>8.96825885772705</v>
       </c>
       <c r="H237" t="n">
         <v>914</v>
@@ -7271,7 +7271,7 @@
         <v>9.82999992370605</v>
       </c>
       <c r="G238" t="n">
-        <v>8.96825790405273</v>
+        <v>8.96825885772705</v>
       </c>
       <c r="H238" t="n">
         <v>0</v>
@@ -7532,7 +7532,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G247" t="n">
-        <v>9.0321216583252</v>
+        <v>9.03212261199951</v>
       </c>
       <c r="H247" t="n">
         <v>200</v>
@@ -7561,7 +7561,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G248" t="n">
-        <v>9.0321216583252</v>
+        <v>9.03212261199951</v>
       </c>
       <c r="H248" t="n">
         <v>0</v>
@@ -7851,7 +7851,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G258" t="n">
-        <v>9.0321216583252</v>
+        <v>9.03212261199951</v>
       </c>
       <c r="H258" t="n">
         <v>300</v>
@@ -7880,7 +7880,7 @@
         <v>9.72999954223633</v>
       </c>
       <c r="G259" t="n">
-        <v>8.87702560424805</v>
+        <v>8.87702465057373</v>
       </c>
       <c r="H259" t="n">
         <v>2776</v>
@@ -7938,7 +7938,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G261" t="n">
-        <v>9.01387596130371</v>
+        <v>9.01387500762939</v>
       </c>
       <c r="H261" t="n">
         <v>519</v>
@@ -8054,7 +8054,7 @@
         <v>9.51000022888184</v>
       </c>
       <c r="G265" t="n">
-        <v>8.67631244659424</v>
+        <v>8.67631149291992</v>
       </c>
       <c r="H265" t="n">
         <v>135</v>
@@ -8083,7 +8083,7 @@
         <v>9.89000034332275</v>
       </c>
       <c r="G266" t="n">
-        <v>9.02299880981445</v>
+        <v>9.02299976348877</v>
       </c>
       <c r="H266" t="n">
         <v>500</v>
@@ -8286,7 +8286,7 @@
         <v>8.92000007629395</v>
       </c>
       <c r="G273" t="n">
-        <v>8.13803386688232</v>
+        <v>8.13803291320801</v>
       </c>
       <c r="H273" t="n">
         <v>1470</v>
@@ -8373,7 +8373,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G276" t="n">
-        <v>8.35699272155762</v>
+        <v>8.35699367523193</v>
       </c>
       <c r="H276" t="n">
         <v>12610</v>
@@ -8547,7 +8547,7 @@
         <v>8.90999984741211</v>
       </c>
       <c r="G282" t="n">
-        <v>8.12891006469727</v>
+        <v>8.12890911102295</v>
       </c>
       <c r="H282" t="n">
         <v>2446</v>
@@ -8605,7 +8605,7 @@
         <v>9.21000003814697</v>
       </c>
       <c r="G284" t="n">
-        <v>8.40261173248291</v>
+        <v>8.40261077880859</v>
       </c>
       <c r="H284" t="n">
         <v>10839</v>
@@ -8663,7 +8663,7 @@
         <v>9.09000015258789</v>
       </c>
       <c r="G286" t="n">
-        <v>8.29312992095947</v>
+        <v>8.29313087463379</v>
       </c>
       <c r="H286" t="n">
         <v>7374</v>
@@ -8692,7 +8692,7 @@
         <v>9.09000015258789</v>
       </c>
       <c r="G287" t="n">
-        <v>8.29312992095947</v>
+        <v>8.29313087463379</v>
       </c>
       <c r="H287" t="n">
         <v>760</v>
@@ -8924,7 +8924,7 @@
         <v>9.27000045776367</v>
       </c>
       <c r="G295" t="n">
-        <v>8.457350730896</v>
+        <v>8.45735168457031</v>
       </c>
       <c r="H295" t="n">
         <v>260</v>
@@ -9011,7 +9011,7 @@
         <v>9.21000003814697</v>
       </c>
       <c r="G298" t="n">
-        <v>8.40261173248291</v>
+        <v>8.40261077880859</v>
       </c>
       <c r="H298" t="n">
         <v>433</v>
@@ -9040,7 +9040,7 @@
         <v>9.21000003814697</v>
       </c>
       <c r="G299" t="n">
-        <v>8.40261173248291</v>
+        <v>8.40261077880859</v>
       </c>
       <c r="H299" t="n">
         <v>0</v>
@@ -9098,7 +9098,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G301" t="n">
-        <v>8.34787082672119</v>
+        <v>8.34786987304688</v>
       </c>
       <c r="H301" t="n">
         <v>519</v>
@@ -9127,7 +9127,7 @@
         <v>8.86999988555908</v>
       </c>
       <c r="G302" t="n">
-        <v>8.09241580963135</v>
+        <v>8.09241676330566</v>
       </c>
       <c r="H302" t="n">
         <v>2131</v>
@@ -9330,7 +9330,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G309" t="n">
-        <v>8.19277286529541</v>
+        <v>8.19277381896973</v>
       </c>
       <c r="H309" t="n">
         <v>191</v>
@@ -9446,7 +9446,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G313" t="n">
-        <v>8.41173458099365</v>
+        <v>8.41173362731934</v>
       </c>
       <c r="H313" t="n">
         <v>269</v>
@@ -9475,7 +9475,7 @@
         <v>9.01000022888184</v>
       </c>
       <c r="G314" t="n">
-        <v>8.22014331817627</v>
+        <v>8.22014427185059</v>
       </c>
       <c r="H314" t="n">
         <v>680</v>
@@ -9504,7 +9504,7 @@
         <v>9.01000022888184</v>
       </c>
       <c r="G315" t="n">
-        <v>8.22014331817627</v>
+        <v>8.22014427185059</v>
       </c>
       <c r="H315" t="n">
         <v>0</v>
@@ -9620,7 +9620,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G319" t="n">
-        <v>7.95556592941284</v>
+        <v>7.95556688308716</v>
       </c>
       <c r="H319" t="n">
         <v>5536</v>
@@ -9852,7 +9852,7 @@
         <v>8.92000007629395</v>
       </c>
       <c r="G327" t="n">
-        <v>8.13803386688232</v>
+        <v>8.13803291320801</v>
       </c>
       <c r="H327" t="n">
         <v>200</v>
@@ -10055,7 +10055,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G334" t="n">
-        <v>8.48472023010254</v>
+        <v>8.48472118377686</v>
       </c>
       <c r="H334" t="n">
         <v>15021</v>
@@ -10113,7 +10113,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G336" t="n">
-        <v>8.41173458099365</v>
+        <v>8.41173362731934</v>
       </c>
       <c r="H336" t="n">
         <v>10609</v>
@@ -10200,7 +10200,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G339" t="n">
-        <v>7.53589200973511</v>
+        <v>7.53589248657227</v>
       </c>
       <c r="H339" t="n">
         <v>74770</v>
@@ -10287,7 +10287,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G342" t="n">
-        <v>7.37167119979858</v>
+        <v>7.37167167663574</v>
       </c>
       <c r="H342" t="n">
         <v>18625</v>
@@ -10316,7 +10316,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G343" t="n">
-        <v>7.40816450119019</v>
+        <v>7.40816497802734</v>
       </c>
       <c r="H343" t="n">
         <v>500</v>
@@ -10374,7 +10374,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G345" t="n">
-        <v>7.33517837524414</v>
+        <v>7.33517789840698</v>
       </c>
       <c r="H345" t="n">
         <v>3152</v>
@@ -10432,7 +10432,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G347" t="n">
-        <v>7.53589200973511</v>
+        <v>7.53589248657227</v>
       </c>
       <c r="H347" t="n">
         <v>1406</v>
@@ -10461,7 +10461,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G348" t="n">
-        <v>7.4264121055603</v>
+        <v>7.42641162872314</v>
       </c>
       <c r="H348" t="n">
         <v>803</v>
@@ -10751,7 +10751,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G358" t="n">
-        <v>7.11621761322021</v>
+        <v>7.11621809005737</v>
       </c>
       <c r="H358" t="n">
         <v>653</v>
@@ -10780,7 +10780,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G359" t="n">
-        <v>7.11621761322021</v>
+        <v>7.11621809005737</v>
       </c>
       <c r="H359" t="n">
         <v>0</v>
@@ -10809,7 +10809,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G360" t="n">
-        <v>7.11621761322021</v>
+        <v>7.11621809005737</v>
       </c>
       <c r="H360" t="n">
         <v>0</v>
@@ -10838,7 +10838,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G361" t="n">
-        <v>7.11621761322021</v>
+        <v>7.11621809005737</v>
       </c>
       <c r="H361" t="n">
         <v>0</v>
@@ -11302,7 +11302,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G377" t="n">
-        <v>7.11621761322021</v>
+        <v>7.11621809005737</v>
       </c>
       <c r="H377" t="n">
         <v>2656</v>
@@ -11505,7 +11505,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G384" t="n">
-        <v>6.91550350189209</v>
+        <v>6.91550397872925</v>
       </c>
       <c r="H384" t="n">
         <v>502</v>
@@ -11534,7 +11534,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G385" t="n">
-        <v>6.91550350189209</v>
+        <v>6.91550397872925</v>
       </c>
       <c r="H385" t="n">
         <v>100</v>
@@ -11563,7 +11563,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G386" t="n">
-        <v>6.91550350189209</v>
+        <v>6.91550397872925</v>
       </c>
       <c r="H386" t="n">
         <v>0</v>
@@ -11592,7 +11592,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G387" t="n">
-        <v>6.91550350189209</v>
+        <v>6.91550397872925</v>
       </c>
       <c r="H387" t="n">
         <v>500</v>
@@ -11650,7 +11650,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G389" t="n">
-        <v>7.17095756530762</v>
+        <v>7.17095804214478</v>
       </c>
       <c r="H389" t="n">
         <v>7937</v>
@@ -11679,7 +11679,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G390" t="n">
-        <v>7.38991832733154</v>
+        <v>7.3899188041687</v>
       </c>
       <c r="H390" t="n">
         <v>4671</v>
@@ -11708,7 +11708,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G391" t="n">
-        <v>7.59063196182251</v>
+        <v>7.59063148498535</v>
       </c>
       <c r="H391" t="n">
         <v>1808</v>
@@ -11882,7 +11882,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G397" t="n">
-        <v>7.62712574005127</v>
+        <v>7.62712526321411</v>
       </c>
       <c r="H397" t="n">
         <v>1616</v>
@@ -11911,7 +11911,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G398" t="n">
-        <v>7.62712574005127</v>
+        <v>7.62712526321411</v>
       </c>
       <c r="H398" t="n">
         <v>0</v>
@@ -11940,7 +11940,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G399" t="n">
-        <v>7.40816450119019</v>
+        <v>7.40816497802734</v>
       </c>
       <c r="H399" t="n">
         <v>350</v>
@@ -12143,7 +12143,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G406" t="n">
-        <v>7.33517837524414</v>
+        <v>7.33517789840698</v>
       </c>
       <c r="H406" t="n">
         <v>3302</v>
@@ -12172,7 +12172,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G407" t="n">
-        <v>7.33517837524414</v>
+        <v>7.33517789840698</v>
       </c>
       <c r="H407" t="n">
         <v>0</v>
@@ -12317,7 +12317,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G412" t="n">
-        <v>7.4264121055603</v>
+        <v>7.42641162872314</v>
       </c>
       <c r="H412" t="n">
         <v>161</v>
@@ -12346,7 +12346,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G413" t="n">
-        <v>7.40816450119019</v>
+        <v>7.40816497802734</v>
       </c>
       <c r="H413" t="n">
         <v>1600</v>
@@ -12433,7 +12433,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G416" t="n">
-        <v>7.4264121055603</v>
+        <v>7.42641162872314</v>
       </c>
       <c r="H416" t="n">
         <v>1900</v>
@@ -12462,7 +12462,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G417" t="n">
-        <v>7.40816450119019</v>
+        <v>7.40816497802734</v>
       </c>
       <c r="H417" t="n">
         <v>4309</v>
@@ -12781,7 +12781,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G428" t="n">
-        <v>7.73660516738892</v>
+        <v>7.73660564422607</v>
       </c>
       <c r="H428" t="n">
         <v>4521</v>
@@ -12810,7 +12810,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G429" t="n">
-        <v>7.66361904144287</v>
+        <v>7.66361808776855</v>
       </c>
       <c r="H429" t="n">
         <v>1230</v>
@@ -12839,7 +12839,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G430" t="n">
-        <v>7.66361904144287</v>
+        <v>7.66361808776855</v>
       </c>
       <c r="H430" t="n">
         <v>0</v>
@@ -13100,7 +13100,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G439" t="n">
-        <v>6.91550350189209</v>
+        <v>6.91550397872925</v>
       </c>
       <c r="H439" t="n">
         <v>5180</v>
@@ -13796,7 +13796,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G463" t="n">
-        <v>6.53232288360596</v>
+        <v>6.5323224067688</v>
       </c>
       <c r="H463" t="n">
         <v>800</v>
@@ -13825,7 +13825,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G464" t="n">
-        <v>6.56881618499756</v>
+        <v>6.5688157081604</v>
       </c>
       <c r="H464" t="n">
         <v>4878</v>
@@ -13854,7 +13854,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G465" t="n">
-        <v>6.56881618499756</v>
+        <v>6.5688157081604</v>
       </c>
       <c r="H465" t="n">
         <v>2702</v>
@@ -13883,7 +13883,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G466" t="n">
-        <v>6.56881618499756</v>
+        <v>6.5688157081604</v>
       </c>
       <c r="H466" t="n">
         <v>0</v>
@@ -13912,7 +13912,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G467" t="n">
-        <v>6.56881618499756</v>
+        <v>6.5688157081604</v>
       </c>
       <c r="H467" t="n">
         <v>0</v>
@@ -13941,7 +13941,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G468" t="n">
-        <v>6.56881618499756</v>
+        <v>6.5688157081604</v>
       </c>
       <c r="H468" t="n">
         <v>0</v>
@@ -14028,7 +14028,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G471" t="n">
-        <v>6.29511594772339</v>
+        <v>6.29511547088623</v>
       </c>
       <c r="H471" t="n">
         <v>882</v>
@@ -14057,7 +14057,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G472" t="n">
-        <v>6.4958291053772</v>
+        <v>6.49582958221436</v>
       </c>
       <c r="H472" t="n">
         <v>1050</v>
@@ -14115,7 +14115,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G474" t="n">
-        <v>6.29511594772339</v>
+        <v>6.29511547088623</v>
       </c>
       <c r="H474" t="n">
         <v>120</v>
@@ -14202,7 +14202,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G477" t="n">
-        <v>6.53232288360596</v>
+        <v>6.5323224067688</v>
       </c>
       <c r="H477" t="n">
         <v>160</v>
@@ -14231,7 +14231,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G478" t="n">
-        <v>6.73303699493408</v>
+        <v>6.73303651809692</v>
       </c>
       <c r="H478" t="n">
         <v>1030</v>
@@ -14260,7 +14260,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G479" t="n">
-        <v>6.73303699493408</v>
+        <v>6.73303651809692</v>
       </c>
       <c r="H479" t="n">
         <v>0</v>
@@ -14289,7 +14289,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G480" t="n">
-        <v>6.73303699493408</v>
+        <v>6.73303651809692</v>
       </c>
       <c r="H480" t="n">
         <v>0</v>
@@ -14318,7 +14318,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G481" t="n">
-        <v>6.73303699493408</v>
+        <v>6.73303651809692</v>
       </c>
       <c r="H481" t="n">
         <v>0</v>
@@ -14347,7 +14347,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G482" t="n">
-        <v>6.73303699493408</v>
+        <v>6.73303651809692</v>
       </c>
       <c r="H482" t="n">
         <v>0</v>
@@ -14376,7 +14376,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G483" t="n">
-        <v>6.73303699493408</v>
+        <v>6.73303651809692</v>
       </c>
       <c r="H483" t="n">
         <v>0</v>
@@ -14608,7 +14608,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G491" t="n">
-        <v>7.18920469284058</v>
+        <v>7.18920421600342</v>
       </c>
       <c r="H491" t="n">
         <v>1500</v>
@@ -14666,7 +14666,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G493" t="n">
-        <v>7.22569799423218</v>
+        <v>7.22569751739502</v>
       </c>
       <c r="H493" t="n">
         <v>800</v>
@@ -14695,7 +14695,7 @@
         <v>7.78000020980835</v>
       </c>
       <c r="G494" t="n">
-        <v>7.09797096252441</v>
+        <v>7.09797048568726</v>
       </c>
       <c r="H494" t="n">
         <v>600</v>
@@ -14724,7 +14724,7 @@
         <v>7.78000020980835</v>
       </c>
       <c r="G495" t="n">
-        <v>7.09797096252441</v>
+        <v>7.09797048568726</v>
       </c>
       <c r="H495" t="n">
         <v>0</v>
@@ -14753,7 +14753,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G496" t="n">
-        <v>7.15271091461182</v>
+        <v>7.15271139144897</v>
       </c>
       <c r="H496" t="n">
         <v>1106</v>
@@ -14869,7 +14869,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G500" t="n">
-        <v>7.4264121055603</v>
+        <v>7.42641162872314</v>
       </c>
       <c r="H500" t="n">
         <v>595</v>
@@ -14927,7 +14927,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G502" t="n">
-        <v>7.33517837524414</v>
+        <v>7.33517789840698</v>
       </c>
       <c r="H502" t="n">
         <v>517</v>
@@ -14985,7 +14985,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G504" t="n">
-        <v>7.37167119979858</v>
+        <v>7.37167167663574</v>
       </c>
       <c r="H504" t="n">
         <v>1968</v>
@@ -15014,7 +15014,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G505" t="n">
-        <v>7.33517837524414</v>
+        <v>7.33517789840698</v>
       </c>
       <c r="H505" t="n">
         <v>731</v>
@@ -15043,7 +15043,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G506" t="n">
-        <v>7.33517837524414</v>
+        <v>7.33517789840698</v>
       </c>
       <c r="H506" t="n">
         <v>300</v>
@@ -15101,7 +15101,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G508" t="n">
-        <v>7.37167119979858</v>
+        <v>7.37167167663574</v>
       </c>
       <c r="H508" t="n">
         <v>1681</v>
@@ -15130,7 +15130,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G509" t="n">
-        <v>7.37167119979858</v>
+        <v>7.37167167663574</v>
       </c>
       <c r="H509" t="n">
         <v>0</v>
@@ -15159,7 +15159,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G510" t="n">
-        <v>7.37167119979858</v>
+        <v>7.37167167663574</v>
       </c>
       <c r="H510" t="n">
         <v>0</v>
@@ -15507,7 +15507,7 @@
         <v>7.42000007629395</v>
       </c>
       <c r="G522" t="n">
-        <v>6.76953029632568</v>
+        <v>6.76952981948853</v>
       </c>
       <c r="H522" t="n">
         <v>100</v>
@@ -15536,7 +15536,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G523" t="n">
-        <v>6.73303699493408</v>
+        <v>6.73303651809692</v>
       </c>
       <c r="H523" t="n">
         <v>740</v>
@@ -15565,7 +15565,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G524" t="n">
-        <v>6.73303699493408</v>
+        <v>6.73303651809692</v>
       </c>
       <c r="H524" t="n">
         <v>1680</v>
@@ -15739,7 +15739,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G530" t="n">
-        <v>7.17095756530762</v>
+        <v>7.17095804214478</v>
       </c>
       <c r="H530" t="n">
         <v>2115</v>
@@ -15913,7 +15913,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G536" t="n">
-        <v>7.38991832733154</v>
+        <v>7.3899188041687</v>
       </c>
       <c r="H536" t="n">
         <v>18461</v>
@@ -15942,7 +15942,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G537" t="n">
-        <v>7.18920469284058</v>
+        <v>7.18920421600342</v>
       </c>
       <c r="H537" t="n">
         <v>29589</v>
@@ -16058,7 +16058,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G541" t="n">
-        <v>7.15271091461182</v>
+        <v>7.15271139144897</v>
       </c>
       <c r="H541" t="n">
         <v>2212</v>
@@ -16087,7 +16087,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G542" t="n">
-        <v>7.15271091461182</v>
+        <v>7.15271139144897</v>
       </c>
       <c r="H542" t="n">
         <v>1250</v>
@@ -16261,7 +16261,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G548" t="n">
-        <v>7.38991832733154</v>
+        <v>7.3899188041687</v>
       </c>
       <c r="H548" t="n">
         <v>1200</v>
@@ -16377,7 +16377,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G552" t="n">
-        <v>7.66361904144287</v>
+        <v>7.66361808776855</v>
       </c>
       <c r="H552" t="n">
         <v>2734</v>
@@ -16406,7 +16406,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G553" t="n">
-        <v>7.68186521530151</v>
+        <v>7.68186616897583</v>
       </c>
       <c r="H553" t="n">
         <v>4691</v>
@@ -16493,7 +16493,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G556" t="n">
-        <v>7.68186521530151</v>
+        <v>7.68186616897583</v>
       </c>
       <c r="H556" t="n">
         <v>409</v>
@@ -16522,7 +16522,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G557" t="n">
-        <v>7.62712574005127</v>
+        <v>7.62712526321411</v>
       </c>
       <c r="H557" t="n">
         <v>3160</v>
@@ -16551,7 +16551,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G558" t="n">
-        <v>7.62712574005127</v>
+        <v>7.62712526321411</v>
       </c>
       <c r="H558" t="n">
         <v>0</v>
@@ -16580,7 +16580,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G559" t="n">
-        <v>7.62712574005127</v>
+        <v>7.62712526321411</v>
       </c>
       <c r="H559" t="n">
         <v>0</v>
@@ -16609,7 +16609,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G560" t="n">
-        <v>7.66361904144287</v>
+        <v>7.66361808776855</v>
       </c>
       <c r="H560" t="n">
         <v>3325</v>
@@ -16638,7 +16638,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G561" t="n">
-        <v>7.66361904144287</v>
+        <v>7.66361808776855</v>
       </c>
       <c r="H561" t="n">
         <v>0</v>
@@ -16667,7 +16667,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G562" t="n">
-        <v>7.66361904144287</v>
+        <v>7.66361808776855</v>
       </c>
       <c r="H562" t="n">
         <v>978</v>
@@ -16928,7 +16928,7 @@
         <v>8.25</v>
       </c>
       <c r="G571" t="n">
-        <v>7.52676868438721</v>
+        <v>7.52676820755005</v>
       </c>
       <c r="H571" t="n">
         <v>2468</v>
@@ -17102,7 +17102,7 @@
         <v>8.25</v>
       </c>
       <c r="G577" t="n">
-        <v>7.52676868438721</v>
+        <v>7.52676820755005</v>
       </c>
       <c r="H577" t="n">
         <v>10687</v>
@@ -17131,7 +17131,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G578" t="n">
-        <v>7.25306749343872</v>
+        <v>7.25306797027588</v>
       </c>
       <c r="H578" t="n">
         <v>14460</v>
@@ -17218,7 +17218,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G581" t="n">
-        <v>7.38991832733154</v>
+        <v>7.3899188041687</v>
       </c>
       <c r="H581" t="n">
         <v>540</v>
@@ -17334,7 +17334,7 @@
         <v>8.25</v>
       </c>
       <c r="G585" t="n">
-        <v>7.52676868438721</v>
+        <v>7.52676820755005</v>
       </c>
       <c r="H585" t="n">
         <v>1560</v>
@@ -17363,7 +17363,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G586" t="n">
-        <v>7.38991832733154</v>
+        <v>7.3899188041687</v>
       </c>
       <c r="H586" t="n">
         <v>3341</v>
@@ -17392,7 +17392,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G587" t="n">
-        <v>7.38991832733154</v>
+        <v>7.3899188041687</v>
       </c>
       <c r="H587" t="n">
         <v>340</v>
@@ -17450,7 +17450,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G589" t="n">
-        <v>7.38991832733154</v>
+        <v>7.3899188041687</v>
       </c>
       <c r="H589" t="n">
         <v>1325</v>
@@ -17479,7 +17479,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G590" t="n">
-        <v>7.38991832733154</v>
+        <v>7.3899188041687</v>
       </c>
       <c r="H590" t="n">
         <v>851</v>
@@ -17508,7 +17508,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G591" t="n">
-        <v>7.38991832733154</v>
+        <v>7.3899188041687</v>
       </c>
       <c r="H591" t="n">
         <v>22104</v>
@@ -17537,7 +17537,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G592" t="n">
-        <v>7.38991832733154</v>
+        <v>7.3899188041687</v>
       </c>
       <c r="H592" t="n">
         <v>0</v>
@@ -17856,7 +17856,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G603" t="n">
-        <v>7.25306749343872</v>
+        <v>7.25306797027588</v>
       </c>
       <c r="H603" t="n">
         <v>19392</v>
@@ -35523,6 +35523,64 @@
         <v>0</v>
       </c>
       <c r="I1212" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1213">
+      <c r="A1213" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1213" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C1213" t="n">
+        <v>8</v>
+      </c>
+      <c r="D1213" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1213" t="n">
+        <v>8</v>
+      </c>
+      <c r="F1213" t="n">
+        <v>8</v>
+      </c>
+      <c r="G1213" t="n">
+        <v>8</v>
+      </c>
+      <c r="H1213" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1213" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1214">
+      <c r="A1214" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1214" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C1214" t="n">
+        <v>7.98000001907349</v>
+      </c>
+      <c r="D1214" t="n">
+        <v>8.03999996185303</v>
+      </c>
+      <c r="E1214" t="n">
+        <v>7.80000019073486</v>
+      </c>
+      <c r="F1214" t="n">
+        <v>8.03999996185303</v>
+      </c>
+      <c r="G1214" t="n">
+        <v>8.03999996185303</v>
+      </c>
+      <c r="H1214" t="n">
+        <v>2501</v>
+      </c>
+      <c r="I1214" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SVS.MI.xlsx
+++ b/data/SVS.MI.xlsx
@@ -427,7 +427,7 @@
         <v>14.7600002288818</v>
       </c>
       <c r="G2" t="n">
-        <v>13.4660730361938</v>
+        <v>13.4660739898682</v>
       </c>
       <c r="H2" t="n">
         <v>1300</v>
@@ -485,7 +485,7 @@
         <v>14.7799997329712</v>
       </c>
       <c r="G4" t="n">
-        <v>13.484320640564</v>
+        <v>13.4843196868896</v>
       </c>
       <c r="H4" t="n">
         <v>3133</v>
@@ -543,7 +543,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G6" t="n">
-        <v>13.4113321304321</v>
+        <v>13.4113330841064</v>
       </c>
       <c r="H6" t="n">
         <v>1997</v>
@@ -601,7 +601,7 @@
         <v>14.3199996948242</v>
       </c>
       <c r="G8" t="n">
-        <v>13.0646448135376</v>
+        <v>13.0646457672119</v>
       </c>
       <c r="H8" t="n">
         <v>13042</v>
@@ -659,7 +659,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G10" t="n">
-        <v>12.5902309417725</v>
+        <v>12.5902318954468</v>
       </c>
       <c r="H10" t="n">
         <v>670</v>
@@ -688,7 +688,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G11" t="n">
-        <v>12.5902309417725</v>
+        <v>12.5902318954468</v>
       </c>
       <c r="H11" t="n">
         <v>13315</v>
@@ -833,7 +833,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G16" t="n">
-        <v>12.2435445785522</v>
+        <v>12.2435436248779</v>
       </c>
       <c r="H16" t="n">
         <v>2540</v>
@@ -920,7 +920,7 @@
         <v>13.3400001525879</v>
       </c>
       <c r="G19" t="n">
-        <v>12.1705570220947</v>
+        <v>12.1705560684204</v>
       </c>
       <c r="H19" t="n">
         <v>3080</v>
@@ -1094,7 +1094,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G25" t="n">
-        <v>12.0428304672241</v>
+        <v>12.0428295135498</v>
       </c>
       <c r="H25" t="n">
         <v>600</v>
@@ -1123,7 +1123,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G26" t="n">
-        <v>11.9698429107666</v>
+        <v>11.9698419570923</v>
       </c>
       <c r="H26" t="n">
         <v>4682</v>
@@ -1239,7 +1239,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G30" t="n">
-        <v>11.3859481811523</v>
+        <v>11.385947227478</v>
       </c>
       <c r="H30" t="n">
         <v>2251</v>
@@ -1297,7 +1297,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G32" t="n">
-        <v>11.5501680374146</v>
+        <v>11.5501689910889</v>
       </c>
       <c r="H32" t="n">
         <v>2810</v>
@@ -1355,7 +1355,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G34" t="n">
-        <v>11.2034816741943</v>
+        <v>11.20348072052</v>
       </c>
       <c r="H34" t="n">
         <v>7092</v>
@@ -1413,7 +1413,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G36" t="n">
-        <v>10.5830926895142</v>
+        <v>10.5830936431885</v>
       </c>
       <c r="H36" t="n">
         <v>6892</v>
@@ -1471,7 +1471,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G38" t="n">
-        <v>10.5830926895142</v>
+        <v>10.5830936431885</v>
       </c>
       <c r="H38" t="n">
         <v>1246</v>
@@ -1616,7 +1616,7 @@
         <v>10.7600002288818</v>
       </c>
       <c r="G43" t="n">
-        <v>9.81673145294189</v>
+        <v>9.81673240661621</v>
       </c>
       <c r="H43" t="n">
         <v>1169</v>
@@ -1645,7 +1645,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G44" t="n">
-        <v>10.2181587219238</v>
+        <v>10.2181577682495</v>
       </c>
       <c r="H44" t="n">
         <v>1100</v>
@@ -1993,7 +1993,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G56" t="n">
-        <v>12.0428304672241</v>
+        <v>12.0428295135498</v>
       </c>
       <c r="H56" t="n">
         <v>275</v>
@@ -2022,7 +2022,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G57" t="n">
-        <v>12.0428304672241</v>
+        <v>12.0428295135498</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G58" t="n">
-        <v>12.0428304672241</v>
+        <v>12.0428295135498</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
@@ -2080,7 +2080,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G59" t="n">
-        <v>12.0428304672241</v>
+        <v>12.0428295135498</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
@@ -2138,7 +2138,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G61" t="n">
-        <v>11.4954290390015</v>
+        <v>11.4954280853271</v>
       </c>
       <c r="H61" t="n">
         <v>400</v>
@@ -2196,7 +2196,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G63" t="n">
-        <v>11.4954290390015</v>
+        <v>11.4954280853271</v>
       </c>
       <c r="H63" t="n">
         <v>490</v>
@@ -2254,7 +2254,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G65" t="n">
-        <v>11.4406871795654</v>
+        <v>11.4406881332397</v>
       </c>
       <c r="H65" t="n">
         <v>360</v>
@@ -2341,7 +2341,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G68" t="n">
-        <v>11.1304941177368</v>
+        <v>11.1304931640625</v>
       </c>
       <c r="H68" t="n">
         <v>700</v>
@@ -2370,7 +2370,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G69" t="n">
-        <v>11.9698429107666</v>
+        <v>11.9698419570923</v>
       </c>
       <c r="H69" t="n">
         <v>660</v>
@@ -2457,7 +2457,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G72" t="n">
-        <v>11.2217283248901</v>
+        <v>11.2217273712158</v>
       </c>
       <c r="H72" t="n">
         <v>850</v>
@@ -2515,7 +2515,7 @@
         <v>12.4399995803833</v>
       </c>
       <c r="G74" t="n">
-        <v>11.3494539260864</v>
+        <v>11.3494548797607</v>
       </c>
       <c r="H74" t="n">
         <v>16133</v>
@@ -2544,7 +2544,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G75" t="n">
-        <v>11.8238687515259</v>
+        <v>11.8238697052002</v>
       </c>
       <c r="H75" t="n">
         <v>727</v>
@@ -2660,7 +2660,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G79" t="n">
-        <v>10.8020534515381</v>
+        <v>10.8020544052124</v>
       </c>
       <c r="H79" t="n">
         <v>950</v>
@@ -2689,7 +2689,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G80" t="n">
-        <v>10.5648460388184</v>
+        <v>10.5648469924927</v>
       </c>
       <c r="H80" t="n">
         <v>2840</v>
@@ -2747,7 +2747,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G82" t="n">
-        <v>11.2217283248901</v>
+        <v>11.2217273712158</v>
       </c>
       <c r="H82" t="n">
         <v>2400</v>
@@ -2805,7 +2805,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G84" t="n">
-        <v>10.2181587219238</v>
+        <v>10.2181577682495</v>
       </c>
       <c r="H84" t="n">
         <v>1810</v>
@@ -2834,7 +2834,7 @@
         <v>11.5</v>
       </c>
       <c r="G85" t="n">
-        <v>10.4918594360352</v>
+        <v>10.4918584823608</v>
       </c>
       <c r="H85" t="n">
         <v>1710</v>
@@ -2863,7 +2863,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G86" t="n">
-        <v>11.2764673233032</v>
+        <v>11.2764682769775</v>
       </c>
       <c r="H86" t="n">
         <v>1046</v>
@@ -2892,7 +2892,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G87" t="n">
-        <v>10.3276376724243</v>
+        <v>10.3276395797729</v>
       </c>
       <c r="H87" t="n">
         <v>13938</v>
@@ -2979,7 +2979,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G90" t="n">
-        <v>10.9297800064087</v>
+        <v>10.9297790527344</v>
       </c>
       <c r="H90" t="n">
         <v>105</v>
@@ -3037,7 +3037,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G92" t="n">
-        <v>10.5648460388184</v>
+        <v>10.5648469924927</v>
       </c>
       <c r="H92" t="n">
         <v>1190</v>
@@ -3066,7 +3066,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G93" t="n">
-        <v>10.5648460388184</v>
+        <v>10.5648469924927</v>
       </c>
       <c r="H93" t="n">
         <v>150</v>
@@ -3124,7 +3124,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G95" t="n">
-        <v>10.5648460388184</v>
+        <v>10.5648469924927</v>
       </c>
       <c r="H95" t="n">
         <v>1620</v>
@@ -3153,7 +3153,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G96" t="n">
-        <v>10.5648460388184</v>
+        <v>10.5648469924927</v>
       </c>
       <c r="H96" t="n">
         <v>7278</v>
@@ -3182,7 +3182,7 @@
         <v>11.5</v>
       </c>
       <c r="G97" t="n">
-        <v>10.4918594360352</v>
+        <v>10.4918584823608</v>
       </c>
       <c r="H97" t="n">
         <v>16862</v>
@@ -3240,7 +3240,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G99" t="n">
-        <v>10.2181587219238</v>
+        <v>10.2181577682495</v>
       </c>
       <c r="H99" t="n">
         <v>1423</v>
@@ -3298,7 +3298,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G101" t="n">
-        <v>10.5648460388184</v>
+        <v>10.5648469924927</v>
       </c>
       <c r="H101" t="n">
         <v>4205</v>
@@ -3414,7 +3414,7 @@
         <v>11.7799997329712</v>
       </c>
       <c r="G105" t="n">
-        <v>10.7473134994507</v>
+        <v>10.7473125457764</v>
       </c>
       <c r="H105" t="n">
         <v>2174</v>
@@ -3443,7 +3443,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G106" t="n">
-        <v>10.3093919754028</v>
+        <v>10.3093929290771</v>
       </c>
       <c r="H106" t="n">
         <v>1804</v>
@@ -3501,7 +3501,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G108" t="n">
-        <v>9.9444580078125</v>
+        <v>9.94445705413818</v>
       </c>
       <c r="H108" t="n">
         <v>4150</v>
@@ -3530,7 +3530,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G109" t="n">
-        <v>10.2181587219238</v>
+        <v>10.2181577682495</v>
       </c>
       <c r="H109" t="n">
         <v>310</v>
@@ -3559,7 +3559,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G110" t="n">
-        <v>10.2181587219238</v>
+        <v>10.2181577682495</v>
       </c>
       <c r="H110" t="n">
         <v>260</v>
@@ -3588,7 +3588,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G111" t="n">
-        <v>10.2181587219238</v>
+        <v>10.2181577682495</v>
       </c>
       <c r="H111" t="n">
         <v>317</v>
@@ -3617,7 +3617,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G112" t="n">
-        <v>9.85322380065918</v>
+        <v>9.8532247543335</v>
       </c>
       <c r="H112" t="n">
         <v>600</v>
@@ -3646,7 +3646,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G113" t="n">
-        <v>10.1269245147705</v>
+        <v>10.1269254684448</v>
       </c>
       <c r="H113" t="n">
         <v>1110</v>
@@ -3675,7 +3675,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G114" t="n">
-        <v>10.1269245147705</v>
+        <v>10.1269254684448</v>
       </c>
       <c r="H114" t="n">
         <v>1005</v>
@@ -3704,7 +3704,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G115" t="n">
-        <v>10.2728996276855</v>
+        <v>10.2728986740112</v>
       </c>
       <c r="H115" t="n">
         <v>970</v>
@@ -3733,7 +3733,7 @@
         <v>11.5</v>
       </c>
       <c r="G116" t="n">
-        <v>10.4918594360352</v>
+        <v>10.4918584823608</v>
       </c>
       <c r="H116" t="n">
         <v>1595</v>
@@ -3820,7 +3820,7 @@
         <v>11.7799997329712</v>
       </c>
       <c r="G119" t="n">
-        <v>10.7473134994507</v>
+        <v>10.7473125457764</v>
       </c>
       <c r="H119" t="n">
         <v>1393</v>
@@ -3849,7 +3849,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G120" t="n">
-        <v>10.2728996276855</v>
+        <v>10.2728986740112</v>
       </c>
       <c r="H120" t="n">
         <v>3314</v>
@@ -3936,7 +3936,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G123" t="n">
-        <v>10.2546520233154</v>
+        <v>10.2546510696411</v>
       </c>
       <c r="H123" t="n">
         <v>923</v>
@@ -4458,7 +4458,7 @@
         <v>11.2799997329712</v>
       </c>
       <c r="G141" t="n">
-        <v>10.291145324707</v>
+        <v>10.2911462783813</v>
       </c>
       <c r="H141" t="n">
         <v>250</v>
@@ -4516,7 +4516,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G143" t="n">
-        <v>10.2728996276855</v>
+        <v>10.2728986740112</v>
       </c>
       <c r="H143" t="n">
         <v>354</v>
@@ -4545,7 +4545,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G144" t="n">
-        <v>9.9444580078125</v>
+        <v>9.94445705413818</v>
       </c>
       <c r="H144" t="n">
         <v>9773</v>
@@ -4632,7 +4632,7 @@
         <v>11.2799997329712</v>
       </c>
       <c r="G147" t="n">
-        <v>10.291145324707</v>
+        <v>10.2911462783813</v>
       </c>
       <c r="H147" t="n">
         <v>780</v>
@@ -4661,7 +4661,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G148" t="n">
-        <v>10.3093919754028</v>
+        <v>10.3093929290771</v>
       </c>
       <c r="H148" t="n">
         <v>480</v>
@@ -4777,7 +4777,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G152" t="n">
-        <v>10.1269245147705</v>
+        <v>10.1269254684448</v>
       </c>
       <c r="H152" t="n">
         <v>398</v>
@@ -4893,7 +4893,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G156" t="n">
-        <v>10.1269245147705</v>
+        <v>10.1269254684448</v>
       </c>
       <c r="H156" t="n">
         <v>206</v>
@@ -4922,7 +4922,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G157" t="n">
-        <v>10.1269245147705</v>
+        <v>10.1269254684448</v>
       </c>
       <c r="H157" t="n">
         <v>0</v>
@@ -4951,7 +4951,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G158" t="n">
-        <v>9.9444580078125</v>
+        <v>9.94445705413818</v>
       </c>
       <c r="H158" t="n">
         <v>320</v>
@@ -4980,7 +4980,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G159" t="n">
-        <v>10.1269245147705</v>
+        <v>10.1269254684448</v>
       </c>
       <c r="H159" t="n">
         <v>378</v>
@@ -5009,7 +5009,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G160" t="n">
-        <v>9.9444580078125</v>
+        <v>9.94445705413818</v>
       </c>
       <c r="H160" t="n">
         <v>220</v>
@@ -5038,7 +5038,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G161" t="n">
-        <v>9.9444580078125</v>
+        <v>9.94445705413818</v>
       </c>
       <c r="H161" t="n">
         <v>1909</v>
@@ -5067,7 +5067,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G162" t="n">
-        <v>9.85322380065918</v>
+        <v>9.8532247543335</v>
       </c>
       <c r="H162" t="n">
         <v>559</v>
@@ -5125,7 +5125,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G164" t="n">
-        <v>10.1269245147705</v>
+        <v>10.1269254684448</v>
       </c>
       <c r="H164" t="n">
         <v>207</v>
@@ -5183,7 +5183,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G166" t="n">
-        <v>10.3093919754028</v>
+        <v>10.3093929290771</v>
       </c>
       <c r="H166" t="n">
         <v>155</v>
@@ -5270,7 +5270,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G169" t="n">
-        <v>9.30582332611084</v>
+        <v>9.30582237243652</v>
       </c>
       <c r="H169" t="n">
         <v>1233</v>
@@ -5589,7 +5589,7 @@
         <v>8.75</v>
       </c>
       <c r="G180" t="n">
-        <v>7.98293685913086</v>
+        <v>7.9829363822937</v>
       </c>
       <c r="H180" t="n">
         <v>2549</v>
@@ -5676,7 +5676,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G183" t="n">
-        <v>7.57238531112671</v>
+        <v>7.57238578796387</v>
       </c>
       <c r="H183" t="n">
         <v>4185</v>
@@ -5705,7 +5705,7 @@
         <v>8.5</v>
       </c>
       <c r="G184" t="n">
-        <v>7.75485229492188</v>
+        <v>7.75485277175903</v>
       </c>
       <c r="H184" t="n">
         <v>1189</v>
@@ -5734,7 +5734,7 @@
         <v>8.60999965667725</v>
       </c>
       <c r="G185" t="n">
-        <v>7.85520887374878</v>
+        <v>7.85520839691162</v>
       </c>
       <c r="H185" t="n">
         <v>840</v>
@@ -5763,7 +5763,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G186" t="n">
-        <v>8.0285530090332</v>
+        <v>8.02855396270752</v>
       </c>
       <c r="H186" t="n">
         <v>820</v>
@@ -5792,7 +5792,7 @@
         <v>9.01000022888184</v>
       </c>
       <c r="G187" t="n">
-        <v>8.22014427185059</v>
+        <v>8.22014331817627</v>
       </c>
       <c r="H187" t="n">
         <v>2520</v>
@@ -5995,7 +5995,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G194" t="n">
-        <v>7.73660564422607</v>
+        <v>7.73660516738892</v>
       </c>
       <c r="H194" t="n">
         <v>727</v>
@@ -6082,7 +6082,7 @@
         <v>8.25</v>
       </c>
       <c r="G197" t="n">
-        <v>7.52676820755005</v>
+        <v>7.52676868438721</v>
       </c>
       <c r="H197" t="n">
         <v>444</v>
@@ -6227,7 +6227,7 @@
         <v>8.60999965667725</v>
       </c>
       <c r="G202" t="n">
-        <v>7.85520887374878</v>
+        <v>7.85520839691162</v>
       </c>
       <c r="H202" t="n">
         <v>924</v>
@@ -6256,7 +6256,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G203" t="n">
-        <v>7.8825798034668</v>
+        <v>7.88257932662964</v>
       </c>
       <c r="H203" t="n">
         <v>60</v>
@@ -6285,7 +6285,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G204" t="n">
-        <v>7.8825798034668</v>
+        <v>7.88257932662964</v>
       </c>
       <c r="H204" t="n">
         <v>0</v>
@@ -6314,7 +6314,7 @@
         <v>8.60999965667725</v>
       </c>
       <c r="G205" t="n">
-        <v>7.85520887374878</v>
+        <v>7.85520839691162</v>
       </c>
       <c r="H205" t="n">
         <v>460</v>
@@ -6488,7 +6488,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G211" t="n">
-        <v>7.97381258010864</v>
+        <v>7.9738130569458</v>
       </c>
       <c r="H211" t="n">
         <v>53910</v>
@@ -6517,7 +6517,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G212" t="n">
-        <v>8.08329296112061</v>
+        <v>8.08329200744629</v>
       </c>
       <c r="H212" t="n">
         <v>173</v>
@@ -6546,7 +6546,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G213" t="n">
-        <v>8.0285530090332</v>
+        <v>8.02855396270752</v>
       </c>
       <c r="H213" t="n">
         <v>11079</v>
@@ -6749,7 +6749,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G220" t="n">
-        <v>8.22926712036133</v>
+        <v>8.22926807403564</v>
       </c>
       <c r="H220" t="n">
         <v>1062</v>
@@ -6778,7 +6778,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G221" t="n">
-        <v>8.22926712036133</v>
+        <v>8.22926807403564</v>
       </c>
       <c r="H221" t="n">
         <v>0</v>
@@ -6807,7 +6807,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G222" t="n">
-        <v>8.22926712036133</v>
+        <v>8.22926807403564</v>
       </c>
       <c r="H222" t="n">
         <v>0</v>
@@ -6836,7 +6836,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G223" t="n">
-        <v>8.32050037384033</v>
+        <v>8.32049942016602</v>
       </c>
       <c r="H223" t="n">
         <v>50</v>
@@ -6865,7 +6865,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G224" t="n">
-        <v>8.32050037384033</v>
+        <v>8.32049942016602</v>
       </c>
       <c r="H224" t="n">
         <v>0</v>
@@ -6894,7 +6894,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G225" t="n">
-        <v>8.32050037384033</v>
+        <v>8.32049942016602</v>
       </c>
       <c r="H225" t="n">
         <v>0</v>
@@ -6923,7 +6923,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G226" t="n">
-        <v>8.32050037384033</v>
+        <v>8.32049942016602</v>
       </c>
       <c r="H226" t="n">
         <v>0</v>
@@ -6952,7 +6952,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G227" t="n">
-        <v>8.41173362731934</v>
+        <v>8.41173458099365</v>
       </c>
       <c r="H227" t="n">
         <v>475</v>
@@ -7010,7 +7010,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G229" t="n">
-        <v>8.57595443725586</v>
+        <v>8.57595348358154</v>
       </c>
       <c r="H229" t="n">
         <v>7583</v>
@@ -7213,7 +7213,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G236" t="n">
-        <v>8.98650550842285</v>
+        <v>8.98650646209717</v>
       </c>
       <c r="H236" t="n">
         <v>2302</v>
@@ -7387,7 +7387,7 @@
         <v>9.63000011444092</v>
       </c>
       <c r="G242" t="n">
-        <v>8.78579139709473</v>
+        <v>8.78579235076904</v>
       </c>
       <c r="H242" t="n">
         <v>348</v>
@@ -7416,7 +7416,7 @@
         <v>9.63000011444092</v>
       </c>
       <c r="G243" t="n">
-        <v>8.78579139709473</v>
+        <v>8.78579235076904</v>
       </c>
       <c r="H243" t="n">
         <v>0</v>
@@ -7445,7 +7445,7 @@
         <v>9.63000011444092</v>
       </c>
       <c r="G244" t="n">
-        <v>8.78579139709473</v>
+        <v>8.78579235076904</v>
       </c>
       <c r="H244" t="n">
         <v>0</v>
@@ -7474,7 +7474,7 @@
         <v>9.63000011444092</v>
       </c>
       <c r="G245" t="n">
-        <v>8.78579139709473</v>
+        <v>8.78579235076904</v>
       </c>
       <c r="H245" t="n">
         <v>0</v>
@@ -7532,7 +7532,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G247" t="n">
-        <v>9.03212261199951</v>
+        <v>9.0321216583252</v>
       </c>
       <c r="H247" t="n">
         <v>200</v>
@@ -7561,7 +7561,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G248" t="n">
-        <v>9.03212261199951</v>
+        <v>9.0321216583252</v>
       </c>
       <c r="H248" t="n">
         <v>0</v>
@@ -7851,7 +7851,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G258" t="n">
-        <v>9.03212261199951</v>
+        <v>9.0321216583252</v>
       </c>
       <c r="H258" t="n">
         <v>300</v>
@@ -7938,7 +7938,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G261" t="n">
-        <v>9.01387500762939</v>
+        <v>9.01387596130371</v>
       </c>
       <c r="H261" t="n">
         <v>519</v>
@@ -8112,7 +8112,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G267" t="n">
-        <v>8.98650550842285</v>
+        <v>8.98650646209717</v>
       </c>
       <c r="H267" t="n">
         <v>2750</v>
@@ -8286,7 +8286,7 @@
         <v>8.92000007629395</v>
       </c>
       <c r="G273" t="n">
-        <v>8.13803291320801</v>
+        <v>8.13803386688232</v>
       </c>
       <c r="H273" t="n">
         <v>1470</v>
@@ -8315,7 +8315,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G274" t="n">
-        <v>8.30225467681885</v>
+        <v>8.30225372314453</v>
       </c>
       <c r="H274" t="n">
         <v>709</v>
@@ -8402,7 +8402,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G277" t="n">
-        <v>8.30225467681885</v>
+        <v>8.30225372314453</v>
       </c>
       <c r="H277" t="n">
         <v>1757</v>
@@ -8489,7 +8489,7 @@
         <v>8.72999954223633</v>
       </c>
       <c r="G280" t="n">
-        <v>7.96468925476074</v>
+        <v>7.9646897315979</v>
       </c>
       <c r="H280" t="n">
         <v>1620</v>
@@ -8547,7 +8547,7 @@
         <v>8.90999984741211</v>
       </c>
       <c r="G282" t="n">
-        <v>8.12890911102295</v>
+        <v>8.12891006469727</v>
       </c>
       <c r="H282" t="n">
         <v>2446</v>
@@ -8576,7 +8576,7 @@
         <v>8.77000045776367</v>
       </c>
       <c r="G283" t="n">
-        <v>8.00118350982666</v>
+        <v>8.00118446350098</v>
       </c>
       <c r="H283" t="n">
         <v>2377</v>
@@ -8924,7 +8924,7 @@
         <v>9.27000045776367</v>
       </c>
       <c r="G295" t="n">
-        <v>8.45735168457031</v>
+        <v>8.457350730896</v>
       </c>
       <c r="H295" t="n">
         <v>260</v>
@@ -9127,7 +9127,7 @@
         <v>8.86999988555908</v>
       </c>
       <c r="G302" t="n">
-        <v>8.09241676330566</v>
+        <v>8.09241580963135</v>
       </c>
       <c r="H302" t="n">
         <v>2131</v>
@@ -9185,7 +9185,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G304" t="n">
-        <v>8.0285530090332</v>
+        <v>8.02855396270752</v>
       </c>
       <c r="H304" t="n">
         <v>300</v>
@@ -9214,7 +9214,7 @@
         <v>8.8100004196167</v>
       </c>
       <c r="G305" t="n">
-        <v>8.03767681121826</v>
+        <v>8.03767776489258</v>
       </c>
       <c r="H305" t="n">
         <v>836</v>
@@ -9243,7 +9243,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G306" t="n">
-        <v>8.25663661956787</v>
+        <v>8.25663757324219</v>
       </c>
       <c r="H306" t="n">
         <v>320</v>
@@ -9330,7 +9330,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G309" t="n">
-        <v>8.19277381896973</v>
+        <v>8.19277286529541</v>
       </c>
       <c r="H309" t="n">
         <v>191</v>
@@ -9359,7 +9359,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G310" t="n">
-        <v>8.22926712036133</v>
+        <v>8.22926807403564</v>
       </c>
       <c r="H310" t="n">
         <v>1</v>
@@ -9388,7 +9388,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G311" t="n">
-        <v>8.22926712036133</v>
+        <v>8.22926807403564</v>
       </c>
       <c r="H311" t="n">
         <v>0</v>
@@ -9417,7 +9417,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G312" t="n">
-        <v>8.22926712036133</v>
+        <v>8.22926807403564</v>
       </c>
       <c r="H312" t="n">
         <v>0</v>
@@ -9446,7 +9446,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G313" t="n">
-        <v>8.41173362731934</v>
+        <v>8.41173458099365</v>
       </c>
       <c r="H313" t="n">
         <v>269</v>
@@ -9475,7 +9475,7 @@
         <v>9.01000022888184</v>
       </c>
       <c r="G314" t="n">
-        <v>8.22014427185059</v>
+        <v>8.22014331817627</v>
       </c>
       <c r="H314" t="n">
         <v>680</v>
@@ -9504,7 +9504,7 @@
         <v>9.01000022888184</v>
       </c>
       <c r="G315" t="n">
-        <v>8.22014427185059</v>
+        <v>8.22014331817627</v>
       </c>
       <c r="H315" t="n">
         <v>0</v>
@@ -9533,7 +9533,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G316" t="n">
-        <v>8.0285530090332</v>
+        <v>8.02855396270752</v>
       </c>
       <c r="H316" t="n">
         <v>3343</v>
@@ -9562,7 +9562,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G317" t="n">
-        <v>8.0285530090332</v>
+        <v>8.02855396270752</v>
       </c>
       <c r="H317" t="n">
         <v>180</v>
@@ -9591,7 +9591,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G318" t="n">
-        <v>8.0285530090332</v>
+        <v>8.02855396270752</v>
       </c>
       <c r="H318" t="n">
         <v>78630</v>
@@ -9620,7 +9620,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G319" t="n">
-        <v>7.95556688308716</v>
+        <v>7.95556640625</v>
       </c>
       <c r="H319" t="n">
         <v>5536</v>
@@ -9794,7 +9794,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G325" t="n">
-        <v>8.22926712036133</v>
+        <v>8.22926807403564</v>
       </c>
       <c r="H325" t="n">
         <v>72</v>
@@ -9823,7 +9823,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G326" t="n">
-        <v>8.22926712036133</v>
+        <v>8.22926807403564</v>
       </c>
       <c r="H326" t="n">
         <v>0</v>
@@ -9852,7 +9852,7 @@
         <v>8.92000007629395</v>
       </c>
       <c r="G327" t="n">
-        <v>8.13803291320801</v>
+        <v>8.13803386688232</v>
       </c>
       <c r="H327" t="n">
         <v>200</v>
@@ -10113,7 +10113,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G336" t="n">
-        <v>8.41173362731934</v>
+        <v>8.41173458099365</v>
       </c>
       <c r="H336" t="n">
         <v>10609</v>
@@ -10200,7 +10200,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G339" t="n">
-        <v>7.53589248657227</v>
+        <v>7.53589200973511</v>
       </c>
       <c r="H339" t="n">
         <v>74770</v>
@@ -10229,7 +10229,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G340" t="n">
-        <v>7.57238531112671</v>
+        <v>7.57238578796387</v>
       </c>
       <c r="H340" t="n">
         <v>7020</v>
@@ -10287,7 +10287,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G342" t="n">
-        <v>7.37167167663574</v>
+        <v>7.37167119979858</v>
       </c>
       <c r="H342" t="n">
         <v>18625</v>
@@ -10316,7 +10316,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G343" t="n">
-        <v>7.40816497802734</v>
+        <v>7.40816450119019</v>
       </c>
       <c r="H343" t="n">
         <v>500</v>
@@ -10374,7 +10374,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G345" t="n">
-        <v>7.33517789840698</v>
+        <v>7.33517837524414</v>
       </c>
       <c r="H345" t="n">
         <v>3152</v>
@@ -10432,7 +10432,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G347" t="n">
-        <v>7.53589248657227</v>
+        <v>7.53589200973511</v>
       </c>
       <c r="H347" t="n">
         <v>1406</v>
@@ -10461,7 +10461,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G348" t="n">
-        <v>7.42641162872314</v>
+        <v>7.4264121055603</v>
       </c>
       <c r="H348" t="n">
         <v>803</v>
@@ -10490,7 +10490,7 @@
         <v>8</v>
       </c>
       <c r="G349" t="n">
-        <v>7.29868507385254</v>
+        <v>7.29868459701538</v>
       </c>
       <c r="H349" t="n">
         <v>1</v>
@@ -10519,7 +10519,7 @@
         <v>8</v>
       </c>
       <c r="G350" t="n">
-        <v>7.29868507385254</v>
+        <v>7.29868459701538</v>
       </c>
       <c r="H350" t="n">
         <v>0</v>
@@ -10548,7 +10548,7 @@
         <v>8</v>
       </c>
       <c r="G351" t="n">
-        <v>7.29868507385254</v>
+        <v>7.29868459701538</v>
       </c>
       <c r="H351" t="n">
         <v>1051</v>
@@ -10606,7 +10606,7 @@
         <v>8</v>
       </c>
       <c r="G353" t="n">
-        <v>7.29868507385254</v>
+        <v>7.29868459701538</v>
       </c>
       <c r="H353" t="n">
         <v>501</v>
@@ -10635,7 +10635,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G354" t="n">
-        <v>7.20745134353638</v>
+        <v>7.20745182037354</v>
       </c>
       <c r="H354" t="n">
         <v>2421</v>
@@ -10751,7 +10751,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G358" t="n">
-        <v>7.11621809005737</v>
+        <v>7.11621761322021</v>
       </c>
       <c r="H358" t="n">
         <v>653</v>
@@ -10780,7 +10780,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G359" t="n">
-        <v>7.11621809005737</v>
+        <v>7.11621761322021</v>
       </c>
       <c r="H359" t="n">
         <v>0</v>
@@ -10809,7 +10809,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G360" t="n">
-        <v>7.11621809005737</v>
+        <v>7.11621761322021</v>
       </c>
       <c r="H360" t="n">
         <v>0</v>
@@ -10838,7 +10838,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G361" t="n">
-        <v>7.11621809005737</v>
+        <v>7.11621761322021</v>
       </c>
       <c r="H361" t="n">
         <v>0</v>
@@ -11302,7 +11302,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G377" t="n">
-        <v>7.11621809005737</v>
+        <v>7.11621761322021</v>
       </c>
       <c r="H377" t="n">
         <v>2656</v>
@@ -11505,7 +11505,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G384" t="n">
-        <v>6.91550397872925</v>
+        <v>6.91550350189209</v>
       </c>
       <c r="H384" t="n">
         <v>502</v>
@@ -11534,7 +11534,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G385" t="n">
-        <v>6.91550397872925</v>
+        <v>6.91550350189209</v>
       </c>
       <c r="H385" t="n">
         <v>100</v>
@@ -11563,7 +11563,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G386" t="n">
-        <v>6.91550397872925</v>
+        <v>6.91550350189209</v>
       </c>
       <c r="H386" t="n">
         <v>0</v>
@@ -11592,7 +11592,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G387" t="n">
-        <v>6.91550397872925</v>
+        <v>6.91550350189209</v>
       </c>
       <c r="H387" t="n">
         <v>500</v>
@@ -11650,7 +11650,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G389" t="n">
-        <v>7.17095804214478</v>
+        <v>7.17095756530762</v>
       </c>
       <c r="H389" t="n">
         <v>7937</v>
@@ -11679,7 +11679,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G390" t="n">
-        <v>7.3899188041687</v>
+        <v>7.38991832733154</v>
       </c>
       <c r="H390" t="n">
         <v>4671</v>
@@ -11708,7 +11708,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G391" t="n">
-        <v>7.59063148498535</v>
+        <v>7.59063243865967</v>
       </c>
       <c r="H391" t="n">
         <v>1808</v>
@@ -11737,7 +11737,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G392" t="n">
-        <v>7.57238531112671</v>
+        <v>7.57238578796387</v>
       </c>
       <c r="H392" t="n">
         <v>630</v>
@@ -11766,7 +11766,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G393" t="n">
-        <v>7.57238531112671</v>
+        <v>7.57238578796387</v>
       </c>
       <c r="H393" t="n">
         <v>0</v>
@@ -11795,7 +11795,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G394" t="n">
-        <v>7.57238531112671</v>
+        <v>7.57238578796387</v>
       </c>
       <c r="H394" t="n">
         <v>100</v>
@@ -11824,7 +11824,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G395" t="n">
-        <v>7.57238531112671</v>
+        <v>7.57238578796387</v>
       </c>
       <c r="H395" t="n">
         <v>24200</v>
@@ -11853,7 +11853,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G396" t="n">
-        <v>7.57238531112671</v>
+        <v>7.57238578796387</v>
       </c>
       <c r="H396" t="n">
         <v>0</v>
@@ -11940,7 +11940,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G399" t="n">
-        <v>7.40816497802734</v>
+        <v>7.40816450119019</v>
       </c>
       <c r="H399" t="n">
         <v>350</v>
@@ -12056,7 +12056,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G403" t="n">
-        <v>7.49939918518066</v>
+        <v>7.49939870834351</v>
       </c>
       <c r="H403" t="n">
         <v>750</v>
@@ -12143,7 +12143,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G406" t="n">
-        <v>7.33517789840698</v>
+        <v>7.33517837524414</v>
       </c>
       <c r="H406" t="n">
         <v>3302</v>
@@ -12172,7 +12172,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G407" t="n">
-        <v>7.33517789840698</v>
+        <v>7.33517837524414</v>
       </c>
       <c r="H407" t="n">
         <v>0</v>
@@ -12201,7 +12201,7 @@
         <v>8</v>
       </c>
       <c r="G408" t="n">
-        <v>7.29868507385254</v>
+        <v>7.29868459701538</v>
       </c>
       <c r="H408" t="n">
         <v>1100</v>
@@ -12230,7 +12230,7 @@
         <v>8</v>
       </c>
       <c r="G409" t="n">
-        <v>7.29868507385254</v>
+        <v>7.29868459701538</v>
       </c>
       <c r="H409" t="n">
         <v>4000</v>
@@ -12259,7 +12259,7 @@
         <v>8</v>
       </c>
       <c r="G410" t="n">
-        <v>7.29868507385254</v>
+        <v>7.29868459701538</v>
       </c>
       <c r="H410" t="n">
         <v>0</v>
@@ -12317,7 +12317,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G412" t="n">
-        <v>7.42641162872314</v>
+        <v>7.4264121055603</v>
       </c>
       <c r="H412" t="n">
         <v>161</v>
@@ -12346,7 +12346,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G413" t="n">
-        <v>7.40816497802734</v>
+        <v>7.40816450119019</v>
       </c>
       <c r="H413" t="n">
         <v>1600</v>
@@ -12375,7 +12375,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G414" t="n">
-        <v>7.44465827941895</v>
+        <v>7.4446587562561</v>
       </c>
       <c r="H414" t="n">
         <v>210</v>
@@ -12404,7 +12404,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G415" t="n">
-        <v>7.44465827941895</v>
+        <v>7.4446587562561</v>
       </c>
       <c r="H415" t="n">
         <v>0</v>
@@ -12433,7 +12433,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G416" t="n">
-        <v>7.42641162872314</v>
+        <v>7.4264121055603</v>
       </c>
       <c r="H416" t="n">
         <v>1900</v>
@@ -12462,7 +12462,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G417" t="n">
-        <v>7.40816497802734</v>
+        <v>7.40816450119019</v>
       </c>
       <c r="H417" t="n">
         <v>4309</v>
@@ -12578,7 +12578,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G421" t="n">
-        <v>7.4629054069519</v>
+        <v>7.46290588378906</v>
       </c>
       <c r="H421" t="n">
         <v>870</v>
@@ -12665,7 +12665,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G424" t="n">
-        <v>7.44465827941895</v>
+        <v>7.4446587562561</v>
       </c>
       <c r="H424" t="n">
         <v>2000</v>
@@ -12723,7 +12723,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G426" t="n">
-        <v>7.79134654998779</v>
+        <v>7.79134607315063</v>
       </c>
       <c r="H426" t="n">
         <v>3239</v>
@@ -12752,7 +12752,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G427" t="n">
-        <v>7.8825798034668</v>
+        <v>7.88257932662964</v>
       </c>
       <c r="H427" t="n">
         <v>41</v>
@@ -12781,7 +12781,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G428" t="n">
-        <v>7.73660564422607</v>
+        <v>7.73660516738892</v>
       </c>
       <c r="H428" t="n">
         <v>4521</v>
@@ -12810,7 +12810,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G429" t="n">
-        <v>7.66361808776855</v>
+        <v>7.66361856460571</v>
       </c>
       <c r="H429" t="n">
         <v>1230</v>
@@ -12839,7 +12839,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G430" t="n">
-        <v>7.66361808776855</v>
+        <v>7.66361856460571</v>
       </c>
       <c r="H430" t="n">
         <v>0</v>
@@ -12955,7 +12955,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G434" t="n">
-        <v>7.4629054069519</v>
+        <v>7.46290588378906</v>
       </c>
       <c r="H434" t="n">
         <v>565</v>
@@ -13071,7 +13071,7 @@
         <v>8</v>
       </c>
       <c r="G438" t="n">
-        <v>7.29868507385254</v>
+        <v>7.29868459701538</v>
       </c>
       <c r="H438" t="n">
         <v>810</v>
@@ -13100,7 +13100,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G439" t="n">
-        <v>6.91550397872925</v>
+        <v>6.91550350189209</v>
       </c>
       <c r="H439" t="n">
         <v>5180</v>
@@ -13564,7 +13564,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G455" t="n">
-        <v>6.58706283569336</v>
+        <v>6.5870623588562</v>
       </c>
       <c r="H455" t="n">
         <v>200</v>
@@ -13796,7 +13796,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G463" t="n">
-        <v>6.5323224067688</v>
+        <v>6.53232288360596</v>
       </c>
       <c r="H463" t="n">
         <v>800</v>
@@ -13825,7 +13825,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G464" t="n">
-        <v>6.5688157081604</v>
+        <v>6.56881618499756</v>
       </c>
       <c r="H464" t="n">
         <v>4878</v>
@@ -13854,7 +13854,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G465" t="n">
-        <v>6.5688157081604</v>
+        <v>6.56881618499756</v>
       </c>
       <c r="H465" t="n">
         <v>2702</v>
@@ -13883,7 +13883,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G466" t="n">
-        <v>6.5688157081604</v>
+        <v>6.56881618499756</v>
       </c>
       <c r="H466" t="n">
         <v>0</v>
@@ -13912,7 +13912,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G467" t="n">
-        <v>6.5688157081604</v>
+        <v>6.56881618499756</v>
       </c>
       <c r="H467" t="n">
         <v>0</v>
@@ -13941,7 +13941,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G468" t="n">
-        <v>6.5688157081604</v>
+        <v>6.56881618499756</v>
       </c>
       <c r="H468" t="n">
         <v>0</v>
@@ -13970,7 +13970,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G469" t="n">
-        <v>6.44108867645264</v>
+        <v>6.44108915328979</v>
       </c>
       <c r="H469" t="n">
         <v>3100</v>
@@ -14028,7 +14028,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G471" t="n">
-        <v>6.29511547088623</v>
+        <v>6.29511594772339</v>
       </c>
       <c r="H471" t="n">
         <v>882</v>
@@ -14057,7 +14057,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G472" t="n">
-        <v>6.49582958221436</v>
+        <v>6.4958291053772</v>
       </c>
       <c r="H472" t="n">
         <v>1050</v>
@@ -14115,7 +14115,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G474" t="n">
-        <v>6.29511547088623</v>
+        <v>6.29511594772339</v>
       </c>
       <c r="H474" t="n">
         <v>120</v>
@@ -14202,7 +14202,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G477" t="n">
-        <v>6.5323224067688</v>
+        <v>6.53232288360596</v>
       </c>
       <c r="H477" t="n">
         <v>160</v>
@@ -14231,7 +14231,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G478" t="n">
-        <v>6.73303651809692</v>
+        <v>6.73303699493408</v>
       </c>
       <c r="H478" t="n">
         <v>1030</v>
@@ -14260,7 +14260,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G479" t="n">
-        <v>6.73303651809692</v>
+        <v>6.73303699493408</v>
       </c>
       <c r="H479" t="n">
         <v>0</v>
@@ -14289,7 +14289,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G480" t="n">
-        <v>6.73303651809692</v>
+        <v>6.73303699493408</v>
       </c>
       <c r="H480" t="n">
         <v>0</v>
@@ -14318,7 +14318,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G481" t="n">
-        <v>6.73303651809692</v>
+        <v>6.73303699493408</v>
       </c>
       <c r="H481" t="n">
         <v>0</v>
@@ -14347,7 +14347,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G482" t="n">
-        <v>6.73303651809692</v>
+        <v>6.73303699493408</v>
       </c>
       <c r="H482" t="n">
         <v>0</v>
@@ -14376,7 +14376,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G483" t="n">
-        <v>6.73303651809692</v>
+        <v>6.73303699493408</v>
       </c>
       <c r="H483" t="n">
         <v>0</v>
@@ -14405,7 +14405,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G484" t="n">
-        <v>6.58706283569336</v>
+        <v>6.5870623588562</v>
       </c>
       <c r="H484" t="n">
         <v>1565</v>
@@ -14434,7 +14434,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G485" t="n">
-        <v>6.58706283569336</v>
+        <v>6.5870623588562</v>
       </c>
       <c r="H485" t="n">
         <v>0</v>
@@ -14463,7 +14463,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G486" t="n">
-        <v>6.58706283569336</v>
+        <v>6.5870623588562</v>
       </c>
       <c r="H486" t="n">
         <v>0</v>
@@ -14579,7 +14579,7 @@
         <v>8</v>
       </c>
       <c r="G490" t="n">
-        <v>7.29868507385254</v>
+        <v>7.29868459701538</v>
       </c>
       <c r="H490" t="n">
         <v>1281</v>
@@ -14608,7 +14608,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G491" t="n">
-        <v>7.18920421600342</v>
+        <v>7.18920469284058</v>
       </c>
       <c r="H491" t="n">
         <v>1500</v>
@@ -14637,7 +14637,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G492" t="n">
-        <v>7.20745134353638</v>
+        <v>7.20745182037354</v>
       </c>
       <c r="H492" t="n">
         <v>1450</v>
@@ -14666,7 +14666,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G493" t="n">
-        <v>7.22569751739502</v>
+        <v>7.22569799423218</v>
       </c>
       <c r="H493" t="n">
         <v>800</v>
@@ -14695,7 +14695,7 @@
         <v>7.78000020980835</v>
       </c>
       <c r="G494" t="n">
-        <v>7.09797048568726</v>
+        <v>7.09797096252441</v>
       </c>
       <c r="H494" t="n">
         <v>600</v>
@@ -14724,7 +14724,7 @@
         <v>7.78000020980835</v>
       </c>
       <c r="G495" t="n">
-        <v>7.09797048568726</v>
+        <v>7.09797096252441</v>
       </c>
       <c r="H495" t="n">
         <v>0</v>
@@ -14753,7 +14753,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G496" t="n">
-        <v>7.15271139144897</v>
+        <v>7.15271091461182</v>
       </c>
       <c r="H496" t="n">
         <v>1106</v>
@@ -14869,7 +14869,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G500" t="n">
-        <v>7.42641162872314</v>
+        <v>7.4264121055603</v>
       </c>
       <c r="H500" t="n">
         <v>595</v>
@@ -14927,7 +14927,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G502" t="n">
-        <v>7.33517789840698</v>
+        <v>7.33517837524414</v>
       </c>
       <c r="H502" t="n">
         <v>517</v>
@@ -14956,7 +14956,7 @@
         <v>8</v>
       </c>
       <c r="G503" t="n">
-        <v>7.29868507385254</v>
+        <v>7.29868459701538</v>
       </c>
       <c r="H503" t="n">
         <v>2647</v>
@@ -14985,7 +14985,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G504" t="n">
-        <v>7.37167167663574</v>
+        <v>7.37167119979858</v>
       </c>
       <c r="H504" t="n">
         <v>1968</v>
@@ -15014,7 +15014,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G505" t="n">
-        <v>7.33517789840698</v>
+        <v>7.33517837524414</v>
       </c>
       <c r="H505" t="n">
         <v>731</v>
@@ -15043,7 +15043,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G506" t="n">
-        <v>7.33517789840698</v>
+        <v>7.33517837524414</v>
       </c>
       <c r="H506" t="n">
         <v>300</v>
@@ -15101,7 +15101,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G508" t="n">
-        <v>7.37167167663574</v>
+        <v>7.37167119979858</v>
       </c>
       <c r="H508" t="n">
         <v>1681</v>
@@ -15130,7 +15130,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G509" t="n">
-        <v>7.37167167663574</v>
+        <v>7.37167119979858</v>
       </c>
       <c r="H509" t="n">
         <v>0</v>
@@ -15159,7 +15159,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G510" t="n">
-        <v>7.37167167663574</v>
+        <v>7.37167119979858</v>
       </c>
       <c r="H510" t="n">
         <v>0</v>
@@ -15188,7 +15188,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G511" t="n">
-        <v>7.20745134353638</v>
+        <v>7.20745182037354</v>
       </c>
       <c r="H511" t="n">
         <v>221</v>
@@ -15246,7 +15246,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G513" t="n">
-        <v>7.20745134353638</v>
+        <v>7.20745182037354</v>
       </c>
       <c r="H513" t="n">
         <v>900</v>
@@ -15507,7 +15507,7 @@
         <v>7.42000007629395</v>
       </c>
       <c r="G522" t="n">
-        <v>6.76952981948853</v>
+        <v>6.76953029632568</v>
       </c>
       <c r="H522" t="n">
         <v>100</v>
@@ -15536,7 +15536,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G523" t="n">
-        <v>6.73303651809692</v>
+        <v>6.73303699493408</v>
       </c>
       <c r="H523" t="n">
         <v>740</v>
@@ -15565,7 +15565,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G524" t="n">
-        <v>6.73303651809692</v>
+        <v>6.73303699493408</v>
       </c>
       <c r="H524" t="n">
         <v>1680</v>
@@ -15681,7 +15681,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G528" t="n">
-        <v>7.13446474075317</v>
+        <v>7.13446426391602</v>
       </c>
       <c r="H528" t="n">
         <v>12040</v>
@@ -15739,7 +15739,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G530" t="n">
-        <v>7.17095804214478</v>
+        <v>7.17095756530762</v>
       </c>
       <c r="H530" t="n">
         <v>2115</v>
@@ -15913,7 +15913,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G536" t="n">
-        <v>7.3899188041687</v>
+        <v>7.38991832733154</v>
       </c>
       <c r="H536" t="n">
         <v>18461</v>
@@ -15942,7 +15942,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G537" t="n">
-        <v>7.18920421600342</v>
+        <v>7.18920469284058</v>
       </c>
       <c r="H537" t="n">
         <v>29589</v>
@@ -15971,7 +15971,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G538" t="n">
-        <v>7.13446474075317</v>
+        <v>7.13446426391602</v>
       </c>
       <c r="H538" t="n">
         <v>2732</v>
@@ -16000,7 +16000,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G539" t="n">
-        <v>7.20745134353638</v>
+        <v>7.20745182037354</v>
       </c>
       <c r="H539" t="n">
         <v>3149</v>
@@ -16029,7 +16029,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G540" t="n">
-        <v>7.20745134353638</v>
+        <v>7.20745182037354</v>
       </c>
       <c r="H540" t="n">
         <v>0</v>
@@ -16058,7 +16058,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G541" t="n">
-        <v>7.15271139144897</v>
+        <v>7.15271091461182</v>
       </c>
       <c r="H541" t="n">
         <v>2212</v>
@@ -16087,7 +16087,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G542" t="n">
-        <v>7.15271139144897</v>
+        <v>7.15271091461182</v>
       </c>
       <c r="H542" t="n">
         <v>1250</v>
@@ -16116,7 +16116,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G543" t="n">
-        <v>7.13446474075317</v>
+        <v>7.13446426391602</v>
       </c>
       <c r="H543" t="n">
         <v>6467</v>
@@ -16174,7 +16174,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G545" t="n">
-        <v>7.20745134353638</v>
+        <v>7.20745182037354</v>
       </c>
       <c r="H545" t="n">
         <v>13099</v>
@@ -16203,7 +16203,7 @@
         <v>8</v>
       </c>
       <c r="G546" t="n">
-        <v>7.29868507385254</v>
+        <v>7.29868459701538</v>
       </c>
       <c r="H546" t="n">
         <v>12524</v>
@@ -16261,7 +16261,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G548" t="n">
-        <v>7.3899188041687</v>
+        <v>7.38991832733154</v>
       </c>
       <c r="H548" t="n">
         <v>1200</v>
@@ -16319,7 +16319,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G550" t="n">
-        <v>7.49939918518066</v>
+        <v>7.49939870834351</v>
       </c>
       <c r="H550" t="n">
         <v>4760</v>
@@ -16377,7 +16377,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G552" t="n">
-        <v>7.66361808776855</v>
+        <v>7.66361856460571</v>
       </c>
       <c r="H552" t="n">
         <v>2734</v>
@@ -16406,7 +16406,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G553" t="n">
-        <v>7.68186616897583</v>
+        <v>7.68186521530151</v>
       </c>
       <c r="H553" t="n">
         <v>4691</v>
@@ -16435,7 +16435,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G554" t="n">
-        <v>7.57238531112671</v>
+        <v>7.57238578796387</v>
       </c>
       <c r="H554" t="n">
         <v>1776</v>
@@ -16464,7 +16464,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G555" t="n">
-        <v>7.57238531112671</v>
+        <v>7.57238578796387</v>
       </c>
       <c r="H555" t="n">
         <v>733</v>
@@ -16493,7 +16493,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G556" t="n">
-        <v>7.68186616897583</v>
+        <v>7.68186521530151</v>
       </c>
       <c r="H556" t="n">
         <v>409</v>
@@ -16609,7 +16609,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G560" t="n">
-        <v>7.66361808776855</v>
+        <v>7.66361856460571</v>
       </c>
       <c r="H560" t="n">
         <v>3325</v>
@@ -16638,7 +16638,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G561" t="n">
-        <v>7.66361808776855</v>
+        <v>7.66361856460571</v>
       </c>
       <c r="H561" t="n">
         <v>0</v>
@@ -16667,7 +16667,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G562" t="n">
-        <v>7.66361808776855</v>
+        <v>7.66361856460571</v>
       </c>
       <c r="H562" t="n">
         <v>978</v>
@@ -16928,7 +16928,7 @@
         <v>8.25</v>
       </c>
       <c r="G571" t="n">
-        <v>7.52676820755005</v>
+        <v>7.52676868438721</v>
       </c>
       <c r="H571" t="n">
         <v>2468</v>
@@ -16957,7 +16957,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G572" t="n">
-        <v>7.43553495407104</v>
+        <v>7.43553447723389</v>
       </c>
       <c r="H572" t="n">
         <v>3030</v>
@@ -16986,7 +16986,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G573" t="n">
-        <v>7.43553495407104</v>
+        <v>7.43553447723389</v>
       </c>
       <c r="H573" t="n">
         <v>0</v>
@@ -17015,7 +17015,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G574" t="n">
-        <v>7.43553495407104</v>
+        <v>7.43553447723389</v>
       </c>
       <c r="H574" t="n">
         <v>3363</v>
@@ -17044,7 +17044,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G575" t="n">
-        <v>7.43553495407104</v>
+        <v>7.43553447723389</v>
       </c>
       <c r="H575" t="n">
         <v>1531</v>
@@ -17102,7 +17102,7 @@
         <v>8.25</v>
       </c>
       <c r="G577" t="n">
-        <v>7.52676820755005</v>
+        <v>7.52676868438721</v>
       </c>
       <c r="H577" t="n">
         <v>10687</v>
@@ -17131,7 +17131,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G578" t="n">
-        <v>7.25306797027588</v>
+        <v>7.25306749343872</v>
       </c>
       <c r="H578" t="n">
         <v>14460</v>
@@ -17160,7 +17160,7 @@
         <v>8</v>
       </c>
       <c r="G579" t="n">
-        <v>7.29868507385254</v>
+        <v>7.29868459701538</v>
       </c>
       <c r="H579" t="n">
         <v>2771</v>
@@ -17218,7 +17218,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G581" t="n">
-        <v>7.3899188041687</v>
+        <v>7.38991832733154</v>
       </c>
       <c r="H581" t="n">
         <v>540</v>
@@ -17334,7 +17334,7 @@
         <v>8.25</v>
       </c>
       <c r="G585" t="n">
-        <v>7.52676820755005</v>
+        <v>7.52676868438721</v>
       </c>
       <c r="H585" t="n">
         <v>1560</v>
@@ -17363,7 +17363,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G586" t="n">
-        <v>7.3899188041687</v>
+        <v>7.38991832733154</v>
       </c>
       <c r="H586" t="n">
         <v>3341</v>
@@ -17392,7 +17392,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G587" t="n">
-        <v>7.3899188041687</v>
+        <v>7.38991832733154</v>
       </c>
       <c r="H587" t="n">
         <v>340</v>
@@ -17421,7 +17421,7 @@
         <v>8</v>
       </c>
       <c r="G588" t="n">
-        <v>7.29868507385254</v>
+        <v>7.29868459701538</v>
       </c>
       <c r="H588" t="n">
         <v>110</v>
@@ -17450,7 +17450,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G589" t="n">
-        <v>7.3899188041687</v>
+        <v>7.38991832733154</v>
       </c>
       <c r="H589" t="n">
         <v>1325</v>
@@ -17479,7 +17479,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G590" t="n">
-        <v>7.3899188041687</v>
+        <v>7.38991832733154</v>
       </c>
       <c r="H590" t="n">
         <v>851</v>
@@ -17508,7 +17508,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G591" t="n">
-        <v>7.3899188041687</v>
+        <v>7.38991832733154</v>
       </c>
       <c r="H591" t="n">
         <v>22104</v>
@@ -17537,7 +17537,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G592" t="n">
-        <v>7.3899188041687</v>
+        <v>7.38991832733154</v>
       </c>
       <c r="H592" t="n">
         <v>0</v>
@@ -17624,7 +17624,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G595" t="n">
-        <v>7.43553495407104</v>
+        <v>7.43553447723389</v>
       </c>
       <c r="H595" t="n">
         <v>1851</v>
@@ -17653,7 +17653,7 @@
         <v>8</v>
       </c>
       <c r="G596" t="n">
-        <v>7.29868507385254</v>
+        <v>7.29868459701538</v>
       </c>
       <c r="H596" t="n">
         <v>17310</v>
@@ -17682,7 +17682,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G597" t="n">
-        <v>7.43553495407104</v>
+        <v>7.43553447723389</v>
       </c>
       <c r="H597" t="n">
         <v>3661</v>
@@ -17740,7 +17740,7 @@
         <v>8</v>
       </c>
       <c r="G599" t="n">
-        <v>7.29868507385254</v>
+        <v>7.29868459701538</v>
       </c>
       <c r="H599" t="n">
         <v>11533</v>
@@ -17769,7 +17769,7 @@
         <v>8</v>
       </c>
       <c r="G600" t="n">
-        <v>7.29868507385254</v>
+        <v>7.29868459701538</v>
       </c>
       <c r="H600" t="n">
         <v>6728</v>
@@ -17856,7 +17856,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G603" t="n">
-        <v>7.25306797027588</v>
+        <v>7.25306749343872</v>
       </c>
       <c r="H603" t="n">
         <v>19392</v>
@@ -18523,7 +18523,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G626" t="n">
-        <v>7.77841663360596</v>
+        <v>7.7784161567688</v>
       </c>
       <c r="H626" t="n">
         <v>9091</v>
@@ -18668,7 +18668,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G631" t="n">
-        <v>7.77841663360596</v>
+        <v>7.7784161567688</v>
       </c>
       <c r="H631" t="n">
         <v>1834</v>
@@ -18755,7 +18755,7 @@
         <v>8.25</v>
       </c>
       <c r="G634" t="n">
-        <v>7.82584571838379</v>
+        <v>7.82584619522095</v>
       </c>
       <c r="H634" t="n">
         <v>811</v>
@@ -18784,7 +18784,7 @@
         <v>8.25</v>
       </c>
       <c r="G635" t="n">
-        <v>7.82584571838379</v>
+        <v>7.82584619522095</v>
       </c>
       <c r="H635" t="n">
         <v>4580</v>
@@ -18813,7 +18813,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G636" t="n">
-        <v>7.77841663360596</v>
+        <v>7.7784161567688</v>
       </c>
       <c r="H636" t="n">
         <v>2333</v>
@@ -19016,7 +19016,7 @@
         <v>8.25</v>
       </c>
       <c r="G643" t="n">
-        <v>7.82584571838379</v>
+        <v>7.82584619522095</v>
       </c>
       <c r="H643" t="n">
         <v>200</v>
@@ -19045,7 +19045,7 @@
         <v>8.25</v>
       </c>
       <c r="G644" t="n">
-        <v>7.82584571838379</v>
+        <v>7.82584619522095</v>
       </c>
       <c r="H644" t="n">
         <v>0</v>
@@ -19074,7 +19074,7 @@
         <v>8.25</v>
       </c>
       <c r="G645" t="n">
-        <v>7.82584571838379</v>
+        <v>7.82584619522095</v>
       </c>
       <c r="H645" t="n">
         <v>350</v>
@@ -19103,7 +19103,7 @@
         <v>8.25</v>
       </c>
       <c r="G646" t="n">
-        <v>7.82584571838379</v>
+        <v>7.82584619522095</v>
       </c>
       <c r="H646" t="n">
         <v>925</v>
@@ -19132,7 +19132,7 @@
         <v>8.25</v>
       </c>
       <c r="G647" t="n">
-        <v>7.82584571838379</v>
+        <v>7.82584619522095</v>
       </c>
       <c r="H647" t="n">
         <v>41854</v>
@@ -21278,7 +21278,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G721" t="n">
-        <v>6.68754100799561</v>
+        <v>6.68754148483276</v>
       </c>
       <c r="H721" t="n">
         <v>4498</v>
@@ -21510,7 +21510,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G729" t="n">
-        <v>6.68754100799561</v>
+        <v>6.68754148483276</v>
       </c>
       <c r="H729" t="n">
         <v>10666</v>
@@ -21655,7 +21655,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G734" t="n">
-        <v>6.35553550720215</v>
+        <v>6.35553503036499</v>
       </c>
       <c r="H734" t="n">
         <v>3775</v>
@@ -22177,7 +22177,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G752" t="n">
-        <v>6.68754100799561</v>
+        <v>6.68754148483276</v>
       </c>
       <c r="H752" t="n">
         <v>210</v>
@@ -22206,7 +22206,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G753" t="n">
-        <v>6.68754100799561</v>
+        <v>6.68754148483276</v>
       </c>
       <c r="H753" t="n">
         <v>0</v>
@@ -22264,7 +22264,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G755" t="n">
-        <v>6.68754100799561</v>
+        <v>6.68754148483276</v>
       </c>
       <c r="H755" t="n">
         <v>2600</v>
@@ -22351,7 +22351,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G758" t="n">
-        <v>6.68754100799561</v>
+        <v>6.68754148483276</v>
       </c>
       <c r="H758" t="n">
         <v>1000</v>
@@ -22380,7 +22380,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G759" t="n">
-        <v>6.68754100799561</v>
+        <v>6.68754148483276</v>
       </c>
       <c r="H759" t="n">
         <v>2199</v>
@@ -23018,7 +23018,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G781" t="n">
-        <v>7.77841663360596</v>
+        <v>7.7784161567688</v>
       </c>
       <c r="H781" t="n">
         <v>3468</v>
@@ -23076,7 +23076,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G783" t="n">
-        <v>7.92070436477661</v>
+        <v>7.92070484161377</v>
       </c>
       <c r="H783" t="n">
         <v>6694</v>
@@ -24062,7 +24062,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G817" t="n">
-        <v>6.68754100799561</v>
+        <v>6.68754148483276</v>
       </c>
       <c r="H817" t="n">
         <v>4357</v>
@@ -24120,7 +24120,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G819" t="n">
-        <v>6.68754100799561</v>
+        <v>6.68754148483276</v>
       </c>
       <c r="H819" t="n">
         <v>800</v>
@@ -24265,7 +24265,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G824" t="n">
-        <v>6.26067638397217</v>
+        <v>6.26067686080933</v>
       </c>
       <c r="H824" t="n">
         <v>2695</v>
@@ -24294,7 +24294,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G825" t="n">
-        <v>6.39347887039185</v>
+        <v>6.39347839355469</v>
       </c>
       <c r="H825" t="n">
         <v>1450</v>
@@ -24439,7 +24439,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G830" t="n">
-        <v>6.94365978240967</v>
+        <v>6.94365930557251</v>
       </c>
       <c r="H830" t="n">
         <v>604</v>
@@ -24584,7 +24584,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G835" t="n">
-        <v>6.77291393280029</v>
+        <v>6.77291345596313</v>
       </c>
       <c r="H835" t="n">
         <v>609</v>
@@ -24613,7 +24613,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G836" t="n">
-        <v>6.77291393280029</v>
+        <v>6.77291345596313</v>
       </c>
       <c r="H836" t="n">
         <v>0</v>
@@ -24671,7 +24671,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G838" t="n">
-        <v>7.2472071647644</v>
+        <v>7.24720764160156</v>
       </c>
       <c r="H838" t="n">
         <v>21285</v>
@@ -24932,7 +24932,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G847" t="n">
-        <v>7.22823524475098</v>
+        <v>7.22823572158813</v>
       </c>
       <c r="H847" t="n">
         <v>3902</v>
@@ -24961,7 +24961,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G848" t="n">
-        <v>7.2472071647644</v>
+        <v>7.24720764160156</v>
       </c>
       <c r="H848" t="n">
         <v>750</v>
@@ -25077,7 +25077,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G852" t="n">
-        <v>7.22823524475098</v>
+        <v>7.22823572158813</v>
       </c>
       <c r="H852" t="n">
         <v>4126</v>
@@ -25222,7 +25222,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G857" t="n">
-        <v>7.77841663360596</v>
+        <v>7.7784161567688</v>
       </c>
       <c r="H857" t="n">
         <v>16854</v>
@@ -25280,7 +25280,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G859" t="n">
-        <v>7.77841663360596</v>
+        <v>7.7784161567688</v>
       </c>
       <c r="H859" t="n">
         <v>1217</v>
@@ -25454,7 +25454,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G865" t="n">
-        <v>7.89224624633789</v>
+        <v>7.89224672317505</v>
       </c>
       <c r="H865" t="n">
         <v>27334</v>
@@ -35581,6 +35581,35 @@
         <v>2501</v>
       </c>
       <c r="I1214" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1215">
+      <c r="A1215" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1215" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C1215" t="n">
+        <v>7.80000019073486</v>
+      </c>
+      <c r="D1215" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1215" t="n">
+        <v>7.53999996185303</v>
+      </c>
+      <c r="F1215" t="n">
+        <v>8</v>
+      </c>
+      <c r="G1215" t="n">
+        <v>8</v>
+      </c>
+      <c r="H1215" t="n">
+        <v>2163</v>
+      </c>
+      <c r="I1215" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SVS.MI.xlsx
+++ b/data/SVS.MI.xlsx
@@ -427,7 +427,7 @@
         <v>14.7600002288818</v>
       </c>
       <c r="G2" t="n">
-        <v>13.4660739898682</v>
+        <v>13.4660730361938</v>
       </c>
       <c r="H2" t="n">
         <v>1300</v>
@@ -485,7 +485,7 @@
         <v>14.7799997329712</v>
       </c>
       <c r="G4" t="n">
-        <v>13.4843196868896</v>
+        <v>13.484320640564</v>
       </c>
       <c r="H4" t="n">
         <v>3133</v>
@@ -659,7 +659,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G10" t="n">
-        <v>12.5902318954468</v>
+        <v>12.5902309417725</v>
       </c>
       <c r="H10" t="n">
         <v>670</v>
@@ -688,7 +688,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G11" t="n">
-        <v>12.5902318954468</v>
+        <v>12.5902309417725</v>
       </c>
       <c r="H11" t="n">
         <v>13315</v>
@@ -804,7 +804,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G15" t="n">
-        <v>12.7544507980347</v>
+        <v>12.754451751709</v>
       </c>
       <c r="H15" t="n">
         <v>2068</v>
@@ -949,7 +949,7 @@
         <v>13.6800003051758</v>
       </c>
       <c r="G20" t="n">
-        <v>12.4807510375977</v>
+        <v>12.480751991272</v>
       </c>
       <c r="H20" t="n">
         <v>2647</v>
@@ -978,7 +978,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G21" t="n">
-        <v>12.4077634811401</v>
+        <v>12.4077644348145</v>
       </c>
       <c r="H21" t="n">
         <v>2900</v>
@@ -1123,7 +1123,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G26" t="n">
-        <v>11.9698419570923</v>
+        <v>11.9698429107666</v>
       </c>
       <c r="H26" t="n">
         <v>4682</v>
@@ -1181,7 +1181,7 @@
         <v>13</v>
       </c>
       <c r="G28" t="n">
-        <v>11.8603630065918</v>
+        <v>11.8603620529175</v>
       </c>
       <c r="H28" t="n">
         <v>2250</v>
@@ -1355,7 +1355,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G34" t="n">
-        <v>11.20348072052</v>
+        <v>11.2034816741943</v>
       </c>
       <c r="H34" t="n">
         <v>7092</v>
@@ -1413,7 +1413,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G36" t="n">
-        <v>10.5830936431885</v>
+        <v>10.5830926895142</v>
       </c>
       <c r="H36" t="n">
         <v>6892</v>
@@ -1471,7 +1471,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G38" t="n">
-        <v>10.5830936431885</v>
+        <v>10.5830926895142</v>
       </c>
       <c r="H38" t="n">
         <v>1246</v>
@@ -1587,7 +1587,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G42" t="n">
-        <v>9.76199054718018</v>
+        <v>9.76199150085449</v>
       </c>
       <c r="H42" t="n">
         <v>550</v>
@@ -1616,7 +1616,7 @@
         <v>10.7600002288818</v>
       </c>
       <c r="G43" t="n">
-        <v>9.81673240661621</v>
+        <v>9.81673145294189</v>
       </c>
       <c r="H43" t="n">
         <v>1169</v>
@@ -1645,7 +1645,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G44" t="n">
-        <v>10.2181577682495</v>
+        <v>10.2181587219238</v>
       </c>
       <c r="H44" t="n">
         <v>1100</v>
@@ -1674,7 +1674,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G45" t="n">
-        <v>10.9845199584961</v>
+        <v>10.9845209121704</v>
       </c>
       <c r="H45" t="n">
         <v>67981</v>
@@ -1790,7 +1790,7 @@
         <v>13</v>
       </c>
       <c r="G49" t="n">
-        <v>11.8603630065918</v>
+        <v>11.8603620529175</v>
       </c>
       <c r="H49" t="n">
         <v>2500</v>
@@ -1819,7 +1819,7 @@
         <v>13</v>
       </c>
       <c r="G50" t="n">
-        <v>11.8603630065918</v>
+        <v>11.8603620529175</v>
       </c>
       <c r="H50" t="n">
         <v>220</v>
@@ -2109,7 +2109,7 @@
         <v>13.039999961853</v>
       </c>
       <c r="G60" t="n">
-        <v>11.8968553543091</v>
+        <v>11.8968563079834</v>
       </c>
       <c r="H60" t="n">
         <v>411</v>
@@ -2138,7 +2138,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G61" t="n">
-        <v>11.4954280853271</v>
+        <v>11.4954290390015</v>
       </c>
       <c r="H61" t="n">
         <v>400</v>
@@ -2167,7 +2167,7 @@
         <v>13</v>
       </c>
       <c r="G62" t="n">
-        <v>11.8603630065918</v>
+        <v>11.8603620529175</v>
       </c>
       <c r="H62" t="n">
         <v>4800</v>
@@ -2196,7 +2196,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G63" t="n">
-        <v>11.4954280853271</v>
+        <v>11.4954290390015</v>
       </c>
       <c r="H63" t="n">
         <v>490</v>
@@ -2254,7 +2254,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G65" t="n">
-        <v>11.4406881332397</v>
+        <v>11.4406871795654</v>
       </c>
       <c r="H65" t="n">
         <v>360</v>
@@ -2312,7 +2312,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G67" t="n">
-        <v>11.5866622924805</v>
+        <v>11.5866613388062</v>
       </c>
       <c r="H67" t="n">
         <v>2052</v>
@@ -2341,7 +2341,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G68" t="n">
-        <v>11.1304931640625</v>
+        <v>11.1304941177368</v>
       </c>
       <c r="H68" t="n">
         <v>700</v>
@@ -2370,7 +2370,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G69" t="n">
-        <v>11.9698419570923</v>
+        <v>11.9698429107666</v>
       </c>
       <c r="H69" t="n">
         <v>660</v>
@@ -2457,7 +2457,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G72" t="n">
-        <v>11.2217273712158</v>
+        <v>11.2217283248901</v>
       </c>
       <c r="H72" t="n">
         <v>850</v>
@@ -2631,7 +2631,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G78" t="n">
-        <v>10.8932857513428</v>
+        <v>10.8932867050171</v>
       </c>
       <c r="H78" t="n">
         <v>100</v>
@@ -2660,7 +2660,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G79" t="n">
-        <v>10.8020544052124</v>
+        <v>10.8020534515381</v>
       </c>
       <c r="H79" t="n">
         <v>950</v>
@@ -2689,7 +2689,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G80" t="n">
-        <v>10.5648469924927</v>
+        <v>10.5648460388184</v>
       </c>
       <c r="H80" t="n">
         <v>2840</v>
@@ -2747,7 +2747,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G82" t="n">
-        <v>11.2217273712158</v>
+        <v>11.2217283248901</v>
       </c>
       <c r="H82" t="n">
         <v>2400</v>
@@ -2805,7 +2805,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G84" t="n">
-        <v>10.2181577682495</v>
+        <v>10.2181587219238</v>
       </c>
       <c r="H84" t="n">
         <v>1810</v>
@@ -2834,7 +2834,7 @@
         <v>11.5</v>
       </c>
       <c r="G85" t="n">
-        <v>10.4918584823608</v>
+        <v>10.4918594360352</v>
       </c>
       <c r="H85" t="n">
         <v>1710</v>
@@ -2892,7 +2892,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G87" t="n">
-        <v>10.3276395797729</v>
+        <v>10.3276386260986</v>
       </c>
       <c r="H87" t="n">
         <v>13938</v>
@@ -3037,7 +3037,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G92" t="n">
-        <v>10.5648469924927</v>
+        <v>10.5648460388184</v>
       </c>
       <c r="H92" t="n">
         <v>1190</v>
@@ -3066,7 +3066,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G93" t="n">
-        <v>10.5648469924927</v>
+        <v>10.5648460388184</v>
       </c>
       <c r="H93" t="n">
         <v>150</v>
@@ -3124,7 +3124,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G95" t="n">
-        <v>10.5648469924927</v>
+        <v>10.5648460388184</v>
       </c>
       <c r="H95" t="n">
         <v>1620</v>
@@ -3153,7 +3153,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G96" t="n">
-        <v>10.5648469924927</v>
+        <v>10.5648460388184</v>
       </c>
       <c r="H96" t="n">
         <v>7278</v>
@@ -3182,7 +3182,7 @@
         <v>11.5</v>
       </c>
       <c r="G97" t="n">
-        <v>10.4918584823608</v>
+        <v>10.4918594360352</v>
       </c>
       <c r="H97" t="n">
         <v>16862</v>
@@ -3240,7 +3240,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G99" t="n">
-        <v>10.2181577682495</v>
+        <v>10.2181587219238</v>
       </c>
       <c r="H99" t="n">
         <v>1423</v>
@@ -3298,7 +3298,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G101" t="n">
-        <v>10.5648469924927</v>
+        <v>10.5648460388184</v>
       </c>
       <c r="H101" t="n">
         <v>4205</v>
@@ -3414,7 +3414,7 @@
         <v>11.7799997329712</v>
       </c>
       <c r="G105" t="n">
-        <v>10.7473125457764</v>
+        <v>10.7473134994507</v>
       </c>
       <c r="H105" t="n">
         <v>2174</v>
@@ -3443,7 +3443,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G106" t="n">
-        <v>10.3093929290771</v>
+        <v>10.3093919754028</v>
       </c>
       <c r="H106" t="n">
         <v>1804</v>
@@ -3501,7 +3501,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G108" t="n">
-        <v>9.94445705413818</v>
+        <v>9.9444580078125</v>
       </c>
       <c r="H108" t="n">
         <v>4150</v>
@@ -3530,7 +3530,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G109" t="n">
-        <v>10.2181577682495</v>
+        <v>10.2181587219238</v>
       </c>
       <c r="H109" t="n">
         <v>310</v>
@@ -3559,7 +3559,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G110" t="n">
-        <v>10.2181577682495</v>
+        <v>10.2181587219238</v>
       </c>
       <c r="H110" t="n">
         <v>260</v>
@@ -3588,7 +3588,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G111" t="n">
-        <v>10.2181577682495</v>
+        <v>10.2181587219238</v>
       </c>
       <c r="H111" t="n">
         <v>317</v>
@@ -3617,7 +3617,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G112" t="n">
-        <v>9.8532247543335</v>
+        <v>9.85322380065918</v>
       </c>
       <c r="H112" t="n">
         <v>600</v>
@@ -3704,7 +3704,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G115" t="n">
-        <v>10.2728986740112</v>
+        <v>10.2728996276855</v>
       </c>
       <c r="H115" t="n">
         <v>970</v>
@@ -3733,7 +3733,7 @@
         <v>11.5</v>
       </c>
       <c r="G116" t="n">
-        <v>10.4918584823608</v>
+        <v>10.4918594360352</v>
       </c>
       <c r="H116" t="n">
         <v>1595</v>
@@ -3820,7 +3820,7 @@
         <v>11.7799997329712</v>
       </c>
       <c r="G119" t="n">
-        <v>10.7473125457764</v>
+        <v>10.7473134994507</v>
       </c>
       <c r="H119" t="n">
         <v>1393</v>
@@ -3849,7 +3849,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G120" t="n">
-        <v>10.2728986740112</v>
+        <v>10.2728996276855</v>
       </c>
       <c r="H120" t="n">
         <v>3314</v>
@@ -3936,7 +3936,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G123" t="n">
-        <v>10.2546510696411</v>
+        <v>10.2546520233154</v>
       </c>
       <c r="H123" t="n">
         <v>923</v>
@@ -4081,7 +4081,7 @@
         <v>11.039999961853</v>
       </c>
       <c r="G128" t="n">
-        <v>10.0721855163574</v>
+        <v>10.0721845626831</v>
       </c>
       <c r="H128" t="n">
         <v>5476</v>
@@ -4110,7 +4110,7 @@
         <v>11.039999961853</v>
       </c>
       <c r="G129" t="n">
-        <v>10.0721855163574</v>
+        <v>10.0721845626831</v>
       </c>
       <c r="H129" t="n">
         <v>0</v>
@@ -4458,7 +4458,7 @@
         <v>11.2799997329712</v>
       </c>
       <c r="G141" t="n">
-        <v>10.2911462783813</v>
+        <v>10.291145324707</v>
       </c>
       <c r="H141" t="n">
         <v>250</v>
@@ -4516,7 +4516,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G143" t="n">
-        <v>10.2728986740112</v>
+        <v>10.2728996276855</v>
       </c>
       <c r="H143" t="n">
         <v>354</v>
@@ -4545,7 +4545,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G144" t="n">
-        <v>9.94445705413818</v>
+        <v>9.9444580078125</v>
       </c>
       <c r="H144" t="n">
         <v>9773</v>
@@ -4632,7 +4632,7 @@
         <v>11.2799997329712</v>
       </c>
       <c r="G147" t="n">
-        <v>10.2911462783813</v>
+        <v>10.291145324707</v>
       </c>
       <c r="H147" t="n">
         <v>780</v>
@@ -4661,7 +4661,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G148" t="n">
-        <v>10.3093929290771</v>
+        <v>10.3093919754028</v>
       </c>
       <c r="H148" t="n">
         <v>480</v>
@@ -4951,7 +4951,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G158" t="n">
-        <v>9.94445705413818</v>
+        <v>9.9444580078125</v>
       </c>
       <c r="H158" t="n">
         <v>320</v>
@@ -5009,7 +5009,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G160" t="n">
-        <v>9.94445705413818</v>
+        <v>9.9444580078125</v>
       </c>
       <c r="H160" t="n">
         <v>220</v>
@@ -5038,7 +5038,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G161" t="n">
-        <v>9.94445705413818</v>
+        <v>9.9444580078125</v>
       </c>
       <c r="H161" t="n">
         <v>1909</v>
@@ -5067,7 +5067,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G162" t="n">
-        <v>9.8532247543335</v>
+        <v>9.85322380065918</v>
       </c>
       <c r="H162" t="n">
         <v>559</v>
@@ -5183,7 +5183,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G166" t="n">
-        <v>10.3093929290771</v>
+        <v>10.3093919754028</v>
       </c>
       <c r="H166" t="n">
         <v>155</v>
@@ -5299,7 +5299,7 @@
         <v>10.3400001525879</v>
       </c>
       <c r="G170" t="n">
-        <v>9.43354988098145</v>
+        <v>9.43354892730713</v>
       </c>
       <c r="H170" t="n">
         <v>1910</v>
@@ -5328,7 +5328,7 @@
         <v>10.3400001525879</v>
       </c>
       <c r="G171" t="n">
-        <v>9.43354988098145</v>
+        <v>9.43354892730713</v>
       </c>
       <c r="H171" t="n">
         <v>388</v>
@@ -5386,7 +5386,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G173" t="n">
-        <v>9.47004318237305</v>
+        <v>9.47004413604736</v>
       </c>
       <c r="H173" t="n">
         <v>1</v>
@@ -5531,7 +5531,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G178" t="n">
-        <v>8.50296783447266</v>
+        <v>8.50296688079834</v>
       </c>
       <c r="H178" t="n">
         <v>369</v>
@@ -5676,7 +5676,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G183" t="n">
-        <v>7.57238578796387</v>
+        <v>7.57238531112671</v>
       </c>
       <c r="H183" t="n">
         <v>4185</v>
@@ -5734,7 +5734,7 @@
         <v>8.60999965667725</v>
       </c>
       <c r="G185" t="n">
-        <v>7.85520839691162</v>
+        <v>7.85520887374878</v>
       </c>
       <c r="H185" t="n">
         <v>840</v>
@@ -5792,7 +5792,7 @@
         <v>9.01000022888184</v>
       </c>
       <c r="G187" t="n">
-        <v>8.22014331817627</v>
+        <v>8.22014427185059</v>
       </c>
       <c r="H187" t="n">
         <v>2520</v>
@@ -5850,7 +5850,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G189" t="n">
-        <v>8.27488422393799</v>
+        <v>8.27488327026367</v>
       </c>
       <c r="H189" t="n">
         <v>700</v>
@@ -5966,7 +5966,7 @@
         <v>8.59000015258789</v>
       </c>
       <c r="G193" t="n">
-        <v>7.83696269989014</v>
+        <v>7.83696222305298</v>
       </c>
       <c r="H193" t="n">
         <v>35</v>
@@ -5995,7 +5995,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G194" t="n">
-        <v>7.73660516738892</v>
+        <v>7.73660564422607</v>
       </c>
       <c r="H194" t="n">
         <v>727</v>
@@ -6111,7 +6111,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G198" t="n">
-        <v>7.48115158081055</v>
+        <v>7.48115205764771</v>
       </c>
       <c r="H198" t="n">
         <v>110</v>
@@ -6140,7 +6140,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G199" t="n">
-        <v>7.48115158081055</v>
+        <v>7.48115205764771</v>
       </c>
       <c r="H199" t="n">
         <v>0</v>
@@ -6227,7 +6227,7 @@
         <v>8.60999965667725</v>
       </c>
       <c r="G202" t="n">
-        <v>7.85520839691162</v>
+        <v>7.85520887374878</v>
       </c>
       <c r="H202" t="n">
         <v>924</v>
@@ -6256,7 +6256,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G203" t="n">
-        <v>7.88257932662964</v>
+        <v>7.8825798034668</v>
       </c>
       <c r="H203" t="n">
         <v>60</v>
@@ -6285,7 +6285,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G204" t="n">
-        <v>7.88257932662964</v>
+        <v>7.8825798034668</v>
       </c>
       <c r="H204" t="n">
         <v>0</v>
@@ -6314,7 +6314,7 @@
         <v>8.60999965667725</v>
       </c>
       <c r="G205" t="n">
-        <v>7.85520839691162</v>
+        <v>7.85520887374878</v>
       </c>
       <c r="H205" t="n">
         <v>460</v>
@@ -6488,7 +6488,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G211" t="n">
-        <v>7.9738130569458</v>
+        <v>7.97381258010864</v>
       </c>
       <c r="H211" t="n">
         <v>53910</v>
@@ -6517,7 +6517,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G212" t="n">
-        <v>8.08329200744629</v>
+        <v>8.08329296112061</v>
       </c>
       <c r="H212" t="n">
         <v>173</v>
@@ -6604,7 +6604,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G215" t="n">
-        <v>8.27488422393799</v>
+        <v>8.27488327026367</v>
       </c>
       <c r="H215" t="n">
         <v>8078</v>
@@ -6633,7 +6633,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G216" t="n">
-        <v>8.50296783447266</v>
+        <v>8.50296688079834</v>
       </c>
       <c r="H216" t="n">
         <v>862</v>
@@ -6662,7 +6662,7 @@
         <v>9.39000034332275</v>
       </c>
       <c r="G217" t="n">
-        <v>8.56683158874512</v>
+        <v>8.5668306350708</v>
       </c>
       <c r="H217" t="n">
         <v>520</v>
@@ -6836,7 +6836,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G223" t="n">
-        <v>8.32049942016602</v>
+        <v>8.32050037384033</v>
       </c>
       <c r="H223" t="n">
         <v>50</v>
@@ -6865,7 +6865,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G224" t="n">
-        <v>8.32049942016602</v>
+        <v>8.32050037384033</v>
       </c>
       <c r="H224" t="n">
         <v>0</v>
@@ -6894,7 +6894,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G225" t="n">
-        <v>8.32049942016602</v>
+        <v>8.32050037384033</v>
       </c>
       <c r="H225" t="n">
         <v>0</v>
@@ -6923,7 +6923,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G226" t="n">
-        <v>8.32049942016602</v>
+        <v>8.32050037384033</v>
       </c>
       <c r="H226" t="n">
         <v>0</v>
@@ -7068,7 +7068,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G231" t="n">
-        <v>8.50296783447266</v>
+        <v>8.50296688079834</v>
       </c>
       <c r="H231" t="n">
         <v>330</v>
@@ -7213,7 +7213,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G236" t="n">
-        <v>8.98650646209717</v>
+        <v>8.98650550842285</v>
       </c>
       <c r="H236" t="n">
         <v>2302</v>
@@ -7300,7 +7300,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G239" t="n">
-        <v>8.6215705871582</v>
+        <v>8.62157154083252</v>
       </c>
       <c r="H239" t="n">
         <v>2238</v>
@@ -7387,7 +7387,7 @@
         <v>9.63000011444092</v>
       </c>
       <c r="G242" t="n">
-        <v>8.78579235076904</v>
+        <v>8.78579139709473</v>
       </c>
       <c r="H242" t="n">
         <v>348</v>
@@ -7416,7 +7416,7 @@
         <v>9.63000011444092</v>
       </c>
       <c r="G243" t="n">
-        <v>8.78579235076904</v>
+        <v>8.78579139709473</v>
       </c>
       <c r="H243" t="n">
         <v>0</v>
@@ -7445,7 +7445,7 @@
         <v>9.63000011444092</v>
       </c>
       <c r="G244" t="n">
-        <v>8.78579235076904</v>
+        <v>8.78579139709473</v>
       </c>
       <c r="H244" t="n">
         <v>0</v>
@@ -7474,7 +7474,7 @@
         <v>9.63000011444092</v>
       </c>
       <c r="G245" t="n">
-        <v>8.78579235076904</v>
+        <v>8.78579139709473</v>
       </c>
       <c r="H245" t="n">
         <v>0</v>
@@ -7532,7 +7532,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G247" t="n">
-        <v>9.0321216583252</v>
+        <v>9.03212261199951</v>
       </c>
       <c r="H247" t="n">
         <v>200</v>
@@ -7561,7 +7561,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G248" t="n">
-        <v>9.0321216583252</v>
+        <v>9.03212261199951</v>
       </c>
       <c r="H248" t="n">
         <v>0</v>
@@ -7706,7 +7706,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G253" t="n">
-        <v>9.19634246826172</v>
+        <v>9.19634342193604</v>
       </c>
       <c r="H253" t="n">
         <v>359</v>
@@ -7735,7 +7735,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G254" t="n">
-        <v>9.19634246826172</v>
+        <v>9.19634342193604</v>
       </c>
       <c r="H254" t="n">
         <v>0</v>
@@ -7851,7 +7851,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G258" t="n">
-        <v>9.0321216583252</v>
+        <v>9.03212261199951</v>
       </c>
       <c r="H258" t="n">
         <v>300</v>
@@ -7909,7 +7909,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G260" t="n">
-        <v>8.84965515136719</v>
+        <v>8.84965419769287</v>
       </c>
       <c r="H260" t="n">
         <v>50</v>
@@ -8025,7 +8025,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G264" t="n">
-        <v>8.75842189788818</v>
+        <v>8.7584228515625</v>
       </c>
       <c r="H264" t="n">
         <v>6946</v>
@@ -8112,7 +8112,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G267" t="n">
-        <v>8.98650646209717</v>
+        <v>8.98650550842285</v>
       </c>
       <c r="H267" t="n">
         <v>2750</v>
@@ -8141,7 +8141,7 @@
         <v>9.75</v>
       </c>
       <c r="G268" t="n">
-        <v>8.89527130126953</v>
+        <v>8.89527225494385</v>
       </c>
       <c r="H268" t="n">
         <v>380</v>
@@ -8170,7 +8170,7 @@
         <v>9.75</v>
       </c>
       <c r="G269" t="n">
-        <v>8.89527130126953</v>
+        <v>8.89527225494385</v>
       </c>
       <c r="H269" t="n">
         <v>1149</v>
@@ -8228,7 +8228,7 @@
         <v>9.47000026702881</v>
       </c>
       <c r="G271" t="n">
-        <v>8.63981819152832</v>
+        <v>8.639817237854</v>
       </c>
       <c r="H271" t="n">
         <v>200</v>
@@ -8286,7 +8286,7 @@
         <v>8.92000007629395</v>
       </c>
       <c r="G273" t="n">
-        <v>8.13803386688232</v>
+        <v>8.13803291320801</v>
       </c>
       <c r="H273" t="n">
         <v>1470</v>
@@ -8344,7 +8344,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G275" t="n">
-        <v>8.64894104003906</v>
+        <v>8.64894008636475</v>
       </c>
       <c r="H275" t="n">
         <v>860</v>
@@ -8460,7 +8460,7 @@
         <v>8.71000003814697</v>
       </c>
       <c r="G279" t="n">
-        <v>7.9464430809021</v>
+        <v>7.94644355773926</v>
       </c>
       <c r="H279" t="n">
         <v>7948</v>
@@ -8489,7 +8489,7 @@
         <v>8.72999954223633</v>
       </c>
       <c r="G280" t="n">
-        <v>7.9646897315979</v>
+        <v>7.96469020843506</v>
       </c>
       <c r="H280" t="n">
         <v>1620</v>
@@ -8547,7 +8547,7 @@
         <v>8.90999984741211</v>
       </c>
       <c r="G282" t="n">
-        <v>8.12891006469727</v>
+        <v>8.12890911102295</v>
       </c>
       <c r="H282" t="n">
         <v>2446</v>
@@ -8576,7 +8576,7 @@
         <v>8.77000045776367</v>
       </c>
       <c r="G283" t="n">
-        <v>8.00118446350098</v>
+        <v>8.00118350982666</v>
       </c>
       <c r="H283" t="n">
         <v>2377</v>
@@ -8634,7 +8634,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G285" t="n">
-        <v>8.37524127960205</v>
+        <v>8.37524032592773</v>
       </c>
       <c r="H285" t="n">
         <v>1200</v>
@@ -8721,7 +8721,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G288" t="n">
-        <v>8.27488422393799</v>
+        <v>8.27488327026367</v>
       </c>
       <c r="H288" t="n">
         <v>6201</v>
@@ -8750,7 +8750,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G289" t="n">
-        <v>8.92264175415039</v>
+        <v>8.92264080047607</v>
       </c>
       <c r="H289" t="n">
         <v>1337</v>
@@ -8866,7 +8866,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G293" t="n">
-        <v>8.27488422393799</v>
+        <v>8.27488327026367</v>
       </c>
       <c r="H293" t="n">
         <v>1783</v>
@@ -8895,7 +8895,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G294" t="n">
-        <v>8.50296783447266</v>
+        <v>8.50296688079834</v>
       </c>
       <c r="H294" t="n">
         <v>3394</v>
@@ -8924,7 +8924,7 @@
         <v>9.27000045776367</v>
       </c>
       <c r="G295" t="n">
-        <v>8.457350730896</v>
+        <v>8.45735168457031</v>
       </c>
       <c r="H295" t="n">
         <v>260</v>
@@ -9069,7 +9069,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G300" t="n">
-        <v>8.50296783447266</v>
+        <v>8.50296688079834</v>
       </c>
       <c r="H300" t="n">
         <v>949</v>
@@ -9127,7 +9127,7 @@
         <v>8.86999988555908</v>
       </c>
       <c r="G302" t="n">
-        <v>8.09241580963135</v>
+        <v>8.09241676330566</v>
       </c>
       <c r="H302" t="n">
         <v>2131</v>
@@ -9214,7 +9214,7 @@
         <v>8.8100004196167</v>
       </c>
       <c r="G305" t="n">
-        <v>8.03767776489258</v>
+        <v>8.03767681121826</v>
       </c>
       <c r="H305" t="n">
         <v>836</v>
@@ -9301,7 +9301,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G308" t="n">
-        <v>8.37524127960205</v>
+        <v>8.37524032592773</v>
       </c>
       <c r="H308" t="n">
         <v>99</v>
@@ -9330,7 +9330,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G309" t="n">
-        <v>8.19277286529541</v>
+        <v>8.19277381896973</v>
       </c>
       <c r="H309" t="n">
         <v>191</v>
@@ -9475,7 +9475,7 @@
         <v>9.01000022888184</v>
       </c>
       <c r="G314" t="n">
-        <v>8.22014331817627</v>
+        <v>8.22014427185059</v>
       </c>
       <c r="H314" t="n">
         <v>680</v>
@@ -9504,7 +9504,7 @@
         <v>9.01000022888184</v>
       </c>
       <c r="G315" t="n">
-        <v>8.22014331817627</v>
+        <v>8.22014427185059</v>
       </c>
       <c r="H315" t="n">
         <v>0</v>
@@ -9620,7 +9620,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G319" t="n">
-        <v>7.95556640625</v>
+        <v>7.95556735992432</v>
       </c>
       <c r="H319" t="n">
         <v>5536</v>
@@ -9707,7 +9707,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G322" t="n">
-        <v>8.64894104003906</v>
+        <v>8.64894008636475</v>
       </c>
       <c r="H322" t="n">
         <v>23858</v>
@@ -9852,7 +9852,7 @@
         <v>8.92000007629395</v>
       </c>
       <c r="G327" t="n">
-        <v>8.13803386688232</v>
+        <v>8.13803291320801</v>
       </c>
       <c r="H327" t="n">
         <v>200</v>
@@ -9997,7 +9997,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G332" t="n">
-        <v>8.50296783447266</v>
+        <v>8.50296688079834</v>
       </c>
       <c r="H332" t="n">
         <v>6347</v>
@@ -10026,7 +10026,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G333" t="n">
-        <v>8.75842189788818</v>
+        <v>8.7584228515625</v>
       </c>
       <c r="H333" t="n">
         <v>19786</v>
@@ -10229,7 +10229,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G340" t="n">
-        <v>7.57238578796387</v>
+        <v>7.57238531112671</v>
       </c>
       <c r="H340" t="n">
         <v>7020</v>
@@ -10287,7 +10287,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G342" t="n">
-        <v>7.37167119979858</v>
+        <v>7.37167167663574</v>
       </c>
       <c r="H342" t="n">
         <v>18625</v>
@@ -10316,7 +10316,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G343" t="n">
-        <v>7.40816450119019</v>
+        <v>7.40816497802734</v>
       </c>
       <c r="H343" t="n">
         <v>500</v>
@@ -10374,7 +10374,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G345" t="n">
-        <v>7.33517837524414</v>
+        <v>7.33517789840698</v>
       </c>
       <c r="H345" t="n">
         <v>3152</v>
@@ -10635,7 +10635,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G354" t="n">
-        <v>7.20745182037354</v>
+        <v>7.20745134353638</v>
       </c>
       <c r="H354" t="n">
         <v>2421</v>
@@ -11012,7 +11012,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G367" t="n">
-        <v>6.82427024841309</v>
+        <v>6.82426977157593</v>
       </c>
       <c r="H367" t="n">
         <v>4636</v>
@@ -11476,7 +11476,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G383" t="n">
-        <v>6.97024393081665</v>
+        <v>6.97024345397949</v>
       </c>
       <c r="H383" t="n">
         <v>1600</v>
@@ -11505,7 +11505,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G384" t="n">
-        <v>6.91550350189209</v>
+        <v>6.91550397872925</v>
       </c>
       <c r="H384" t="n">
         <v>502</v>
@@ -11534,7 +11534,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G385" t="n">
-        <v>6.91550350189209</v>
+        <v>6.91550397872925</v>
       </c>
       <c r="H385" t="n">
         <v>100</v>
@@ -11563,7 +11563,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G386" t="n">
-        <v>6.91550350189209</v>
+        <v>6.91550397872925</v>
       </c>
       <c r="H386" t="n">
         <v>0</v>
@@ -11592,7 +11592,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G387" t="n">
-        <v>6.91550350189209</v>
+        <v>6.91550397872925</v>
       </c>
       <c r="H387" t="n">
         <v>500</v>
@@ -11650,7 +11650,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G389" t="n">
-        <v>7.17095756530762</v>
+        <v>7.17095804214478</v>
       </c>
       <c r="H389" t="n">
         <v>7937</v>
@@ -11679,7 +11679,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G390" t="n">
-        <v>7.38991832733154</v>
+        <v>7.3899188041687</v>
       </c>
       <c r="H390" t="n">
         <v>4671</v>
@@ -11708,7 +11708,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G391" t="n">
-        <v>7.59063243865967</v>
+        <v>7.59063148498535</v>
       </c>
       <c r="H391" t="n">
         <v>1808</v>
@@ -11737,7 +11737,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G392" t="n">
-        <v>7.57238578796387</v>
+        <v>7.57238531112671</v>
       </c>
       <c r="H392" t="n">
         <v>630</v>
@@ -11766,7 +11766,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G393" t="n">
-        <v>7.57238578796387</v>
+        <v>7.57238531112671</v>
       </c>
       <c r="H393" t="n">
         <v>0</v>
@@ -11795,7 +11795,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G394" t="n">
-        <v>7.57238578796387</v>
+        <v>7.57238531112671</v>
       </c>
       <c r="H394" t="n">
         <v>100</v>
@@ -11824,7 +11824,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G395" t="n">
-        <v>7.57238578796387</v>
+        <v>7.57238531112671</v>
       </c>
       <c r="H395" t="n">
         <v>24200</v>
@@ -11853,7 +11853,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G396" t="n">
-        <v>7.57238578796387</v>
+        <v>7.57238531112671</v>
       </c>
       <c r="H396" t="n">
         <v>0</v>
@@ -11882,7 +11882,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G397" t="n">
-        <v>7.62712526321411</v>
+        <v>7.62712478637695</v>
       </c>
       <c r="H397" t="n">
         <v>1616</v>
@@ -11911,7 +11911,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G398" t="n">
-        <v>7.62712526321411</v>
+        <v>7.62712478637695</v>
       </c>
       <c r="H398" t="n">
         <v>0</v>
@@ -11940,7 +11940,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G399" t="n">
-        <v>7.40816450119019</v>
+        <v>7.40816497802734</v>
       </c>
       <c r="H399" t="n">
         <v>350</v>
@@ -11998,7 +11998,7 @@
         <v>8.4399995803833</v>
       </c>
       <c r="G401" t="n">
-        <v>7.70011234283447</v>
+        <v>7.70011186599731</v>
       </c>
       <c r="H401" t="n">
         <v>1732</v>
@@ -12027,7 +12027,7 @@
         <v>8.4399995803833</v>
       </c>
       <c r="G402" t="n">
-        <v>7.70011234283447</v>
+        <v>7.70011186599731</v>
       </c>
       <c r="H402" t="n">
         <v>1250</v>
@@ -12085,7 +12085,7 @@
         <v>8.4399995803833</v>
       </c>
       <c r="G404" t="n">
-        <v>7.70011234283447</v>
+        <v>7.70011186599731</v>
       </c>
       <c r="H404" t="n">
         <v>100</v>
@@ -12143,7 +12143,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G406" t="n">
-        <v>7.33517837524414</v>
+        <v>7.33517789840698</v>
       </c>
       <c r="H406" t="n">
         <v>3302</v>
@@ -12172,7 +12172,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G407" t="n">
-        <v>7.33517837524414</v>
+        <v>7.33517789840698</v>
       </c>
       <c r="H407" t="n">
         <v>0</v>
@@ -12288,7 +12288,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G411" t="n">
-        <v>7.48115158081055</v>
+        <v>7.48115205764771</v>
       </c>
       <c r="H411" t="n">
         <v>1500</v>
@@ -12346,7 +12346,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G413" t="n">
-        <v>7.40816450119019</v>
+        <v>7.40816497802734</v>
       </c>
       <c r="H413" t="n">
         <v>1600</v>
@@ -12375,7 +12375,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G414" t="n">
-        <v>7.4446587562561</v>
+        <v>7.44465827941895</v>
       </c>
       <c r="H414" t="n">
         <v>210</v>
@@ -12404,7 +12404,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G415" t="n">
-        <v>7.4446587562561</v>
+        <v>7.44465827941895</v>
       </c>
       <c r="H415" t="n">
         <v>0</v>
@@ -12462,7 +12462,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G417" t="n">
-        <v>7.40816450119019</v>
+        <v>7.40816497802734</v>
       </c>
       <c r="H417" t="n">
         <v>4309</v>
@@ -12491,7 +12491,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G418" t="n">
-        <v>7.48115158081055</v>
+        <v>7.48115205764771</v>
       </c>
       <c r="H418" t="n">
         <v>130</v>
@@ -12520,7 +12520,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G419" t="n">
-        <v>7.48115158081055</v>
+        <v>7.48115205764771</v>
       </c>
       <c r="H419" t="n">
         <v>0</v>
@@ -12549,7 +12549,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G420" t="n">
-        <v>7.48115158081055</v>
+        <v>7.48115205764771</v>
       </c>
       <c r="H420" t="n">
         <v>1975</v>
@@ -12578,7 +12578,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G421" t="n">
-        <v>7.46290588378906</v>
+        <v>7.4629054069519</v>
       </c>
       <c r="H421" t="n">
         <v>870</v>
@@ -12607,7 +12607,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G422" t="n">
-        <v>7.48115158081055</v>
+        <v>7.48115205764771</v>
       </c>
       <c r="H422" t="n">
         <v>1500</v>
@@ -12636,7 +12636,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G423" t="n">
-        <v>7.48115158081055</v>
+        <v>7.48115205764771</v>
       </c>
       <c r="H423" t="n">
         <v>0</v>
@@ -12665,7 +12665,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G424" t="n">
-        <v>7.4446587562561</v>
+        <v>7.44465827941895</v>
       </c>
       <c r="H424" t="n">
         <v>2000</v>
@@ -12723,7 +12723,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G426" t="n">
-        <v>7.79134607315063</v>
+        <v>7.79134559631348</v>
       </c>
       <c r="H426" t="n">
         <v>3239</v>
@@ -12752,7 +12752,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G427" t="n">
-        <v>7.88257932662964</v>
+        <v>7.8825798034668</v>
       </c>
       <c r="H427" t="n">
         <v>41</v>
@@ -12781,7 +12781,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G428" t="n">
-        <v>7.73660516738892</v>
+        <v>7.73660564422607</v>
       </c>
       <c r="H428" t="n">
         <v>4521</v>
@@ -12810,7 +12810,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G429" t="n">
-        <v>7.66361856460571</v>
+        <v>7.66361808776855</v>
       </c>
       <c r="H429" t="n">
         <v>1230</v>
@@ -12839,7 +12839,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G430" t="n">
-        <v>7.66361856460571</v>
+        <v>7.66361808776855</v>
       </c>
       <c r="H430" t="n">
         <v>0</v>
@@ -12926,7 +12926,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G433" t="n">
-        <v>7.48115158081055</v>
+        <v>7.48115205764771</v>
       </c>
       <c r="H433" t="n">
         <v>2702</v>
@@ -12955,7 +12955,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G434" t="n">
-        <v>7.46290588378906</v>
+        <v>7.4629054069519</v>
       </c>
       <c r="H434" t="n">
         <v>565</v>
@@ -12984,7 +12984,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G435" t="n">
-        <v>7.24394464492798</v>
+        <v>7.24394512176514</v>
       </c>
       <c r="H435" t="n">
         <v>3622</v>
@@ -13100,7 +13100,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G439" t="n">
-        <v>6.91550350189209</v>
+        <v>6.91550397872925</v>
       </c>
       <c r="H439" t="n">
         <v>5180</v>
@@ -13216,7 +13216,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G443" t="n">
-        <v>6.75128364562988</v>
+        <v>6.75128316879272</v>
       </c>
       <c r="H443" t="n">
         <v>690</v>
@@ -13245,7 +13245,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G444" t="n">
-        <v>6.75128364562988</v>
+        <v>6.75128316879272</v>
       </c>
       <c r="H444" t="n">
         <v>740</v>
@@ -13274,7 +13274,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G445" t="n">
-        <v>6.78777694702148</v>
+        <v>6.78777647018433</v>
       </c>
       <c r="H445" t="n">
         <v>660</v>
@@ -13303,7 +13303,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G446" t="n">
-        <v>6.78777694702148</v>
+        <v>6.78777647018433</v>
       </c>
       <c r="H446" t="n">
         <v>100</v>
@@ -13332,7 +13332,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G447" t="n">
-        <v>6.82427024841309</v>
+        <v>6.82426977157593</v>
       </c>
       <c r="H447" t="n">
         <v>24314</v>
@@ -13390,7 +13390,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G449" t="n">
-        <v>6.75128364562988</v>
+        <v>6.75128316879272</v>
       </c>
       <c r="H449" t="n">
         <v>1995</v>
@@ -13419,7 +13419,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G450" t="n">
-        <v>6.75128364562988</v>
+        <v>6.75128316879272</v>
       </c>
       <c r="H450" t="n">
         <v>0</v>
@@ -13448,7 +13448,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G451" t="n">
-        <v>6.75128364562988</v>
+        <v>6.75128316879272</v>
       </c>
       <c r="H451" t="n">
         <v>0</v>
@@ -13477,7 +13477,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G452" t="n">
-        <v>6.75128364562988</v>
+        <v>6.75128316879272</v>
       </c>
       <c r="H452" t="n">
         <v>0</v>
@@ -13506,7 +13506,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G453" t="n">
-        <v>6.75128364562988</v>
+        <v>6.75128316879272</v>
       </c>
       <c r="H453" t="n">
         <v>0</v>
@@ -13535,7 +13535,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G454" t="n">
-        <v>6.75128364562988</v>
+        <v>6.75128316879272</v>
       </c>
       <c r="H454" t="n">
         <v>1400</v>
@@ -14028,7 +14028,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G471" t="n">
-        <v>6.29511594772339</v>
+        <v>6.29511547088623</v>
       </c>
       <c r="H471" t="n">
         <v>882</v>
@@ -14057,7 +14057,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G472" t="n">
-        <v>6.4958291053772</v>
+        <v>6.49582958221436</v>
       </c>
       <c r="H472" t="n">
         <v>1050</v>
@@ -14115,7 +14115,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G474" t="n">
-        <v>6.29511594772339</v>
+        <v>6.29511547088623</v>
       </c>
       <c r="H474" t="n">
         <v>120</v>
@@ -14231,7 +14231,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G478" t="n">
-        <v>6.73303699493408</v>
+        <v>6.73303651809692</v>
       </c>
       <c r="H478" t="n">
         <v>1030</v>
@@ -14260,7 +14260,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G479" t="n">
-        <v>6.73303699493408</v>
+        <v>6.73303651809692</v>
       </c>
       <c r="H479" t="n">
         <v>0</v>
@@ -14289,7 +14289,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G480" t="n">
-        <v>6.73303699493408</v>
+        <v>6.73303651809692</v>
       </c>
       <c r="H480" t="n">
         <v>0</v>
@@ -14318,7 +14318,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G481" t="n">
-        <v>6.73303699493408</v>
+        <v>6.73303651809692</v>
       </c>
       <c r="H481" t="n">
         <v>0</v>
@@ -14347,7 +14347,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G482" t="n">
-        <v>6.73303699493408</v>
+        <v>6.73303651809692</v>
       </c>
       <c r="H482" t="n">
         <v>0</v>
@@ -14376,7 +14376,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G483" t="n">
-        <v>6.73303699493408</v>
+        <v>6.73303651809692</v>
       </c>
       <c r="H483" t="n">
         <v>0</v>
@@ -14608,7 +14608,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G491" t="n">
-        <v>7.18920469284058</v>
+        <v>7.18920421600342</v>
       </c>
       <c r="H491" t="n">
         <v>1500</v>
@@ -14637,7 +14637,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G492" t="n">
-        <v>7.20745182037354</v>
+        <v>7.20745134353638</v>
       </c>
       <c r="H492" t="n">
         <v>1450</v>
@@ -14666,7 +14666,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G493" t="n">
-        <v>7.22569799423218</v>
+        <v>7.22569751739502</v>
       </c>
       <c r="H493" t="n">
         <v>800</v>
@@ -14898,7 +14898,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G501" t="n">
-        <v>7.48115158081055</v>
+        <v>7.48115205764771</v>
       </c>
       <c r="H501" t="n">
         <v>1173</v>
@@ -14927,7 +14927,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G502" t="n">
-        <v>7.33517837524414</v>
+        <v>7.33517789840698</v>
       </c>
       <c r="H502" t="n">
         <v>517</v>
@@ -14985,7 +14985,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G504" t="n">
-        <v>7.37167119979858</v>
+        <v>7.37167167663574</v>
       </c>
       <c r="H504" t="n">
         <v>1968</v>
@@ -15014,7 +15014,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G505" t="n">
-        <v>7.33517837524414</v>
+        <v>7.33517789840698</v>
       </c>
       <c r="H505" t="n">
         <v>731</v>
@@ -15043,7 +15043,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G506" t="n">
-        <v>7.33517837524414</v>
+        <v>7.33517789840698</v>
       </c>
       <c r="H506" t="n">
         <v>300</v>
@@ -15101,7 +15101,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G508" t="n">
-        <v>7.37167119979858</v>
+        <v>7.37167167663574</v>
       </c>
       <c r="H508" t="n">
         <v>1681</v>
@@ -15130,7 +15130,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G509" t="n">
-        <v>7.37167119979858</v>
+        <v>7.37167167663574</v>
       </c>
       <c r="H509" t="n">
         <v>0</v>
@@ -15159,7 +15159,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G510" t="n">
-        <v>7.37167119979858</v>
+        <v>7.37167167663574</v>
       </c>
       <c r="H510" t="n">
         <v>0</v>
@@ -15188,7 +15188,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G511" t="n">
-        <v>7.20745182037354</v>
+        <v>7.20745134353638</v>
       </c>
       <c r="H511" t="n">
         <v>221</v>
@@ -15246,7 +15246,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G513" t="n">
-        <v>7.20745182037354</v>
+        <v>7.20745134353638</v>
       </c>
       <c r="H513" t="n">
         <v>900</v>
@@ -15478,7 +15478,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G521" t="n">
-        <v>6.82427024841309</v>
+        <v>6.82426977157593</v>
       </c>
       <c r="H521" t="n">
         <v>13563</v>
@@ -15536,7 +15536,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G523" t="n">
-        <v>6.73303699493408</v>
+        <v>6.73303651809692</v>
       </c>
       <c r="H523" t="n">
         <v>740</v>
@@ -15565,7 +15565,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G524" t="n">
-        <v>6.73303699493408</v>
+        <v>6.73303651809692</v>
       </c>
       <c r="H524" t="n">
         <v>1680</v>
@@ -15594,7 +15594,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G525" t="n">
-        <v>6.82427024841309</v>
+        <v>6.82426977157593</v>
       </c>
       <c r="H525" t="n">
         <v>4481</v>
@@ -15681,7 +15681,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G528" t="n">
-        <v>7.13446426391602</v>
+        <v>7.13446474075317</v>
       </c>
       <c r="H528" t="n">
         <v>12040</v>
@@ -15739,7 +15739,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G530" t="n">
-        <v>7.17095756530762</v>
+        <v>7.17095804214478</v>
       </c>
       <c r="H530" t="n">
         <v>2115</v>
@@ -15913,7 +15913,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G536" t="n">
-        <v>7.38991832733154</v>
+        <v>7.3899188041687</v>
       </c>
       <c r="H536" t="n">
         <v>18461</v>
@@ -15942,7 +15942,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G537" t="n">
-        <v>7.18920469284058</v>
+        <v>7.18920421600342</v>
       </c>
       <c r="H537" t="n">
         <v>29589</v>
@@ -15971,7 +15971,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G538" t="n">
-        <v>7.13446426391602</v>
+        <v>7.13446474075317</v>
       </c>
       <c r="H538" t="n">
         <v>2732</v>
@@ -16000,7 +16000,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G539" t="n">
-        <v>7.20745182037354</v>
+        <v>7.20745134353638</v>
       </c>
       <c r="H539" t="n">
         <v>3149</v>
@@ -16029,7 +16029,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G540" t="n">
-        <v>7.20745182037354</v>
+        <v>7.20745134353638</v>
       </c>
       <c r="H540" t="n">
         <v>0</v>
@@ -16116,7 +16116,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G543" t="n">
-        <v>7.13446426391602</v>
+        <v>7.13446474075317</v>
       </c>
       <c r="H543" t="n">
         <v>6467</v>
@@ -16174,7 +16174,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G545" t="n">
-        <v>7.20745182037354</v>
+        <v>7.20745134353638</v>
       </c>
       <c r="H545" t="n">
         <v>13099</v>
@@ -16232,7 +16232,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G547" t="n">
-        <v>7.48115158081055</v>
+        <v>7.48115205764771</v>
       </c>
       <c r="H547" t="n">
         <v>18284</v>
@@ -16261,7 +16261,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G548" t="n">
-        <v>7.38991832733154</v>
+        <v>7.3899188041687</v>
       </c>
       <c r="H548" t="n">
         <v>1200</v>
@@ -16348,7 +16348,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G551" t="n">
-        <v>7.48115158081055</v>
+        <v>7.48115205764771</v>
       </c>
       <c r="H551" t="n">
         <v>61620</v>
@@ -16377,7 +16377,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G552" t="n">
-        <v>7.66361856460571</v>
+        <v>7.66361808776855</v>
       </c>
       <c r="H552" t="n">
         <v>2734</v>
@@ -16406,7 +16406,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G553" t="n">
-        <v>7.68186521530151</v>
+        <v>7.68186569213867</v>
       </c>
       <c r="H553" t="n">
         <v>4691</v>
@@ -16435,7 +16435,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G554" t="n">
-        <v>7.57238578796387</v>
+        <v>7.57238531112671</v>
       </c>
       <c r="H554" t="n">
         <v>1776</v>
@@ -16464,7 +16464,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G555" t="n">
-        <v>7.57238578796387</v>
+        <v>7.57238531112671</v>
       </c>
       <c r="H555" t="n">
         <v>733</v>
@@ -16493,7 +16493,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G556" t="n">
-        <v>7.68186521530151</v>
+        <v>7.68186569213867</v>
       </c>
       <c r="H556" t="n">
         <v>409</v>
@@ -16522,7 +16522,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G557" t="n">
-        <v>7.62712526321411</v>
+        <v>7.62712478637695</v>
       </c>
       <c r="H557" t="n">
         <v>3160</v>
@@ -16551,7 +16551,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G558" t="n">
-        <v>7.62712526321411</v>
+        <v>7.62712478637695</v>
       </c>
       <c r="H558" t="n">
         <v>0</v>
@@ -16580,7 +16580,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G559" t="n">
-        <v>7.62712526321411</v>
+        <v>7.62712478637695</v>
       </c>
       <c r="H559" t="n">
         <v>0</v>
@@ -16609,7 +16609,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G560" t="n">
-        <v>7.66361856460571</v>
+        <v>7.66361808776855</v>
       </c>
       <c r="H560" t="n">
         <v>3325</v>
@@ -16638,7 +16638,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G561" t="n">
-        <v>7.66361856460571</v>
+        <v>7.66361808776855</v>
       </c>
       <c r="H561" t="n">
         <v>0</v>
@@ -16667,7 +16667,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G562" t="n">
-        <v>7.66361856460571</v>
+        <v>7.66361808776855</v>
       </c>
       <c r="H562" t="n">
         <v>978</v>
@@ -16812,7 +16812,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G567" t="n">
-        <v>7.48115158081055</v>
+        <v>7.48115205764771</v>
       </c>
       <c r="H567" t="n">
         <v>801</v>
@@ -16841,7 +16841,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G568" t="n">
-        <v>7.48115158081055</v>
+        <v>7.48115205764771</v>
       </c>
       <c r="H568" t="n">
         <v>797</v>
@@ -16870,7 +16870,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G569" t="n">
-        <v>7.48115158081055</v>
+        <v>7.48115205764771</v>
       </c>
       <c r="H569" t="n">
         <v>1207</v>
@@ -16899,7 +16899,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G570" t="n">
-        <v>7.48115158081055</v>
+        <v>7.48115205764771</v>
       </c>
       <c r="H570" t="n">
         <v>3300</v>
@@ -17218,7 +17218,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G581" t="n">
-        <v>7.38991832733154</v>
+        <v>7.3899188041687</v>
       </c>
       <c r="H581" t="n">
         <v>540</v>
@@ -17247,7 +17247,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G582" t="n">
-        <v>7.48115158081055</v>
+        <v>7.48115205764771</v>
       </c>
       <c r="H582" t="n">
         <v>30</v>
@@ -17276,7 +17276,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G583" t="n">
-        <v>7.48115158081055</v>
+        <v>7.48115205764771</v>
       </c>
       <c r="H583" t="n">
         <v>604</v>
@@ -17305,7 +17305,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G584" t="n">
-        <v>7.48115158081055</v>
+        <v>7.48115205764771</v>
       </c>
       <c r="H584" t="n">
         <v>0</v>
@@ -17363,7 +17363,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G586" t="n">
-        <v>7.38991832733154</v>
+        <v>7.3899188041687</v>
       </c>
       <c r="H586" t="n">
         <v>3341</v>
@@ -17392,7 +17392,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G587" t="n">
-        <v>7.38991832733154</v>
+        <v>7.3899188041687</v>
       </c>
       <c r="H587" t="n">
         <v>340</v>
@@ -17450,7 +17450,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G589" t="n">
-        <v>7.38991832733154</v>
+        <v>7.3899188041687</v>
       </c>
       <c r="H589" t="n">
         <v>1325</v>
@@ -17479,7 +17479,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G590" t="n">
-        <v>7.38991832733154</v>
+        <v>7.3899188041687</v>
       </c>
       <c r="H590" t="n">
         <v>851</v>
@@ -17508,7 +17508,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G591" t="n">
-        <v>7.38991832733154</v>
+        <v>7.3899188041687</v>
       </c>
       <c r="H591" t="n">
         <v>22104</v>
@@ -17537,7 +17537,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G592" t="n">
-        <v>7.38991832733154</v>
+        <v>7.3899188041687</v>
       </c>
       <c r="H592" t="n">
         <v>0</v>
@@ -18523,7 +18523,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G626" t="n">
-        <v>7.7784161567688</v>
+        <v>7.77841663360596</v>
       </c>
       <c r="H626" t="n">
         <v>9091</v>
@@ -18668,7 +18668,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G631" t="n">
-        <v>7.7784161567688</v>
+        <v>7.77841663360596</v>
       </c>
       <c r="H631" t="n">
         <v>1834</v>
@@ -18755,7 +18755,7 @@
         <v>8.25</v>
       </c>
       <c r="G634" t="n">
-        <v>7.82584619522095</v>
+        <v>7.82584571838379</v>
       </c>
       <c r="H634" t="n">
         <v>811</v>
@@ -18784,7 +18784,7 @@
         <v>8.25</v>
       </c>
       <c r="G635" t="n">
-        <v>7.82584619522095</v>
+        <v>7.82584571838379</v>
       </c>
       <c r="H635" t="n">
         <v>4580</v>
@@ -18813,7 +18813,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G636" t="n">
-        <v>7.7784161567688</v>
+        <v>7.77841663360596</v>
       </c>
       <c r="H636" t="n">
         <v>2333</v>
@@ -19016,7 +19016,7 @@
         <v>8.25</v>
       </c>
       <c r="G643" t="n">
-        <v>7.82584619522095</v>
+        <v>7.82584571838379</v>
       </c>
       <c r="H643" t="n">
         <v>200</v>
@@ -19045,7 +19045,7 @@
         <v>8.25</v>
       </c>
       <c r="G644" t="n">
-        <v>7.82584619522095</v>
+        <v>7.82584571838379</v>
       </c>
       <c r="H644" t="n">
         <v>0</v>
@@ -19074,7 +19074,7 @@
         <v>8.25</v>
       </c>
       <c r="G645" t="n">
-        <v>7.82584619522095</v>
+        <v>7.82584571838379</v>
       </c>
       <c r="H645" t="n">
         <v>350</v>
@@ -19103,7 +19103,7 @@
         <v>8.25</v>
       </c>
       <c r="G646" t="n">
-        <v>7.82584619522095</v>
+        <v>7.82584571838379</v>
       </c>
       <c r="H646" t="n">
         <v>925</v>
@@ -19132,7 +19132,7 @@
         <v>8.25</v>
       </c>
       <c r="G647" t="n">
-        <v>7.82584619522095</v>
+        <v>7.82584571838379</v>
       </c>
       <c r="H647" t="n">
         <v>41854</v>
@@ -21278,7 +21278,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G721" t="n">
-        <v>6.68754148483276</v>
+        <v>6.68754100799561</v>
       </c>
       <c r="H721" t="n">
         <v>4498</v>
@@ -21510,7 +21510,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G729" t="n">
-        <v>6.68754148483276</v>
+        <v>6.68754100799561</v>
       </c>
       <c r="H729" t="n">
         <v>10666</v>
@@ -21655,7 +21655,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G734" t="n">
-        <v>6.35553503036499</v>
+        <v>6.35553550720215</v>
       </c>
       <c r="H734" t="n">
         <v>3775</v>
@@ -22177,7 +22177,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G752" t="n">
-        <v>6.68754148483276</v>
+        <v>6.68754100799561</v>
       </c>
       <c r="H752" t="n">
         <v>210</v>
@@ -22206,7 +22206,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G753" t="n">
-        <v>6.68754148483276</v>
+        <v>6.68754100799561</v>
       </c>
       <c r="H753" t="n">
         <v>0</v>
@@ -22264,7 +22264,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G755" t="n">
-        <v>6.68754148483276</v>
+        <v>6.68754100799561</v>
       </c>
       <c r="H755" t="n">
         <v>2600</v>
@@ -22351,7 +22351,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G758" t="n">
-        <v>6.68754148483276</v>
+        <v>6.68754100799561</v>
       </c>
       <c r="H758" t="n">
         <v>1000</v>
@@ -22380,7 +22380,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G759" t="n">
-        <v>6.68754148483276</v>
+        <v>6.68754100799561</v>
       </c>
       <c r="H759" t="n">
         <v>2199</v>
@@ -23018,7 +23018,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G781" t="n">
-        <v>7.7784161567688</v>
+        <v>7.77841663360596</v>
       </c>
       <c r="H781" t="n">
         <v>3468</v>
@@ -23076,7 +23076,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G783" t="n">
-        <v>7.92070484161377</v>
+        <v>7.92070436477661</v>
       </c>
       <c r="H783" t="n">
         <v>6694</v>
@@ -24062,7 +24062,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G817" t="n">
-        <v>6.68754148483276</v>
+        <v>6.68754100799561</v>
       </c>
       <c r="H817" t="n">
         <v>4357</v>
@@ -24120,7 +24120,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G819" t="n">
-        <v>6.68754148483276</v>
+        <v>6.68754100799561</v>
       </c>
       <c r="H819" t="n">
         <v>800</v>
@@ -24265,7 +24265,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G824" t="n">
-        <v>6.26067686080933</v>
+        <v>6.26067638397217</v>
       </c>
       <c r="H824" t="n">
         <v>2695</v>
@@ -24294,7 +24294,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G825" t="n">
-        <v>6.39347839355469</v>
+        <v>6.39347887039185</v>
       </c>
       <c r="H825" t="n">
         <v>1450</v>
@@ -24439,7 +24439,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G830" t="n">
-        <v>6.94365930557251</v>
+        <v>6.94365978240967</v>
       </c>
       <c r="H830" t="n">
         <v>604</v>
@@ -24584,7 +24584,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G835" t="n">
-        <v>6.77291345596313</v>
+        <v>6.77291393280029</v>
       </c>
       <c r="H835" t="n">
         <v>609</v>
@@ -24613,7 +24613,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G836" t="n">
-        <v>6.77291345596313</v>
+        <v>6.77291393280029</v>
       </c>
       <c r="H836" t="n">
         <v>0</v>
@@ -24671,7 +24671,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G838" t="n">
-        <v>7.24720764160156</v>
+        <v>7.2472071647644</v>
       </c>
       <c r="H838" t="n">
         <v>21285</v>
@@ -24932,7 +24932,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G847" t="n">
-        <v>7.22823572158813</v>
+        <v>7.22823524475098</v>
       </c>
       <c r="H847" t="n">
         <v>3902</v>
@@ -24961,7 +24961,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G848" t="n">
-        <v>7.24720764160156</v>
+        <v>7.2472071647644</v>
       </c>
       <c r="H848" t="n">
         <v>750</v>
@@ -25077,7 +25077,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G852" t="n">
-        <v>7.22823572158813</v>
+        <v>7.22823524475098</v>
       </c>
       <c r="H852" t="n">
         <v>4126</v>
@@ -25222,7 +25222,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G857" t="n">
-        <v>7.7784161567688</v>
+        <v>7.77841663360596</v>
       </c>
       <c r="H857" t="n">
         <v>16854</v>
@@ -25280,7 +25280,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G859" t="n">
-        <v>7.7784161567688</v>
+        <v>7.77841663360596</v>
       </c>
       <c r="H859" t="n">
         <v>1217</v>
@@ -25454,7 +25454,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G865" t="n">
-        <v>7.89224672317505</v>
+        <v>7.89224624633789</v>
       </c>
       <c r="H865" t="n">
         <v>27334</v>
@@ -35610,6 +35610,35 @@
         <v>2163</v>
       </c>
       <c r="I1215" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1216">
+      <c r="A1216" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1216" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C1216" t="n">
+        <v>7.92000007629395</v>
+      </c>
+      <c r="D1216" t="n">
+        <v>8.03999996185303</v>
+      </c>
+      <c r="E1216" t="n">
+        <v>7.71999979019165</v>
+      </c>
+      <c r="F1216" t="n">
+        <v>8.03999996185303</v>
+      </c>
+      <c r="G1216" t="n">
+        <v>8.03999996185303</v>
+      </c>
+      <c r="H1216" t="n">
+        <v>1387</v>
+      </c>
+      <c r="I1216" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SVS.MI.xlsx
+++ b/data/SVS.MI.xlsx
@@ -427,7 +427,7 @@
         <v>14.7600002288818</v>
       </c>
       <c r="G2" t="n">
-        <v>13.4660730361938</v>
+        <v>13.4660739898682</v>
       </c>
       <c r="H2" t="n">
         <v>1300</v>
@@ -485,7 +485,7 @@
         <v>14.7799997329712</v>
       </c>
       <c r="G4" t="n">
-        <v>13.484320640564</v>
+        <v>13.4843196868896</v>
       </c>
       <c r="H4" t="n">
         <v>3133</v>
@@ -514,7 +514,7 @@
         <v>14.5600004196167</v>
       </c>
       <c r="G5" t="n">
-        <v>13.2836065292358</v>
+        <v>13.2836055755615</v>
       </c>
       <c r="H5" t="n">
         <v>2134</v>
@@ -572,7 +572,7 @@
         <v>14.539999961853</v>
       </c>
       <c r="G7" t="n">
-        <v>13.26535987854</v>
+        <v>13.2653589248657</v>
       </c>
       <c r="H7" t="n">
         <v>2735</v>
@@ -891,7 +891,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G18" t="n">
-        <v>12.2252969741821</v>
+        <v>12.2252960205078</v>
       </c>
       <c r="H18" t="n">
         <v>2456</v>
@@ -1036,7 +1036,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G23" t="n">
-        <v>12.2252969741821</v>
+        <v>12.2252960205078</v>
       </c>
       <c r="H23" t="n">
         <v>1882</v>
@@ -1094,7 +1094,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G25" t="n">
-        <v>12.0428295135498</v>
+        <v>12.0428304672241</v>
       </c>
       <c r="H25" t="n">
         <v>600</v>
@@ -1210,7 +1210,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G29" t="n">
-        <v>11.6778955459595</v>
+        <v>11.6778964996338</v>
       </c>
       <c r="H29" t="n">
         <v>1108</v>
@@ -1384,7 +1384,7 @@
         <v>11.3800001144409</v>
       </c>
       <c r="G35" t="n">
-        <v>10.382378578186</v>
+        <v>10.3823795318604</v>
       </c>
       <c r="H35" t="n">
         <v>16969</v>
@@ -1558,7 +1558,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G41" t="n">
-        <v>10.1086778640747</v>
+        <v>10.108678817749</v>
       </c>
       <c r="H41" t="n">
         <v>22904</v>
@@ -1616,7 +1616,7 @@
         <v>10.7600002288818</v>
       </c>
       <c r="G43" t="n">
-        <v>9.81673145294189</v>
+        <v>9.81673049926758</v>
       </c>
       <c r="H43" t="n">
         <v>1169</v>
@@ -1645,7 +1645,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G44" t="n">
-        <v>10.2181587219238</v>
+        <v>10.2181577682495</v>
       </c>
       <c r="H44" t="n">
         <v>1100</v>
@@ -1674,7 +1674,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G45" t="n">
-        <v>10.9845209121704</v>
+        <v>10.9845199584961</v>
       </c>
       <c r="H45" t="n">
         <v>67981</v>
@@ -1732,7 +1732,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G47" t="n">
-        <v>11.6778955459595</v>
+        <v>11.6778964996338</v>
       </c>
       <c r="H47" t="n">
         <v>838</v>
@@ -1761,7 +1761,7 @@
         <v>13.0600004196167</v>
       </c>
       <c r="G48" t="n">
-        <v>11.9151029586792</v>
+        <v>11.9151039123535</v>
       </c>
       <c r="H48" t="n">
         <v>2600</v>
@@ -1848,7 +1848,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G51" t="n">
-        <v>12.2252969741821</v>
+        <v>12.2252960205078</v>
       </c>
       <c r="H51" t="n">
         <v>1595</v>
@@ -1993,7 +1993,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G56" t="n">
-        <v>12.0428295135498</v>
+        <v>12.0428304672241</v>
       </c>
       <c r="H56" t="n">
         <v>275</v>
@@ -2022,7 +2022,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G57" t="n">
-        <v>12.0428295135498</v>
+        <v>12.0428304672241</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G58" t="n">
-        <v>12.0428295135498</v>
+        <v>12.0428304672241</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
@@ -2080,7 +2080,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G59" t="n">
-        <v>12.0428295135498</v>
+        <v>12.0428304672241</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
@@ -2138,7 +2138,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G61" t="n">
-        <v>11.4954290390015</v>
+        <v>11.4954280853271</v>
       </c>
       <c r="H61" t="n">
         <v>400</v>
@@ -2196,7 +2196,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G63" t="n">
-        <v>11.4954290390015</v>
+        <v>11.4954280853271</v>
       </c>
       <c r="H63" t="n">
         <v>490</v>
@@ -2254,7 +2254,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G65" t="n">
-        <v>11.4406871795654</v>
+        <v>11.4406881332397</v>
       </c>
       <c r="H65" t="n">
         <v>360</v>
@@ -2457,7 +2457,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G72" t="n">
-        <v>11.2217283248901</v>
+        <v>11.2217273712158</v>
       </c>
       <c r="H72" t="n">
         <v>850</v>
@@ -2515,7 +2515,7 @@
         <v>12.4399995803833</v>
       </c>
       <c r="G74" t="n">
-        <v>11.3494548797607</v>
+        <v>11.3494539260864</v>
       </c>
       <c r="H74" t="n">
         <v>16133</v>
@@ -2544,7 +2544,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G75" t="n">
-        <v>11.8238697052002</v>
+        <v>11.8238687515259</v>
       </c>
       <c r="H75" t="n">
         <v>727</v>
@@ -2747,7 +2747,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G82" t="n">
-        <v>11.2217283248901</v>
+        <v>11.2217273712158</v>
       </c>
       <c r="H82" t="n">
         <v>2400</v>
@@ -2805,7 +2805,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G84" t="n">
-        <v>10.2181587219238</v>
+        <v>10.2181577682495</v>
       </c>
       <c r="H84" t="n">
         <v>1810</v>
@@ -2979,7 +2979,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G90" t="n">
-        <v>10.9297790527344</v>
+        <v>10.9297800064087</v>
       </c>
       <c r="H90" t="n">
         <v>105</v>
@@ -3211,7 +3211,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G98" t="n">
-        <v>10.1816644668579</v>
+        <v>10.1816654205322</v>
       </c>
       <c r="H98" t="n">
         <v>35194</v>
@@ -3240,7 +3240,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G99" t="n">
-        <v>10.2181587219238</v>
+        <v>10.2181577682495</v>
       </c>
       <c r="H99" t="n">
         <v>1423</v>
@@ -3414,7 +3414,7 @@
         <v>11.7799997329712</v>
       </c>
       <c r="G105" t="n">
-        <v>10.7473134994507</v>
+        <v>10.7473125457764</v>
       </c>
       <c r="H105" t="n">
         <v>2174</v>
@@ -3501,7 +3501,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G108" t="n">
-        <v>9.9444580078125</v>
+        <v>9.94445705413818</v>
       </c>
       <c r="H108" t="n">
         <v>4150</v>
@@ -3530,7 +3530,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G109" t="n">
-        <v>10.2181587219238</v>
+        <v>10.2181577682495</v>
       </c>
       <c r="H109" t="n">
         <v>310</v>
@@ -3559,7 +3559,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G110" t="n">
-        <v>10.2181587219238</v>
+        <v>10.2181577682495</v>
       </c>
       <c r="H110" t="n">
         <v>260</v>
@@ -3588,7 +3588,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G111" t="n">
-        <v>10.2181587219238</v>
+        <v>10.2181577682495</v>
       </c>
       <c r="H111" t="n">
         <v>317</v>
@@ -3646,7 +3646,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G113" t="n">
-        <v>10.1269254684448</v>
+        <v>10.1269264221191</v>
       </c>
       <c r="H113" t="n">
         <v>1110</v>
@@ -3675,7 +3675,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G114" t="n">
-        <v>10.1269254684448</v>
+        <v>10.1269264221191</v>
       </c>
       <c r="H114" t="n">
         <v>1005</v>
@@ -3704,7 +3704,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G115" t="n">
-        <v>10.2728996276855</v>
+        <v>10.2728986740112</v>
       </c>
       <c r="H115" t="n">
         <v>970</v>
@@ -3820,7 +3820,7 @@
         <v>11.7799997329712</v>
       </c>
       <c r="G119" t="n">
-        <v>10.7473134994507</v>
+        <v>10.7473125457764</v>
       </c>
       <c r="H119" t="n">
         <v>1393</v>
@@ -3849,7 +3849,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G120" t="n">
-        <v>10.2728996276855</v>
+        <v>10.2728986740112</v>
       </c>
       <c r="H120" t="n">
         <v>3314</v>
@@ -3965,7 +3965,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G124" t="n">
-        <v>10.1816644668579</v>
+        <v>10.1816654205322</v>
       </c>
       <c r="H124" t="n">
         <v>695</v>
@@ -4400,7 +4400,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G139" t="n">
-        <v>10.1816644668579</v>
+        <v>10.1816654205322</v>
       </c>
       <c r="H139" t="n">
         <v>280</v>
@@ -4458,7 +4458,7 @@
         <v>11.2799997329712</v>
       </c>
       <c r="G141" t="n">
-        <v>10.291145324707</v>
+        <v>10.2911443710327</v>
       </c>
       <c r="H141" t="n">
         <v>250</v>
@@ -4516,7 +4516,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G143" t="n">
-        <v>10.2728996276855</v>
+        <v>10.2728986740112</v>
       </c>
       <c r="H143" t="n">
         <v>354</v>
@@ -4545,7 +4545,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G144" t="n">
-        <v>9.9444580078125</v>
+        <v>9.94445705413818</v>
       </c>
       <c r="H144" t="n">
         <v>9773</v>
@@ -4632,7 +4632,7 @@
         <v>11.2799997329712</v>
       </c>
       <c r="G147" t="n">
-        <v>10.291145324707</v>
+        <v>10.2911443710327</v>
       </c>
       <c r="H147" t="n">
         <v>780</v>
@@ -4777,7 +4777,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G152" t="n">
-        <v>10.1269254684448</v>
+        <v>10.1269264221191</v>
       </c>
       <c r="H152" t="n">
         <v>398</v>
@@ -4893,7 +4893,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G156" t="n">
-        <v>10.1269254684448</v>
+        <v>10.1269264221191</v>
       </c>
       <c r="H156" t="n">
         <v>206</v>
@@ -4922,7 +4922,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G157" t="n">
-        <v>10.1269254684448</v>
+        <v>10.1269264221191</v>
       </c>
       <c r="H157" t="n">
         <v>0</v>
@@ -4951,7 +4951,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G158" t="n">
-        <v>9.9444580078125</v>
+        <v>9.94445705413818</v>
       </c>
       <c r="H158" t="n">
         <v>320</v>
@@ -4980,7 +4980,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G159" t="n">
-        <v>10.1269254684448</v>
+        <v>10.1269264221191</v>
       </c>
       <c r="H159" t="n">
         <v>378</v>
@@ -5009,7 +5009,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G160" t="n">
-        <v>9.9444580078125</v>
+        <v>9.94445705413818</v>
       </c>
       <c r="H160" t="n">
         <v>220</v>
@@ -5038,7 +5038,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G161" t="n">
-        <v>9.9444580078125</v>
+        <v>9.94445705413818</v>
       </c>
       <c r="H161" t="n">
         <v>1909</v>
@@ -5125,7 +5125,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G164" t="n">
-        <v>10.1269254684448</v>
+        <v>10.1269264221191</v>
       </c>
       <c r="H164" t="n">
         <v>207</v>
@@ -5154,7 +5154,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G165" t="n">
-        <v>10.1816644668579</v>
+        <v>10.1816654205322</v>
       </c>
       <c r="H165" t="n">
         <v>40</v>
@@ -5212,7 +5212,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G167" t="n">
-        <v>10.1816644668579</v>
+        <v>10.1816654205322</v>
       </c>
       <c r="H167" t="n">
         <v>3600</v>
@@ -5270,7 +5270,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G169" t="n">
-        <v>9.30582237243652</v>
+        <v>9.30582332611084</v>
       </c>
       <c r="H169" t="n">
         <v>1233</v>
@@ -5299,7 +5299,7 @@
         <v>10.3400001525879</v>
       </c>
       <c r="G170" t="n">
-        <v>9.43354892730713</v>
+        <v>9.43354988098145</v>
       </c>
       <c r="H170" t="n">
         <v>1910</v>
@@ -5328,7 +5328,7 @@
         <v>10.3400001525879</v>
       </c>
       <c r="G171" t="n">
-        <v>9.43354892730713</v>
+        <v>9.43354988098145</v>
       </c>
       <c r="H171" t="n">
         <v>388</v>
@@ -5357,7 +5357,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G172" t="n">
-        <v>9.39705657958984</v>
+        <v>9.39705753326416</v>
       </c>
       <c r="H172" t="n">
         <v>1640</v>
@@ -5386,7 +5386,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G173" t="n">
-        <v>9.47004413604736</v>
+        <v>9.47004318237305</v>
       </c>
       <c r="H173" t="n">
         <v>1</v>
@@ -5444,7 +5444,7 @@
         <v>9.56999969482422</v>
       </c>
       <c r="G175" t="n">
-        <v>8.73105144500732</v>
+        <v>8.73105049133301</v>
       </c>
       <c r="H175" t="n">
         <v>6256</v>
@@ -5734,7 +5734,7 @@
         <v>8.60999965667725</v>
       </c>
       <c r="G185" t="n">
-        <v>7.85520887374878</v>
+        <v>7.8552098274231</v>
       </c>
       <c r="H185" t="n">
         <v>840</v>
@@ -5763,7 +5763,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G186" t="n">
-        <v>8.02855396270752</v>
+        <v>8.0285530090332</v>
       </c>
       <c r="H186" t="n">
         <v>820</v>
@@ -5821,7 +5821,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G188" t="n">
-        <v>8.11978626251221</v>
+        <v>8.11978721618652</v>
       </c>
       <c r="H188" t="n">
         <v>1750</v>
@@ -5850,7 +5850,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G189" t="n">
-        <v>8.27488327026367</v>
+        <v>8.27488231658936</v>
       </c>
       <c r="H189" t="n">
         <v>700</v>
@@ -5966,7 +5966,7 @@
         <v>8.59000015258789</v>
       </c>
       <c r="G193" t="n">
-        <v>7.83696222305298</v>
+        <v>7.83696317672729</v>
       </c>
       <c r="H193" t="n">
         <v>35</v>
@@ -6024,7 +6024,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G195" t="n">
-        <v>7.61800193786621</v>
+        <v>7.61800241470337</v>
       </c>
       <c r="H195" t="n">
         <v>289</v>
@@ -6053,7 +6053,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G196" t="n">
-        <v>7.61800193786621</v>
+        <v>7.61800241470337</v>
       </c>
       <c r="H196" t="n">
         <v>0</v>
@@ -6082,7 +6082,7 @@
         <v>8.25</v>
       </c>
       <c r="G197" t="n">
-        <v>7.52676868438721</v>
+        <v>7.52676916122437</v>
       </c>
       <c r="H197" t="n">
         <v>444</v>
@@ -6111,7 +6111,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G198" t="n">
-        <v>7.48115205764771</v>
+        <v>7.48115158081055</v>
       </c>
       <c r="H198" t="n">
         <v>110</v>
@@ -6140,7 +6140,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G199" t="n">
-        <v>7.48115205764771</v>
+        <v>7.48115158081055</v>
       </c>
       <c r="H199" t="n">
         <v>0</v>
@@ -6227,7 +6227,7 @@
         <v>8.60999965667725</v>
       </c>
       <c r="G202" t="n">
-        <v>7.85520887374878</v>
+        <v>7.8552098274231</v>
       </c>
       <c r="H202" t="n">
         <v>924</v>
@@ -6314,7 +6314,7 @@
         <v>8.60999965667725</v>
       </c>
       <c r="G205" t="n">
-        <v>7.85520887374878</v>
+        <v>7.8552098274231</v>
       </c>
       <c r="H205" t="n">
         <v>460</v>
@@ -6343,7 +6343,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G206" t="n">
-        <v>7.9373197555542</v>
+        <v>7.93731880187988</v>
       </c>
       <c r="H206" t="n">
         <v>1640</v>
@@ -6372,7 +6372,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G207" t="n">
-        <v>7.9373197555542</v>
+        <v>7.93731880187988</v>
       </c>
       <c r="H207" t="n">
         <v>0</v>
@@ -6401,7 +6401,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G208" t="n">
-        <v>7.9373197555542</v>
+        <v>7.93731880187988</v>
       </c>
       <c r="H208" t="n">
         <v>1100</v>
@@ -6430,7 +6430,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G209" t="n">
-        <v>7.9373197555542</v>
+        <v>7.93731880187988</v>
       </c>
       <c r="H209" t="n">
         <v>230</v>
@@ -6459,7 +6459,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G210" t="n">
-        <v>7.9373197555542</v>
+        <v>7.93731880187988</v>
       </c>
       <c r="H210" t="n">
         <v>0</v>
@@ -6546,7 +6546,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G213" t="n">
-        <v>8.02855396270752</v>
+        <v>8.0285530090332</v>
       </c>
       <c r="H213" t="n">
         <v>11079</v>
@@ -6604,7 +6604,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G215" t="n">
-        <v>8.27488327026367</v>
+        <v>8.27488231658936</v>
       </c>
       <c r="H215" t="n">
         <v>8078</v>
@@ -6662,7 +6662,7 @@
         <v>9.39000034332275</v>
       </c>
       <c r="G217" t="n">
-        <v>8.5668306350708</v>
+        <v>8.56683158874512</v>
       </c>
       <c r="H217" t="n">
         <v>520</v>
@@ -7010,7 +7010,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G229" t="n">
-        <v>8.57595348358154</v>
+        <v>8.57595443725586</v>
       </c>
       <c r="H229" t="n">
         <v>7583</v>
@@ -7648,7 +7648,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G251" t="n">
-        <v>9.21459007263184</v>
+        <v>9.21458911895752</v>
       </c>
       <c r="H251" t="n">
         <v>1480</v>
@@ -7677,7 +7677,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G252" t="n">
-        <v>9.21459007263184</v>
+        <v>9.21458911895752</v>
       </c>
       <c r="H252" t="n">
         <v>331</v>
@@ -8025,7 +8025,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G264" t="n">
-        <v>8.7584228515625</v>
+        <v>8.75842189788818</v>
       </c>
       <c r="H264" t="n">
         <v>6946</v>
@@ -8228,7 +8228,7 @@
         <v>9.47000026702881</v>
       </c>
       <c r="G271" t="n">
-        <v>8.639817237854</v>
+        <v>8.63981819152832</v>
       </c>
       <c r="H271" t="n">
         <v>200</v>
@@ -8344,7 +8344,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G275" t="n">
-        <v>8.64894008636475</v>
+        <v>8.64894104003906</v>
       </c>
       <c r="H275" t="n">
         <v>860</v>
@@ -8431,7 +8431,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G278" t="n">
-        <v>8.11978626251221</v>
+        <v>8.11978721618652</v>
       </c>
       <c r="H278" t="n">
         <v>43332</v>
@@ -8460,7 +8460,7 @@
         <v>8.71000003814697</v>
       </c>
       <c r="G279" t="n">
-        <v>7.94644355773926</v>
+        <v>7.94644260406494</v>
       </c>
       <c r="H279" t="n">
         <v>7948</v>
@@ -8489,7 +8489,7 @@
         <v>8.72999954223633</v>
       </c>
       <c r="G280" t="n">
-        <v>7.96469020843506</v>
+        <v>7.96468925476074</v>
       </c>
       <c r="H280" t="n">
         <v>1620</v>
@@ -8518,7 +8518,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G281" t="n">
-        <v>8.11978626251221</v>
+        <v>8.11978721618652</v>
       </c>
       <c r="H281" t="n">
         <v>1100</v>
@@ -8547,7 +8547,7 @@
         <v>8.90999984741211</v>
       </c>
       <c r="G282" t="n">
-        <v>8.12890911102295</v>
+        <v>8.12891006469727</v>
       </c>
       <c r="H282" t="n">
         <v>2446</v>
@@ -8663,7 +8663,7 @@
         <v>9.09000015258789</v>
       </c>
       <c r="G286" t="n">
-        <v>8.29313087463379</v>
+        <v>8.29312992095947</v>
       </c>
       <c r="H286" t="n">
         <v>7374</v>
@@ -8692,7 +8692,7 @@
         <v>9.09000015258789</v>
       </c>
       <c r="G287" t="n">
-        <v>8.29313087463379</v>
+        <v>8.29312992095947</v>
       </c>
       <c r="H287" t="n">
         <v>760</v>
@@ -8721,7 +8721,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G288" t="n">
-        <v>8.27488327026367</v>
+        <v>8.27488231658936</v>
       </c>
       <c r="H288" t="n">
         <v>6201</v>
@@ -8750,7 +8750,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G289" t="n">
-        <v>8.92264080047607</v>
+        <v>8.92264175415039</v>
       </c>
       <c r="H289" t="n">
         <v>1337</v>
@@ -8866,7 +8866,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G293" t="n">
-        <v>8.27488327026367</v>
+        <v>8.27488231658936</v>
       </c>
       <c r="H293" t="n">
         <v>1783</v>
@@ -9185,7 +9185,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G304" t="n">
-        <v>8.02855396270752</v>
+        <v>8.0285530090332</v>
       </c>
       <c r="H304" t="n">
         <v>300</v>
@@ -9533,7 +9533,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G316" t="n">
-        <v>8.02855396270752</v>
+        <v>8.0285530090332</v>
       </c>
       <c r="H316" t="n">
         <v>3343</v>
@@ -9562,7 +9562,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G317" t="n">
-        <v>8.02855396270752</v>
+        <v>8.0285530090332</v>
       </c>
       <c r="H317" t="n">
         <v>180</v>
@@ -9591,7 +9591,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G318" t="n">
-        <v>8.02855396270752</v>
+        <v>8.0285530090332</v>
       </c>
       <c r="H318" t="n">
         <v>78630</v>
@@ -9620,7 +9620,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G319" t="n">
-        <v>7.95556735992432</v>
+        <v>7.95556640625</v>
       </c>
       <c r="H319" t="n">
         <v>5536</v>
@@ -9707,7 +9707,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G322" t="n">
-        <v>8.64894008636475</v>
+        <v>8.64894104003906</v>
       </c>
       <c r="H322" t="n">
         <v>23858</v>
@@ -9736,7 +9736,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G323" t="n">
-        <v>8.28400707244873</v>
+        <v>8.28400611877441</v>
       </c>
       <c r="H323" t="n">
         <v>8366</v>
@@ -9765,7 +9765,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G324" t="n">
-        <v>8.28400707244873</v>
+        <v>8.28400611877441</v>
       </c>
       <c r="H324" t="n">
         <v>0</v>
@@ -9881,7 +9881,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G328" t="n">
-        <v>8.11978626251221</v>
+        <v>8.11978721618652</v>
       </c>
       <c r="H328" t="n">
         <v>3732</v>
@@ -9910,7 +9910,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G329" t="n">
-        <v>8.11978626251221</v>
+        <v>8.11978721618652</v>
       </c>
       <c r="H329" t="n">
         <v>200</v>
@@ -9939,7 +9939,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G330" t="n">
-        <v>8.11978626251221</v>
+        <v>8.11978721618652</v>
       </c>
       <c r="H330" t="n">
         <v>451</v>
@@ -9968,7 +9968,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G331" t="n">
-        <v>8.59420108795166</v>
+        <v>8.59420204162598</v>
       </c>
       <c r="H331" t="n">
         <v>5649</v>
@@ -10026,7 +10026,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G333" t="n">
-        <v>8.7584228515625</v>
+        <v>8.75842189788818</v>
       </c>
       <c r="H333" t="n">
         <v>19786</v>
@@ -10084,7 +10084,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G335" t="n">
-        <v>8.24751377105713</v>
+        <v>8.24751472473145</v>
       </c>
       <c r="H335" t="n">
         <v>7514</v>
@@ -10171,7 +10171,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G338" t="n">
-        <v>7.9373197555542</v>
+        <v>7.93731880187988</v>
       </c>
       <c r="H338" t="n">
         <v>2490</v>
@@ -10316,7 +10316,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G343" t="n">
-        <v>7.40816497802734</v>
+        <v>7.40816450119019</v>
       </c>
       <c r="H343" t="n">
         <v>500</v>
@@ -10403,7 +10403,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G346" t="n">
-        <v>7.35342502593994</v>
+        <v>7.3534255027771</v>
       </c>
       <c r="H346" t="n">
         <v>470</v>
@@ -10577,7 +10577,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G352" t="n">
-        <v>7.31693172454834</v>
+        <v>7.3169322013855</v>
       </c>
       <c r="H352" t="n">
         <v>63</v>
@@ -10693,7 +10693,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G356" t="n">
-        <v>7.04323053359985</v>
+        <v>7.0432300567627</v>
       </c>
       <c r="H356" t="n">
         <v>3056</v>
@@ -10896,7 +10896,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G363" t="n">
-        <v>7.04323053359985</v>
+        <v>7.0432300567627</v>
       </c>
       <c r="H363" t="n">
         <v>2201</v>
@@ -10983,7 +10983,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G366" t="n">
-        <v>6.95199680328369</v>
+        <v>6.95199728012085</v>
       </c>
       <c r="H366" t="n">
         <v>3628</v>
@@ -11041,7 +11041,7 @@
         <v>7.51999998092651</v>
       </c>
       <c r="G368" t="n">
-        <v>6.86076354980469</v>
+        <v>6.86076307296753</v>
       </c>
       <c r="H368" t="n">
         <v>5487</v>
@@ -11070,7 +11070,7 @@
         <v>7.51999998092651</v>
       </c>
       <c r="G369" t="n">
-        <v>6.86076354980469</v>
+        <v>6.86076307296753</v>
       </c>
       <c r="H369" t="n">
         <v>45</v>
@@ -11128,7 +11128,7 @@
         <v>7.51999998092651</v>
       </c>
       <c r="G371" t="n">
-        <v>6.86076354980469</v>
+        <v>6.86076307296753</v>
       </c>
       <c r="H371" t="n">
         <v>50</v>
@@ -11157,7 +11157,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G372" t="n">
-        <v>6.95199680328369</v>
+        <v>6.95199728012085</v>
       </c>
       <c r="H372" t="n">
         <v>500</v>
@@ -11476,7 +11476,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G383" t="n">
-        <v>6.97024345397949</v>
+        <v>6.97024393081665</v>
       </c>
       <c r="H383" t="n">
         <v>1600</v>
@@ -11505,7 +11505,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G384" t="n">
-        <v>6.91550397872925</v>
+        <v>6.91550350189209</v>
       </c>
       <c r="H384" t="n">
         <v>502</v>
@@ -11534,7 +11534,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G385" t="n">
-        <v>6.91550397872925</v>
+        <v>6.91550350189209</v>
       </c>
       <c r="H385" t="n">
         <v>100</v>
@@ -11563,7 +11563,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G386" t="n">
-        <v>6.91550397872925</v>
+        <v>6.91550350189209</v>
       </c>
       <c r="H386" t="n">
         <v>0</v>
@@ -11592,7 +11592,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G387" t="n">
-        <v>6.91550397872925</v>
+        <v>6.91550350189209</v>
       </c>
       <c r="H387" t="n">
         <v>500</v>
@@ -11708,7 +11708,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G391" t="n">
-        <v>7.59063148498535</v>
+        <v>7.59063196182251</v>
       </c>
       <c r="H391" t="n">
         <v>1808</v>
@@ -11882,7 +11882,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G397" t="n">
-        <v>7.62712478637695</v>
+        <v>7.62712526321411</v>
       </c>
       <c r="H397" t="n">
         <v>1616</v>
@@ -11911,7 +11911,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G398" t="n">
-        <v>7.62712478637695</v>
+        <v>7.62712526321411</v>
       </c>
       <c r="H398" t="n">
         <v>0</v>
@@ -11940,7 +11940,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G399" t="n">
-        <v>7.40816497802734</v>
+        <v>7.40816450119019</v>
       </c>
       <c r="H399" t="n">
         <v>350</v>
@@ -12288,7 +12288,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G411" t="n">
-        <v>7.48115205764771</v>
+        <v>7.48115158081055</v>
       </c>
       <c r="H411" t="n">
         <v>1500</v>
@@ -12346,7 +12346,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G413" t="n">
-        <v>7.40816497802734</v>
+        <v>7.40816450119019</v>
       </c>
       <c r="H413" t="n">
         <v>1600</v>
@@ -12462,7 +12462,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G417" t="n">
-        <v>7.40816497802734</v>
+        <v>7.40816450119019</v>
       </c>
       <c r="H417" t="n">
         <v>4309</v>
@@ -12491,7 +12491,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G418" t="n">
-        <v>7.48115205764771</v>
+        <v>7.48115158081055</v>
       </c>
       <c r="H418" t="n">
         <v>130</v>
@@ -12520,7 +12520,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G419" t="n">
-        <v>7.48115205764771</v>
+        <v>7.48115158081055</v>
       </c>
       <c r="H419" t="n">
         <v>0</v>
@@ -12549,7 +12549,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G420" t="n">
-        <v>7.48115205764771</v>
+        <v>7.48115158081055</v>
       </c>
       <c r="H420" t="n">
         <v>1975</v>
@@ -12607,7 +12607,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G422" t="n">
-        <v>7.48115205764771</v>
+        <v>7.48115158081055</v>
       </c>
       <c r="H422" t="n">
         <v>1500</v>
@@ -12636,7 +12636,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G423" t="n">
-        <v>7.48115205764771</v>
+        <v>7.48115158081055</v>
       </c>
       <c r="H423" t="n">
         <v>0</v>
@@ -12926,7 +12926,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G433" t="n">
-        <v>7.48115205764771</v>
+        <v>7.48115158081055</v>
       </c>
       <c r="H433" t="n">
         <v>2702</v>
@@ -12984,7 +12984,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G435" t="n">
-        <v>7.24394512176514</v>
+        <v>7.24394464492798</v>
       </c>
       <c r="H435" t="n">
         <v>3622</v>
@@ -13013,7 +13013,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G436" t="n">
-        <v>7.35342502593994</v>
+        <v>7.3534255027771</v>
       </c>
       <c r="H436" t="n">
         <v>4810</v>
@@ -13042,7 +13042,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G437" t="n">
-        <v>7.35342502593994</v>
+        <v>7.3534255027771</v>
       </c>
       <c r="H437" t="n">
         <v>1654</v>
@@ -13100,7 +13100,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G439" t="n">
-        <v>6.91550397872925</v>
+        <v>6.91550350189209</v>
       </c>
       <c r="H439" t="n">
         <v>5180</v>
@@ -13274,7 +13274,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G445" t="n">
-        <v>6.78777647018433</v>
+        <v>6.78777694702148</v>
       </c>
       <c r="H445" t="n">
         <v>660</v>
@@ -13303,7 +13303,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G446" t="n">
-        <v>6.78777647018433</v>
+        <v>6.78777694702148</v>
       </c>
       <c r="H446" t="n">
         <v>100</v>
@@ -13564,7 +13564,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G455" t="n">
-        <v>6.5870623588562</v>
+        <v>6.58706283569336</v>
       </c>
       <c r="H455" t="n">
         <v>200</v>
@@ -13709,7 +13709,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G460" t="n">
-        <v>6.51407623291016</v>
+        <v>6.514075756073</v>
       </c>
       <c r="H460" t="n">
         <v>2800</v>
@@ -13970,7 +13970,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G469" t="n">
-        <v>6.44108915328979</v>
+        <v>6.44108867645264</v>
       </c>
       <c r="H469" t="n">
         <v>3100</v>
@@ -14086,7 +14086,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G473" t="n">
-        <v>6.42284250259399</v>
+        <v>6.42284297943115</v>
       </c>
       <c r="H473" t="n">
         <v>600</v>
@@ -14144,7 +14144,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G475" t="n">
-        <v>6.67829656600952</v>
+        <v>6.67829608917236</v>
       </c>
       <c r="H475" t="n">
         <v>1738</v>
@@ -14173,7 +14173,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G476" t="n">
-        <v>6.67829656600952</v>
+        <v>6.67829608917236</v>
       </c>
       <c r="H476" t="n">
         <v>1500</v>
@@ -14231,7 +14231,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G478" t="n">
-        <v>6.73303651809692</v>
+        <v>6.73303699493408</v>
       </c>
       <c r="H478" t="n">
         <v>1030</v>
@@ -14260,7 +14260,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G479" t="n">
-        <v>6.73303651809692</v>
+        <v>6.73303699493408</v>
       </c>
       <c r="H479" t="n">
         <v>0</v>
@@ -14289,7 +14289,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G480" t="n">
-        <v>6.73303651809692</v>
+        <v>6.73303699493408</v>
       </c>
       <c r="H480" t="n">
         <v>0</v>
@@ -14318,7 +14318,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G481" t="n">
-        <v>6.73303651809692</v>
+        <v>6.73303699493408</v>
       </c>
       <c r="H481" t="n">
         <v>0</v>
@@ -14347,7 +14347,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G482" t="n">
-        <v>6.73303651809692</v>
+        <v>6.73303699493408</v>
       </c>
       <c r="H482" t="n">
         <v>0</v>
@@ -14376,7 +14376,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G483" t="n">
-        <v>6.73303651809692</v>
+        <v>6.73303699493408</v>
       </c>
       <c r="H483" t="n">
         <v>0</v>
@@ -14405,7 +14405,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G484" t="n">
-        <v>6.5870623588562</v>
+        <v>6.58706283569336</v>
       </c>
       <c r="H484" t="n">
         <v>1565</v>
@@ -14434,7 +14434,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G485" t="n">
-        <v>6.5870623588562</v>
+        <v>6.58706283569336</v>
       </c>
       <c r="H485" t="n">
         <v>0</v>
@@ -14463,7 +14463,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G486" t="n">
-        <v>6.5870623588562</v>
+        <v>6.58706283569336</v>
       </c>
       <c r="H486" t="n">
         <v>0</v>
@@ -14492,7 +14492,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G487" t="n">
-        <v>6.64180326461792</v>
+        <v>6.64180278778076</v>
       </c>
       <c r="H487" t="n">
         <v>565</v>
@@ -14608,7 +14608,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G491" t="n">
-        <v>7.18920421600342</v>
+        <v>7.18920469284058</v>
       </c>
       <c r="H491" t="n">
         <v>1500</v>
@@ -14898,7 +14898,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G501" t="n">
-        <v>7.48115205764771</v>
+        <v>7.48115158081055</v>
       </c>
       <c r="H501" t="n">
         <v>1173</v>
@@ -15072,7 +15072,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G507" t="n">
-        <v>7.31693172454834</v>
+        <v>7.3169322013855</v>
       </c>
       <c r="H507" t="n">
         <v>772</v>
@@ -15217,7 +15217,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G512" t="n">
-        <v>7.31693172454834</v>
+        <v>7.3169322013855</v>
       </c>
       <c r="H512" t="n">
         <v>1280</v>
@@ -15362,7 +15362,7 @@
         <v>7.51999998092651</v>
       </c>
       <c r="G517" t="n">
-        <v>6.86076354980469</v>
+        <v>6.86076307296753</v>
       </c>
       <c r="H517" t="n">
         <v>3626</v>
@@ -15536,7 +15536,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G523" t="n">
-        <v>6.73303651809692</v>
+        <v>6.73303699493408</v>
       </c>
       <c r="H523" t="n">
         <v>740</v>
@@ -15565,7 +15565,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G524" t="n">
-        <v>6.73303651809692</v>
+        <v>6.73303699493408</v>
       </c>
       <c r="H524" t="n">
         <v>1680</v>
@@ -15826,7 +15826,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G533" t="n">
-        <v>7.35342502593994</v>
+        <v>7.3534255027771</v>
       </c>
       <c r="H533" t="n">
         <v>2000</v>
@@ -15855,7 +15855,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G534" t="n">
-        <v>7.35342502593994</v>
+        <v>7.3534255027771</v>
       </c>
       <c r="H534" t="n">
         <v>2413</v>
@@ -15884,7 +15884,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G535" t="n">
-        <v>7.64537191390991</v>
+        <v>7.64537239074707</v>
       </c>
       <c r="H535" t="n">
         <v>12922</v>
@@ -15942,7 +15942,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G537" t="n">
-        <v>7.18920421600342</v>
+        <v>7.18920469284058</v>
       </c>
       <c r="H537" t="n">
         <v>29589</v>
@@ -16145,7 +16145,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G544" t="n">
-        <v>7.31693172454834</v>
+        <v>7.3169322013855</v>
       </c>
       <c r="H544" t="n">
         <v>3852</v>
@@ -16232,7 +16232,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G547" t="n">
-        <v>7.48115205764771</v>
+        <v>7.48115158081055</v>
       </c>
       <c r="H547" t="n">
         <v>18284</v>
@@ -16348,7 +16348,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G551" t="n">
-        <v>7.48115205764771</v>
+        <v>7.48115158081055</v>
       </c>
       <c r="H551" t="n">
         <v>61620</v>
@@ -16406,7 +16406,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G553" t="n">
-        <v>7.68186569213867</v>
+        <v>7.68186521530151</v>
       </c>
       <c r="H553" t="n">
         <v>4691</v>
@@ -16493,7 +16493,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G556" t="n">
-        <v>7.68186569213867</v>
+        <v>7.68186521530151</v>
       </c>
       <c r="H556" t="n">
         <v>409</v>
@@ -16522,7 +16522,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G557" t="n">
-        <v>7.62712478637695</v>
+        <v>7.62712526321411</v>
       </c>
       <c r="H557" t="n">
         <v>3160</v>
@@ -16551,7 +16551,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G558" t="n">
-        <v>7.62712478637695</v>
+        <v>7.62712526321411</v>
       </c>
       <c r="H558" t="n">
         <v>0</v>
@@ -16580,7 +16580,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G559" t="n">
-        <v>7.62712478637695</v>
+        <v>7.62712526321411</v>
       </c>
       <c r="H559" t="n">
         <v>0</v>
@@ -16696,7 +16696,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G563" t="n">
-        <v>7.64537191390991</v>
+        <v>7.64537239074707</v>
       </c>
       <c r="H563" t="n">
         <v>900</v>
@@ -16725,7 +16725,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G564" t="n">
-        <v>7.64537191390991</v>
+        <v>7.64537239074707</v>
       </c>
       <c r="H564" t="n">
         <v>0</v>
@@ -16754,7 +16754,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G565" t="n">
-        <v>7.64537191390991</v>
+        <v>7.64537239074707</v>
       </c>
       <c r="H565" t="n">
         <v>0</v>
@@ -16783,7 +16783,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G566" t="n">
-        <v>7.64537191390991</v>
+        <v>7.64537239074707</v>
       </c>
       <c r="H566" t="n">
         <v>0</v>
@@ -16812,7 +16812,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G567" t="n">
-        <v>7.48115205764771</v>
+        <v>7.48115158081055</v>
       </c>
       <c r="H567" t="n">
         <v>801</v>
@@ -16841,7 +16841,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G568" t="n">
-        <v>7.48115205764771</v>
+        <v>7.48115158081055</v>
       </c>
       <c r="H568" t="n">
         <v>797</v>
@@ -16870,7 +16870,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G569" t="n">
-        <v>7.48115205764771</v>
+        <v>7.48115158081055</v>
       </c>
       <c r="H569" t="n">
         <v>1207</v>
@@ -16899,7 +16899,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G570" t="n">
-        <v>7.48115205764771</v>
+        <v>7.48115158081055</v>
       </c>
       <c r="H570" t="n">
         <v>3300</v>
@@ -16928,7 +16928,7 @@
         <v>8.25</v>
       </c>
       <c r="G571" t="n">
-        <v>7.52676868438721</v>
+        <v>7.52676916122437</v>
       </c>
       <c r="H571" t="n">
         <v>2468</v>
@@ -17073,7 +17073,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G576" t="n">
-        <v>7.61800193786621</v>
+        <v>7.61800241470337</v>
       </c>
       <c r="H576" t="n">
         <v>4229</v>
@@ -17102,7 +17102,7 @@
         <v>8.25</v>
       </c>
       <c r="G577" t="n">
-        <v>7.52676868438721</v>
+        <v>7.52676916122437</v>
       </c>
       <c r="H577" t="n">
         <v>10687</v>
@@ -17247,7 +17247,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G582" t="n">
-        <v>7.48115205764771</v>
+        <v>7.48115158081055</v>
       </c>
       <c r="H582" t="n">
         <v>30</v>
@@ -17276,7 +17276,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G583" t="n">
-        <v>7.48115205764771</v>
+        <v>7.48115158081055</v>
       </c>
       <c r="H583" t="n">
         <v>604</v>
@@ -17305,7 +17305,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G584" t="n">
-        <v>7.48115205764771</v>
+        <v>7.48115158081055</v>
       </c>
       <c r="H584" t="n">
         <v>0</v>
@@ -17334,7 +17334,7 @@
         <v>8.25</v>
       </c>
       <c r="G585" t="n">
-        <v>7.52676868438721</v>
+        <v>7.52676916122437</v>
       </c>
       <c r="H585" t="n">
         <v>1560</v>
@@ -18523,7 +18523,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G626" t="n">
-        <v>7.77841663360596</v>
+        <v>7.7784161567688</v>
       </c>
       <c r="H626" t="n">
         <v>9091</v>
@@ -18668,7 +18668,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G631" t="n">
-        <v>7.77841663360596</v>
+        <v>7.7784161567688</v>
       </c>
       <c r="H631" t="n">
         <v>1834</v>
@@ -18755,7 +18755,7 @@
         <v>8.25</v>
       </c>
       <c r="G634" t="n">
-        <v>7.82584571838379</v>
+        <v>7.82584619522095</v>
       </c>
       <c r="H634" t="n">
         <v>811</v>
@@ -18784,7 +18784,7 @@
         <v>8.25</v>
       </c>
       <c r="G635" t="n">
-        <v>7.82584571838379</v>
+        <v>7.82584619522095</v>
       </c>
       <c r="H635" t="n">
         <v>4580</v>
@@ -18813,7 +18813,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G636" t="n">
-        <v>7.77841663360596</v>
+        <v>7.7784161567688</v>
       </c>
       <c r="H636" t="n">
         <v>2333</v>
@@ -19016,7 +19016,7 @@
         <v>8.25</v>
       </c>
       <c r="G643" t="n">
-        <v>7.82584571838379</v>
+        <v>7.82584619522095</v>
       </c>
       <c r="H643" t="n">
         <v>200</v>
@@ -19045,7 +19045,7 @@
         <v>8.25</v>
       </c>
       <c r="G644" t="n">
-        <v>7.82584571838379</v>
+        <v>7.82584619522095</v>
       </c>
       <c r="H644" t="n">
         <v>0</v>
@@ -19074,7 +19074,7 @@
         <v>8.25</v>
       </c>
       <c r="G645" t="n">
-        <v>7.82584571838379</v>
+        <v>7.82584619522095</v>
       </c>
       <c r="H645" t="n">
         <v>350</v>
@@ -19103,7 +19103,7 @@
         <v>8.25</v>
       </c>
       <c r="G646" t="n">
-        <v>7.82584571838379</v>
+        <v>7.82584619522095</v>
       </c>
       <c r="H646" t="n">
         <v>925</v>
@@ -19132,7 +19132,7 @@
         <v>8.25</v>
       </c>
       <c r="G647" t="n">
-        <v>7.82584571838379</v>
+        <v>7.82584619522095</v>
       </c>
       <c r="H647" t="n">
         <v>41854</v>
@@ -21278,7 +21278,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G721" t="n">
-        <v>6.68754100799561</v>
+        <v>6.68754148483276</v>
       </c>
       <c r="H721" t="n">
         <v>4498</v>
@@ -21510,7 +21510,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G729" t="n">
-        <v>6.68754100799561</v>
+        <v>6.68754148483276</v>
       </c>
       <c r="H729" t="n">
         <v>10666</v>
@@ -21655,7 +21655,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G734" t="n">
-        <v>6.35553550720215</v>
+        <v>6.35553503036499</v>
       </c>
       <c r="H734" t="n">
         <v>3775</v>
@@ -22177,7 +22177,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G752" t="n">
-        <v>6.68754100799561</v>
+        <v>6.68754148483276</v>
       </c>
       <c r="H752" t="n">
         <v>210</v>
@@ -22206,7 +22206,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G753" t="n">
-        <v>6.68754100799561</v>
+        <v>6.68754148483276</v>
       </c>
       <c r="H753" t="n">
         <v>0</v>
@@ -22264,7 +22264,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G755" t="n">
-        <v>6.68754100799561</v>
+        <v>6.68754148483276</v>
       </c>
       <c r="H755" t="n">
         <v>2600</v>
@@ -22351,7 +22351,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G758" t="n">
-        <v>6.68754100799561</v>
+        <v>6.68754148483276</v>
       </c>
       <c r="H758" t="n">
         <v>1000</v>
@@ -22380,7 +22380,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G759" t="n">
-        <v>6.68754100799561</v>
+        <v>6.68754148483276</v>
       </c>
       <c r="H759" t="n">
         <v>2199</v>
@@ -23018,7 +23018,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G781" t="n">
-        <v>7.77841663360596</v>
+        <v>7.7784161567688</v>
       </c>
       <c r="H781" t="n">
         <v>3468</v>
@@ -23076,7 +23076,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G783" t="n">
-        <v>7.92070436477661</v>
+        <v>7.92070484161377</v>
       </c>
       <c r="H783" t="n">
         <v>6694</v>
@@ -24062,7 +24062,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G817" t="n">
-        <v>6.68754100799561</v>
+        <v>6.68754148483276</v>
       </c>
       <c r="H817" t="n">
         <v>4357</v>
@@ -24120,7 +24120,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G819" t="n">
-        <v>6.68754100799561</v>
+        <v>6.68754148483276</v>
       </c>
       <c r="H819" t="n">
         <v>800</v>
@@ -24265,7 +24265,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G824" t="n">
-        <v>6.26067638397217</v>
+        <v>6.26067686080933</v>
       </c>
       <c r="H824" t="n">
         <v>2695</v>
@@ -24294,7 +24294,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G825" t="n">
-        <v>6.39347887039185</v>
+        <v>6.39347839355469</v>
       </c>
       <c r="H825" t="n">
         <v>1450</v>
@@ -24439,7 +24439,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G830" t="n">
-        <v>6.94365978240967</v>
+        <v>6.94365930557251</v>
       </c>
       <c r="H830" t="n">
         <v>604</v>
@@ -24584,7 +24584,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G835" t="n">
-        <v>6.77291393280029</v>
+        <v>6.77291345596313</v>
       </c>
       <c r="H835" t="n">
         <v>609</v>
@@ -24613,7 +24613,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G836" t="n">
-        <v>6.77291393280029</v>
+        <v>6.77291345596313</v>
       </c>
       <c r="H836" t="n">
         <v>0</v>
@@ -24671,7 +24671,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G838" t="n">
-        <v>7.2472071647644</v>
+        <v>7.24720764160156</v>
       </c>
       <c r="H838" t="n">
         <v>21285</v>
@@ -24932,7 +24932,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G847" t="n">
-        <v>7.22823524475098</v>
+        <v>7.22823572158813</v>
       </c>
       <c r="H847" t="n">
         <v>3902</v>
@@ -24961,7 +24961,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G848" t="n">
-        <v>7.2472071647644</v>
+        <v>7.24720764160156</v>
       </c>
       <c r="H848" t="n">
         <v>750</v>
@@ -25077,7 +25077,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G852" t="n">
-        <v>7.22823524475098</v>
+        <v>7.22823572158813</v>
       </c>
       <c r="H852" t="n">
         <v>4126</v>
@@ -25222,7 +25222,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G857" t="n">
-        <v>7.77841663360596</v>
+        <v>7.7784161567688</v>
       </c>
       <c r="H857" t="n">
         <v>16854</v>
@@ -25280,7 +25280,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G859" t="n">
-        <v>7.77841663360596</v>
+        <v>7.7784161567688</v>
       </c>
       <c r="H859" t="n">
         <v>1217</v>
@@ -25454,7 +25454,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G865" t="n">
-        <v>7.89224624633789</v>
+        <v>7.89224672317505</v>
       </c>
       <c r="H865" t="n">
         <v>27334</v>
@@ -35639,6 +35639,35 @@
         <v>1387</v>
       </c>
       <c r="I1216" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1217">
+      <c r="A1217" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1217" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C1217" t="n">
+        <v>8</v>
+      </c>
+      <c r="D1217" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1217" t="n">
+        <v>8</v>
+      </c>
+      <c r="F1217" t="n">
+        <v>8</v>
+      </c>
+      <c r="G1217" t="n">
+        <v>8</v>
+      </c>
+      <c r="H1217" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I1217" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SVS.MI.xlsx
+++ b/data/SVS.MI.xlsx
@@ -514,7 +514,7 @@
         <v>14.5600004196167</v>
       </c>
       <c r="G5" t="n">
-        <v>13.2836055755615</v>
+        <v>13.2836065292358</v>
       </c>
       <c r="H5" t="n">
         <v>2134</v>
@@ -543,7 +543,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G6" t="n">
-        <v>13.4113330841064</v>
+        <v>13.4113321304321</v>
       </c>
       <c r="H6" t="n">
         <v>1997</v>
@@ -833,7 +833,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G16" t="n">
-        <v>12.2435436248779</v>
+        <v>12.2435445785522</v>
       </c>
       <c r="H16" t="n">
         <v>2540</v>
@@ -891,7 +891,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G18" t="n">
-        <v>12.2252960205078</v>
+        <v>12.2252969741821</v>
       </c>
       <c r="H18" t="n">
         <v>2456</v>
@@ -978,7 +978,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G21" t="n">
-        <v>12.4077644348145</v>
+        <v>12.4077634811401</v>
       </c>
       <c r="H21" t="n">
         <v>2900</v>
@@ -1036,7 +1036,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G23" t="n">
-        <v>12.2252960205078</v>
+        <v>12.2252969741821</v>
       </c>
       <c r="H23" t="n">
         <v>1882</v>
@@ -1123,7 +1123,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G26" t="n">
-        <v>11.9698429107666</v>
+        <v>11.9698419570923</v>
       </c>
       <c r="H26" t="n">
         <v>4682</v>
@@ -1181,7 +1181,7 @@
         <v>13</v>
       </c>
       <c r="G28" t="n">
-        <v>11.8603620529175</v>
+        <v>11.8603630065918</v>
       </c>
       <c r="H28" t="n">
         <v>2250</v>
@@ -1210,7 +1210,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G29" t="n">
-        <v>11.6778964996338</v>
+        <v>11.6778955459595</v>
       </c>
       <c r="H29" t="n">
         <v>1108</v>
@@ -1355,7 +1355,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G34" t="n">
-        <v>11.2034816741943</v>
+        <v>11.20348072052</v>
       </c>
       <c r="H34" t="n">
         <v>7092</v>
@@ -1413,7 +1413,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G36" t="n">
-        <v>10.5830926895142</v>
+        <v>10.5830936431885</v>
       </c>
       <c r="H36" t="n">
         <v>6892</v>
@@ -1471,7 +1471,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G38" t="n">
-        <v>10.5830926895142</v>
+        <v>10.5830936431885</v>
       </c>
       <c r="H38" t="n">
         <v>1246</v>
@@ -1500,7 +1500,7 @@
         <v>11</v>
       </c>
       <c r="G39" t="n">
-        <v>10.0356912612915</v>
+        <v>10.0356903076172</v>
       </c>
       <c r="H39" t="n">
         <v>4188</v>
@@ -1529,7 +1529,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G40" t="n">
-        <v>9.79848384857178</v>
+        <v>9.79848289489746</v>
       </c>
       <c r="H40" t="n">
         <v>1526</v>
@@ -1587,7 +1587,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G42" t="n">
-        <v>9.76199150085449</v>
+        <v>9.76199054718018</v>
       </c>
       <c r="H42" t="n">
         <v>550</v>
@@ -1616,7 +1616,7 @@
         <v>10.7600002288818</v>
       </c>
       <c r="G43" t="n">
-        <v>9.81673049926758</v>
+        <v>9.81673145294189</v>
       </c>
       <c r="H43" t="n">
         <v>1169</v>
@@ -1645,7 +1645,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G44" t="n">
-        <v>10.2181577682495</v>
+        <v>10.2181587219238</v>
       </c>
       <c r="H44" t="n">
         <v>1100</v>
@@ -1732,7 +1732,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G47" t="n">
-        <v>11.6778964996338</v>
+        <v>11.6778955459595</v>
       </c>
       <c r="H47" t="n">
         <v>838</v>
@@ -1761,7 +1761,7 @@
         <v>13.0600004196167</v>
       </c>
       <c r="G48" t="n">
-        <v>11.9151039123535</v>
+        <v>11.9151029586792</v>
       </c>
       <c r="H48" t="n">
         <v>2600</v>
@@ -1790,7 +1790,7 @@
         <v>13</v>
       </c>
       <c r="G49" t="n">
-        <v>11.8603620529175</v>
+        <v>11.8603630065918</v>
       </c>
       <c r="H49" t="n">
         <v>2500</v>
@@ -1819,7 +1819,7 @@
         <v>13</v>
       </c>
       <c r="G50" t="n">
-        <v>11.8603620529175</v>
+        <v>11.8603630065918</v>
       </c>
       <c r="H50" t="n">
         <v>220</v>
@@ -1848,7 +1848,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G51" t="n">
-        <v>12.2252960205078</v>
+        <v>12.2252969741821</v>
       </c>
       <c r="H51" t="n">
         <v>1595</v>
@@ -2167,7 +2167,7 @@
         <v>13</v>
       </c>
       <c r="G62" t="n">
-        <v>11.8603620529175</v>
+        <v>11.8603630065918</v>
       </c>
       <c r="H62" t="n">
         <v>4800</v>
@@ -2283,7 +2283,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G66" t="n">
-        <v>11.2399740219116</v>
+        <v>11.2399730682373</v>
       </c>
       <c r="H66" t="n">
         <v>1218</v>
@@ -2370,7 +2370,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G69" t="n">
-        <v>11.9698429107666</v>
+        <v>11.9698419570923</v>
       </c>
       <c r="H69" t="n">
         <v>660</v>
@@ -2573,7 +2573,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G76" t="n">
-        <v>10.7655601501465</v>
+        <v>10.7655591964722</v>
       </c>
       <c r="H76" t="n">
         <v>20870</v>
@@ -2805,7 +2805,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G84" t="n">
-        <v>10.2181577682495</v>
+        <v>10.2181587219238</v>
       </c>
       <c r="H84" t="n">
         <v>1810</v>
@@ -3008,7 +3008,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G91" t="n">
-        <v>10.7655601501465</v>
+        <v>10.7655591964722</v>
       </c>
       <c r="H91" t="n">
         <v>1005</v>
@@ -3211,7 +3211,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G98" t="n">
-        <v>10.1816654205322</v>
+        <v>10.1816644668579</v>
       </c>
       <c r="H98" t="n">
         <v>35194</v>
@@ -3240,7 +3240,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G99" t="n">
-        <v>10.2181577682495</v>
+        <v>10.2181587219238</v>
       </c>
       <c r="H99" t="n">
         <v>1423</v>
@@ -3443,7 +3443,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G106" t="n">
-        <v>10.3093919754028</v>
+        <v>10.3093929290771</v>
       </c>
       <c r="H106" t="n">
         <v>1804</v>
@@ -3472,7 +3472,7 @@
         <v>11</v>
       </c>
       <c r="G107" t="n">
-        <v>10.0356912612915</v>
+        <v>10.0356903076172</v>
       </c>
       <c r="H107" t="n">
         <v>1778</v>
@@ -3530,7 +3530,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G109" t="n">
-        <v>10.2181577682495</v>
+        <v>10.2181587219238</v>
       </c>
       <c r="H109" t="n">
         <v>310</v>
@@ -3559,7 +3559,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G110" t="n">
-        <v>10.2181577682495</v>
+        <v>10.2181587219238</v>
       </c>
       <c r="H110" t="n">
         <v>260</v>
@@ -3588,7 +3588,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G111" t="n">
-        <v>10.2181577682495</v>
+        <v>10.2181587219238</v>
       </c>
       <c r="H111" t="n">
         <v>317</v>
@@ -3617,7 +3617,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G112" t="n">
-        <v>9.85322380065918</v>
+        <v>9.8532247543335</v>
       </c>
       <c r="H112" t="n">
         <v>600</v>
@@ -3646,7 +3646,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G113" t="n">
-        <v>10.1269264221191</v>
+        <v>10.1269254684448</v>
       </c>
       <c r="H113" t="n">
         <v>1110</v>
@@ -3675,7 +3675,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G114" t="n">
-        <v>10.1269264221191</v>
+        <v>10.1269254684448</v>
       </c>
       <c r="H114" t="n">
         <v>1005</v>
@@ -3704,7 +3704,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G115" t="n">
-        <v>10.2728986740112</v>
+        <v>10.2728977203369</v>
       </c>
       <c r="H115" t="n">
         <v>970</v>
@@ -3849,7 +3849,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G120" t="n">
-        <v>10.2728986740112</v>
+        <v>10.2728977203369</v>
       </c>
       <c r="H120" t="n">
         <v>3314</v>
@@ -3965,7 +3965,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G124" t="n">
-        <v>10.1816654205322</v>
+        <v>10.1816644668579</v>
       </c>
       <c r="H124" t="n">
         <v>695</v>
@@ -4081,7 +4081,7 @@
         <v>11.039999961853</v>
       </c>
       <c r="G128" t="n">
-        <v>10.0721845626831</v>
+        <v>10.0721855163574</v>
       </c>
       <c r="H128" t="n">
         <v>5476</v>
@@ -4110,7 +4110,7 @@
         <v>11.039999961853</v>
       </c>
       <c r="G129" t="n">
-        <v>10.0721845626831</v>
+        <v>10.0721855163574</v>
       </c>
       <c r="H129" t="n">
         <v>0</v>
@@ -4139,7 +4139,7 @@
         <v>11</v>
       </c>
       <c r="G130" t="n">
-        <v>10.0356912612915</v>
+        <v>10.0356903076172</v>
       </c>
       <c r="H130" t="n">
         <v>320</v>
@@ -4168,7 +4168,7 @@
         <v>11</v>
       </c>
       <c r="G131" t="n">
-        <v>10.0356912612915</v>
+        <v>10.0356903076172</v>
       </c>
       <c r="H131" t="n">
         <v>200</v>
@@ -4197,7 +4197,7 @@
         <v>11</v>
       </c>
       <c r="G132" t="n">
-        <v>10.0356912612915</v>
+        <v>10.0356903076172</v>
       </c>
       <c r="H132" t="n">
         <v>286</v>
@@ -4226,7 +4226,7 @@
         <v>11</v>
       </c>
       <c r="G133" t="n">
-        <v>10.0356912612915</v>
+        <v>10.0356903076172</v>
       </c>
       <c r="H133" t="n">
         <v>300</v>
@@ -4255,7 +4255,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="G134" t="n">
-        <v>10.510106086731</v>
+        <v>10.5101051330566</v>
       </c>
       <c r="H134" t="n">
         <v>274</v>
@@ -4400,7 +4400,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G139" t="n">
-        <v>10.1816654205322</v>
+        <v>10.1816644668579</v>
       </c>
       <c r="H139" t="n">
         <v>280</v>
@@ -4458,7 +4458,7 @@
         <v>11.2799997329712</v>
       </c>
       <c r="G141" t="n">
-        <v>10.2911443710327</v>
+        <v>10.291145324707</v>
       </c>
       <c r="H141" t="n">
         <v>250</v>
@@ -4516,7 +4516,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G143" t="n">
-        <v>10.2728986740112</v>
+        <v>10.2728977203369</v>
       </c>
       <c r="H143" t="n">
         <v>354</v>
@@ -4574,7 +4574,7 @@
         <v>11</v>
       </c>
       <c r="G145" t="n">
-        <v>10.0356912612915</v>
+        <v>10.0356903076172</v>
       </c>
       <c r="H145" t="n">
         <v>524</v>
@@ -4603,7 +4603,7 @@
         <v>11</v>
       </c>
       <c r="G146" t="n">
-        <v>10.0356912612915</v>
+        <v>10.0356903076172</v>
       </c>
       <c r="H146" t="n">
         <v>240</v>
@@ -4632,7 +4632,7 @@
         <v>11.2799997329712</v>
       </c>
       <c r="G147" t="n">
-        <v>10.2911443710327</v>
+        <v>10.291145324707</v>
       </c>
       <c r="H147" t="n">
         <v>780</v>
@@ -4661,7 +4661,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G148" t="n">
-        <v>10.3093919754028</v>
+        <v>10.3093929290771</v>
       </c>
       <c r="H148" t="n">
         <v>480</v>
@@ -4777,7 +4777,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G152" t="n">
-        <v>10.1269264221191</v>
+        <v>10.1269254684448</v>
       </c>
       <c r="H152" t="n">
         <v>398</v>
@@ -4893,7 +4893,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G156" t="n">
-        <v>10.1269264221191</v>
+        <v>10.1269254684448</v>
       </c>
       <c r="H156" t="n">
         <v>206</v>
@@ -4922,7 +4922,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G157" t="n">
-        <v>10.1269264221191</v>
+        <v>10.1269254684448</v>
       </c>
       <c r="H157" t="n">
         <v>0</v>
@@ -4980,7 +4980,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G159" t="n">
-        <v>10.1269264221191</v>
+        <v>10.1269254684448</v>
       </c>
       <c r="H159" t="n">
         <v>378</v>
@@ -5067,7 +5067,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G162" t="n">
-        <v>9.85322380065918</v>
+        <v>9.8532247543335</v>
       </c>
       <c r="H162" t="n">
         <v>559</v>
@@ -5125,7 +5125,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G164" t="n">
-        <v>10.1269264221191</v>
+        <v>10.1269254684448</v>
       </c>
       <c r="H164" t="n">
         <v>207</v>
@@ -5154,7 +5154,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G165" t="n">
-        <v>10.1816654205322</v>
+        <v>10.1816644668579</v>
       </c>
       <c r="H165" t="n">
         <v>40</v>
@@ -5183,7 +5183,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G166" t="n">
-        <v>10.3093919754028</v>
+        <v>10.3093929290771</v>
       </c>
       <c r="H166" t="n">
         <v>155</v>
@@ -5212,7 +5212,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G167" t="n">
-        <v>10.1816654205322</v>
+        <v>10.1816644668579</v>
       </c>
       <c r="H167" t="n">
         <v>3600</v>
@@ -5241,7 +5241,7 @@
         <v>11</v>
       </c>
       <c r="G168" t="n">
-        <v>10.0356912612915</v>
+        <v>10.0356903076172</v>
       </c>
       <c r="H168" t="n">
         <v>300</v>
@@ -5270,7 +5270,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G169" t="n">
-        <v>9.30582332611084</v>
+        <v>9.30582237243652</v>
       </c>
       <c r="H169" t="n">
         <v>1233</v>
@@ -5299,7 +5299,7 @@
         <v>10.3400001525879</v>
       </c>
       <c r="G170" t="n">
-        <v>9.43354988098145</v>
+        <v>9.43355083465576</v>
       </c>
       <c r="H170" t="n">
         <v>1910</v>
@@ -5328,7 +5328,7 @@
         <v>10.3400001525879</v>
       </c>
       <c r="G171" t="n">
-        <v>9.43354988098145</v>
+        <v>9.43355083465576</v>
       </c>
       <c r="H171" t="n">
         <v>388</v>
@@ -5357,7 +5357,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G172" t="n">
-        <v>9.39705753326416</v>
+        <v>9.39705657958984</v>
       </c>
       <c r="H172" t="n">
         <v>1640</v>
@@ -5444,7 +5444,7 @@
         <v>9.56999969482422</v>
       </c>
       <c r="G175" t="n">
-        <v>8.73105049133301</v>
+        <v>8.73105144500732</v>
       </c>
       <c r="H175" t="n">
         <v>6256</v>
@@ -5473,7 +5473,7 @@
         <v>9.5</v>
       </c>
       <c r="G176" t="n">
-        <v>8.66718769073486</v>
+        <v>8.66718864440918</v>
       </c>
       <c r="H176" t="n">
         <v>763</v>
@@ -5560,7 +5560,7 @@
         <v>9.43000030517578</v>
       </c>
       <c r="G179" t="n">
-        <v>8.60332489013672</v>
+        <v>8.6033239364624</v>
       </c>
       <c r="H179" t="n">
         <v>255</v>
@@ -5676,7 +5676,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G183" t="n">
-        <v>7.57238531112671</v>
+        <v>7.57238578796387</v>
       </c>
       <c r="H183" t="n">
         <v>4185</v>
@@ -5734,7 +5734,7 @@
         <v>8.60999965667725</v>
       </c>
       <c r="G185" t="n">
-        <v>7.8552098274231</v>
+        <v>7.85520935058594</v>
       </c>
       <c r="H185" t="n">
         <v>840</v>
@@ -5792,7 +5792,7 @@
         <v>9.01000022888184</v>
       </c>
       <c r="G187" t="n">
-        <v>8.22014427185059</v>
+        <v>8.22014331817627</v>
       </c>
       <c r="H187" t="n">
         <v>2520</v>
@@ -5850,7 +5850,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G189" t="n">
-        <v>8.27488231658936</v>
+        <v>8.27488327026367</v>
       </c>
       <c r="H189" t="n">
         <v>700</v>
@@ -5966,7 +5966,7 @@
         <v>8.59000015258789</v>
       </c>
       <c r="G193" t="n">
-        <v>7.83696317672729</v>
+        <v>7.83696269989014</v>
       </c>
       <c r="H193" t="n">
         <v>35</v>
@@ -6024,7 +6024,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G195" t="n">
-        <v>7.61800241470337</v>
+        <v>7.61800289154053</v>
       </c>
       <c r="H195" t="n">
         <v>289</v>
@@ -6053,7 +6053,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G196" t="n">
-        <v>7.61800241470337</v>
+        <v>7.61800289154053</v>
       </c>
       <c r="H196" t="n">
         <v>0</v>
@@ -6082,7 +6082,7 @@
         <v>8.25</v>
       </c>
       <c r="G197" t="n">
-        <v>7.52676916122437</v>
+        <v>7.52676868438721</v>
       </c>
       <c r="H197" t="n">
         <v>444</v>
@@ -6227,7 +6227,7 @@
         <v>8.60999965667725</v>
       </c>
       <c r="G202" t="n">
-        <v>7.8552098274231</v>
+        <v>7.85520935058594</v>
       </c>
       <c r="H202" t="n">
         <v>924</v>
@@ -6256,7 +6256,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G203" t="n">
-        <v>7.8825798034668</v>
+        <v>7.88258028030396</v>
       </c>
       <c r="H203" t="n">
         <v>60</v>
@@ -6285,7 +6285,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G204" t="n">
-        <v>7.8825798034668</v>
+        <v>7.88258028030396</v>
       </c>
       <c r="H204" t="n">
         <v>0</v>
@@ -6314,7 +6314,7 @@
         <v>8.60999965667725</v>
       </c>
       <c r="G205" t="n">
-        <v>7.8552098274231</v>
+        <v>7.85520935058594</v>
       </c>
       <c r="H205" t="n">
         <v>460</v>
@@ -6343,7 +6343,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G206" t="n">
-        <v>7.93731880187988</v>
+        <v>7.9373197555542</v>
       </c>
       <c r="H206" t="n">
         <v>1640</v>
@@ -6372,7 +6372,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G207" t="n">
-        <v>7.93731880187988</v>
+        <v>7.9373197555542</v>
       </c>
       <c r="H207" t="n">
         <v>0</v>
@@ -6401,7 +6401,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G208" t="n">
-        <v>7.93731880187988</v>
+        <v>7.9373197555542</v>
       </c>
       <c r="H208" t="n">
         <v>1100</v>
@@ -6430,7 +6430,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G209" t="n">
-        <v>7.93731880187988</v>
+        <v>7.9373197555542</v>
       </c>
       <c r="H209" t="n">
         <v>230</v>
@@ -6459,7 +6459,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G210" t="n">
-        <v>7.93731880187988</v>
+        <v>7.9373197555542</v>
       </c>
       <c r="H210" t="n">
         <v>0</v>
@@ -6488,7 +6488,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G211" t="n">
-        <v>7.97381258010864</v>
+        <v>7.9738130569458</v>
       </c>
       <c r="H211" t="n">
         <v>53910</v>
@@ -6604,7 +6604,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G215" t="n">
-        <v>8.27488231658936</v>
+        <v>8.27488327026367</v>
       </c>
       <c r="H215" t="n">
         <v>8078</v>
@@ -7010,7 +7010,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G229" t="n">
-        <v>8.57595443725586</v>
+        <v>8.57595348358154</v>
       </c>
       <c r="H229" t="n">
         <v>7583</v>
@@ -7039,7 +7039,7 @@
         <v>9.43000030517578</v>
       </c>
       <c r="G230" t="n">
-        <v>8.60332489013672</v>
+        <v>8.6033239364624</v>
       </c>
       <c r="H230" t="n">
         <v>26080</v>
@@ -7155,7 +7155,7 @@
         <v>9.43000030517578</v>
       </c>
       <c r="G234" t="n">
-        <v>8.60332489013672</v>
+        <v>8.6033239364624</v>
       </c>
       <c r="H234" t="n">
         <v>96</v>
@@ -7184,7 +7184,7 @@
         <v>9.43000030517578</v>
       </c>
       <c r="G235" t="n">
-        <v>8.60332489013672</v>
+        <v>8.6033239364624</v>
       </c>
       <c r="H235" t="n">
         <v>0</v>
@@ -7300,7 +7300,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G239" t="n">
-        <v>8.62157154083252</v>
+        <v>8.6215705871582</v>
       </c>
       <c r="H239" t="n">
         <v>2238</v>
@@ -7387,7 +7387,7 @@
         <v>9.63000011444092</v>
       </c>
       <c r="G242" t="n">
-        <v>8.78579139709473</v>
+        <v>8.78579235076904</v>
       </c>
       <c r="H242" t="n">
         <v>348</v>
@@ -7416,7 +7416,7 @@
         <v>9.63000011444092</v>
       </c>
       <c r="G243" t="n">
-        <v>8.78579139709473</v>
+        <v>8.78579235076904</v>
       </c>
       <c r="H243" t="n">
         <v>0</v>
@@ -7445,7 +7445,7 @@
         <v>9.63000011444092</v>
       </c>
       <c r="G244" t="n">
-        <v>8.78579139709473</v>
+        <v>8.78579235076904</v>
       </c>
       <c r="H244" t="n">
         <v>0</v>
@@ -7474,7 +7474,7 @@
         <v>9.63000011444092</v>
       </c>
       <c r="G245" t="n">
-        <v>8.78579139709473</v>
+        <v>8.78579235076904</v>
       </c>
       <c r="H245" t="n">
         <v>0</v>
@@ -7532,7 +7532,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G247" t="n">
-        <v>9.03212261199951</v>
+        <v>9.0321216583252</v>
       </c>
       <c r="H247" t="n">
         <v>200</v>
@@ -7561,7 +7561,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G248" t="n">
-        <v>9.03212261199951</v>
+        <v>9.0321216583252</v>
       </c>
       <c r="H248" t="n">
         <v>0</v>
@@ -7851,7 +7851,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G258" t="n">
-        <v>9.03212261199951</v>
+        <v>9.0321216583252</v>
       </c>
       <c r="H258" t="n">
         <v>300</v>
@@ -7909,7 +7909,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G260" t="n">
-        <v>8.84965419769287</v>
+        <v>8.84965515136719</v>
       </c>
       <c r="H260" t="n">
         <v>50</v>
@@ -7938,7 +7938,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G261" t="n">
-        <v>9.01387596130371</v>
+        <v>9.01387500762939</v>
       </c>
       <c r="H261" t="n">
         <v>519</v>
@@ -8141,7 +8141,7 @@
         <v>9.75</v>
       </c>
       <c r="G268" t="n">
-        <v>8.89527225494385</v>
+        <v>8.89527130126953</v>
       </c>
       <c r="H268" t="n">
         <v>380</v>
@@ -8170,7 +8170,7 @@
         <v>9.75</v>
       </c>
       <c r="G269" t="n">
-        <v>8.89527225494385</v>
+        <v>8.89527130126953</v>
       </c>
       <c r="H269" t="n">
         <v>1149</v>
@@ -8286,7 +8286,7 @@
         <v>8.92000007629395</v>
       </c>
       <c r="G273" t="n">
-        <v>8.13803291320801</v>
+        <v>8.13803386688232</v>
       </c>
       <c r="H273" t="n">
         <v>1470</v>
@@ -8373,7 +8373,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G276" t="n">
-        <v>8.35699367523193</v>
+        <v>8.35699462890625</v>
       </c>
       <c r="H276" t="n">
         <v>12610</v>
@@ -8460,7 +8460,7 @@
         <v>8.71000003814697</v>
       </c>
       <c r="G279" t="n">
-        <v>7.94644260406494</v>
+        <v>7.9464430809021</v>
       </c>
       <c r="H279" t="n">
         <v>7948</v>
@@ -8489,7 +8489,7 @@
         <v>8.72999954223633</v>
       </c>
       <c r="G280" t="n">
-        <v>7.96468925476074</v>
+        <v>7.9646897315979</v>
       </c>
       <c r="H280" t="n">
         <v>1620</v>
@@ -8576,7 +8576,7 @@
         <v>8.77000045776367</v>
       </c>
       <c r="G283" t="n">
-        <v>8.00118350982666</v>
+        <v>8.00118446350098</v>
       </c>
       <c r="H283" t="n">
         <v>2377</v>
@@ -8634,7 +8634,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G285" t="n">
-        <v>8.37524032592773</v>
+        <v>8.37524127960205</v>
       </c>
       <c r="H285" t="n">
         <v>1200</v>
@@ -8663,7 +8663,7 @@
         <v>9.09000015258789</v>
       </c>
       <c r="G286" t="n">
-        <v>8.29312992095947</v>
+        <v>8.29313087463379</v>
       </c>
       <c r="H286" t="n">
         <v>7374</v>
@@ -8692,7 +8692,7 @@
         <v>9.09000015258789</v>
       </c>
       <c r="G287" t="n">
-        <v>8.29312992095947</v>
+        <v>8.29313087463379</v>
       </c>
       <c r="H287" t="n">
         <v>760</v>
@@ -8721,7 +8721,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G288" t="n">
-        <v>8.27488231658936</v>
+        <v>8.27488327026367</v>
       </c>
       <c r="H288" t="n">
         <v>6201</v>
@@ -8866,7 +8866,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G293" t="n">
-        <v>8.27488231658936</v>
+        <v>8.27488327026367</v>
       </c>
       <c r="H293" t="n">
         <v>1783</v>
@@ -8924,7 +8924,7 @@
         <v>9.27000045776367</v>
       </c>
       <c r="G295" t="n">
-        <v>8.45735168457031</v>
+        <v>8.457350730896</v>
       </c>
       <c r="H295" t="n">
         <v>260</v>
@@ -9098,7 +9098,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G301" t="n">
-        <v>8.34786987304688</v>
+        <v>8.34787082672119</v>
       </c>
       <c r="H301" t="n">
         <v>519</v>
@@ -9301,7 +9301,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G308" t="n">
-        <v>8.37524032592773</v>
+        <v>8.37524127960205</v>
       </c>
       <c r="H308" t="n">
         <v>99</v>
@@ -9330,7 +9330,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G309" t="n">
-        <v>8.19277381896973</v>
+        <v>8.19277286529541</v>
       </c>
       <c r="H309" t="n">
         <v>191</v>
@@ -9475,7 +9475,7 @@
         <v>9.01000022888184</v>
       </c>
       <c r="G314" t="n">
-        <v>8.22014427185059</v>
+        <v>8.22014331817627</v>
       </c>
       <c r="H314" t="n">
         <v>680</v>
@@ -9504,7 +9504,7 @@
         <v>9.01000022888184</v>
       </c>
       <c r="G315" t="n">
-        <v>8.22014427185059</v>
+        <v>8.22014331817627</v>
       </c>
       <c r="H315" t="n">
         <v>0</v>
@@ -9678,7 +9678,7 @@
         <v>9.5</v>
       </c>
       <c r="G321" t="n">
-        <v>8.66718769073486</v>
+        <v>8.66718864440918</v>
       </c>
       <c r="H321" t="n">
         <v>38099</v>
@@ -9736,7 +9736,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G323" t="n">
-        <v>8.28400611877441</v>
+        <v>8.28400707244873</v>
       </c>
       <c r="H323" t="n">
         <v>8366</v>
@@ -9765,7 +9765,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G324" t="n">
-        <v>8.28400611877441</v>
+        <v>8.28400707244873</v>
       </c>
       <c r="H324" t="n">
         <v>0</v>
@@ -9852,7 +9852,7 @@
         <v>8.92000007629395</v>
       </c>
       <c r="G327" t="n">
-        <v>8.13803291320801</v>
+        <v>8.13803386688232</v>
       </c>
       <c r="H327" t="n">
         <v>200</v>
@@ -9968,7 +9968,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G331" t="n">
-        <v>8.59420204162598</v>
+        <v>8.59420108795166</v>
       </c>
       <c r="H331" t="n">
         <v>5649</v>
@@ -10084,7 +10084,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G335" t="n">
-        <v>8.24751472473145</v>
+        <v>8.24751377105713</v>
       </c>
       <c r="H335" t="n">
         <v>7514</v>
@@ -10171,7 +10171,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G338" t="n">
-        <v>7.93731880187988</v>
+        <v>7.9373197555542</v>
       </c>
       <c r="H338" t="n">
         <v>2490</v>
@@ -10200,7 +10200,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G339" t="n">
-        <v>7.53589200973511</v>
+        <v>7.53589153289795</v>
       </c>
       <c r="H339" t="n">
         <v>74770</v>
@@ -10229,7 +10229,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G340" t="n">
-        <v>7.57238531112671</v>
+        <v>7.57238578796387</v>
       </c>
       <c r="H340" t="n">
         <v>7020</v>
@@ -10432,7 +10432,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G347" t="n">
-        <v>7.53589200973511</v>
+        <v>7.53589153289795</v>
       </c>
       <c r="H347" t="n">
         <v>1406</v>
@@ -10577,7 +10577,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G352" t="n">
-        <v>7.3169322013855</v>
+        <v>7.31693172454834</v>
       </c>
       <c r="H352" t="n">
         <v>63</v>
@@ -10635,7 +10635,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G354" t="n">
-        <v>7.20745134353638</v>
+        <v>7.20745182037354</v>
       </c>
       <c r="H354" t="n">
         <v>2421</v>
@@ -10983,7 +10983,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G366" t="n">
-        <v>6.95199728012085</v>
+        <v>6.95199680328369</v>
       </c>
       <c r="H366" t="n">
         <v>3628</v>
@@ -11041,7 +11041,7 @@
         <v>7.51999998092651</v>
       </c>
       <c r="G368" t="n">
-        <v>6.86076307296753</v>
+        <v>6.86076354980469</v>
       </c>
       <c r="H368" t="n">
         <v>5487</v>
@@ -11070,7 +11070,7 @@
         <v>7.51999998092651</v>
       </c>
       <c r="G369" t="n">
-        <v>6.86076307296753</v>
+        <v>6.86076354980469</v>
       </c>
       <c r="H369" t="n">
         <v>45</v>
@@ -11099,7 +11099,7 @@
         <v>7.5</v>
       </c>
       <c r="G370" t="n">
-        <v>6.84251689910889</v>
+        <v>6.84251737594604</v>
       </c>
       <c r="H370" t="n">
         <v>3522</v>
@@ -11128,7 +11128,7 @@
         <v>7.51999998092651</v>
       </c>
       <c r="G371" t="n">
-        <v>6.86076307296753</v>
+        <v>6.86076354980469</v>
       </c>
       <c r="H371" t="n">
         <v>50</v>
@@ -11157,7 +11157,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G372" t="n">
-        <v>6.95199728012085</v>
+        <v>6.95199680328369</v>
       </c>
       <c r="H372" t="n">
         <v>500</v>
@@ -11389,7 +11389,7 @@
         <v>7.5</v>
       </c>
       <c r="G380" t="n">
-        <v>6.84251689910889</v>
+        <v>6.84251737594604</v>
       </c>
       <c r="H380" t="n">
         <v>884</v>
@@ -11418,7 +11418,7 @@
         <v>7.5</v>
       </c>
       <c r="G381" t="n">
-        <v>6.84251689910889</v>
+        <v>6.84251737594604</v>
       </c>
       <c r="H381" t="n">
         <v>2217</v>
@@ -11447,7 +11447,7 @@
         <v>7.5</v>
       </c>
       <c r="G382" t="n">
-        <v>6.84251689910889</v>
+        <v>6.84251737594604</v>
       </c>
       <c r="H382" t="n">
         <v>0</v>
@@ -11650,7 +11650,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G389" t="n">
-        <v>7.17095804214478</v>
+        <v>7.17095756530762</v>
       </c>
       <c r="H389" t="n">
         <v>7937</v>
@@ -11679,7 +11679,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G390" t="n">
-        <v>7.3899188041687</v>
+        <v>7.38991832733154</v>
       </c>
       <c r="H390" t="n">
         <v>4671</v>
@@ -11737,7 +11737,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G392" t="n">
-        <v>7.57238531112671</v>
+        <v>7.57238578796387</v>
       </c>
       <c r="H392" t="n">
         <v>630</v>
@@ -11766,7 +11766,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G393" t="n">
-        <v>7.57238531112671</v>
+        <v>7.57238578796387</v>
       </c>
       <c r="H393" t="n">
         <v>0</v>
@@ -11795,7 +11795,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G394" t="n">
-        <v>7.57238531112671</v>
+        <v>7.57238578796387</v>
       </c>
       <c r="H394" t="n">
         <v>100</v>
@@ -11824,7 +11824,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G395" t="n">
-        <v>7.57238531112671</v>
+        <v>7.57238578796387</v>
       </c>
       <c r="H395" t="n">
         <v>24200</v>
@@ -11853,7 +11853,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G396" t="n">
-        <v>7.57238531112671</v>
+        <v>7.57238578796387</v>
       </c>
       <c r="H396" t="n">
         <v>0</v>
@@ -12056,7 +12056,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G403" t="n">
-        <v>7.49939870834351</v>
+        <v>7.49939918518066</v>
       </c>
       <c r="H403" t="n">
         <v>750</v>
@@ -12375,7 +12375,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G414" t="n">
-        <v>7.44465827941895</v>
+        <v>7.4446587562561</v>
       </c>
       <c r="H414" t="n">
         <v>210</v>
@@ -12404,7 +12404,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G415" t="n">
-        <v>7.44465827941895</v>
+        <v>7.4446587562561</v>
       </c>
       <c r="H415" t="n">
         <v>0</v>
@@ -12665,7 +12665,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G424" t="n">
-        <v>7.44465827941895</v>
+        <v>7.4446587562561</v>
       </c>
       <c r="H424" t="n">
         <v>2000</v>
@@ -12694,7 +12694,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G425" t="n">
-        <v>7.60887861251831</v>
+        <v>7.60887908935547</v>
       </c>
       <c r="H425" t="n">
         <v>12400</v>
@@ -12723,7 +12723,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G426" t="n">
-        <v>7.79134559631348</v>
+        <v>7.79134511947632</v>
       </c>
       <c r="H426" t="n">
         <v>3239</v>
@@ -12752,7 +12752,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G427" t="n">
-        <v>7.8825798034668</v>
+        <v>7.88258028030396</v>
       </c>
       <c r="H427" t="n">
         <v>41</v>
@@ -12868,7 +12868,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G431" t="n">
-        <v>7.55413818359375</v>
+        <v>7.55413770675659</v>
       </c>
       <c r="H431" t="n">
         <v>428</v>
@@ -12897,7 +12897,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G432" t="n">
-        <v>7.55413818359375</v>
+        <v>7.55413770675659</v>
       </c>
       <c r="H432" t="n">
         <v>0</v>
@@ -13187,7 +13187,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G442" t="n">
-        <v>6.80602359771729</v>
+        <v>6.80602312088013</v>
       </c>
       <c r="H442" t="n">
         <v>1912</v>
@@ -13216,7 +13216,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G443" t="n">
-        <v>6.75128316879272</v>
+        <v>6.75128364562988</v>
       </c>
       <c r="H443" t="n">
         <v>690</v>
@@ -13245,7 +13245,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G444" t="n">
-        <v>6.75128316879272</v>
+        <v>6.75128364562988</v>
       </c>
       <c r="H444" t="n">
         <v>740</v>
@@ -13390,7 +13390,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G449" t="n">
-        <v>6.75128316879272</v>
+        <v>6.75128364562988</v>
       </c>
       <c r="H449" t="n">
         <v>1995</v>
@@ -13419,7 +13419,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G450" t="n">
-        <v>6.75128316879272</v>
+        <v>6.75128364562988</v>
       </c>
       <c r="H450" t="n">
         <v>0</v>
@@ -13448,7 +13448,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G451" t="n">
-        <v>6.75128316879272</v>
+        <v>6.75128364562988</v>
       </c>
       <c r="H451" t="n">
         <v>0</v>
@@ -13477,7 +13477,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G452" t="n">
-        <v>6.75128316879272</v>
+        <v>6.75128364562988</v>
       </c>
       <c r="H452" t="n">
         <v>0</v>
@@ -13506,7 +13506,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G453" t="n">
-        <v>6.75128316879272</v>
+        <v>6.75128364562988</v>
       </c>
       <c r="H453" t="n">
         <v>0</v>
@@ -13535,7 +13535,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G454" t="n">
-        <v>6.75128316879272</v>
+        <v>6.75128364562988</v>
       </c>
       <c r="H454" t="n">
         <v>1400</v>
@@ -13564,7 +13564,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G455" t="n">
-        <v>6.58706283569336</v>
+        <v>6.5870623588562</v>
       </c>
       <c r="H455" t="n">
         <v>200</v>
@@ -13593,7 +13593,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G456" t="n">
-        <v>6.4775824546814</v>
+        <v>6.47758293151855</v>
       </c>
       <c r="H456" t="n">
         <v>1083</v>
@@ -13680,7 +13680,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G459" t="n">
-        <v>6.4775824546814</v>
+        <v>6.47758293151855</v>
       </c>
       <c r="H459" t="n">
         <v>1900</v>
@@ -13825,7 +13825,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G464" t="n">
-        <v>6.56881618499756</v>
+        <v>6.5688157081604</v>
       </c>
       <c r="H464" t="n">
         <v>4878</v>
@@ -13854,7 +13854,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G465" t="n">
-        <v>6.56881618499756</v>
+        <v>6.5688157081604</v>
       </c>
       <c r="H465" t="n">
         <v>2702</v>
@@ -13883,7 +13883,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G466" t="n">
-        <v>6.56881618499756</v>
+        <v>6.5688157081604</v>
       </c>
       <c r="H466" t="n">
         <v>0</v>
@@ -13912,7 +13912,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G467" t="n">
-        <v>6.56881618499756</v>
+        <v>6.5688157081604</v>
       </c>
       <c r="H467" t="n">
         <v>0</v>
@@ -13941,7 +13941,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G468" t="n">
-        <v>6.56881618499756</v>
+        <v>6.5688157081604</v>
       </c>
       <c r="H468" t="n">
         <v>0</v>
@@ -14086,7 +14086,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G473" t="n">
-        <v>6.42284297943115</v>
+        <v>6.42284250259399</v>
       </c>
       <c r="H473" t="n">
         <v>600</v>
@@ -14144,7 +14144,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G475" t="n">
-        <v>6.67829608917236</v>
+        <v>6.67829656600952</v>
       </c>
       <c r="H475" t="n">
         <v>1738</v>
@@ -14173,7 +14173,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G476" t="n">
-        <v>6.67829608917236</v>
+        <v>6.67829656600952</v>
       </c>
       <c r="H476" t="n">
         <v>1500</v>
@@ -14405,7 +14405,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G484" t="n">
-        <v>6.58706283569336</v>
+        <v>6.5870623588562</v>
       </c>
       <c r="H484" t="n">
         <v>1565</v>
@@ -14434,7 +14434,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G485" t="n">
-        <v>6.58706283569336</v>
+        <v>6.5870623588562</v>
       </c>
       <c r="H485" t="n">
         <v>0</v>
@@ -14463,7 +14463,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G486" t="n">
-        <v>6.58706283569336</v>
+        <v>6.5870623588562</v>
       </c>
       <c r="H486" t="n">
         <v>0</v>
@@ -14492,7 +14492,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G487" t="n">
-        <v>6.64180278778076</v>
+        <v>6.64180326461792</v>
       </c>
       <c r="H487" t="n">
         <v>565</v>
@@ -14521,7 +14521,7 @@
         <v>7.5</v>
       </c>
       <c r="G488" t="n">
-        <v>6.84251689910889</v>
+        <v>6.84251737594604</v>
       </c>
       <c r="H488" t="n">
         <v>1463</v>
@@ -14608,7 +14608,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G491" t="n">
-        <v>7.18920469284058</v>
+        <v>7.18920421600342</v>
       </c>
       <c r="H491" t="n">
         <v>1500</v>
@@ -14637,7 +14637,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G492" t="n">
-        <v>7.20745134353638</v>
+        <v>7.20745182037354</v>
       </c>
       <c r="H492" t="n">
         <v>1450</v>
@@ -14666,7 +14666,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G493" t="n">
-        <v>7.22569751739502</v>
+        <v>7.22569799423218</v>
       </c>
       <c r="H493" t="n">
         <v>800</v>
@@ -15072,7 +15072,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G507" t="n">
-        <v>7.3169322013855</v>
+        <v>7.31693172454834</v>
       </c>
       <c r="H507" t="n">
         <v>772</v>
@@ -15188,7 +15188,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G511" t="n">
-        <v>7.20745134353638</v>
+        <v>7.20745182037354</v>
       </c>
       <c r="H511" t="n">
         <v>221</v>
@@ -15217,7 +15217,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G512" t="n">
-        <v>7.3169322013855</v>
+        <v>7.31693172454834</v>
       </c>
       <c r="H512" t="n">
         <v>1280</v>
@@ -15246,7 +15246,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G513" t="n">
-        <v>7.20745134353638</v>
+        <v>7.20745182037354</v>
       </c>
       <c r="H513" t="n">
         <v>900</v>
@@ -15362,7 +15362,7 @@
         <v>7.51999998092651</v>
       </c>
       <c r="G517" t="n">
-        <v>6.86076307296753</v>
+        <v>6.86076354980469</v>
       </c>
       <c r="H517" t="n">
         <v>3626</v>
@@ -15391,7 +15391,7 @@
         <v>7.5</v>
       </c>
       <c r="G518" t="n">
-        <v>6.84251689910889</v>
+        <v>6.84251737594604</v>
       </c>
       <c r="H518" t="n">
         <v>3782</v>
@@ -15420,7 +15420,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G519" t="n">
-        <v>6.80602359771729</v>
+        <v>6.80602312088013</v>
       </c>
       <c r="H519" t="n">
         <v>109</v>
@@ -15739,7 +15739,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G530" t="n">
-        <v>7.17095804214478</v>
+        <v>7.17095756530762</v>
       </c>
       <c r="H530" t="n">
         <v>2115</v>
@@ -15913,7 +15913,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G536" t="n">
-        <v>7.3899188041687</v>
+        <v>7.38991832733154</v>
       </c>
       <c r="H536" t="n">
         <v>18461</v>
@@ -15942,7 +15942,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G537" t="n">
-        <v>7.18920469284058</v>
+        <v>7.18920421600342</v>
       </c>
       <c r="H537" t="n">
         <v>29589</v>
@@ -16000,7 +16000,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G539" t="n">
-        <v>7.20745134353638</v>
+        <v>7.20745182037354</v>
       </c>
       <c r="H539" t="n">
         <v>3149</v>
@@ -16029,7 +16029,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G540" t="n">
-        <v>7.20745134353638</v>
+        <v>7.20745182037354</v>
       </c>
       <c r="H540" t="n">
         <v>0</v>
@@ -16145,7 +16145,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G544" t="n">
-        <v>7.3169322013855</v>
+        <v>7.31693172454834</v>
       </c>
       <c r="H544" t="n">
         <v>3852</v>
@@ -16174,7 +16174,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G545" t="n">
-        <v>7.20745134353638</v>
+        <v>7.20745182037354</v>
       </c>
       <c r="H545" t="n">
         <v>13099</v>
@@ -16261,7 +16261,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G548" t="n">
-        <v>7.3899188041687</v>
+        <v>7.38991832733154</v>
       </c>
       <c r="H548" t="n">
         <v>1200</v>
@@ -16290,7 +16290,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G549" t="n">
-        <v>7.55413818359375</v>
+        <v>7.55413770675659</v>
       </c>
       <c r="H549" t="n">
         <v>217</v>
@@ -16319,7 +16319,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G550" t="n">
-        <v>7.49939870834351</v>
+        <v>7.49939918518066</v>
       </c>
       <c r="H550" t="n">
         <v>4760</v>
@@ -16435,7 +16435,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G554" t="n">
-        <v>7.57238531112671</v>
+        <v>7.57238578796387</v>
       </c>
       <c r="H554" t="n">
         <v>1776</v>
@@ -16464,7 +16464,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G555" t="n">
-        <v>7.57238531112671</v>
+        <v>7.57238578796387</v>
       </c>
       <c r="H555" t="n">
         <v>733</v>
@@ -16928,7 +16928,7 @@
         <v>8.25</v>
       </c>
       <c r="G571" t="n">
-        <v>7.52676916122437</v>
+        <v>7.52676868438721</v>
       </c>
       <c r="H571" t="n">
         <v>2468</v>
@@ -17073,7 +17073,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G576" t="n">
-        <v>7.61800241470337</v>
+        <v>7.61800289154053</v>
       </c>
       <c r="H576" t="n">
         <v>4229</v>
@@ -17102,7 +17102,7 @@
         <v>8.25</v>
       </c>
       <c r="G577" t="n">
-        <v>7.52676916122437</v>
+        <v>7.52676868438721</v>
       </c>
       <c r="H577" t="n">
         <v>10687</v>
@@ -17131,7 +17131,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G578" t="n">
-        <v>7.25306749343872</v>
+        <v>7.25306797027588</v>
       </c>
       <c r="H578" t="n">
         <v>14460</v>
@@ -17218,7 +17218,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G581" t="n">
-        <v>7.3899188041687</v>
+        <v>7.38991832733154</v>
       </c>
       <c r="H581" t="n">
         <v>540</v>
@@ -17334,7 +17334,7 @@
         <v>8.25</v>
       </c>
       <c r="G585" t="n">
-        <v>7.52676916122437</v>
+        <v>7.52676868438721</v>
       </c>
       <c r="H585" t="n">
         <v>1560</v>
@@ -17363,7 +17363,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G586" t="n">
-        <v>7.3899188041687</v>
+        <v>7.38991832733154</v>
       </c>
       <c r="H586" t="n">
         <v>3341</v>
@@ -17392,7 +17392,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G587" t="n">
-        <v>7.3899188041687</v>
+        <v>7.38991832733154</v>
       </c>
       <c r="H587" t="n">
         <v>340</v>
@@ -17450,7 +17450,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G589" t="n">
-        <v>7.3899188041687</v>
+        <v>7.38991832733154</v>
       </c>
       <c r="H589" t="n">
         <v>1325</v>
@@ -17479,7 +17479,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G590" t="n">
-        <v>7.3899188041687</v>
+        <v>7.38991832733154</v>
       </c>
       <c r="H590" t="n">
         <v>851</v>
@@ -17508,7 +17508,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G591" t="n">
-        <v>7.3899188041687</v>
+        <v>7.38991832733154</v>
       </c>
       <c r="H591" t="n">
         <v>22104</v>
@@ -17537,7 +17537,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G592" t="n">
-        <v>7.3899188041687</v>
+        <v>7.38991832733154</v>
       </c>
       <c r="H592" t="n">
         <v>0</v>
@@ -17856,7 +17856,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G603" t="n">
-        <v>7.25306749343872</v>
+        <v>7.25306797027588</v>
       </c>
       <c r="H603" t="n">
         <v>19392</v>

--- a/data/SVS.MI.xlsx
+++ b/data/SVS.MI.xlsx
@@ -514,7 +514,7 @@
         <v>14.5600004196167</v>
       </c>
       <c r="G5" t="n">
-        <v>13.2836065292358</v>
+        <v>13.2836055755615</v>
       </c>
       <c r="H5" t="n">
         <v>2134</v>
@@ -543,7 +543,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G6" t="n">
-        <v>13.4113321304321</v>
+        <v>13.4113330841064</v>
       </c>
       <c r="H6" t="n">
         <v>1997</v>
@@ -833,7 +833,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G16" t="n">
-        <v>12.2435445785522</v>
+        <v>12.2435436248779</v>
       </c>
       <c r="H16" t="n">
         <v>2540</v>
@@ -891,7 +891,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G18" t="n">
-        <v>12.2252969741821</v>
+        <v>12.2252960205078</v>
       </c>
       <c r="H18" t="n">
         <v>2456</v>
@@ -978,7 +978,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G21" t="n">
-        <v>12.4077634811401</v>
+        <v>12.4077644348145</v>
       </c>
       <c r="H21" t="n">
         <v>2900</v>
@@ -1036,7 +1036,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G23" t="n">
-        <v>12.2252969741821</v>
+        <v>12.2252960205078</v>
       </c>
       <c r="H23" t="n">
         <v>1882</v>
@@ -1123,7 +1123,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G26" t="n">
-        <v>11.9698419570923</v>
+        <v>11.9698429107666</v>
       </c>
       <c r="H26" t="n">
         <v>4682</v>
@@ -1181,7 +1181,7 @@
         <v>13</v>
       </c>
       <c r="G28" t="n">
-        <v>11.8603630065918</v>
+        <v>11.8603620529175</v>
       </c>
       <c r="H28" t="n">
         <v>2250</v>
@@ -1210,7 +1210,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G29" t="n">
-        <v>11.6778955459595</v>
+        <v>11.6778964996338</v>
       </c>
       <c r="H29" t="n">
         <v>1108</v>
@@ -1355,7 +1355,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G34" t="n">
-        <v>11.20348072052</v>
+        <v>11.2034816741943</v>
       </c>
       <c r="H34" t="n">
         <v>7092</v>
@@ -1413,7 +1413,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G36" t="n">
-        <v>10.5830936431885</v>
+        <v>10.5830926895142</v>
       </c>
       <c r="H36" t="n">
         <v>6892</v>
@@ -1471,7 +1471,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G38" t="n">
-        <v>10.5830936431885</v>
+        <v>10.5830926895142</v>
       </c>
       <c r="H38" t="n">
         <v>1246</v>
@@ -1500,7 +1500,7 @@
         <v>11</v>
       </c>
       <c r="G39" t="n">
-        <v>10.0356903076172</v>
+        <v>10.0356912612915</v>
       </c>
       <c r="H39" t="n">
         <v>4188</v>
@@ -1529,7 +1529,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G40" t="n">
-        <v>9.79848289489746</v>
+        <v>9.79848384857178</v>
       </c>
       <c r="H40" t="n">
         <v>1526</v>
@@ -1587,7 +1587,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G42" t="n">
-        <v>9.76199054718018</v>
+        <v>9.76199150085449</v>
       </c>
       <c r="H42" t="n">
         <v>550</v>
@@ -1616,7 +1616,7 @@
         <v>10.7600002288818</v>
       </c>
       <c r="G43" t="n">
-        <v>9.81673145294189</v>
+        <v>9.81673049926758</v>
       </c>
       <c r="H43" t="n">
         <v>1169</v>
@@ -1645,7 +1645,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G44" t="n">
-        <v>10.2181587219238</v>
+        <v>10.2181577682495</v>
       </c>
       <c r="H44" t="n">
         <v>1100</v>
@@ -1732,7 +1732,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G47" t="n">
-        <v>11.6778955459595</v>
+        <v>11.6778964996338</v>
       </c>
       <c r="H47" t="n">
         <v>838</v>
@@ -1761,7 +1761,7 @@
         <v>13.0600004196167</v>
       </c>
       <c r="G48" t="n">
-        <v>11.9151029586792</v>
+        <v>11.9151039123535</v>
       </c>
       <c r="H48" t="n">
         <v>2600</v>
@@ -1790,7 +1790,7 @@
         <v>13</v>
       </c>
       <c r="G49" t="n">
-        <v>11.8603630065918</v>
+        <v>11.8603620529175</v>
       </c>
       <c r="H49" t="n">
         <v>2500</v>
@@ -1819,7 +1819,7 @@
         <v>13</v>
       </c>
       <c r="G50" t="n">
-        <v>11.8603630065918</v>
+        <v>11.8603620529175</v>
       </c>
       <c r="H50" t="n">
         <v>220</v>
@@ -1848,7 +1848,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G51" t="n">
-        <v>12.2252969741821</v>
+        <v>12.2252960205078</v>
       </c>
       <c r="H51" t="n">
         <v>1595</v>
@@ -2167,7 +2167,7 @@
         <v>13</v>
       </c>
       <c r="G62" t="n">
-        <v>11.8603630065918</v>
+        <v>11.8603620529175</v>
       </c>
       <c r="H62" t="n">
         <v>4800</v>
@@ -2283,7 +2283,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G66" t="n">
-        <v>11.2399730682373</v>
+        <v>11.2399740219116</v>
       </c>
       <c r="H66" t="n">
         <v>1218</v>
@@ -2370,7 +2370,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G69" t="n">
-        <v>11.9698419570923</v>
+        <v>11.9698429107666</v>
       </c>
       <c r="H69" t="n">
         <v>660</v>
@@ -2573,7 +2573,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G76" t="n">
-        <v>10.7655591964722</v>
+        <v>10.7655601501465</v>
       </c>
       <c r="H76" t="n">
         <v>20870</v>
@@ -2805,7 +2805,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G84" t="n">
-        <v>10.2181587219238</v>
+        <v>10.2181577682495</v>
       </c>
       <c r="H84" t="n">
         <v>1810</v>
@@ -3008,7 +3008,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G91" t="n">
-        <v>10.7655591964722</v>
+        <v>10.7655601501465</v>
       </c>
       <c r="H91" t="n">
         <v>1005</v>
@@ -3211,7 +3211,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G98" t="n">
-        <v>10.1816644668579</v>
+        <v>10.1816654205322</v>
       </c>
       <c r="H98" t="n">
         <v>35194</v>
@@ -3240,7 +3240,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G99" t="n">
-        <v>10.2181587219238</v>
+        <v>10.2181577682495</v>
       </c>
       <c r="H99" t="n">
         <v>1423</v>
@@ -3443,7 +3443,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G106" t="n">
-        <v>10.3093929290771</v>
+        <v>10.3093919754028</v>
       </c>
       <c r="H106" t="n">
         <v>1804</v>
@@ -3472,7 +3472,7 @@
         <v>11</v>
       </c>
       <c r="G107" t="n">
-        <v>10.0356903076172</v>
+        <v>10.0356912612915</v>
       </c>
       <c r="H107" t="n">
         <v>1778</v>
@@ -3530,7 +3530,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G109" t="n">
-        <v>10.2181587219238</v>
+        <v>10.2181577682495</v>
       </c>
       <c r="H109" t="n">
         <v>310</v>
@@ -3559,7 +3559,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G110" t="n">
-        <v>10.2181587219238</v>
+        <v>10.2181577682495</v>
       </c>
       <c r="H110" t="n">
         <v>260</v>
@@ -3588,7 +3588,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G111" t="n">
-        <v>10.2181587219238</v>
+        <v>10.2181577682495</v>
       </c>
       <c r="H111" t="n">
         <v>317</v>
@@ -3617,7 +3617,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G112" t="n">
-        <v>9.8532247543335</v>
+        <v>9.85322380065918</v>
       </c>
       <c r="H112" t="n">
         <v>600</v>
@@ -3646,7 +3646,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G113" t="n">
-        <v>10.1269254684448</v>
+        <v>10.1269264221191</v>
       </c>
       <c r="H113" t="n">
         <v>1110</v>
@@ -3675,7 +3675,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G114" t="n">
-        <v>10.1269254684448</v>
+        <v>10.1269264221191</v>
       </c>
       <c r="H114" t="n">
         <v>1005</v>
@@ -3704,7 +3704,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G115" t="n">
-        <v>10.2728977203369</v>
+        <v>10.2728986740112</v>
       </c>
       <c r="H115" t="n">
         <v>970</v>
@@ -3849,7 +3849,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G120" t="n">
-        <v>10.2728977203369</v>
+        <v>10.2728986740112</v>
       </c>
       <c r="H120" t="n">
         <v>3314</v>
@@ -3965,7 +3965,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G124" t="n">
-        <v>10.1816644668579</v>
+        <v>10.1816654205322</v>
       </c>
       <c r="H124" t="n">
         <v>695</v>
@@ -4081,7 +4081,7 @@
         <v>11.039999961853</v>
       </c>
       <c r="G128" t="n">
-        <v>10.0721855163574</v>
+        <v>10.0721845626831</v>
       </c>
       <c r="H128" t="n">
         <v>5476</v>
@@ -4110,7 +4110,7 @@
         <v>11.039999961853</v>
       </c>
       <c r="G129" t="n">
-        <v>10.0721855163574</v>
+        <v>10.0721845626831</v>
       </c>
       <c r="H129" t="n">
         <v>0</v>
@@ -4139,7 +4139,7 @@
         <v>11</v>
       </c>
       <c r="G130" t="n">
-        <v>10.0356903076172</v>
+        <v>10.0356912612915</v>
       </c>
       <c r="H130" t="n">
         <v>320</v>
@@ -4168,7 +4168,7 @@
         <v>11</v>
       </c>
       <c r="G131" t="n">
-        <v>10.0356903076172</v>
+        <v>10.0356912612915</v>
       </c>
       <c r="H131" t="n">
         <v>200</v>
@@ -4197,7 +4197,7 @@
         <v>11</v>
       </c>
       <c r="G132" t="n">
-        <v>10.0356903076172</v>
+        <v>10.0356912612915</v>
       </c>
       <c r="H132" t="n">
         <v>286</v>
@@ -4226,7 +4226,7 @@
         <v>11</v>
       </c>
       <c r="G133" t="n">
-        <v>10.0356903076172</v>
+        <v>10.0356912612915</v>
       </c>
       <c r="H133" t="n">
         <v>300</v>
@@ -4255,7 +4255,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="G134" t="n">
-        <v>10.5101051330566</v>
+        <v>10.510106086731</v>
       </c>
       <c r="H134" t="n">
         <v>274</v>
@@ -4400,7 +4400,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G139" t="n">
-        <v>10.1816644668579</v>
+        <v>10.1816654205322</v>
       </c>
       <c r="H139" t="n">
         <v>280</v>
@@ -4458,7 +4458,7 @@
         <v>11.2799997329712</v>
       </c>
       <c r="G141" t="n">
-        <v>10.291145324707</v>
+        <v>10.2911443710327</v>
       </c>
       <c r="H141" t="n">
         <v>250</v>
@@ -4516,7 +4516,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G143" t="n">
-        <v>10.2728977203369</v>
+        <v>10.2728986740112</v>
       </c>
       <c r="H143" t="n">
         <v>354</v>
@@ -4574,7 +4574,7 @@
         <v>11</v>
       </c>
       <c r="G145" t="n">
-        <v>10.0356903076172</v>
+        <v>10.0356912612915</v>
       </c>
       <c r="H145" t="n">
         <v>524</v>
@@ -4603,7 +4603,7 @@
         <v>11</v>
       </c>
       <c r="G146" t="n">
-        <v>10.0356903076172</v>
+        <v>10.0356912612915</v>
       </c>
       <c r="H146" t="n">
         <v>240</v>
@@ -4632,7 +4632,7 @@
         <v>11.2799997329712</v>
       </c>
       <c r="G147" t="n">
-        <v>10.291145324707</v>
+        <v>10.2911443710327</v>
       </c>
       <c r="H147" t="n">
         <v>780</v>
@@ -4661,7 +4661,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G148" t="n">
-        <v>10.3093929290771</v>
+        <v>10.3093919754028</v>
       </c>
       <c r="H148" t="n">
         <v>480</v>
@@ -4777,7 +4777,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G152" t="n">
-        <v>10.1269254684448</v>
+        <v>10.1269264221191</v>
       </c>
       <c r="H152" t="n">
         <v>398</v>
@@ -4893,7 +4893,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G156" t="n">
-        <v>10.1269254684448</v>
+        <v>10.1269264221191</v>
       </c>
       <c r="H156" t="n">
         <v>206</v>
@@ -4922,7 +4922,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G157" t="n">
-        <v>10.1269254684448</v>
+        <v>10.1269264221191</v>
       </c>
       <c r="H157" t="n">
         <v>0</v>
@@ -4980,7 +4980,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G159" t="n">
-        <v>10.1269254684448</v>
+        <v>10.1269264221191</v>
       </c>
       <c r="H159" t="n">
         <v>378</v>
@@ -5067,7 +5067,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G162" t="n">
-        <v>9.8532247543335</v>
+        <v>9.85322380065918</v>
       </c>
       <c r="H162" t="n">
         <v>559</v>
@@ -5125,7 +5125,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G164" t="n">
-        <v>10.1269254684448</v>
+        <v>10.1269264221191</v>
       </c>
       <c r="H164" t="n">
         <v>207</v>
@@ -5154,7 +5154,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G165" t="n">
-        <v>10.1816644668579</v>
+        <v>10.1816654205322</v>
       </c>
       <c r="H165" t="n">
         <v>40</v>
@@ -5183,7 +5183,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G166" t="n">
-        <v>10.3093929290771</v>
+        <v>10.3093919754028</v>
       </c>
       <c r="H166" t="n">
         <v>155</v>
@@ -5212,7 +5212,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G167" t="n">
-        <v>10.1816644668579</v>
+        <v>10.1816654205322</v>
       </c>
       <c r="H167" t="n">
         <v>3600</v>
@@ -5241,7 +5241,7 @@
         <v>11</v>
       </c>
       <c r="G168" t="n">
-        <v>10.0356903076172</v>
+        <v>10.0356912612915</v>
       </c>
       <c r="H168" t="n">
         <v>300</v>
@@ -5270,7 +5270,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G169" t="n">
-        <v>9.30582237243652</v>
+        <v>9.30582332611084</v>
       </c>
       <c r="H169" t="n">
         <v>1233</v>
@@ -5299,7 +5299,7 @@
         <v>10.3400001525879</v>
       </c>
       <c r="G170" t="n">
-        <v>9.43355083465576</v>
+        <v>9.43354988098145</v>
       </c>
       <c r="H170" t="n">
         <v>1910</v>
@@ -5328,7 +5328,7 @@
         <v>10.3400001525879</v>
       </c>
       <c r="G171" t="n">
-        <v>9.43355083465576</v>
+        <v>9.43354988098145</v>
       </c>
       <c r="H171" t="n">
         <v>388</v>
@@ -5357,7 +5357,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G172" t="n">
-        <v>9.39705657958984</v>
+        <v>9.39705753326416</v>
       </c>
       <c r="H172" t="n">
         <v>1640</v>
@@ -5444,7 +5444,7 @@
         <v>9.56999969482422</v>
       </c>
       <c r="G175" t="n">
-        <v>8.73105144500732</v>
+        <v>8.73105049133301</v>
       </c>
       <c r="H175" t="n">
         <v>6256</v>
@@ -5473,7 +5473,7 @@
         <v>9.5</v>
       </c>
       <c r="G176" t="n">
-        <v>8.66718864440918</v>
+        <v>8.66718769073486</v>
       </c>
       <c r="H176" t="n">
         <v>763</v>
@@ -5560,7 +5560,7 @@
         <v>9.43000030517578</v>
       </c>
       <c r="G179" t="n">
-        <v>8.6033239364624</v>
+        <v>8.60332489013672</v>
       </c>
       <c r="H179" t="n">
         <v>255</v>
@@ -5676,7 +5676,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G183" t="n">
-        <v>7.57238578796387</v>
+        <v>7.57238531112671</v>
       </c>
       <c r="H183" t="n">
         <v>4185</v>
@@ -5734,7 +5734,7 @@
         <v>8.60999965667725</v>
       </c>
       <c r="G185" t="n">
-        <v>7.85520935058594</v>
+        <v>7.8552098274231</v>
       </c>
       <c r="H185" t="n">
         <v>840</v>
@@ -5792,7 +5792,7 @@
         <v>9.01000022888184</v>
       </c>
       <c r="G187" t="n">
-        <v>8.22014331817627</v>
+        <v>8.22014427185059</v>
       </c>
       <c r="H187" t="n">
         <v>2520</v>
@@ -5850,7 +5850,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G189" t="n">
-        <v>8.27488327026367</v>
+        <v>8.27488231658936</v>
       </c>
       <c r="H189" t="n">
         <v>700</v>
@@ -5966,7 +5966,7 @@
         <v>8.59000015258789</v>
       </c>
       <c r="G193" t="n">
-        <v>7.83696269989014</v>
+        <v>7.83696317672729</v>
       </c>
       <c r="H193" t="n">
         <v>35</v>
@@ -6024,7 +6024,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G195" t="n">
-        <v>7.61800289154053</v>
+        <v>7.61800241470337</v>
       </c>
       <c r="H195" t="n">
         <v>289</v>
@@ -6053,7 +6053,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G196" t="n">
-        <v>7.61800289154053</v>
+        <v>7.61800241470337</v>
       </c>
       <c r="H196" t="n">
         <v>0</v>
@@ -6082,7 +6082,7 @@
         <v>8.25</v>
       </c>
       <c r="G197" t="n">
-        <v>7.52676868438721</v>
+        <v>7.52676916122437</v>
       </c>
       <c r="H197" t="n">
         <v>444</v>
@@ -6227,7 +6227,7 @@
         <v>8.60999965667725</v>
       </c>
       <c r="G202" t="n">
-        <v>7.85520935058594</v>
+        <v>7.8552098274231</v>
       </c>
       <c r="H202" t="n">
         <v>924</v>
@@ -6256,7 +6256,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G203" t="n">
-        <v>7.88258028030396</v>
+        <v>7.8825798034668</v>
       </c>
       <c r="H203" t="n">
         <v>60</v>
@@ -6285,7 +6285,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G204" t="n">
-        <v>7.88258028030396</v>
+        <v>7.8825798034668</v>
       </c>
       <c r="H204" t="n">
         <v>0</v>
@@ -6314,7 +6314,7 @@
         <v>8.60999965667725</v>
       </c>
       <c r="G205" t="n">
-        <v>7.85520935058594</v>
+        <v>7.8552098274231</v>
       </c>
       <c r="H205" t="n">
         <v>460</v>
@@ -6343,7 +6343,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G206" t="n">
-        <v>7.9373197555542</v>
+        <v>7.93731880187988</v>
       </c>
       <c r="H206" t="n">
         <v>1640</v>
@@ -6372,7 +6372,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G207" t="n">
-        <v>7.9373197555542</v>
+        <v>7.93731880187988</v>
       </c>
       <c r="H207" t="n">
         <v>0</v>
@@ -6401,7 +6401,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G208" t="n">
-        <v>7.9373197555542</v>
+        <v>7.93731880187988</v>
       </c>
       <c r="H208" t="n">
         <v>1100</v>
@@ -6430,7 +6430,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G209" t="n">
-        <v>7.9373197555542</v>
+        <v>7.93731880187988</v>
       </c>
       <c r="H209" t="n">
         <v>230</v>
@@ -6459,7 +6459,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G210" t="n">
-        <v>7.9373197555542</v>
+        <v>7.93731880187988</v>
       </c>
       <c r="H210" t="n">
         <v>0</v>
@@ -6488,7 +6488,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G211" t="n">
-        <v>7.9738130569458</v>
+        <v>7.97381258010864</v>
       </c>
       <c r="H211" t="n">
         <v>53910</v>
@@ -6604,7 +6604,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G215" t="n">
-        <v>8.27488327026367</v>
+        <v>8.27488231658936</v>
       </c>
       <c r="H215" t="n">
         <v>8078</v>
@@ -7010,7 +7010,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G229" t="n">
-        <v>8.57595348358154</v>
+        <v>8.57595443725586</v>
       </c>
       <c r="H229" t="n">
         <v>7583</v>
@@ -7039,7 +7039,7 @@
         <v>9.43000030517578</v>
       </c>
       <c r="G230" t="n">
-        <v>8.6033239364624</v>
+        <v>8.60332489013672</v>
       </c>
       <c r="H230" t="n">
         <v>26080</v>
@@ -7155,7 +7155,7 @@
         <v>9.43000030517578</v>
       </c>
       <c r="G234" t="n">
-        <v>8.6033239364624</v>
+        <v>8.60332489013672</v>
       </c>
       <c r="H234" t="n">
         <v>96</v>
@@ -7184,7 +7184,7 @@
         <v>9.43000030517578</v>
       </c>
       <c r="G235" t="n">
-        <v>8.6033239364624</v>
+        <v>8.60332489013672</v>
       </c>
       <c r="H235" t="n">
         <v>0</v>
@@ -7300,7 +7300,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G239" t="n">
-        <v>8.6215705871582</v>
+        <v>8.62157154083252</v>
       </c>
       <c r="H239" t="n">
         <v>2238</v>
@@ -7387,7 +7387,7 @@
         <v>9.63000011444092</v>
       </c>
       <c r="G242" t="n">
-        <v>8.78579235076904</v>
+        <v>8.78579139709473</v>
       </c>
       <c r="H242" t="n">
         <v>348</v>
@@ -7416,7 +7416,7 @@
         <v>9.63000011444092</v>
       </c>
       <c r="G243" t="n">
-        <v>8.78579235076904</v>
+        <v>8.78579139709473</v>
       </c>
       <c r="H243" t="n">
         <v>0</v>
@@ -7445,7 +7445,7 @@
         <v>9.63000011444092</v>
       </c>
       <c r="G244" t="n">
-        <v>8.78579235076904</v>
+        <v>8.78579139709473</v>
       </c>
       <c r="H244" t="n">
         <v>0</v>
@@ -7474,7 +7474,7 @@
         <v>9.63000011444092</v>
       </c>
       <c r="G245" t="n">
-        <v>8.78579235076904</v>
+        <v>8.78579139709473</v>
       </c>
       <c r="H245" t="n">
         <v>0</v>
@@ -7532,7 +7532,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G247" t="n">
-        <v>9.0321216583252</v>
+        <v>9.03212261199951</v>
       </c>
       <c r="H247" t="n">
         <v>200</v>
@@ -7561,7 +7561,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G248" t="n">
-        <v>9.0321216583252</v>
+        <v>9.03212261199951</v>
       </c>
       <c r="H248" t="n">
         <v>0</v>
@@ -7851,7 +7851,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G258" t="n">
-        <v>9.0321216583252</v>
+        <v>9.03212261199951</v>
       </c>
       <c r="H258" t="n">
         <v>300</v>
@@ -7909,7 +7909,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G260" t="n">
-        <v>8.84965515136719</v>
+        <v>8.84965419769287</v>
       </c>
       <c r="H260" t="n">
         <v>50</v>
@@ -7938,7 +7938,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G261" t="n">
-        <v>9.01387500762939</v>
+        <v>9.01387596130371</v>
       </c>
       <c r="H261" t="n">
         <v>519</v>
@@ -8141,7 +8141,7 @@
         <v>9.75</v>
       </c>
       <c r="G268" t="n">
-        <v>8.89527130126953</v>
+        <v>8.89527225494385</v>
       </c>
       <c r="H268" t="n">
         <v>380</v>
@@ -8170,7 +8170,7 @@
         <v>9.75</v>
       </c>
       <c r="G269" t="n">
-        <v>8.89527130126953</v>
+        <v>8.89527225494385</v>
       </c>
       <c r="H269" t="n">
         <v>1149</v>
@@ -8286,7 +8286,7 @@
         <v>8.92000007629395</v>
       </c>
       <c r="G273" t="n">
-        <v>8.13803386688232</v>
+        <v>8.13803291320801</v>
       </c>
       <c r="H273" t="n">
         <v>1470</v>
@@ -8373,7 +8373,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G276" t="n">
-        <v>8.35699462890625</v>
+        <v>8.35699367523193</v>
       </c>
       <c r="H276" t="n">
         <v>12610</v>
@@ -8460,7 +8460,7 @@
         <v>8.71000003814697</v>
       </c>
       <c r="G279" t="n">
-        <v>7.9464430809021</v>
+        <v>7.94644260406494</v>
       </c>
       <c r="H279" t="n">
         <v>7948</v>
@@ -8489,7 +8489,7 @@
         <v>8.72999954223633</v>
       </c>
       <c r="G280" t="n">
-        <v>7.9646897315979</v>
+        <v>7.96468925476074</v>
       </c>
       <c r="H280" t="n">
         <v>1620</v>
@@ -8576,7 +8576,7 @@
         <v>8.77000045776367</v>
       </c>
       <c r="G283" t="n">
-        <v>8.00118446350098</v>
+        <v>8.00118350982666</v>
       </c>
       <c r="H283" t="n">
         <v>2377</v>
@@ -8634,7 +8634,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G285" t="n">
-        <v>8.37524127960205</v>
+        <v>8.37524032592773</v>
       </c>
       <c r="H285" t="n">
         <v>1200</v>
@@ -8663,7 +8663,7 @@
         <v>9.09000015258789</v>
       </c>
       <c r="G286" t="n">
-        <v>8.29313087463379</v>
+        <v>8.29312992095947</v>
       </c>
       <c r="H286" t="n">
         <v>7374</v>
@@ -8692,7 +8692,7 @@
         <v>9.09000015258789</v>
       </c>
       <c r="G287" t="n">
-        <v>8.29313087463379</v>
+        <v>8.29312992095947</v>
       </c>
       <c r="H287" t="n">
         <v>760</v>
@@ -8721,7 +8721,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G288" t="n">
-        <v>8.27488327026367</v>
+        <v>8.27488231658936</v>
       </c>
       <c r="H288" t="n">
         <v>6201</v>
@@ -8866,7 +8866,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G293" t="n">
-        <v>8.27488327026367</v>
+        <v>8.27488231658936</v>
       </c>
       <c r="H293" t="n">
         <v>1783</v>
@@ -8924,7 +8924,7 @@
         <v>9.27000045776367</v>
       </c>
       <c r="G295" t="n">
-        <v>8.457350730896</v>
+        <v>8.45735168457031</v>
       </c>
       <c r="H295" t="n">
         <v>260</v>
@@ -9098,7 +9098,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G301" t="n">
-        <v>8.34787082672119</v>
+        <v>8.34786987304688</v>
       </c>
       <c r="H301" t="n">
         <v>519</v>
@@ -9301,7 +9301,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G308" t="n">
-        <v>8.37524127960205</v>
+        <v>8.37524032592773</v>
       </c>
       <c r="H308" t="n">
         <v>99</v>
@@ -9330,7 +9330,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G309" t="n">
-        <v>8.19277286529541</v>
+        <v>8.19277381896973</v>
       </c>
       <c r="H309" t="n">
         <v>191</v>
@@ -9475,7 +9475,7 @@
         <v>9.01000022888184</v>
       </c>
       <c r="G314" t="n">
-        <v>8.22014331817627</v>
+        <v>8.22014427185059</v>
       </c>
       <c r="H314" t="n">
         <v>680</v>
@@ -9504,7 +9504,7 @@
         <v>9.01000022888184</v>
       </c>
       <c r="G315" t="n">
-        <v>8.22014331817627</v>
+        <v>8.22014427185059</v>
       </c>
       <c r="H315" t="n">
         <v>0</v>
@@ -9678,7 +9678,7 @@
         <v>9.5</v>
       </c>
       <c r="G321" t="n">
-        <v>8.66718864440918</v>
+        <v>8.66718769073486</v>
       </c>
       <c r="H321" t="n">
         <v>38099</v>
@@ -9736,7 +9736,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G323" t="n">
-        <v>8.28400707244873</v>
+        <v>8.28400611877441</v>
       </c>
       <c r="H323" t="n">
         <v>8366</v>
@@ -9765,7 +9765,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G324" t="n">
-        <v>8.28400707244873</v>
+        <v>8.28400611877441</v>
       </c>
       <c r="H324" t="n">
         <v>0</v>
@@ -9852,7 +9852,7 @@
         <v>8.92000007629395</v>
       </c>
       <c r="G327" t="n">
-        <v>8.13803386688232</v>
+        <v>8.13803291320801</v>
       </c>
       <c r="H327" t="n">
         <v>200</v>
@@ -9968,7 +9968,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G331" t="n">
-        <v>8.59420108795166</v>
+        <v>8.59420204162598</v>
       </c>
       <c r="H331" t="n">
         <v>5649</v>
@@ -10084,7 +10084,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G335" t="n">
-        <v>8.24751377105713</v>
+        <v>8.24751472473145</v>
       </c>
       <c r="H335" t="n">
         <v>7514</v>
@@ -10171,7 +10171,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G338" t="n">
-        <v>7.9373197555542</v>
+        <v>7.93731880187988</v>
       </c>
       <c r="H338" t="n">
         <v>2490</v>
@@ -10200,7 +10200,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G339" t="n">
-        <v>7.53589153289795</v>
+        <v>7.53589200973511</v>
       </c>
       <c r="H339" t="n">
         <v>74770</v>
@@ -10229,7 +10229,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G340" t="n">
-        <v>7.57238578796387</v>
+        <v>7.57238531112671</v>
       </c>
       <c r="H340" t="n">
         <v>7020</v>
@@ -10432,7 +10432,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G347" t="n">
-        <v>7.53589153289795</v>
+        <v>7.53589200973511</v>
       </c>
       <c r="H347" t="n">
         <v>1406</v>
@@ -10577,7 +10577,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G352" t="n">
-        <v>7.31693172454834</v>
+        <v>7.3169322013855</v>
       </c>
       <c r="H352" t="n">
         <v>63</v>
@@ -10635,7 +10635,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G354" t="n">
-        <v>7.20745182037354</v>
+        <v>7.20745134353638</v>
       </c>
       <c r="H354" t="n">
         <v>2421</v>
@@ -10983,7 +10983,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G366" t="n">
-        <v>6.95199680328369</v>
+        <v>6.95199728012085</v>
       </c>
       <c r="H366" t="n">
         <v>3628</v>
@@ -11041,7 +11041,7 @@
         <v>7.51999998092651</v>
       </c>
       <c r="G368" t="n">
-        <v>6.86076354980469</v>
+        <v>6.86076307296753</v>
       </c>
       <c r="H368" t="n">
         <v>5487</v>
@@ -11070,7 +11070,7 @@
         <v>7.51999998092651</v>
       </c>
       <c r="G369" t="n">
-        <v>6.86076354980469</v>
+        <v>6.86076307296753</v>
       </c>
       <c r="H369" t="n">
         <v>45</v>
@@ -11099,7 +11099,7 @@
         <v>7.5</v>
       </c>
       <c r="G370" t="n">
-        <v>6.84251737594604</v>
+        <v>6.84251689910889</v>
       </c>
       <c r="H370" t="n">
         <v>3522</v>
@@ -11128,7 +11128,7 @@
         <v>7.51999998092651</v>
       </c>
       <c r="G371" t="n">
-        <v>6.86076354980469</v>
+        <v>6.86076307296753</v>
       </c>
       <c r="H371" t="n">
         <v>50</v>
@@ -11157,7 +11157,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G372" t="n">
-        <v>6.95199680328369</v>
+        <v>6.95199728012085</v>
       </c>
       <c r="H372" t="n">
         <v>500</v>
@@ -11389,7 +11389,7 @@
         <v>7.5</v>
       </c>
       <c r="G380" t="n">
-        <v>6.84251737594604</v>
+        <v>6.84251689910889</v>
       </c>
       <c r="H380" t="n">
         <v>884</v>
@@ -11418,7 +11418,7 @@
         <v>7.5</v>
       </c>
       <c r="G381" t="n">
-        <v>6.84251737594604</v>
+        <v>6.84251689910889</v>
       </c>
       <c r="H381" t="n">
         <v>2217</v>
@@ -11447,7 +11447,7 @@
         <v>7.5</v>
       </c>
       <c r="G382" t="n">
-        <v>6.84251737594604</v>
+        <v>6.84251689910889</v>
       </c>
       <c r="H382" t="n">
         <v>0</v>
@@ -11650,7 +11650,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G389" t="n">
-        <v>7.17095756530762</v>
+        <v>7.17095804214478</v>
       </c>
       <c r="H389" t="n">
         <v>7937</v>
@@ -11679,7 +11679,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G390" t="n">
-        <v>7.38991832733154</v>
+        <v>7.3899188041687</v>
       </c>
       <c r="H390" t="n">
         <v>4671</v>
@@ -11737,7 +11737,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G392" t="n">
-        <v>7.57238578796387</v>
+        <v>7.57238531112671</v>
       </c>
       <c r="H392" t="n">
         <v>630</v>
@@ -11766,7 +11766,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G393" t="n">
-        <v>7.57238578796387</v>
+        <v>7.57238531112671</v>
       </c>
       <c r="H393" t="n">
         <v>0</v>
@@ -11795,7 +11795,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G394" t="n">
-        <v>7.57238578796387</v>
+        <v>7.57238531112671</v>
       </c>
       <c r="H394" t="n">
         <v>100</v>
@@ -11824,7 +11824,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G395" t="n">
-        <v>7.57238578796387</v>
+        <v>7.57238531112671</v>
       </c>
       <c r="H395" t="n">
         <v>24200</v>
@@ -11853,7 +11853,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G396" t="n">
-        <v>7.57238578796387</v>
+        <v>7.57238531112671</v>
       </c>
       <c r="H396" t="n">
         <v>0</v>
@@ -12056,7 +12056,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G403" t="n">
-        <v>7.49939918518066</v>
+        <v>7.49939870834351</v>
       </c>
       <c r="H403" t="n">
         <v>750</v>
@@ -12375,7 +12375,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G414" t="n">
-        <v>7.4446587562561</v>
+        <v>7.44465827941895</v>
       </c>
       <c r="H414" t="n">
         <v>210</v>
@@ -12404,7 +12404,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G415" t="n">
-        <v>7.4446587562561</v>
+        <v>7.44465827941895</v>
       </c>
       <c r="H415" t="n">
         <v>0</v>
@@ -12665,7 +12665,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G424" t="n">
-        <v>7.4446587562561</v>
+        <v>7.44465827941895</v>
       </c>
       <c r="H424" t="n">
         <v>2000</v>
@@ -12694,7 +12694,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G425" t="n">
-        <v>7.60887908935547</v>
+        <v>7.60887861251831</v>
       </c>
       <c r="H425" t="n">
         <v>12400</v>
@@ -12723,7 +12723,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G426" t="n">
-        <v>7.79134511947632</v>
+        <v>7.79134559631348</v>
       </c>
       <c r="H426" t="n">
         <v>3239</v>
@@ -12752,7 +12752,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G427" t="n">
-        <v>7.88258028030396</v>
+        <v>7.8825798034668</v>
       </c>
       <c r="H427" t="n">
         <v>41</v>
@@ -12868,7 +12868,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G431" t="n">
-        <v>7.55413770675659</v>
+        <v>7.55413818359375</v>
       </c>
       <c r="H431" t="n">
         <v>428</v>
@@ -12897,7 +12897,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G432" t="n">
-        <v>7.55413770675659</v>
+        <v>7.55413818359375</v>
       </c>
       <c r="H432" t="n">
         <v>0</v>
@@ -13187,7 +13187,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G442" t="n">
-        <v>6.80602312088013</v>
+        <v>6.80602359771729</v>
       </c>
       <c r="H442" t="n">
         <v>1912</v>
@@ -13216,7 +13216,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G443" t="n">
-        <v>6.75128364562988</v>
+        <v>6.75128316879272</v>
       </c>
       <c r="H443" t="n">
         <v>690</v>
@@ -13245,7 +13245,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G444" t="n">
-        <v>6.75128364562988</v>
+        <v>6.75128316879272</v>
       </c>
       <c r="H444" t="n">
         <v>740</v>
@@ -13390,7 +13390,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G449" t="n">
-        <v>6.75128364562988</v>
+        <v>6.75128316879272</v>
       </c>
       <c r="H449" t="n">
         <v>1995</v>
@@ -13419,7 +13419,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G450" t="n">
-        <v>6.75128364562988</v>
+        <v>6.75128316879272</v>
       </c>
       <c r="H450" t="n">
         <v>0</v>
@@ -13448,7 +13448,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G451" t="n">
-        <v>6.75128364562988</v>
+        <v>6.75128316879272</v>
       </c>
       <c r="H451" t="n">
         <v>0</v>
@@ -13477,7 +13477,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G452" t="n">
-        <v>6.75128364562988</v>
+        <v>6.75128316879272</v>
       </c>
       <c r="H452" t="n">
         <v>0</v>
@@ -13506,7 +13506,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G453" t="n">
-        <v>6.75128364562988</v>
+        <v>6.75128316879272</v>
       </c>
       <c r="H453" t="n">
         <v>0</v>
@@ -13535,7 +13535,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G454" t="n">
-        <v>6.75128364562988</v>
+        <v>6.75128316879272</v>
       </c>
       <c r="H454" t="n">
         <v>1400</v>
@@ -13564,7 +13564,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G455" t="n">
-        <v>6.5870623588562</v>
+        <v>6.58706283569336</v>
       </c>
       <c r="H455" t="n">
         <v>200</v>
@@ -13593,7 +13593,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G456" t="n">
-        <v>6.47758293151855</v>
+        <v>6.4775824546814</v>
       </c>
       <c r="H456" t="n">
         <v>1083</v>
@@ -13680,7 +13680,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G459" t="n">
-        <v>6.47758293151855</v>
+        <v>6.4775824546814</v>
       </c>
       <c r="H459" t="n">
         <v>1900</v>
@@ -13825,7 +13825,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G464" t="n">
-        <v>6.5688157081604</v>
+        <v>6.56881618499756</v>
       </c>
       <c r="H464" t="n">
         <v>4878</v>
@@ -13854,7 +13854,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G465" t="n">
-        <v>6.5688157081604</v>
+        <v>6.56881618499756</v>
       </c>
       <c r="H465" t="n">
         <v>2702</v>
@@ -13883,7 +13883,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G466" t="n">
-        <v>6.5688157081604</v>
+        <v>6.56881618499756</v>
       </c>
       <c r="H466" t="n">
         <v>0</v>
@@ -13912,7 +13912,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G467" t="n">
-        <v>6.5688157081604</v>
+        <v>6.56881618499756</v>
       </c>
       <c r="H467" t="n">
         <v>0</v>
@@ -13941,7 +13941,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G468" t="n">
-        <v>6.5688157081604</v>
+        <v>6.56881618499756</v>
       </c>
       <c r="H468" t="n">
         <v>0</v>
@@ -14086,7 +14086,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G473" t="n">
-        <v>6.42284250259399</v>
+        <v>6.42284297943115</v>
       </c>
       <c r="H473" t="n">
         <v>600</v>
@@ -14144,7 +14144,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G475" t="n">
-        <v>6.67829656600952</v>
+        <v>6.67829608917236</v>
       </c>
       <c r="H475" t="n">
         <v>1738</v>
@@ -14173,7 +14173,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G476" t="n">
-        <v>6.67829656600952</v>
+        <v>6.67829608917236</v>
       </c>
       <c r="H476" t="n">
         <v>1500</v>
@@ -14405,7 +14405,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G484" t="n">
-        <v>6.5870623588562</v>
+        <v>6.58706283569336</v>
       </c>
       <c r="H484" t="n">
         <v>1565</v>
@@ -14434,7 +14434,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G485" t="n">
-        <v>6.5870623588562</v>
+        <v>6.58706283569336</v>
       </c>
       <c r="H485" t="n">
         <v>0</v>
@@ -14463,7 +14463,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G486" t="n">
-        <v>6.5870623588562</v>
+        <v>6.58706283569336</v>
       </c>
       <c r="H486" t="n">
         <v>0</v>
@@ -14492,7 +14492,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G487" t="n">
-        <v>6.64180326461792</v>
+        <v>6.64180278778076</v>
       </c>
       <c r="H487" t="n">
         <v>565</v>
@@ -14521,7 +14521,7 @@
         <v>7.5</v>
       </c>
       <c r="G488" t="n">
-        <v>6.84251737594604</v>
+        <v>6.84251689910889</v>
       </c>
       <c r="H488" t="n">
         <v>1463</v>
@@ -14608,7 +14608,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G491" t="n">
-        <v>7.18920421600342</v>
+        <v>7.18920469284058</v>
       </c>
       <c r="H491" t="n">
         <v>1500</v>
@@ -14637,7 +14637,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G492" t="n">
-        <v>7.20745182037354</v>
+        <v>7.20745134353638</v>
       </c>
       <c r="H492" t="n">
         <v>1450</v>
@@ -14666,7 +14666,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G493" t="n">
-        <v>7.22569799423218</v>
+        <v>7.22569751739502</v>
       </c>
       <c r="H493" t="n">
         <v>800</v>
@@ -15072,7 +15072,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G507" t="n">
-        <v>7.31693172454834</v>
+        <v>7.3169322013855</v>
       </c>
       <c r="H507" t="n">
         <v>772</v>
@@ -15188,7 +15188,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G511" t="n">
-        <v>7.20745182037354</v>
+        <v>7.20745134353638</v>
       </c>
       <c r="H511" t="n">
         <v>221</v>
@@ -15217,7 +15217,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G512" t="n">
-        <v>7.31693172454834</v>
+        <v>7.3169322013855</v>
       </c>
       <c r="H512" t="n">
         <v>1280</v>
@@ -15246,7 +15246,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G513" t="n">
-        <v>7.20745182037354</v>
+        <v>7.20745134353638</v>
       </c>
       <c r="H513" t="n">
         <v>900</v>
@@ -15362,7 +15362,7 @@
         <v>7.51999998092651</v>
       </c>
       <c r="G517" t="n">
-        <v>6.86076354980469</v>
+        <v>6.86076307296753</v>
       </c>
       <c r="H517" t="n">
         <v>3626</v>
@@ -15391,7 +15391,7 @@
         <v>7.5</v>
       </c>
       <c r="G518" t="n">
-        <v>6.84251737594604</v>
+        <v>6.84251689910889</v>
       </c>
       <c r="H518" t="n">
         <v>3782</v>
@@ -15420,7 +15420,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G519" t="n">
-        <v>6.80602312088013</v>
+        <v>6.80602359771729</v>
       </c>
       <c r="H519" t="n">
         <v>109</v>
@@ -15739,7 +15739,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G530" t="n">
-        <v>7.17095756530762</v>
+        <v>7.17095804214478</v>
       </c>
       <c r="H530" t="n">
         <v>2115</v>
@@ -15913,7 +15913,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G536" t="n">
-        <v>7.38991832733154</v>
+        <v>7.3899188041687</v>
       </c>
       <c r="H536" t="n">
         <v>18461</v>
@@ -15942,7 +15942,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G537" t="n">
-        <v>7.18920421600342</v>
+        <v>7.18920469284058</v>
       </c>
       <c r="H537" t="n">
         <v>29589</v>
@@ -16000,7 +16000,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G539" t="n">
-        <v>7.20745182037354</v>
+        <v>7.20745134353638</v>
       </c>
       <c r="H539" t="n">
         <v>3149</v>
@@ -16029,7 +16029,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G540" t="n">
-        <v>7.20745182037354</v>
+        <v>7.20745134353638</v>
       </c>
       <c r="H540" t="n">
         <v>0</v>
@@ -16145,7 +16145,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G544" t="n">
-        <v>7.31693172454834</v>
+        <v>7.3169322013855</v>
       </c>
       <c r="H544" t="n">
         <v>3852</v>
@@ -16174,7 +16174,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G545" t="n">
-        <v>7.20745182037354</v>
+        <v>7.20745134353638</v>
       </c>
       <c r="H545" t="n">
         <v>13099</v>
@@ -16261,7 +16261,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G548" t="n">
-        <v>7.38991832733154</v>
+        <v>7.3899188041687</v>
       </c>
       <c r="H548" t="n">
         <v>1200</v>
@@ -16290,7 +16290,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G549" t="n">
-        <v>7.55413770675659</v>
+        <v>7.55413818359375</v>
       </c>
       <c r="H549" t="n">
         <v>217</v>
@@ -16319,7 +16319,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G550" t="n">
-        <v>7.49939918518066</v>
+        <v>7.49939870834351</v>
       </c>
       <c r="H550" t="n">
         <v>4760</v>
@@ -16435,7 +16435,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G554" t="n">
-        <v>7.57238578796387</v>
+        <v>7.57238531112671</v>
       </c>
       <c r="H554" t="n">
         <v>1776</v>
@@ -16464,7 +16464,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G555" t="n">
-        <v>7.57238578796387</v>
+        <v>7.57238531112671</v>
       </c>
       <c r="H555" t="n">
         <v>733</v>
@@ -16928,7 +16928,7 @@
         <v>8.25</v>
       </c>
       <c r="G571" t="n">
-        <v>7.52676868438721</v>
+        <v>7.52676916122437</v>
       </c>
       <c r="H571" t="n">
         <v>2468</v>
@@ -17073,7 +17073,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G576" t="n">
-        <v>7.61800289154053</v>
+        <v>7.61800241470337</v>
       </c>
       <c r="H576" t="n">
         <v>4229</v>
@@ -17102,7 +17102,7 @@
         <v>8.25</v>
       </c>
       <c r="G577" t="n">
-        <v>7.52676868438721</v>
+        <v>7.52676916122437</v>
       </c>
       <c r="H577" t="n">
         <v>10687</v>
@@ -17131,7 +17131,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G578" t="n">
-        <v>7.25306797027588</v>
+        <v>7.25306749343872</v>
       </c>
       <c r="H578" t="n">
         <v>14460</v>
@@ -17218,7 +17218,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G581" t="n">
-        <v>7.38991832733154</v>
+        <v>7.3899188041687</v>
       </c>
       <c r="H581" t="n">
         <v>540</v>
@@ -17334,7 +17334,7 @@
         <v>8.25</v>
       </c>
       <c r="G585" t="n">
-        <v>7.52676868438721</v>
+        <v>7.52676916122437</v>
       </c>
       <c r="H585" t="n">
         <v>1560</v>
@@ -17363,7 +17363,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G586" t="n">
-        <v>7.38991832733154</v>
+        <v>7.3899188041687</v>
       </c>
       <c r="H586" t="n">
         <v>3341</v>
@@ -17392,7 +17392,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G587" t="n">
-        <v>7.38991832733154</v>
+        <v>7.3899188041687</v>
       </c>
       <c r="H587" t="n">
         <v>340</v>
@@ -17450,7 +17450,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G589" t="n">
-        <v>7.38991832733154</v>
+        <v>7.3899188041687</v>
       </c>
       <c r="H589" t="n">
         <v>1325</v>
@@ -17479,7 +17479,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G590" t="n">
-        <v>7.38991832733154</v>
+        <v>7.3899188041687</v>
       </c>
       <c r="H590" t="n">
         <v>851</v>
@@ -17508,7 +17508,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G591" t="n">
-        <v>7.38991832733154</v>
+        <v>7.3899188041687</v>
       </c>
       <c r="H591" t="n">
         <v>22104</v>
@@ -17537,7 +17537,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G592" t="n">
-        <v>7.38991832733154</v>
+        <v>7.3899188041687</v>
       </c>
       <c r="H592" t="n">
         <v>0</v>
@@ -17856,7 +17856,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G603" t="n">
-        <v>7.25306797027588</v>
+        <v>7.25306749343872</v>
       </c>
       <c r="H603" t="n">
         <v>19392</v>
@@ -35668,6 +35668,35 @@
         <v>1000</v>
       </c>
       <c r="I1217" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1218">
+      <c r="A1218" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1218" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C1218" t="n">
+        <v>8</v>
+      </c>
+      <c r="D1218" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1218" t="n">
+        <v>8</v>
+      </c>
+      <c r="F1218" t="n">
+        <v>8</v>
+      </c>
+      <c r="G1218" t="n">
+        <v>8</v>
+      </c>
+      <c r="H1218" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1218" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SVS.MI.xlsx
+++ b/data/SVS.MI.xlsx
@@ -514,7 +514,7 @@
         <v>14.5600004196167</v>
       </c>
       <c r="G5" t="n">
-        <v>13.2836055755615</v>
+        <v>13.2836065292358</v>
       </c>
       <c r="H5" t="n">
         <v>2134</v>
@@ -572,7 +572,7 @@
         <v>14.539999961853</v>
       </c>
       <c r="G7" t="n">
-        <v>13.2653589248657</v>
+        <v>13.26535987854</v>
       </c>
       <c r="H7" t="n">
         <v>2735</v>
@@ -659,7 +659,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G10" t="n">
-        <v>12.5902309417725</v>
+        <v>12.5902318954468</v>
       </c>
       <c r="H10" t="n">
         <v>670</v>
@@ -688,7 +688,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G11" t="n">
-        <v>12.5902309417725</v>
+        <v>12.5902318954468</v>
       </c>
       <c r="H11" t="n">
         <v>13315</v>
@@ -804,7 +804,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G15" t="n">
-        <v>12.754451751709</v>
+        <v>12.7544507980347</v>
       </c>
       <c r="H15" t="n">
         <v>2068</v>
@@ -891,7 +891,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G18" t="n">
-        <v>12.2252960205078</v>
+        <v>12.2252969741821</v>
       </c>
       <c r="H18" t="n">
         <v>2456</v>
@@ -949,7 +949,7 @@
         <v>13.6800003051758</v>
       </c>
       <c r="G20" t="n">
-        <v>12.480751991272</v>
+        <v>12.4807510375977</v>
       </c>
       <c r="H20" t="n">
         <v>2647</v>
@@ -978,7 +978,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G21" t="n">
-        <v>12.4077644348145</v>
+        <v>12.4077634811401</v>
       </c>
       <c r="H21" t="n">
         <v>2900</v>
@@ -1036,7 +1036,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G23" t="n">
-        <v>12.2252960205078</v>
+        <v>12.2252969741821</v>
       </c>
       <c r="H23" t="n">
         <v>1882</v>
@@ -1094,7 +1094,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G25" t="n">
-        <v>12.0428304672241</v>
+        <v>12.0428295135498</v>
       </c>
       <c r="H25" t="n">
         <v>600</v>
@@ -1123,7 +1123,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G26" t="n">
-        <v>11.9698429107666</v>
+        <v>11.9698419570923</v>
       </c>
       <c r="H26" t="n">
         <v>4682</v>
@@ -1181,7 +1181,7 @@
         <v>13</v>
       </c>
       <c r="G28" t="n">
-        <v>11.8603620529175</v>
+        <v>11.8603630065918</v>
       </c>
       <c r="H28" t="n">
         <v>2250</v>
@@ -1210,7 +1210,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G29" t="n">
-        <v>11.6778964996338</v>
+        <v>11.6778955459595</v>
       </c>
       <c r="H29" t="n">
         <v>1108</v>
@@ -1355,7 +1355,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G34" t="n">
-        <v>11.2034816741943</v>
+        <v>11.20348072052</v>
       </c>
       <c r="H34" t="n">
         <v>7092</v>
@@ -1384,7 +1384,7 @@
         <v>11.3800001144409</v>
       </c>
       <c r="G35" t="n">
-        <v>10.3823795318604</v>
+        <v>10.382378578186</v>
       </c>
       <c r="H35" t="n">
         <v>16969</v>
@@ -1413,7 +1413,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G36" t="n">
-        <v>10.5830926895142</v>
+        <v>10.5830936431885</v>
       </c>
       <c r="H36" t="n">
         <v>6892</v>
@@ -1471,7 +1471,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G38" t="n">
-        <v>10.5830926895142</v>
+        <v>10.5830936431885</v>
       </c>
       <c r="H38" t="n">
         <v>1246</v>
@@ -1558,7 +1558,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G41" t="n">
-        <v>10.108678817749</v>
+        <v>10.1086778640747</v>
       </c>
       <c r="H41" t="n">
         <v>22904</v>
@@ -1587,7 +1587,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G42" t="n">
-        <v>9.76199150085449</v>
+        <v>9.76199054718018</v>
       </c>
       <c r="H42" t="n">
         <v>550</v>
@@ -1616,7 +1616,7 @@
         <v>10.7600002288818</v>
       </c>
       <c r="G43" t="n">
-        <v>9.81673049926758</v>
+        <v>9.81673240661621</v>
       </c>
       <c r="H43" t="n">
         <v>1169</v>
@@ -1732,7 +1732,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G47" t="n">
-        <v>11.6778964996338</v>
+        <v>11.6778955459595</v>
       </c>
       <c r="H47" t="n">
         <v>838</v>
@@ -1761,7 +1761,7 @@
         <v>13.0600004196167</v>
       </c>
       <c r="G48" t="n">
-        <v>11.9151039123535</v>
+        <v>11.9151029586792</v>
       </c>
       <c r="H48" t="n">
         <v>2600</v>
@@ -1790,7 +1790,7 @@
         <v>13</v>
       </c>
       <c r="G49" t="n">
-        <v>11.8603620529175</v>
+        <v>11.8603630065918</v>
       </c>
       <c r="H49" t="n">
         <v>2500</v>
@@ -1819,7 +1819,7 @@
         <v>13</v>
       </c>
       <c r="G50" t="n">
-        <v>11.8603620529175</v>
+        <v>11.8603630065918</v>
       </c>
       <c r="H50" t="n">
         <v>220</v>
@@ -1848,7 +1848,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G51" t="n">
-        <v>12.2252960205078</v>
+        <v>12.2252969741821</v>
       </c>
       <c r="H51" t="n">
         <v>1595</v>
@@ -1993,7 +1993,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G56" t="n">
-        <v>12.0428304672241</v>
+        <v>12.0428295135498</v>
       </c>
       <c r="H56" t="n">
         <v>275</v>
@@ -2022,7 +2022,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G57" t="n">
-        <v>12.0428304672241</v>
+        <v>12.0428295135498</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G58" t="n">
-        <v>12.0428304672241</v>
+        <v>12.0428295135498</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
@@ -2080,7 +2080,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G59" t="n">
-        <v>12.0428304672241</v>
+        <v>12.0428295135498</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
@@ -2109,7 +2109,7 @@
         <v>13.039999961853</v>
       </c>
       <c r="G60" t="n">
-        <v>11.8968563079834</v>
+        <v>11.8968553543091</v>
       </c>
       <c r="H60" t="n">
         <v>411</v>
@@ -2167,7 +2167,7 @@
         <v>13</v>
       </c>
       <c r="G62" t="n">
-        <v>11.8603620529175</v>
+        <v>11.8603630065918</v>
       </c>
       <c r="H62" t="n">
         <v>4800</v>
@@ -2312,7 +2312,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G67" t="n">
-        <v>11.5866613388062</v>
+        <v>11.5866622924805</v>
       </c>
       <c r="H67" t="n">
         <v>2052</v>
@@ -2341,7 +2341,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G68" t="n">
-        <v>11.1304941177368</v>
+        <v>11.1304931640625</v>
       </c>
       <c r="H68" t="n">
         <v>700</v>
@@ -2370,7 +2370,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G69" t="n">
-        <v>11.9698429107666</v>
+        <v>11.9698419570923</v>
       </c>
       <c r="H69" t="n">
         <v>660</v>
@@ -2515,7 +2515,7 @@
         <v>12.4399995803833</v>
       </c>
       <c r="G74" t="n">
-        <v>11.3494539260864</v>
+        <v>11.3494548797607</v>
       </c>
       <c r="H74" t="n">
         <v>16133</v>
@@ -2544,7 +2544,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G75" t="n">
-        <v>11.8238687515259</v>
+        <v>11.8238697052002</v>
       </c>
       <c r="H75" t="n">
         <v>727</v>
@@ -2631,7 +2631,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G78" t="n">
-        <v>10.8932867050171</v>
+        <v>10.8932857513428</v>
       </c>
       <c r="H78" t="n">
         <v>100</v>
@@ -2660,7 +2660,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G79" t="n">
-        <v>10.8020534515381</v>
+        <v>10.8020544052124</v>
       </c>
       <c r="H79" t="n">
         <v>950</v>
@@ -2689,7 +2689,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G80" t="n">
-        <v>10.5648460388184</v>
+        <v>10.5648469924927</v>
       </c>
       <c r="H80" t="n">
         <v>2840</v>
@@ -2834,7 +2834,7 @@
         <v>11.5</v>
       </c>
       <c r="G85" t="n">
-        <v>10.4918594360352</v>
+        <v>10.4918584823608</v>
       </c>
       <c r="H85" t="n">
         <v>1710</v>
@@ -2892,7 +2892,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G87" t="n">
-        <v>10.3276386260986</v>
+        <v>10.3276395797729</v>
       </c>
       <c r="H87" t="n">
         <v>13938</v>
@@ -2979,7 +2979,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G90" t="n">
-        <v>10.9297800064087</v>
+        <v>10.9297790527344</v>
       </c>
       <c r="H90" t="n">
         <v>105</v>
@@ -3037,7 +3037,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G92" t="n">
-        <v>10.5648460388184</v>
+        <v>10.5648469924927</v>
       </c>
       <c r="H92" t="n">
         <v>1190</v>
@@ -3066,7 +3066,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G93" t="n">
-        <v>10.5648460388184</v>
+        <v>10.5648469924927</v>
       </c>
       <c r="H93" t="n">
         <v>150</v>
@@ -3124,7 +3124,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G95" t="n">
-        <v>10.5648460388184</v>
+        <v>10.5648469924927</v>
       </c>
       <c r="H95" t="n">
         <v>1620</v>
@@ -3153,7 +3153,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G96" t="n">
-        <v>10.5648460388184</v>
+        <v>10.5648469924927</v>
       </c>
       <c r="H96" t="n">
         <v>7278</v>
@@ -3182,7 +3182,7 @@
         <v>11.5</v>
       </c>
       <c r="G97" t="n">
-        <v>10.4918594360352</v>
+        <v>10.4918584823608</v>
       </c>
       <c r="H97" t="n">
         <v>16862</v>
@@ -3211,7 +3211,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G98" t="n">
-        <v>10.1816654205322</v>
+        <v>10.1816644668579</v>
       </c>
       <c r="H98" t="n">
         <v>35194</v>
@@ -3298,7 +3298,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G101" t="n">
-        <v>10.5648460388184</v>
+        <v>10.5648469924927</v>
       </c>
       <c r="H101" t="n">
         <v>4205</v>
@@ -3443,7 +3443,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G106" t="n">
-        <v>10.3093919754028</v>
+        <v>10.3093929290771</v>
       </c>
       <c r="H106" t="n">
         <v>1804</v>
@@ -3617,7 +3617,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G112" t="n">
-        <v>9.85322380065918</v>
+        <v>9.8532247543335</v>
       </c>
       <c r="H112" t="n">
         <v>600</v>
@@ -3646,7 +3646,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G113" t="n">
-        <v>10.1269264221191</v>
+        <v>10.1269254684448</v>
       </c>
       <c r="H113" t="n">
         <v>1110</v>
@@ -3675,7 +3675,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G114" t="n">
-        <v>10.1269264221191</v>
+        <v>10.1269254684448</v>
       </c>
       <c r="H114" t="n">
         <v>1005</v>
@@ -3733,7 +3733,7 @@
         <v>11.5</v>
       </c>
       <c r="G116" t="n">
-        <v>10.4918594360352</v>
+        <v>10.4918584823608</v>
       </c>
       <c r="H116" t="n">
         <v>1595</v>
@@ -3936,7 +3936,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G123" t="n">
-        <v>10.2546520233154</v>
+        <v>10.2546510696411</v>
       </c>
       <c r="H123" t="n">
         <v>923</v>
@@ -3965,7 +3965,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G124" t="n">
-        <v>10.1816654205322</v>
+        <v>10.1816644668579</v>
       </c>
       <c r="H124" t="n">
         <v>695</v>
@@ -4081,7 +4081,7 @@
         <v>11.039999961853</v>
       </c>
       <c r="G128" t="n">
-        <v>10.0721845626831</v>
+        <v>10.0721855163574</v>
       </c>
       <c r="H128" t="n">
         <v>5476</v>
@@ -4110,7 +4110,7 @@
         <v>11.039999961853</v>
       </c>
       <c r="G129" t="n">
-        <v>10.0721845626831</v>
+        <v>10.0721855163574</v>
       </c>
       <c r="H129" t="n">
         <v>0</v>
@@ -4400,7 +4400,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G139" t="n">
-        <v>10.1816654205322</v>
+        <v>10.1816644668579</v>
       </c>
       <c r="H139" t="n">
         <v>280</v>
@@ -4458,7 +4458,7 @@
         <v>11.2799997329712</v>
       </c>
       <c r="G141" t="n">
-        <v>10.2911443710327</v>
+        <v>10.2911462783813</v>
       </c>
       <c r="H141" t="n">
         <v>250</v>
@@ -4632,7 +4632,7 @@
         <v>11.2799997329712</v>
       </c>
       <c r="G147" t="n">
-        <v>10.2911443710327</v>
+        <v>10.2911462783813</v>
       </c>
       <c r="H147" t="n">
         <v>780</v>
@@ -4661,7 +4661,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G148" t="n">
-        <v>10.3093919754028</v>
+        <v>10.3093929290771</v>
       </c>
       <c r="H148" t="n">
         <v>480</v>
@@ -4777,7 +4777,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G152" t="n">
-        <v>10.1269264221191</v>
+        <v>10.1269254684448</v>
       </c>
       <c r="H152" t="n">
         <v>398</v>
@@ -4893,7 +4893,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G156" t="n">
-        <v>10.1269264221191</v>
+        <v>10.1269254684448</v>
       </c>
       <c r="H156" t="n">
         <v>206</v>
@@ -4922,7 +4922,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G157" t="n">
-        <v>10.1269264221191</v>
+        <v>10.1269254684448</v>
       </c>
       <c r="H157" t="n">
         <v>0</v>
@@ -4980,7 +4980,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G159" t="n">
-        <v>10.1269264221191</v>
+        <v>10.1269254684448</v>
       </c>
       <c r="H159" t="n">
         <v>378</v>
@@ -5067,7 +5067,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G162" t="n">
-        <v>9.85322380065918</v>
+        <v>9.8532247543335</v>
       </c>
       <c r="H162" t="n">
         <v>559</v>
@@ -5125,7 +5125,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G164" t="n">
-        <v>10.1269264221191</v>
+        <v>10.1269254684448</v>
       </c>
       <c r="H164" t="n">
         <v>207</v>
@@ -5154,7 +5154,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G165" t="n">
-        <v>10.1816654205322</v>
+        <v>10.1816644668579</v>
       </c>
       <c r="H165" t="n">
         <v>40</v>
@@ -5183,7 +5183,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G166" t="n">
-        <v>10.3093919754028</v>
+        <v>10.3093929290771</v>
       </c>
       <c r="H166" t="n">
         <v>155</v>
@@ -5212,7 +5212,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G167" t="n">
-        <v>10.1816654205322</v>
+        <v>10.1816644668579</v>
       </c>
       <c r="H167" t="n">
         <v>3600</v>
@@ -5270,7 +5270,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G169" t="n">
-        <v>9.30582332611084</v>
+        <v>9.30582237243652</v>
       </c>
       <c r="H169" t="n">
         <v>1233</v>
@@ -5357,7 +5357,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G172" t="n">
-        <v>9.39705753326416</v>
+        <v>9.39705657958984</v>
       </c>
       <c r="H172" t="n">
         <v>1640</v>
@@ -5444,7 +5444,7 @@
         <v>9.56999969482422</v>
       </c>
       <c r="G175" t="n">
-        <v>8.73105049133301</v>
+        <v>8.73105144500732</v>
       </c>
       <c r="H175" t="n">
         <v>6256</v>
@@ -5531,7 +5531,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G178" t="n">
-        <v>8.50296688079834</v>
+        <v>8.50296783447266</v>
       </c>
       <c r="H178" t="n">
         <v>369</v>
@@ -5676,7 +5676,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G183" t="n">
-        <v>7.57238531112671</v>
+        <v>7.57238578796387</v>
       </c>
       <c r="H183" t="n">
         <v>4185</v>
@@ -5734,7 +5734,7 @@
         <v>8.60999965667725</v>
       </c>
       <c r="G185" t="n">
-        <v>7.8552098274231</v>
+        <v>7.85520839691162</v>
       </c>
       <c r="H185" t="n">
         <v>840</v>
@@ -5763,7 +5763,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G186" t="n">
-        <v>8.0285530090332</v>
+        <v>8.02855396270752</v>
       </c>
       <c r="H186" t="n">
         <v>820</v>
@@ -5792,7 +5792,7 @@
         <v>9.01000022888184</v>
       </c>
       <c r="G187" t="n">
-        <v>8.22014427185059</v>
+        <v>8.22014331817627</v>
       </c>
       <c r="H187" t="n">
         <v>2520</v>
@@ -5821,7 +5821,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G188" t="n">
-        <v>8.11978721618652</v>
+        <v>8.11978626251221</v>
       </c>
       <c r="H188" t="n">
         <v>1750</v>
@@ -5850,7 +5850,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G189" t="n">
-        <v>8.27488231658936</v>
+        <v>8.27488422393799</v>
       </c>
       <c r="H189" t="n">
         <v>700</v>
@@ -5966,7 +5966,7 @@
         <v>8.59000015258789</v>
       </c>
       <c r="G193" t="n">
-        <v>7.83696317672729</v>
+        <v>7.83696269989014</v>
       </c>
       <c r="H193" t="n">
         <v>35</v>
@@ -5995,7 +5995,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G194" t="n">
-        <v>7.73660564422607</v>
+        <v>7.73660516738892</v>
       </c>
       <c r="H194" t="n">
         <v>727</v>
@@ -6024,7 +6024,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G195" t="n">
-        <v>7.61800241470337</v>
+        <v>7.61800193786621</v>
       </c>
       <c r="H195" t="n">
         <v>289</v>
@@ -6053,7 +6053,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G196" t="n">
-        <v>7.61800241470337</v>
+        <v>7.61800193786621</v>
       </c>
       <c r="H196" t="n">
         <v>0</v>
@@ -6082,7 +6082,7 @@
         <v>8.25</v>
       </c>
       <c r="G197" t="n">
-        <v>7.52676916122437</v>
+        <v>7.52676868438721</v>
       </c>
       <c r="H197" t="n">
         <v>444</v>
@@ -6227,7 +6227,7 @@
         <v>8.60999965667725</v>
       </c>
       <c r="G202" t="n">
-        <v>7.8552098274231</v>
+        <v>7.85520839691162</v>
       </c>
       <c r="H202" t="n">
         <v>924</v>
@@ -6256,7 +6256,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G203" t="n">
-        <v>7.8825798034668</v>
+        <v>7.88257932662964</v>
       </c>
       <c r="H203" t="n">
         <v>60</v>
@@ -6285,7 +6285,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G204" t="n">
-        <v>7.8825798034668</v>
+        <v>7.88257932662964</v>
       </c>
       <c r="H204" t="n">
         <v>0</v>
@@ -6314,7 +6314,7 @@
         <v>8.60999965667725</v>
       </c>
       <c r="G205" t="n">
-        <v>7.8552098274231</v>
+        <v>7.85520839691162</v>
       </c>
       <c r="H205" t="n">
         <v>460</v>
@@ -6343,7 +6343,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G206" t="n">
-        <v>7.93731880187988</v>
+        <v>7.9373197555542</v>
       </c>
       <c r="H206" t="n">
         <v>1640</v>
@@ -6372,7 +6372,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G207" t="n">
-        <v>7.93731880187988</v>
+        <v>7.9373197555542</v>
       </c>
       <c r="H207" t="n">
         <v>0</v>
@@ -6401,7 +6401,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G208" t="n">
-        <v>7.93731880187988</v>
+        <v>7.9373197555542</v>
       </c>
       <c r="H208" t="n">
         <v>1100</v>
@@ -6430,7 +6430,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G209" t="n">
-        <v>7.93731880187988</v>
+        <v>7.9373197555542</v>
       </c>
       <c r="H209" t="n">
         <v>230</v>
@@ -6459,7 +6459,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G210" t="n">
-        <v>7.93731880187988</v>
+        <v>7.9373197555542</v>
       </c>
       <c r="H210" t="n">
         <v>0</v>
@@ -6488,7 +6488,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G211" t="n">
-        <v>7.97381258010864</v>
+        <v>7.9738130569458</v>
       </c>
       <c r="H211" t="n">
         <v>53910</v>
@@ -6517,7 +6517,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G212" t="n">
-        <v>8.08329296112061</v>
+        <v>8.08329200744629</v>
       </c>
       <c r="H212" t="n">
         <v>173</v>
@@ -6546,7 +6546,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G213" t="n">
-        <v>8.0285530090332</v>
+        <v>8.02855396270752</v>
       </c>
       <c r="H213" t="n">
         <v>11079</v>
@@ -6604,7 +6604,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G215" t="n">
-        <v>8.27488231658936</v>
+        <v>8.27488422393799</v>
       </c>
       <c r="H215" t="n">
         <v>8078</v>
@@ -6633,7 +6633,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G216" t="n">
-        <v>8.50296688079834</v>
+        <v>8.50296783447266</v>
       </c>
       <c r="H216" t="n">
         <v>862</v>
@@ -6836,7 +6836,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G223" t="n">
-        <v>8.32050037384033</v>
+        <v>8.32049942016602</v>
       </c>
       <c r="H223" t="n">
         <v>50</v>
@@ -6865,7 +6865,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G224" t="n">
-        <v>8.32050037384033</v>
+        <v>8.32049942016602</v>
       </c>
       <c r="H224" t="n">
         <v>0</v>
@@ -6894,7 +6894,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G225" t="n">
-        <v>8.32050037384033</v>
+        <v>8.32049942016602</v>
       </c>
       <c r="H225" t="n">
         <v>0</v>
@@ -6923,7 +6923,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G226" t="n">
-        <v>8.32050037384033</v>
+        <v>8.32049942016602</v>
       </c>
       <c r="H226" t="n">
         <v>0</v>
@@ -7010,7 +7010,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G229" t="n">
-        <v>8.57595443725586</v>
+        <v>8.57595348358154</v>
       </c>
       <c r="H229" t="n">
         <v>7583</v>
@@ -7068,7 +7068,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G231" t="n">
-        <v>8.50296688079834</v>
+        <v>8.50296783447266</v>
       </c>
       <c r="H231" t="n">
         <v>330</v>
@@ -7213,7 +7213,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G236" t="n">
-        <v>8.98650550842285</v>
+        <v>8.98650646209717</v>
       </c>
       <c r="H236" t="n">
         <v>2302</v>
@@ -7300,7 +7300,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G239" t="n">
-        <v>8.62157154083252</v>
+        <v>8.6215705871582</v>
       </c>
       <c r="H239" t="n">
         <v>2238</v>
@@ -7387,7 +7387,7 @@
         <v>9.63000011444092</v>
       </c>
       <c r="G242" t="n">
-        <v>8.78579139709473</v>
+        <v>8.78579235076904</v>
       </c>
       <c r="H242" t="n">
         <v>348</v>
@@ -7416,7 +7416,7 @@
         <v>9.63000011444092</v>
       </c>
       <c r="G243" t="n">
-        <v>8.78579139709473</v>
+        <v>8.78579235076904</v>
       </c>
       <c r="H243" t="n">
         <v>0</v>
@@ -7445,7 +7445,7 @@
         <v>9.63000011444092</v>
       </c>
       <c r="G244" t="n">
-        <v>8.78579139709473</v>
+        <v>8.78579235076904</v>
       </c>
       <c r="H244" t="n">
         <v>0</v>
@@ -7474,7 +7474,7 @@
         <v>9.63000011444092</v>
       </c>
       <c r="G245" t="n">
-        <v>8.78579139709473</v>
+        <v>8.78579235076904</v>
       </c>
       <c r="H245" t="n">
         <v>0</v>
@@ -7532,7 +7532,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G247" t="n">
-        <v>9.03212261199951</v>
+        <v>9.0321216583252</v>
       </c>
       <c r="H247" t="n">
         <v>200</v>
@@ -7561,7 +7561,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G248" t="n">
-        <v>9.03212261199951</v>
+        <v>9.0321216583252</v>
       </c>
       <c r="H248" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G251" t="n">
-        <v>9.21458911895752</v>
+        <v>9.21459007263184</v>
       </c>
       <c r="H251" t="n">
         <v>1480</v>
@@ -7677,7 +7677,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G252" t="n">
-        <v>9.21458911895752</v>
+        <v>9.21459007263184</v>
       </c>
       <c r="H252" t="n">
         <v>331</v>
@@ -7706,7 +7706,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G253" t="n">
-        <v>9.19634342193604</v>
+        <v>9.19634246826172</v>
       </c>
       <c r="H253" t="n">
         <v>359</v>
@@ -7735,7 +7735,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G254" t="n">
-        <v>9.19634342193604</v>
+        <v>9.19634246826172</v>
       </c>
       <c r="H254" t="n">
         <v>0</v>
@@ -7851,7 +7851,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G258" t="n">
-        <v>9.03212261199951</v>
+        <v>9.0321216583252</v>
       </c>
       <c r="H258" t="n">
         <v>300</v>
@@ -7909,7 +7909,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G260" t="n">
-        <v>8.84965419769287</v>
+        <v>8.84965515136719</v>
       </c>
       <c r="H260" t="n">
         <v>50</v>
@@ -8112,7 +8112,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G267" t="n">
-        <v>8.98650550842285</v>
+        <v>8.98650646209717</v>
       </c>
       <c r="H267" t="n">
         <v>2750</v>
@@ -8141,7 +8141,7 @@
         <v>9.75</v>
       </c>
       <c r="G268" t="n">
-        <v>8.89527225494385</v>
+        <v>8.89527130126953</v>
       </c>
       <c r="H268" t="n">
         <v>380</v>
@@ -8170,7 +8170,7 @@
         <v>9.75</v>
       </c>
       <c r="G269" t="n">
-        <v>8.89527225494385</v>
+        <v>8.89527130126953</v>
       </c>
       <c r="H269" t="n">
         <v>1149</v>
@@ -8286,7 +8286,7 @@
         <v>8.92000007629395</v>
       </c>
       <c r="G273" t="n">
-        <v>8.13803291320801</v>
+        <v>8.13803386688232</v>
       </c>
       <c r="H273" t="n">
         <v>1470</v>
@@ -8431,7 +8431,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G278" t="n">
-        <v>8.11978721618652</v>
+        <v>8.11978626251221</v>
       </c>
       <c r="H278" t="n">
         <v>43332</v>
@@ -8460,7 +8460,7 @@
         <v>8.71000003814697</v>
       </c>
       <c r="G279" t="n">
-        <v>7.94644260406494</v>
+        <v>7.9464430809021</v>
       </c>
       <c r="H279" t="n">
         <v>7948</v>
@@ -8489,7 +8489,7 @@
         <v>8.72999954223633</v>
       </c>
       <c r="G280" t="n">
-        <v>7.96468925476074</v>
+        <v>7.9646897315979</v>
       </c>
       <c r="H280" t="n">
         <v>1620</v>
@@ -8518,7 +8518,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G281" t="n">
-        <v>8.11978721618652</v>
+        <v>8.11978626251221</v>
       </c>
       <c r="H281" t="n">
         <v>1100</v>
@@ -8576,7 +8576,7 @@
         <v>8.77000045776367</v>
       </c>
       <c r="G283" t="n">
-        <v>8.00118350982666</v>
+        <v>8.00118446350098</v>
       </c>
       <c r="H283" t="n">
         <v>2377</v>
@@ -8634,7 +8634,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G285" t="n">
-        <v>8.37524032592773</v>
+        <v>8.37524127960205</v>
       </c>
       <c r="H285" t="n">
         <v>1200</v>
@@ -8663,7 +8663,7 @@
         <v>9.09000015258789</v>
       </c>
       <c r="G286" t="n">
-        <v>8.29312992095947</v>
+        <v>8.29313087463379</v>
       </c>
       <c r="H286" t="n">
         <v>7374</v>
@@ -8692,7 +8692,7 @@
         <v>9.09000015258789</v>
       </c>
       <c r="G287" t="n">
-        <v>8.29312992095947</v>
+        <v>8.29313087463379</v>
       </c>
       <c r="H287" t="n">
         <v>760</v>
@@ -8721,7 +8721,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G288" t="n">
-        <v>8.27488231658936</v>
+        <v>8.27488422393799</v>
       </c>
       <c r="H288" t="n">
         <v>6201</v>
@@ -8866,7 +8866,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G293" t="n">
-        <v>8.27488231658936</v>
+        <v>8.27488422393799</v>
       </c>
       <c r="H293" t="n">
         <v>1783</v>
@@ -8895,7 +8895,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G294" t="n">
-        <v>8.50296688079834</v>
+        <v>8.50296783447266</v>
       </c>
       <c r="H294" t="n">
         <v>3394</v>
@@ -8924,7 +8924,7 @@
         <v>9.27000045776367</v>
       </c>
       <c r="G295" t="n">
-        <v>8.45735168457031</v>
+        <v>8.457350730896</v>
       </c>
       <c r="H295" t="n">
         <v>260</v>
@@ -9069,7 +9069,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G300" t="n">
-        <v>8.50296688079834</v>
+        <v>8.50296783447266</v>
       </c>
       <c r="H300" t="n">
         <v>949</v>
@@ -9127,7 +9127,7 @@
         <v>8.86999988555908</v>
       </c>
       <c r="G302" t="n">
-        <v>8.09241676330566</v>
+        <v>8.09241580963135</v>
       </c>
       <c r="H302" t="n">
         <v>2131</v>
@@ -9185,7 +9185,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G304" t="n">
-        <v>8.0285530090332</v>
+        <v>8.02855396270752</v>
       </c>
       <c r="H304" t="n">
         <v>300</v>
@@ -9214,7 +9214,7 @@
         <v>8.8100004196167</v>
       </c>
       <c r="G305" t="n">
-        <v>8.03767681121826</v>
+        <v>8.03767776489258</v>
       </c>
       <c r="H305" t="n">
         <v>836</v>
@@ -9301,7 +9301,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G308" t="n">
-        <v>8.37524032592773</v>
+        <v>8.37524127960205</v>
       </c>
       <c r="H308" t="n">
         <v>99</v>
@@ -9330,7 +9330,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G309" t="n">
-        <v>8.19277381896973</v>
+        <v>8.19277286529541</v>
       </c>
       <c r="H309" t="n">
         <v>191</v>
@@ -9475,7 +9475,7 @@
         <v>9.01000022888184</v>
       </c>
       <c r="G314" t="n">
-        <v>8.22014427185059</v>
+        <v>8.22014331817627</v>
       </c>
       <c r="H314" t="n">
         <v>680</v>
@@ -9504,7 +9504,7 @@
         <v>9.01000022888184</v>
       </c>
       <c r="G315" t="n">
-        <v>8.22014427185059</v>
+        <v>8.22014331817627</v>
       </c>
       <c r="H315" t="n">
         <v>0</v>
@@ -9533,7 +9533,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G316" t="n">
-        <v>8.0285530090332</v>
+        <v>8.02855396270752</v>
       </c>
       <c r="H316" t="n">
         <v>3343</v>
@@ -9562,7 +9562,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G317" t="n">
-        <v>8.0285530090332</v>
+        <v>8.02855396270752</v>
       </c>
       <c r="H317" t="n">
         <v>180</v>
@@ -9591,7 +9591,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G318" t="n">
-        <v>8.0285530090332</v>
+        <v>8.02855396270752</v>
       </c>
       <c r="H318" t="n">
         <v>78630</v>
@@ -9736,7 +9736,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G323" t="n">
-        <v>8.28400611877441</v>
+        <v>8.28400707244873</v>
       </c>
       <c r="H323" t="n">
         <v>8366</v>
@@ -9765,7 +9765,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G324" t="n">
-        <v>8.28400611877441</v>
+        <v>8.28400707244873</v>
       </c>
       <c r="H324" t="n">
         <v>0</v>
@@ -9852,7 +9852,7 @@
         <v>8.92000007629395</v>
       </c>
       <c r="G327" t="n">
-        <v>8.13803291320801</v>
+        <v>8.13803386688232</v>
       </c>
       <c r="H327" t="n">
         <v>200</v>
@@ -9881,7 +9881,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G328" t="n">
-        <v>8.11978721618652</v>
+        <v>8.11978626251221</v>
       </c>
       <c r="H328" t="n">
         <v>3732</v>
@@ -9910,7 +9910,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G329" t="n">
-        <v>8.11978721618652</v>
+        <v>8.11978626251221</v>
       </c>
       <c r="H329" t="n">
         <v>200</v>
@@ -9939,7 +9939,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G330" t="n">
-        <v>8.11978721618652</v>
+        <v>8.11978626251221</v>
       </c>
       <c r="H330" t="n">
         <v>451</v>
@@ -9968,7 +9968,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G331" t="n">
-        <v>8.59420204162598</v>
+        <v>8.59420108795166</v>
       </c>
       <c r="H331" t="n">
         <v>5649</v>
@@ -9997,7 +9997,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G332" t="n">
-        <v>8.50296688079834</v>
+        <v>8.50296783447266</v>
       </c>
       <c r="H332" t="n">
         <v>6347</v>
@@ -10084,7 +10084,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G335" t="n">
-        <v>8.24751472473145</v>
+        <v>8.24751377105713</v>
       </c>
       <c r="H335" t="n">
         <v>7514</v>
@@ -10171,7 +10171,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G338" t="n">
-        <v>7.93731880187988</v>
+        <v>7.9373197555542</v>
       </c>
       <c r="H338" t="n">
         <v>2490</v>
@@ -10229,7 +10229,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G340" t="n">
-        <v>7.57238531112671</v>
+        <v>7.57238578796387</v>
       </c>
       <c r="H340" t="n">
         <v>7020</v>
@@ -10287,7 +10287,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G342" t="n">
-        <v>7.37167167663574</v>
+        <v>7.37167119979858</v>
       </c>
       <c r="H342" t="n">
         <v>18625</v>
@@ -10374,7 +10374,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G345" t="n">
-        <v>7.33517789840698</v>
+        <v>7.33517837524414</v>
       </c>
       <c r="H345" t="n">
         <v>3152</v>
@@ -10403,7 +10403,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G346" t="n">
-        <v>7.3534255027771</v>
+        <v>7.35342502593994</v>
       </c>
       <c r="H346" t="n">
         <v>470</v>
@@ -10577,7 +10577,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G352" t="n">
-        <v>7.3169322013855</v>
+        <v>7.31693172454834</v>
       </c>
       <c r="H352" t="n">
         <v>63</v>
@@ -10635,7 +10635,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G354" t="n">
-        <v>7.20745134353638</v>
+        <v>7.20745182037354</v>
       </c>
       <c r="H354" t="n">
         <v>2421</v>
@@ -10693,7 +10693,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G356" t="n">
-        <v>7.0432300567627</v>
+        <v>7.04323053359985</v>
       </c>
       <c r="H356" t="n">
         <v>3056</v>
@@ -10896,7 +10896,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G363" t="n">
-        <v>7.0432300567627</v>
+        <v>7.04323053359985</v>
       </c>
       <c r="H363" t="n">
         <v>2201</v>
@@ -10983,7 +10983,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G366" t="n">
-        <v>6.95199728012085</v>
+        <v>6.95199680328369</v>
       </c>
       <c r="H366" t="n">
         <v>3628</v>
@@ -11012,7 +11012,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G367" t="n">
-        <v>6.82426977157593</v>
+        <v>6.82427024841309</v>
       </c>
       <c r="H367" t="n">
         <v>4636</v>
@@ -11041,7 +11041,7 @@
         <v>7.51999998092651</v>
       </c>
       <c r="G368" t="n">
-        <v>6.86076307296753</v>
+        <v>6.86076354980469</v>
       </c>
       <c r="H368" t="n">
         <v>5487</v>
@@ -11070,7 +11070,7 @@
         <v>7.51999998092651</v>
       </c>
       <c r="G369" t="n">
-        <v>6.86076307296753</v>
+        <v>6.86076354980469</v>
       </c>
       <c r="H369" t="n">
         <v>45</v>
@@ -11128,7 +11128,7 @@
         <v>7.51999998092651</v>
       </c>
       <c r="G371" t="n">
-        <v>6.86076307296753</v>
+        <v>6.86076354980469</v>
       </c>
       <c r="H371" t="n">
         <v>50</v>
@@ -11157,7 +11157,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G372" t="n">
-        <v>6.95199728012085</v>
+        <v>6.95199680328369</v>
       </c>
       <c r="H372" t="n">
         <v>500</v>
@@ -11650,7 +11650,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G389" t="n">
-        <v>7.17095804214478</v>
+        <v>7.17095756530762</v>
       </c>
       <c r="H389" t="n">
         <v>7937</v>
@@ -11679,7 +11679,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G390" t="n">
-        <v>7.3899188041687</v>
+        <v>7.38991832733154</v>
       </c>
       <c r="H390" t="n">
         <v>4671</v>
@@ -11708,7 +11708,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G391" t="n">
-        <v>7.59063196182251</v>
+        <v>7.59063243865967</v>
       </c>
       <c r="H391" t="n">
         <v>1808</v>
@@ -11737,7 +11737,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G392" t="n">
-        <v>7.57238531112671</v>
+        <v>7.57238578796387</v>
       </c>
       <c r="H392" t="n">
         <v>630</v>
@@ -11766,7 +11766,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G393" t="n">
-        <v>7.57238531112671</v>
+        <v>7.57238578796387</v>
       </c>
       <c r="H393" t="n">
         <v>0</v>
@@ -11795,7 +11795,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G394" t="n">
-        <v>7.57238531112671</v>
+        <v>7.57238578796387</v>
       </c>
       <c r="H394" t="n">
         <v>100</v>
@@ -11824,7 +11824,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G395" t="n">
-        <v>7.57238531112671</v>
+        <v>7.57238578796387</v>
       </c>
       <c r="H395" t="n">
         <v>24200</v>
@@ -11853,7 +11853,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G396" t="n">
-        <v>7.57238531112671</v>
+        <v>7.57238578796387</v>
       </c>
       <c r="H396" t="n">
         <v>0</v>
@@ -11998,7 +11998,7 @@
         <v>8.4399995803833</v>
       </c>
       <c r="G401" t="n">
-        <v>7.70011186599731</v>
+        <v>7.70011234283447</v>
       </c>
       <c r="H401" t="n">
         <v>1732</v>
@@ -12027,7 +12027,7 @@
         <v>8.4399995803833</v>
       </c>
       <c r="G402" t="n">
-        <v>7.70011186599731</v>
+        <v>7.70011234283447</v>
       </c>
       <c r="H402" t="n">
         <v>1250</v>
@@ -12085,7 +12085,7 @@
         <v>8.4399995803833</v>
       </c>
       <c r="G404" t="n">
-        <v>7.70011186599731</v>
+        <v>7.70011234283447</v>
       </c>
       <c r="H404" t="n">
         <v>100</v>
@@ -12143,7 +12143,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G406" t="n">
-        <v>7.33517789840698</v>
+        <v>7.33517837524414</v>
       </c>
       <c r="H406" t="n">
         <v>3302</v>
@@ -12172,7 +12172,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G407" t="n">
-        <v>7.33517789840698</v>
+        <v>7.33517837524414</v>
       </c>
       <c r="H407" t="n">
         <v>0</v>
@@ -12375,7 +12375,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G414" t="n">
-        <v>7.44465827941895</v>
+        <v>7.4446587562561</v>
       </c>
       <c r="H414" t="n">
         <v>210</v>
@@ -12404,7 +12404,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G415" t="n">
-        <v>7.44465827941895</v>
+        <v>7.4446587562561</v>
       </c>
       <c r="H415" t="n">
         <v>0</v>
@@ -12578,7 +12578,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G421" t="n">
-        <v>7.4629054069519</v>
+        <v>7.46290588378906</v>
       </c>
       <c r="H421" t="n">
         <v>870</v>
@@ -12665,7 +12665,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G424" t="n">
-        <v>7.44465827941895</v>
+        <v>7.4446587562561</v>
       </c>
       <c r="H424" t="n">
         <v>2000</v>
@@ -12723,7 +12723,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G426" t="n">
-        <v>7.79134559631348</v>
+        <v>7.79134607315063</v>
       </c>
       <c r="H426" t="n">
         <v>3239</v>
@@ -12752,7 +12752,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G427" t="n">
-        <v>7.8825798034668</v>
+        <v>7.88257932662964</v>
       </c>
       <c r="H427" t="n">
         <v>41</v>
@@ -12781,7 +12781,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G428" t="n">
-        <v>7.73660564422607</v>
+        <v>7.73660516738892</v>
       </c>
       <c r="H428" t="n">
         <v>4521</v>
@@ -12810,7 +12810,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G429" t="n">
-        <v>7.66361808776855</v>
+        <v>7.66361856460571</v>
       </c>
       <c r="H429" t="n">
         <v>1230</v>
@@ -12839,7 +12839,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G430" t="n">
-        <v>7.66361808776855</v>
+        <v>7.66361856460571</v>
       </c>
       <c r="H430" t="n">
         <v>0</v>
@@ -12955,7 +12955,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G434" t="n">
-        <v>7.4629054069519</v>
+        <v>7.46290588378906</v>
       </c>
       <c r="H434" t="n">
         <v>565</v>
@@ -13013,7 +13013,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G436" t="n">
-        <v>7.3534255027771</v>
+        <v>7.35342502593994</v>
       </c>
       <c r="H436" t="n">
         <v>4810</v>
@@ -13042,7 +13042,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G437" t="n">
-        <v>7.3534255027771</v>
+        <v>7.35342502593994</v>
       </c>
       <c r="H437" t="n">
         <v>1654</v>
@@ -13216,7 +13216,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G443" t="n">
-        <v>6.75128316879272</v>
+        <v>6.75128364562988</v>
       </c>
       <c r="H443" t="n">
         <v>690</v>
@@ -13245,7 +13245,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G444" t="n">
-        <v>6.75128316879272</v>
+        <v>6.75128364562988</v>
       </c>
       <c r="H444" t="n">
         <v>740</v>
@@ -13332,7 +13332,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G447" t="n">
-        <v>6.82426977157593</v>
+        <v>6.82427024841309</v>
       </c>
       <c r="H447" t="n">
         <v>24314</v>
@@ -13390,7 +13390,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G449" t="n">
-        <v>6.75128316879272</v>
+        <v>6.75128364562988</v>
       </c>
       <c r="H449" t="n">
         <v>1995</v>
@@ -13419,7 +13419,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G450" t="n">
-        <v>6.75128316879272</v>
+        <v>6.75128364562988</v>
       </c>
       <c r="H450" t="n">
         <v>0</v>
@@ -13448,7 +13448,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G451" t="n">
-        <v>6.75128316879272</v>
+        <v>6.75128364562988</v>
       </c>
       <c r="H451" t="n">
         <v>0</v>
@@ -13477,7 +13477,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G452" t="n">
-        <v>6.75128316879272</v>
+        <v>6.75128364562988</v>
       </c>
       <c r="H452" t="n">
         <v>0</v>
@@ -13506,7 +13506,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G453" t="n">
-        <v>6.75128316879272</v>
+        <v>6.75128364562988</v>
       </c>
       <c r="H453" t="n">
         <v>0</v>
@@ -13535,7 +13535,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G454" t="n">
-        <v>6.75128316879272</v>
+        <v>6.75128364562988</v>
       </c>
       <c r="H454" t="n">
         <v>1400</v>
@@ -13564,7 +13564,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G455" t="n">
-        <v>6.58706283569336</v>
+        <v>6.5870623588562</v>
       </c>
       <c r="H455" t="n">
         <v>200</v>
@@ -13709,7 +13709,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G460" t="n">
-        <v>6.514075756073</v>
+        <v>6.51407623291016</v>
       </c>
       <c r="H460" t="n">
         <v>2800</v>
@@ -13970,7 +13970,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G469" t="n">
-        <v>6.44108867645264</v>
+        <v>6.44108915328979</v>
       </c>
       <c r="H469" t="n">
         <v>3100</v>
@@ -14028,7 +14028,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G471" t="n">
-        <v>6.29511547088623</v>
+        <v>6.29511594772339</v>
       </c>
       <c r="H471" t="n">
         <v>882</v>
@@ -14057,7 +14057,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G472" t="n">
-        <v>6.49582958221436</v>
+        <v>6.4958291053772</v>
       </c>
       <c r="H472" t="n">
         <v>1050</v>
@@ -14086,7 +14086,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G473" t="n">
-        <v>6.42284297943115</v>
+        <v>6.42284250259399</v>
       </c>
       <c r="H473" t="n">
         <v>600</v>
@@ -14115,7 +14115,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G474" t="n">
-        <v>6.29511547088623</v>
+        <v>6.29511594772339</v>
       </c>
       <c r="H474" t="n">
         <v>120</v>
@@ -14144,7 +14144,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G475" t="n">
-        <v>6.67829608917236</v>
+        <v>6.67829656600952</v>
       </c>
       <c r="H475" t="n">
         <v>1738</v>
@@ -14173,7 +14173,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G476" t="n">
-        <v>6.67829608917236</v>
+        <v>6.67829656600952</v>
       </c>
       <c r="H476" t="n">
         <v>1500</v>
@@ -14405,7 +14405,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G484" t="n">
-        <v>6.58706283569336</v>
+        <v>6.5870623588562</v>
       </c>
       <c r="H484" t="n">
         <v>1565</v>
@@ -14434,7 +14434,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G485" t="n">
-        <v>6.58706283569336</v>
+        <v>6.5870623588562</v>
       </c>
       <c r="H485" t="n">
         <v>0</v>
@@ -14463,7 +14463,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G486" t="n">
-        <v>6.58706283569336</v>
+        <v>6.5870623588562</v>
       </c>
       <c r="H486" t="n">
         <v>0</v>
@@ -14492,7 +14492,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G487" t="n">
-        <v>6.64180278778076</v>
+        <v>6.64180326461792</v>
       </c>
       <c r="H487" t="n">
         <v>565</v>
@@ -14637,7 +14637,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G492" t="n">
-        <v>7.20745134353638</v>
+        <v>7.20745182037354</v>
       </c>
       <c r="H492" t="n">
         <v>1450</v>
@@ -14666,7 +14666,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G493" t="n">
-        <v>7.22569751739502</v>
+        <v>7.22569799423218</v>
       </c>
       <c r="H493" t="n">
         <v>800</v>
@@ -14927,7 +14927,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G502" t="n">
-        <v>7.33517789840698</v>
+        <v>7.33517837524414</v>
       </c>
       <c r="H502" t="n">
         <v>517</v>
@@ -14985,7 +14985,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G504" t="n">
-        <v>7.37167167663574</v>
+        <v>7.37167119979858</v>
       </c>
       <c r="H504" t="n">
         <v>1968</v>
@@ -15014,7 +15014,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G505" t="n">
-        <v>7.33517789840698</v>
+        <v>7.33517837524414</v>
       </c>
       <c r="H505" t="n">
         <v>731</v>
@@ -15043,7 +15043,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G506" t="n">
-        <v>7.33517789840698</v>
+        <v>7.33517837524414</v>
       </c>
       <c r="H506" t="n">
         <v>300</v>
@@ -15072,7 +15072,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G507" t="n">
-        <v>7.3169322013855</v>
+        <v>7.31693172454834</v>
       </c>
       <c r="H507" t="n">
         <v>772</v>
@@ -15101,7 +15101,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G508" t="n">
-        <v>7.37167167663574</v>
+        <v>7.37167119979858</v>
       </c>
       <c r="H508" t="n">
         <v>1681</v>
@@ -15130,7 +15130,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G509" t="n">
-        <v>7.37167167663574</v>
+        <v>7.37167119979858</v>
       </c>
       <c r="H509" t="n">
         <v>0</v>
@@ -15159,7 +15159,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G510" t="n">
-        <v>7.37167167663574</v>
+        <v>7.37167119979858</v>
       </c>
       <c r="H510" t="n">
         <v>0</v>
@@ -15188,7 +15188,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G511" t="n">
-        <v>7.20745134353638</v>
+        <v>7.20745182037354</v>
       </c>
       <c r="H511" t="n">
         <v>221</v>
@@ -15217,7 +15217,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G512" t="n">
-        <v>7.3169322013855</v>
+        <v>7.31693172454834</v>
       </c>
       <c r="H512" t="n">
         <v>1280</v>
@@ -15246,7 +15246,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G513" t="n">
-        <v>7.20745134353638</v>
+        <v>7.20745182037354</v>
       </c>
       <c r="H513" t="n">
         <v>900</v>
@@ -15362,7 +15362,7 @@
         <v>7.51999998092651</v>
       </c>
       <c r="G517" t="n">
-        <v>6.86076307296753</v>
+        <v>6.86076354980469</v>
       </c>
       <c r="H517" t="n">
         <v>3626</v>
@@ -15478,7 +15478,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G521" t="n">
-        <v>6.82426977157593</v>
+        <v>6.82427024841309</v>
       </c>
       <c r="H521" t="n">
         <v>13563</v>
@@ -15594,7 +15594,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G525" t="n">
-        <v>6.82426977157593</v>
+        <v>6.82427024841309</v>
       </c>
       <c r="H525" t="n">
         <v>4481</v>
@@ -15681,7 +15681,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G528" t="n">
-        <v>7.13446474075317</v>
+        <v>7.13446426391602</v>
       </c>
       <c r="H528" t="n">
         <v>12040</v>
@@ -15739,7 +15739,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G530" t="n">
-        <v>7.17095804214478</v>
+        <v>7.17095756530762</v>
       </c>
       <c r="H530" t="n">
         <v>2115</v>
@@ -15826,7 +15826,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G533" t="n">
-        <v>7.3534255027771</v>
+        <v>7.35342502593994</v>
       </c>
       <c r="H533" t="n">
         <v>2000</v>
@@ -15855,7 +15855,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G534" t="n">
-        <v>7.3534255027771</v>
+        <v>7.35342502593994</v>
       </c>
       <c r="H534" t="n">
         <v>2413</v>
@@ -15884,7 +15884,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G535" t="n">
-        <v>7.64537239074707</v>
+        <v>7.64537191390991</v>
       </c>
       <c r="H535" t="n">
         <v>12922</v>
@@ -15913,7 +15913,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G536" t="n">
-        <v>7.3899188041687</v>
+        <v>7.38991832733154</v>
       </c>
       <c r="H536" t="n">
         <v>18461</v>
@@ -15971,7 +15971,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G538" t="n">
-        <v>7.13446474075317</v>
+        <v>7.13446426391602</v>
       </c>
       <c r="H538" t="n">
         <v>2732</v>
@@ -16000,7 +16000,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G539" t="n">
-        <v>7.20745134353638</v>
+        <v>7.20745182037354</v>
       </c>
       <c r="H539" t="n">
         <v>3149</v>
@@ -16029,7 +16029,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G540" t="n">
-        <v>7.20745134353638</v>
+        <v>7.20745182037354</v>
       </c>
       <c r="H540" t="n">
         <v>0</v>
@@ -16116,7 +16116,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G543" t="n">
-        <v>7.13446474075317</v>
+        <v>7.13446426391602</v>
       </c>
       <c r="H543" t="n">
         <v>6467</v>
@@ -16145,7 +16145,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G544" t="n">
-        <v>7.3169322013855</v>
+        <v>7.31693172454834</v>
       </c>
       <c r="H544" t="n">
         <v>3852</v>
@@ -16174,7 +16174,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G545" t="n">
-        <v>7.20745134353638</v>
+        <v>7.20745182037354</v>
       </c>
       <c r="H545" t="n">
         <v>13099</v>
@@ -16261,7 +16261,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G548" t="n">
-        <v>7.3899188041687</v>
+        <v>7.38991832733154</v>
       </c>
       <c r="H548" t="n">
         <v>1200</v>
@@ -16377,7 +16377,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G552" t="n">
-        <v>7.66361808776855</v>
+        <v>7.66361856460571</v>
       </c>
       <c r="H552" t="n">
         <v>2734</v>
@@ -16435,7 +16435,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G554" t="n">
-        <v>7.57238531112671</v>
+        <v>7.57238578796387</v>
       </c>
       <c r="H554" t="n">
         <v>1776</v>
@@ -16464,7 +16464,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G555" t="n">
-        <v>7.57238531112671</v>
+        <v>7.57238578796387</v>
       </c>
       <c r="H555" t="n">
         <v>733</v>
@@ -16609,7 +16609,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G560" t="n">
-        <v>7.66361808776855</v>
+        <v>7.66361856460571</v>
       </c>
       <c r="H560" t="n">
         <v>3325</v>
@@ -16638,7 +16638,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G561" t="n">
-        <v>7.66361808776855</v>
+        <v>7.66361856460571</v>
       </c>
       <c r="H561" t="n">
         <v>0</v>
@@ -16667,7 +16667,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G562" t="n">
-        <v>7.66361808776855</v>
+        <v>7.66361856460571</v>
       </c>
       <c r="H562" t="n">
         <v>978</v>
@@ -16696,7 +16696,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G563" t="n">
-        <v>7.64537239074707</v>
+        <v>7.64537191390991</v>
       </c>
       <c r="H563" t="n">
         <v>900</v>
@@ -16725,7 +16725,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G564" t="n">
-        <v>7.64537239074707</v>
+        <v>7.64537191390991</v>
       </c>
       <c r="H564" t="n">
         <v>0</v>
@@ -16754,7 +16754,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G565" t="n">
-        <v>7.64537239074707</v>
+        <v>7.64537191390991</v>
       </c>
       <c r="H565" t="n">
         <v>0</v>
@@ -16783,7 +16783,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G566" t="n">
-        <v>7.64537239074707</v>
+        <v>7.64537191390991</v>
       </c>
       <c r="H566" t="n">
         <v>0</v>
@@ -16928,7 +16928,7 @@
         <v>8.25</v>
       </c>
       <c r="G571" t="n">
-        <v>7.52676916122437</v>
+        <v>7.52676868438721</v>
       </c>
       <c r="H571" t="n">
         <v>2468</v>
@@ -17073,7 +17073,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G576" t="n">
-        <v>7.61800241470337</v>
+        <v>7.61800193786621</v>
       </c>
       <c r="H576" t="n">
         <v>4229</v>
@@ -17102,7 +17102,7 @@
         <v>8.25</v>
       </c>
       <c r="G577" t="n">
-        <v>7.52676916122437</v>
+        <v>7.52676868438721</v>
       </c>
       <c r="H577" t="n">
         <v>10687</v>
@@ -17218,7 +17218,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G581" t="n">
-        <v>7.3899188041687</v>
+        <v>7.38991832733154</v>
       </c>
       <c r="H581" t="n">
         <v>540</v>
@@ -17334,7 +17334,7 @@
         <v>8.25</v>
       </c>
       <c r="G585" t="n">
-        <v>7.52676916122437</v>
+        <v>7.52676868438721</v>
       </c>
       <c r="H585" t="n">
         <v>1560</v>
@@ -17363,7 +17363,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G586" t="n">
-        <v>7.3899188041687</v>
+        <v>7.38991832733154</v>
       </c>
       <c r="H586" t="n">
         <v>3341</v>
@@ -17392,7 +17392,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G587" t="n">
-        <v>7.3899188041687</v>
+        <v>7.38991832733154</v>
       </c>
       <c r="H587" t="n">
         <v>340</v>
@@ -17450,7 +17450,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G589" t="n">
-        <v>7.3899188041687</v>
+        <v>7.38991832733154</v>
       </c>
       <c r="H589" t="n">
         <v>1325</v>
@@ -17479,7 +17479,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G590" t="n">
-        <v>7.3899188041687</v>
+        <v>7.38991832733154</v>
       </c>
       <c r="H590" t="n">
         <v>851</v>
@@ -17508,7 +17508,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G591" t="n">
-        <v>7.3899188041687</v>
+        <v>7.38991832733154</v>
       </c>
       <c r="H591" t="n">
         <v>22104</v>
@@ -17537,7 +17537,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G592" t="n">
-        <v>7.3899188041687</v>
+        <v>7.38991832733154</v>
       </c>
       <c r="H592" t="n">
         <v>0</v>
@@ -35697,6 +35697,35 @@
         <v>0</v>
       </c>
       <c r="I1218" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1219">
+      <c r="A1219" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1219" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C1219" t="n">
+        <v>8</v>
+      </c>
+      <c r="D1219" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1219" t="n">
+        <v>8</v>
+      </c>
+      <c r="F1219" t="n">
+        <v>8</v>
+      </c>
+      <c r="G1219" t="n">
+        <v>8</v>
+      </c>
+      <c r="H1219" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1219" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SVS.MI.xlsx
+++ b/data/SVS.MI.xlsx
@@ -35729,6 +35729,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1220">
+      <c r="A1220" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1220" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C1220" t="n">
+        <v>8</v>
+      </c>
+      <c r="D1220" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1220" t="n">
+        <v>8</v>
+      </c>
+      <c r="F1220" t="n">
+        <v>8</v>
+      </c>
+      <c r="G1220" t="n">
+        <v>8</v>
+      </c>
+      <c r="H1220" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1220" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1221">
+      <c r="A1221" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1221" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C1221" t="n">
+        <v>7.92000007629395</v>
+      </c>
+      <c r="D1221" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1221" t="n">
+        <v>7.92000007629395</v>
+      </c>
+      <c r="F1221" t="n">
+        <v>8</v>
+      </c>
+      <c r="G1221" t="n">
+        <v>8</v>
+      </c>
+      <c r="H1221" t="n">
+        <v>310</v>
+      </c>
+      <c r="I1221" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
